--- a/productos.xlsx
+++ b/productos.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0526577688ca4eec/Escritorio/Proyectos developer/Diseños_Gasper/Back-end/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{BE4454A7-18C4-42FA-8BB3-4EA646E7908D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80764D80-552A-4784-A6EC-1E273BADAE7E}"/>
+  <xr:revisionPtr revIDLastSave="148" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{658F7071-6F7C-4D44-9A7F-1A5B99463D12}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="productos" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">productos!$A$1:$K$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="189">
   <si>
     <t>name</t>
   </si>
@@ -52,29 +55,595 @@
     <t>isPromo</t>
   </si>
   <si>
+    <t>rompevientos</t>
+  </si>
+  <si>
+    <t>hombre</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>L,XL</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>pricesBySize</t>
+  </si>
+  <si>
+    <t>Rompevientos SemiReflectiva Combinado lateral</t>
+  </si>
+  <si>
+    <t>M,L,XL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaleco Reflectivo </t>
+  </si>
+  <si>
+    <t>Reflectivo Tipo Triangulo Combinado</t>
+  </si>
+  <si>
+    <t>Mujer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chaqueta Semireflectiva </t>
+  </si>
+  <si>
+    <t>Reflectivo Seme-Impermeable en Conjunto</t>
+  </si>
+  <si>
+    <t>Reflectiva con Cinta Rompevientos Cola de Pato</t>
+  </si>
+  <si>
+    <t>Reflectiva de cremallera en Tela Galleta</t>
+  </si>
+  <si>
+    <t>Reflectiva 100% Tipo Robotica</t>
+  </si>
+  <si>
+    <t>M,L,XL,XXL</t>
+  </si>
+  <si>
     <t>mujer</t>
   </si>
   <si>
-    <t>conjuntos</t>
-  </si>
-  <si>
-    <t>Conjunto Braga y Top</t>
-  </si>
-  <si>
-    <t>U</t>
-  </si>
-  <si>
-    <t>hotpink,lavender,silver,gold,black,plum,skyblue</t>
-  </si>
-  <si>
-    <t>{"hotpink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771800278/h2zw0cxijowhbbyimshe.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771800279/uezn0mo9juhqxrigtvfd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771800278/ujj1peqpylvlbdpnkclt.png"],"lavender":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771800434/uzytdtm3or8ndacb42w8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771800430/z1asiwb2bi7mnrmnzvzw.png"], "silver": ["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771800431/xzakx8xiy9z88ze2td5x.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771800437/kjhato4xnjinrtmkapsp.png"], "gold": ["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771800436/lvfwbva23xz1skm2qfgo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771800437/sv4w0r2enzz7zknqi6zi.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771800438/kvrj5hyjtbrqtq9pznyj.png"], "black": ["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771800431/h7cjdcwcjqxqtx713hyu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771800277/uwig1fqc1vx63iigxb8v.png"],"plum":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771800436/tiwv6gtap4bivecjqpaw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771800438/bxgo1t7et2b1wyztglix.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771800438/yrwnum7kibcca9ffjxax.png"], "skyblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771800277/lm280d2bz8b4kehurtix.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771800279/j6uyvyt8fgsj8sgdbw9f.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771800430/n5loehcbujpjvmjph57l.png"]}</t>
+    <t>14-16,18-20</t>
+  </si>
+  <si>
+    <t>Chaqueta Tricolor Reflectiva Pecho</t>
+  </si>
+  <si>
+    <t>niños</t>
+  </si>
+  <si>
+    <t>Reflectiva Combinada tipo Biker</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>Badana Larga</t>
+  </si>
+  <si>
+    <t>{"M":{"wholesale":33000,"retail":49500},"L":{"wholesale":33000,"retail":49500},"XL":{"wholesale":34000,"retail":49500}}</t>
+  </si>
+  <si>
+    <t>{"M":{"wholesale":28000,"retail":42000},"L":{"wholesale":28000,"retail":42000},"XL":{"wholesale":29000,"retail":42000}}</t>
+  </si>
+  <si>
+    <t>{"L":{"wholesale":20000,"retail":30000},"XL":{"wholesale":20000,"retail":30000}}</t>
+  </si>
+  <si>
+    <t>{"M":{"wholesale":35000,"retail":57000},"L":{"wholesale":38000,"retail":57000},"XL":{"wholesale":39000,"retail":57000},"XXL":{"wholesale":39000,"retail":57000}}</t>
+  </si>
+  <si>
+    <t>Jersey manga larga</t>
+  </si>
+  <si>
+    <t>Rompevientos Tipo N.F</t>
+  </si>
+  <si>
+    <t>Badana Corta en Licra</t>
+  </si>
+  <si>
+    <t>S,M,L,XL,XXL</t>
+  </si>
+  <si>
+    <t>Rompevientos Arcoiris</t>
+  </si>
+  <si>
+    <t>{"S":{"retail":28500,"wholesale":19000},"M":{"retail":28500,"wholesale":20000}}</t>
+  </si>
+  <si>
+    <t>S,M</t>
+  </si>
+  <si>
+    <t>S,M,L,XL</t>
+  </si>
+  <si>
+    <t>{"S":{"retail":27000,"wholesale":18000},"M":{"retail":27000,"wholesale":18000},"L":{"retail":27000,"wholesale":18000},"XL":{"retail":27000,"wholesale":20000}}</t>
+  </si>
+  <si>
+    <t>Rompevientos Equipos de Fútbol</t>
+  </si>
+  <si>
+    <t>Rompevientos Tipo Casper</t>
+  </si>
+  <si>
+    <t>Rompevientos Clásica con Cremallera</t>
+  </si>
+  <si>
+    <t>Rompevientos Clásica</t>
+  </si>
+  <si>
+    <t>Chaqueta Tornasol</t>
+  </si>
+  <si>
+    <t>S,M,L</t>
+  </si>
+  <si>
+    <t>Rompevientos Maya Interna</t>
+  </si>
+  <si>
+    <t>Chaqueta Selección Colombia</t>
+  </si>
+  <si>
+    <t>Buso Oversize</t>
+  </si>
+  <si>
+    <t>6-8,10-12,14-16,18-20</t>
+  </si>
+  <si>
+    <t>{"6-8":{"retail":18000,"wholesale":10000},"10-12":{"retail":18000,"wholesale":10000},"14-16":{"retail":18000,"wholesale":10000},"18-20":{"retail":18000,"wholesale":10000}}</t>
+  </si>
+  <si>
+    <t>Buso Rompevientos</t>
+  </si>
+  <si>
+    <t>10-12,14-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buso Combinado </t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Chaqueta en Tela Antifluido</t>
+  </si>
+  <si>
+    <t>Chaqueta Baiker-Pro</t>
+  </si>
+  <si>
+    <t>Chaqueta Tricolor Rompevientos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaleco Rompevientos </t>
+  </si>
+  <si>
+    <t>Licra de Pecho Manga larga</t>
+  </si>
+  <si>
+    <t>Licra de Pecho Manga corta</t>
+  </si>
+  <si>
+    <t>Chaqueta Triángulo Reflectiva con forro Interno</t>
+  </si>
+  <si>
+    <t>Chaqueta Robótica con forro Interno</t>
+  </si>
+  <si>
+    <t>blue,red,black, darkred</t>
+  </si>
+  <si>
+    <t>{ "blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253382/k5shc79l7qjtrz6ci2u8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253382/g6vshxggogiqr9sohubg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253382/i1rxwb30h6txzqwls9a9.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/bnlvhnp5unrky6m3hrq9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253384/nibqhcfcluku6e2sjuf3.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253384/fa3gtcxcbbujpmz1q32y.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/gt8labiuzvzqteqiuki9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/pllztvi8ue5dtb9xd26j.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/dxofsgljvhppxhvxcf9q.png"],"darkred":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/uqqd6kygifncoygwvzfk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253382/kiy5vdzzlhglrhntyfpf.png"]}</t>
+  </si>
+  <si>
+    <t>red,blue</t>
+  </si>
+  <si>
+    <t>{ "red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204994/ciz9eayk0ncioycgi6md.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204989/kbdzejtejhebqpcgfq9h.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204991/vmjyoodcogoisj569jqi.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204990/te1ar1hzxwpa63bosi7y.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204996/jysdhm98z84oslidk3of.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204993/gtced3dtobo1xhsfddog.png"]}</t>
+  </si>
+  <si>
+    <t>green,red,blue,orange,darkred,cyan,royalblue</t>
+  </si>
+  <si>
+    <t>{ "green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250776/mcawzvresxrrnrk3ogqr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250769/y0knrubbecdqqywrw7j1.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250772/ll3ugzq0gkiqbeg8uhsi.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250749/kwj7js1it6va4mtgqclr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250752/sffwgsdgjgbot2hm7xni.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250755/dyhjarpligttdltd5nsg.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250735/ricla5mgztr8sb8ogoas.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250741/hi3b7znyezif4eldufgv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250745/kozk5k5pdvcccjaaja4z.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250794/i4z7atvxzrma1ftao2mw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250799/fcqaju8y2v5g9ugrpzwu.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250799/skinlhrfnnqzm8gwr17n.png"],"darkred":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250718/mrwvetq8bn87eyfmm4xh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250733/m5dckhblgewkathxmtxn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250734/ivqsjgkrysdimxh5xegw.png"],"cyan":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250736/hkdpjdm3vgpn0trmnztu.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250735/v25abklh1z7fp2k3p2lv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250737/cfnjbquo6hidwayjksyw.png"],"royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250759/q2mkxttwrvsb4z5fnlef.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250761/bgk29pi1iz3fjxtxlfqq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250765/pjuzfbjvmndc0h4xgfep.png"]}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	deepink,red,blue,orange,darkred,cyan,royalblue,green,olive</t>
+  </si>
+  <si>
+    <t>{ "deeppink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250982/dvmu9dgiwvufb7191usm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250955/slshdhn4kio9xddrtrmq.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250918/fqhuo4tjpp4yczwzdshf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250921/ahlr0dgh0r98xw4wqud5.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250911/indvbpbsahhllbr2demt.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250914/cx8wavuzsrrfeqgehwan.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250940/hi9axizusckhejfco5s0.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250943/raziqm5ewrpzzjidxqim.png"],"darkred":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250891/zcfxokfughsvu67yjcdh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250897/gtzajz8mpqk30anhwnhq.png"],"cyan":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250901/nndijkiq3dplak0kmfwk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250904/wh8ugd1vd4yfscmrb8mr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250907/onk3n4ptbomthsd5ycfk.png"],"royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250924/ur5hr32mcpowkradyc1d.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250928/xhpn1wpn0hhufkbbxbci.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250947/ypiwxkfwgbloipv08r3c.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250951/l9xl1h9afd08rzvpze3v.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250932/hwq3ugjjcdq3xshspdyf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250936/ima8bakxaxo6mvsch85s.png"]}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	deepink,orange,blue,yellow,red,black,steelblue,olive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	deepink,orange,blue,yellow,red,black,steelblue,olive,gray</t>
+  </si>
+  <si>
+    <t>{"deepink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250668/wr3birigvcczhipu6f6b.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250661/bwrwnlrrzbemqhwezjs3.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250664/kf7cxffjt9v8rnivdpjq.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250674/m0zgh5r2w9jrsupizmlr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250677/h0axfsbqji10ikh93gro.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250681/j3pfgwp8lbn2uwblfgkk.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250591/neflcst2k6ca3z50sqmw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250595/d9wnhi8wolybvyze5bhf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250598/l8zk3dfpfi6mus9dugpt.png"],"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250583/cla7lli8tpekp0vagslg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250583/trbe9ncnkutck5dwtaej.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250587/ufparkeluojp5mno5qyg.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250557/hjrgzqbdqgif5qjv6ubg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250560/h99wigyd1eyaeliptbgx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250578/yuujfqysnlb9zd1usu7m.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250547/h4rswumx0oekhu5bdsvl.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250550/wxle71udpbzovfk16lql.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250553/vvvcrtyf235mjgnz402s.png"],"steelblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250537/kol5crynodqpe9xfhrka.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250540/ald94s4ire08qmvov9hf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250544/o2ckxwtxoewp8ufxto0q.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250528/cq8rviwowjfbqpsd1mht.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250531/hyed4wj9doos3g2leqjf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250534/pfeghmv1cewqmzjahztt.png"]}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	deepink,orange,blue,red,black,steelblue,olive,gray,lime</t>
+  </si>
+  <si>
+    <t>{"deepink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247449/mbiicglzbydkwfoh233f.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247459/v6vnzpc3cyvdfuk5zrbr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247463/gxcvgyemsb9a1g4jannc.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247453/vf6g3nzmktgmd0oek6x2.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247470/cioaxq3dacrflinanrec.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247473/q2knwuvxaouxl616nu0y.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247489/w4lantjyyywajf4gqify.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247494/ltbfr9zpzyyeygc4g5qz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247500/y0thblgz7p7ecscmezpb.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247515/h7r40gxpjjxdydmwq7tm.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247520/bokd4azbko7wnietxire.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247532/vhxna77dvjfjcromtacl.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247536/b6z49h6m2u99orr3fqp0.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247523/yu0dirajzqwinrvrlkmq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247547/uc8eh8qomlicwhudnyhl.png"],"steelblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247498/npekuijfbpxp9gyvdtl4.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247507/x8ius7gfnndv7jrfne2l.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247513/t2gtho7xdt2hsw7q4ex4.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247545/fq4vamlt3mdwxmqhsjpq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247539/ni9o1yqdtio1swvdhwvc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247553/u2iqumegoxifhzvu67zs.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247457/jjxwdvyjl5f2bwr88ikk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247466/txbv2nuh8nrmlqfzcgkd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247446/jmnga1ngme5agctddffz.png"],"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247478/m2sn49fkxidrpohkq16p.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247481/q0qlj4azkeaypsd07woi.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247483/uykfjf0irkpoltysv3cb.png"]}</t>
+  </si>
+  <si>
+    <t>black,blue,red,olive,yellow</t>
+  </si>
+  <si>
+    <t>{"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247724/vfxu4h0wyhfsyqn3zolt.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247711/axzxwi1n4btigodueqir.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247707/wnrcikcpbfvm7uqlgz7p.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247698/iqhbcsmxcm0ruoqqxmub.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247701/arn9orzmqqmrhgvjrp8m.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247703/erhd8qyhwny7e8ymzrrw.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247715/wjxvtplmj6kjmwypecvr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247723/m8fsjfaz9umsttdyosu9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247718/gdmxw5dspnonhpmvbnwa.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247688/f62vfwxjsixfz7s1xqtz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247691/zskamilsv3tcexxvsznn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247694/x1vgkrnvumbh3fxzg5ni.png"],"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247729/a6otwus8dh3mgk8qdah9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247733/wplnrxidbnvzwi2sdppa.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247738/dkrrya9d8u48e7pshxit.png"]}</t>
+  </si>
+  <si>
+    <t>Chaqueta Tricolor Reflectiva Hombros</t>
+  </si>
+  <si>
+    <t>lime,red,yellow,blue,orange,gray,olive,deepink,white,black,green,aqua</t>
+  </si>
+  <si>
+    <t>steelblue,orange,black</t>
+  </si>
+  <si>
+    <t>green,red,black</t>
+  </si>
+  <si>
+    <t>yellow,blue,red,lime,orange,gray,white,black,steelblue,olive,deepink</t>
+  </si>
+  <si>
+    <t>gray,red,blue,green,steelblue,olive</t>
+  </si>
+  <si>
+    <t>green,black,red,lime,blue,crimson</t>
+  </si>
+  <si>
+    <t>green,red,blue,black,steelblue</t>
+  </si>
+  <si>
+    <t>{"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252333/osa3ymwwye7jeb8ildet.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252325/doe9jefe7loznqbux6da.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252330/x01eyusrbndxewf4jkxz.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252301/jbgk24ihrhe9nvxumrnf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252305/nyytgo9oyln4gpwxhqh0.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252309/veirdgpkm636ujmcuwcb.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252345/qdjjvejzjoofpdmbmzk9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252341/orcp3gqvyekxk4u2rwk2.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252345/gro4dkgj8mxfvmdc55fu.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252349/v6dvkfe0kq1azslvqszg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252353/pcd9tspgvfaisqybm5lc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252357/yn04pl8chvwoqitpatvt.png"],"steelblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252313/nqlunqt2il4ivgdntmkc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252317/nalieq2cp4rfuduhdgmw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252321/slepxzqdf4hzpgfwbj8t.png"]}</t>
+  </si>
+  <si>
+    <t>blue,black,red,gray,olive,steelblue,green</t>
+  </si>
+  <si>
+    <t>{"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203780/k5rtxzclrfumderyism7.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203778/ymjsavmkmtauqbtitx2x.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203779/hdmqz9h8z02qprjnvhds.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203774/jl0echggf3rjsotkhmsh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203773/enewcsn9jim3jaszqyw4.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203774/nfsnxo4vlxnpd56cfn21.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203775/tziy4yhoelkmvrww8iim.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203776/he3pkchiywakple9okdz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203777/oahoezpaaespaknkdfef.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203781/ceiyy07mpcgu7f7wucts.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203782/zdswbtcjdqfnrsqmcjis.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203783/zmy79uehmiktvgr7jbd8.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203787/d451dpj4rsfeghruhctj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203788/g0mfw00ghp2tyyjm83dq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203789/hfchndfzq8l7al6orlwi.png"],"steelblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203785/nfdwhwitzl1j0mbnwdv5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203784/cv2ntl5dfl3ekuyikns7.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203786/zo2xsitkgwb0tlj7qf7z.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203790/g5zkqv0xo3eypsfe76xt.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203791/xduhtjwqzeqcpp8upwdw.png"]}</t>
+  </si>
+  <si>
+    <t>pink,black,gray,green,blue,purple,peru,olive,crimson,darkgreen,royalblue,mediumblue</t>
+  </si>
+  <si>
+    <t>blue,black,gray,green,pink,purple,peru,olive,crimson,darkgreen,royalblue,mediumblue</t>
+  </si>
+  <si>
+    <t>{"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251664/ijndhbic77sjsvz4jsjp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251661/y2k5hjadokwmatjtya5g.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251587/epkzanarlt3q7rs484gw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251590/theee0mlsr3gsf8okzr2.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251593/sd1edurozsxzp4edo6ms.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251684/wnicwlt9clvdljk5lbys.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251689/tbxbyucp1zslkmzgszv2.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251597/zymswqgx1slaxzwiaa48.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251605/hkipimpjsbqdqundlqht.png"],"pink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251612/uqz5nuumtbxnoorqi4sf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251616/orqxtb4l8xlw7a7tzgxt.png"],"purple":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251633/j2uuumlymteqbql2mojv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251637/oslre1dphfzblvddjftw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251640/mocihz8evdcknlrnyhnf.png"],"peru":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251644/udb7f9a6gmxqks8cwswi.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251648/o90mhvu1cebb7qhlhwa3.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251669/ouhcdmc7tjxu5gv69mqr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251672/l6b0sqxzrx0s9jodeif4.png"],"crimson":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251601/gmj8huimxcabrtzzetry.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251608/kfyj6yaedp1bkr6njgwe.png"],"darkgreen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251652/yptxpoodigmez63kdglz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251656/e5k2wj7li5pku07aog54.png"],"royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251678/ajphvuw6t2yvfc2lzsuk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251682/tipmh5j6dnmlhnogcucy.png"],"mediumblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251622/gtfy6muersqrg5imzzkx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251625/qm8xkhlh9rs5p2wvfjqb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251628/zukgp1p1qseufmlh2dag.png"]}</t>
+  </si>
+  <si>
+    <t>lime,white,purple,blue,green</t>
+  </si>
+  <si>
+    <t>{"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072227/zned2rdwsnuje5gyetpw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072225/mcpyzs2htpma6hk2jgjp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072224/tsq3puqox4ytuymzgy3s.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072222/wot382r8wtu3vkm3920i.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072226/ygp8ncjsdkydxzpywhf9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072221/g9oj9rvqvflmaujlo6i2.png"],"purple":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072225/w4wcecbjgn6lic87kngr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072224/tmgmz705vopa0mn7a9xw.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072222/r7hn7vra5uq5ri2fwnhu.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072222/s1aav69wbcs9zfwvyjzd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072222/ycudqaojbq955ncuazrm.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072222/divcyovz0kubdgzz5mkm.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072222/nikwyex99f9l4zszdtcs.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072222/kjqljr24htkx5vtgvfno.png"]}</t>
+  </si>
+  <si>
+    <t>yellow,blue,red,black,green,orange,royalblue,mediumblue</t>
+  </si>
+  <si>
+    <t>{"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270323/p6k7eqjzznst2bxrg2vz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270317/t5cdbjnctbumlg675bnh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270319/lggiyj7ykumexocgdg3w.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270300/dph8v8zxcw4oobwmchp6.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270300/wheagvkqjkcca47yvhlb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270301/fo3oopc2w4gguhsxbwky.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270308/gtl37zjvfml3vmuv2o9l.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270313/z5kuunpfvxclcend8okq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270310/kk0wsleipwg1z2mbcqku.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270304/hl9fado9nquhxaicselq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270305/ru5vmxdsif5kt61snx2u.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270306/vodvrpkiopfd6onb91ix.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270311/ku0bx9n4tm9yljlo0wf7.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270321/ojw3mz6n6hix4ube3qne.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270316/fg6dnjtwpxwm4hoghz91.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270325/eduy6ep0xxc17tqusqq2.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270329/gvwagkni5jgyouq7z2oc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270326/r9qvdtgbdeyir30bac22.png"],"royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270330/z2mavjespmfokq9blbck.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270335/amahc57ashuhn1en1uus.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270333/uqc0lg7dkqsbpk9lul2p.png"],"mediumblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270341/fmj9dftl1oejpyyv9f5e.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270341/nc1781x31vupdepm9piz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270343/kh5eadc7awmjbgrychhh.png"]}</t>
+  </si>
+  <si>
+    <t>black,white,blue,royalblue,mediumblue,green,darkgreen,palegreen,red,crimson</t>
+  </si>
+  <si>
+    <t>{"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251884/ec6qea5mjwajn6nk0dln.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251877/hkcop8xbp6padhtnueg5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251881/u3sf21qmczzhmkc9chvn.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252051/kklwfmuzcbmquhjwr1le.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252055/gj58jpkwmgolvaueqotb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252059/txlffqcfnjip066ftd8k.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251911/jsswfj3yfpgbp0fneaot.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251916/jnbw9puupo8igk8ff0lv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251920/zkn50gnfqb1ab9knzrtr.png"],"royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252003/arjirrtfe28hrruk98by.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252007/aeprferwkxtmejtmbnt4.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252011/o5ppb5ekeva72tecdsb6.png"],"mediumblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251888/cnlog1ryadij1b1nfw4o.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251892/rbhc0i968a6azm11l6kd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251896/dmpmycsic51qpiehjzze.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252026/lu0evxujmcpajk0alk78.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252030/p1jsjnd3p5sah6f8yzfd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252039/m9pzvfpixsmhbu9hmv6n.png"],"darkgreen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252062/fmoab07kdfbqnzoh0cfe.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252066/gcx3hzyojzuimxllhakv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252071/jotsfswaol54s09fbfsm.png"],"palegreen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252034/nnvtss7oi7g69wu0jljp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252042/cm0q4cexpjve8e1m8quj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252047/gogphkry0pzgvwsbz7q5.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252015/p1arccwljiinxatuwq2z.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252018/iafldqth4txewfsqgm3h.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252022/ndnjgaf5il8pc2oos882.png"],"crimson":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251899/tvxqa3edphyb1hdrtmsh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251903/o9hsbfufrpx0n2n2budn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251907/hgknyxcfxcewldkkz0a2.png"]}</t>
+  </si>
+  <si>
+    <t>olive,red,green,blue,crimson,purple,yellow</t>
+  </si>
+  <si>
+    <t>{"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252930/hbihvyjdkb8dxbqi74t8.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252843/qd84u0bkum5jcn3bvq7c.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252844/maugsjv6quoobzfjppfd.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252938/phsxzm7ep4futpsiaqfn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252943/i07ow5pr2c7f4dr4vspg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252988/ldk3mkqfk7ujpqax1zyj.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252828/mq1rp9spdu64l9xdgndo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252834/ncwp3pociq94agob9dui.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252836/jtnk3zok8seesgoiany4.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252798/tnp7j6yaab4gbw7otzib.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252803/ivfco3xf0tlsj3hraeoq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252806/xja0nunxmuk8e7eswxem.png"],"crimson":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252784/uxqckf6soklrbzlpxive.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252788/rqpzcxnhpqndorf3tbez.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252793/c1hlcxr1blya15vl4jkg.png"],"purple":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252772/x0xkb8qhi69mkgbztqvj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252775/hmaeweoghycujhmevatq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252779/cbtiwseig4xigz1wburo.png"],"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252759/ixpuoagsxmh3kocrh0ya.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252763/kgpljnb5krrqagxy1bei.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252767/qonnjw4i4dzwbmhfcqbj.png"]}</t>
+  </si>
+  <si>
+    <t>Rompevientos Clásica.</t>
+  </si>
+  <si>
+    <t>yellow,green,olive,blue,aqua,red,sienna,mediumblue,royalblue,gray</t>
+  </si>
+  <si>
+    <t>{"yello":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243081/rhtdth4oa2agn7ggzuij.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243077/piyjvyj7qd82esunuxrq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243079/mbpoajoskyc6jzoee2w0.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243322/ksjnvfbsv2a2clec1zsl.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243075/noqyagw6q8rhqodthyfu.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243076/npt7u02eed14unar0zrf.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243083/j4ddz8dl4iifozdgnf3u.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243085/wky5b3lo7kh2vi8jzkvl.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243086/t3oxy92spy3iqtustuul.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243088/igzmgmcbj3k8fwmavnud.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243090/umztnw7c1oqsuugreail.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243092/sww4itzwtxa5axmaow7p.png"],"aqua":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243094/ho9rqy6m6payqzlrkqu6.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243095/yhnnzmoy3oq1izulhr6k.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243098/qoyytx0aiqiehec825fs.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243100/s7z0ao2wb0bnvs14ion9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243102/vixajcnjp918lty1e8td.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243103/qdr6jull5ufs8pdsv94v.png"],"sienna":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243105/abipmjdlydc2wzxxefqy.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243107/ou3g33tqx0olh1skbgi6.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243110/hdg7olsdmwojv9mnczld.png"],"mediumblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243112/pns9841ekezcvt8fks8v.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243114/b22chetes2p4nuaksbzo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243116/ldf4reoysog8iyrjaguq.png"],"royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243119/ojixyba9pqap2hd7yjws.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243120/d2yzy0dahisur97lten8.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243124/egvuokp86rxybohppbjb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243126/xajy8ib99wq9m2h2s8yf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243127/jdkex1zvyzpsn18jpty3.png"]}</t>
+  </si>
+  <si>
+    <t>blue,lime,crimson,pink,yellow,gray,royalblue,purple,orange,dimgray,darkslategray,black</t>
+  </si>
+  <si>
+    <t>aqua,blue,sienna,yellow,lime,crimson,green,mediumblue,red,darkgreen,palegreen</t>
+  </si>
+  <si>
+    <t>pink,gray,blue,purple,black,yellow,aqua,mediumblue,sienna,crimson,darkgray</t>
+  </si>
+  <si>
+    <t>{"pink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243566/phgw8xfefwkroqsgwyeq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243561/iy16nmgwrowzitokphtl.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243565/t6on35wuh3ye4pxflkkr.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243557/zmksmwygfsi9un8gituy.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243558/cvnywkmdvumnyrxdmnpp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243562/lemrucagycfctmurfeep.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243568/kkkplenrfsqqdsltol8t.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243572/uakcjpz6kfrxomnlj2sl.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243570/vkdbbzem5sorctlsu65y.png"],"purple":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243574/tenwcdq671rjrvubx7uw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243578/rvo3wkxpetwmce5fycjq.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243580/i9g6ewvhv7xlxwu2he9e.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243582/dimvr5tawzk9bzkkcyo1.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243584/onc08nj7h8vvmsi0jdyj.png"],"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243586/fq7101kvabnnmb7kejv2.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243589/ifui3z0jkz3urfpzmua1.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243591/uyg0prdcsezukwhxbhsn.png"],"aqua":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243598/q8ycdyx5h8huipycve5x.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243595/lthdqdkkdzjt5jvj05wn.png"],"mediumblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243600/obstt9izd3t76j51caxw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243603/b3pj6cruh66xy5kjp53p.png"],"sienna":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243605/qnlxeq3l6phixazbgjoi.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243608/ozyl1nw5rbfgxcbaoakd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243609/weg2agj1szstoezhsbzr.png"],"crimson":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243615/bkszddwhyo5jq4hejur5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243612/jzjwqco6kgwmblvwro2g.png"],"darkgray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243617/qn6yujwcnyo73ys7ltdy.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243746/m2pj5fkpkvsyb9kw6gqa.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243748/uumrcdrzpnuynwf6fh1m.png"]}</t>
+  </si>
+  <si>
+    <t>purple,white,gray</t>
+  </si>
+  <si>
+    <t>{"purple":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240706/c53c2borfmcscllmu3eh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240716/lumhmrxmzohanms06svw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240706/cup06z97uf8hbtt0hjqp.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240710/p3ro0okwwk2tdjfqjzwb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240710/cwvbdr043vsfmzi00b7k.jpg","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240711/aqshonev4wo1zb7eek5i.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240706/yjszvaakraiipdnpkxko.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240707/hwxe9snnoxwvnueitakh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240707/epvbehsng5yrlvsfcbew.png"]}</t>
+  </si>
+  <si>
+    <t>{"purple":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240832/qpsuqlyso1igun5nrd5m.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240831/lio2nz9g4hvztwsr7s9g.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240832/m6eq8ccnjuczismrrins.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240832/u6rlh2s472edszv74vhg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240829/aa6n4a8wk7fdww8l4dlb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240829/agst08veaxhe2ozyor8w.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240836/hxwsy1xs6kjusxjtmszn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240834/ckokcm6btipgh0nhtyrv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240837/i9ajxfyy3mmevza6pnxq.png"]}</t>
+  </si>
+  <si>
+    <t>linen,lime,red,blue,white,gray,black</t>
+  </si>
+  <si>
+    <t>{"linen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252118/qcmvoblhtnccxxzsxl5o.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252122/w16ibu8i1xc6yorge8nh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252203/qc204i3puf1hihfy5gn0.png"],"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252105/qypua06cqbl1i6ecs6pp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252102/sts6ctjwdfcpuk1qtp4r.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252108/p6gis82ulknftnqea6u2.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252219/dmrkaiewceovfg2bqau9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252223/boestksrbqhywzvfkrjw.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252211/k6wsj7hml60rrgxuxq6e.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252215/ri6sbm2l7bryawgdojwc.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252227/wkjhbclrdpcz5ml13bet.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252232/vc3tmqzt9wbemwrqix14.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252235/gxknhpvsarsas4r2jbr7.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252243/ubrfbbwvitxhcqk5y6lm.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252251/exehhzke9umilojxxv8q.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252255/biacnlvh87hfpq3wf5vd.png"]}</t>
+  </si>
+  <si>
+    <t>yellow,blue,red,white,black,mediumblue,royalblue</t>
+  </si>
+  <si>
+    <t>mediumblue,black,yellow,blue,red,white,royalblue</t>
+  </si>
+  <si>
+    <t>{"mediumblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240533/n60eaikcezvynntuau0v.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240528/zyo9kzojtxho9wvesmrp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240531/ooyr3pz6uhvfsm77ejvk.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240532/bz2psdzgpyuyvjzjsdel.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240534/ub1joafbr0olhdtmbw0i.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240535/lwawv9dqvmiu5lxu728m.png"],"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240515/p9y8b9e5niqyywlk9sui.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240516/jp1rmju1wb5fxw9bxn3n.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240517/aafn2qd9tgpmekskj9vh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240517/mudhcxxp6flsivis2qbr.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240522/zfl1xwdjcwzcxpwwbqdw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240523/vgozlwbmddque7ctdpxu.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240525/ypie8z5xidufdlcheiso.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240520/gsfb4nwft4oko0lkclv1.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240519/xurbgbhtwpunfux4x3tq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240520/vyqamob8xq85rfqkr6q1.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240526/cxrgavd3mfsemkwkyatd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240527/zdq90d5lcagyjfdkjji5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240526/nqsgpezieko4rfklfth6.png"],"royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240540/ytouuhvitxe4wl7xmgcz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240541/geo8emnkqncogehf5qxb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240540/risndn1ndpkwnagacnsn.png"]}</t>
+  </si>
+  <si>
+    <t>sienna,red,green,blue,pink,purple,gray,darkblue,aqua</t>
+  </si>
+  <si>
+    <t>{"sienna":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204571/rkcauwdzs6jgeratl9ec.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204568/ioxhqy5xy0oq1wrhcehu.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204569/oan5nrqbfsqypbeqhidt.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204561/duwq6qi8wfrgp89mpbjs.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204559/ighobxv0gxjbzoumdgwk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204563/wmvhsdj73gzsnleekcpg.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204562/rt4qwaidcxlpqw6cwrzv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204566/k2ua1gohhgtkercwdprk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204566/k2ua1gohhgtkercwdprk.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204601/fyv4gkv15lax7lkjfnv4.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204605/e7jhnqd8biahfavjhslb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204605/lcvfgcxmp4g1ebktlowf.png"],"pink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204572/wgz1hj8fbajhl7tqdmkj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204574/ugaqohzi2jyghldh16jd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204575/wuewltpzlrn9adwlqi4r.png"],"purple":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204578/nexkekptxpmwl9q8xbxr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204579/rudlg0lfwojkamq3j5r9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204581/bgnzj1fc2szshj73adbd.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204583/kgqpcl63triyw4gbq666.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204585/vkhr8xo08dv8kecffzzj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204589/vbhopcissflqgso8ti1c.png"],"darkblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204563/ovbge4jhaovvni5tbm8o.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204594/hwjqfa14rugvedj5pzny.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204595/fvw0ygqxpslajts5lyei.png"],"aqua":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204594/jg4rp3seg4qdctunm5iz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204600/e5w5h2dbbth6byeel0zx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204600/ermpdq0pnvgsdeh1lwfx.png"]}</t>
+  </si>
+  <si>
+    <t>aqua,white,orange,lime,red,blue,black,darkblue,pink</t>
+  </si>
+  <si>
+    <t>{"aqua":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240326/d6r5bkfqztubiecypb5c.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240327/tx7znzzzibdhbi0tdwbx.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240331/pzmkidvn0xevfpefdll2.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240315/culnerksqhgu9lycpzik.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240315/ljz9rl553mm8e6oellmu.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240315/i5jciilu0u7vtiafm8vu.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240317/dhl8c3drwq6kja8kbofx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240316/pzhitikv5jqvnv8cyyux.png"],"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240317/p0ts01taw2hcswwkayq6.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240319/gj5xozdijodnxd1tpsxl.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240318/ogn1qifkkblho6tgxxuj.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240319/mqsfmq5yibzfhtcoqsmd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240320/iyhjjlkfsn2mzobssw5q.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240321/jj6wc83wyg8hv6rjf0k3.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240322/i2m7mv8q2axslomzcn7q.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240323/plixjxdjrhxkvz9evwbz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240323/qauxwvfjqaecayhon2fr.png"],"darkblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240324/lxp4pfpllw7gopbm65pw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240326/kkfzwv6k3jjrv7xevinr.png"],"pink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240328/b0n6erhuus2wvpvlgnkf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240329/rv2kerx0db2q0ufhcviu.png"]}</t>
+  </si>
+  <si>
+    <t>orange,red,white,green,black,pink</t>
+  </si>
+  <si>
+    <t>{"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204827/wfb0s6ht7y1yjy8w9ree.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204847/ni5yqfmfthjlxjxlwbq8.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204850/nejkqvzhvh4tbbz5xxfd.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204833/hmx7jiistqwo7ns8xnvj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204835/adh56smt1qwvnm9qfbib.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204830/juwp1tfvqrdzmsvm63qc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204832/l441cpb36etyn9cmbwe3.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204836/drlieinth9sskx69d8rn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204838/k2hpyhof83m70d9tlqrz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204839/yrhidsfjcsanh3rpvhi4.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204828/ff4ixlvwdaqdjlgjuxig.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204830/fqbxit9rqmevan0omtu1.png"],"pink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204842/mlswrrorkpf2uggcahzm.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204842/fp1y5cjoltkbl3djuazs.png"]}</t>
+  </si>
+  <si>
+    <t>white,blue,red,black,pink,green,darkblue,lime,olive,lawngreen,mediumblue,skyblue</t>
+  </si>
+  <si>
+    <t>purple,white,blue,black,pink</t>
+  </si>
+  <si>
+    <t>{"purple":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240092/kashajlylfyous0myy8p.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240092/nynsdrkqemer51ygln09.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240092/jk3ve5vkbqltfoln0zju.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240092/vf6bw6cbqaus3ajjiej4.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240092/sucsr5by0khe0ogmnye9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240092/tnhjb9yh0vogzsxnghlv.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240093/uqfjez19vcqk7i8f7wl5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240092/nosv8yuzhnnx2buiqcvs.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240093/ftek6pn45vfs64yueoc4.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240096/gh5bwwsk34ysqkmwx4ke.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240097/o2z7kxfetcnf1urmcfoq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240097/bd38vrculglyrqxupcdy.png"],"pink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240096/tkcqkuve9326uuysuy23.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240096/wcn5bczsuxpqxgme7enb.png"]}</t>
+  </si>
+  <si>
+    <t>red,orange,green,black,darkred,yellow,blue,maroon,gray,firebrick,turquoise,peru</t>
+  </si>
+  <si>
+    <t>blue,black,red,green,olive</t>
+  </si>
+  <si>
+    <t>{"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205963/iqugy93ruijx2qs6albr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205963/q6ouylsvbgqejbwf7ylc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205962/kwzacjzqbafzsjs5fixy.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072968/riy6rimanvqxwxzlay7x.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072970/dsfskf4hd98akspwscqp.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072961/bkqyk3gc00ddzqxykogc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072962/nowuvxkhdkur9vgrobql.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072962/lhnh9ojgrwatsvbsdzeg.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072966/ghqmghlhv83i5vvcas7y.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072968/xcsewhi1ixqg5zsl7ooo.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072964/nbkvbujd0eextzgqc2qu.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072965/pn8avdaq3ufr5vtacwpb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072966/ditkur6no6op4lvydks4.png"]}</t>
+  </si>
+  <si>
+    <t>white,lime,gray,olive,green,black</t>
+  </si>
+  <si>
+    <t>lime,blue,green,red,darkblue,orange,turquoise,gray,darkgreen,skyblue,peru</t>
+  </si>
+  <si>
+    <t>blue,red,green,lime,black,gray,skyblue</t>
+  </si>
+  <si>
+    <t>lime,black,red,green,blue,gray,skyblue</t>
+  </si>
+  <si>
+    <t>blue,gray,red,purple,green,skyblue</t>
+  </si>
+  <si>
+    <t>white</t>
+  </si>
+  <si>
+    <t>{"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205752/mfwiprr6tvgovwpuue2v.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205755/cnpmodwwbutausd84kzo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205754/vuzoeqyobfg2u01bmwry.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205752/m1pbnbpak4qv1eurewfs.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205758/yii0fqmgiqr2vcn6jobs.png"]}</t>
+  </si>
+  <si>
+    <t>{"deepink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253062/zptpktvgxg3f8kktmdoc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253054/lgmv12q6kdnnihthu2c5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253058/esrhz9htyzmbtw8lprlb.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253066/cu60ygho9ju8nhgs9u0i.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253071/yxibzfzbdieldwpk4rj6.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253075/pzfosnwlpivkyqw3spua.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253175/wy1mdakj1rgi8npqbnes.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253179/j1pocuccycfwko4n1lvc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253183/us4odbmjtwnoosljrf4i.png"],"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253188/mxfmivtle98ap5ucsrqh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253192/unqydmy6xqan8ns2c8w9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253196/uoy5ksbucjxis24dmvjg.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253201/ayeeoh6cxmydwakscp1e.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253205/za5icspaghp6ejbvcv0f.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253210/amsnseat5x3qul0ced8w.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253214/kxwpnvvjy9srtea3vnjo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253218/lxluzyp8ltavizaho5kh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253223/meumpynjfc5fiidbslqz.png"],"steelblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253228/hhj9g92uudrv9rka6fsq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253232/xjvbxl1bpa8jjedw0pg5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253237/pte8vrflbtvl8mami0jk.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253242/wvcutbu8mdpijx9ue7uq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253246/mqiabyzb4qz1d6andsuz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253251/muflvb9qdzympgejtlam.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253256/bvykxavqeornwqnln7qo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253260/dmhygcjblo6xnn6yhclc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253265/k2adwky6ak2i5jdiobl5.png"]}</t>
+  </si>
+  <si>
+    <r>
+      <t>{"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242437/dmbpdy0o8zo774yg0esp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242493/phwa4ghsnghxaad8rs0s.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242496/z0ckuych5747dbdjbblh.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242497/mllydvsxp8bsmjxtudpf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242438/gbxh6ouluwykgpjacnn5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242440/jbincqszbskytgzid1xr.png"],"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242442/rjagdaxpyr2ekyatvpnc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242443/omnxdetafnsovhyqsrrk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242445/tfuorgusbozzg5qangpa.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242446/vrqh5h2ds6suivfhxsg9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242448/arvjdgaypjnno56lfvbk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242450/yzbjosqrehdwxvwhcyfo.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242452/mzxqsxz8cz3pfkwggyzv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242454/xburffuwfdwwt6917fav.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242455/qgkevnsapc7o43ad0bq7.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242460/burfwilllus1qaxskiqw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242460/yspgkvybbozucaqc9ap1.png</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242462/ngof4yshn3cjaat7tglk.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242498/c9jctj0oy5awxkw7qhps.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242456/lqgzodgnyvwdgdski6al.png"],"deepink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242501/dzn9seysibv5yjlylqkz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242464/lxs8m7ci4bwqqyfbrjz5.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242485/t4lvqrs96uqcbrzscv68.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242488/c7sam295q1wiuiiakyt7.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242489/n1csydhjwtdmhlpf30te.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242479/ony3dvs6kvxistz3fxic.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242481/mmu22qpkw9rz2ecm79rk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242484/afwxcc8qacktmzbo5pcn.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242473/h5jrcvlasfsfetqinrzi.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242473/dfhfnav2renc5azvzicn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242474/dcsjwceh9gzre70xl9n7.png"],"aqua":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242466/wxbkzpewkatvhqphl8vc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242469/zlrfrhmdw24co5sql2xg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242469/oxccamqqxqe81hbdryqd.png"]}</t>
+    </r>
+  </si>
+  <si>
+    <t>{"steelblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206521/lgdrcsg1bhg9kh7qjnhs.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206518/hzeq19gaqctil3pzrsi7.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206525/u9vdtg7rq4zp8awiwcvk.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206510/q3vtqnmiruti86ckrgbu.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206515/me4zdvq6donb2neznfwx.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206507/nrjilgz3harir9vbblte.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206512/sgr2zgufvyugwtetnfwq.png"]}</t>
+  </si>
+  <si>
+    <t>{"steelblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206431/chw3zigygyv3inpyuvqq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206428/dpd4tmtaaqza6dyt2did.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206419/yy8irefmctqlb5zcfg8o.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206422/x1mq71osh5on96tmco1r.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206425/tszk3w3o2iadgwgwahdy.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206419/evwkicwrgexeqbw1zunt.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206416/gldj7bzghm6jnqtfo7kf.png"]}</t>
+  </si>
+  <si>
+    <t>{"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205850/krzni89svcg4v5gsqcuw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205849/iu07rz8ksuxhxxjxxu8l.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205844/ysacjarjibcamythvsfn.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205852/yjhnp8kcprzmdlbz27vu.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205854/cvcelpjomduh4jts5ebj.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205847/acp23tselbbcvxfuusjn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205845/mbsg3lgx0szz3bmtdzsy.png"]}</t>
+  </si>
+  <si>
+    <t>{"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242029/t8uqnnz3xquyods3yjuo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242026/bhk2ra8bxegg1nett1dy.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242027/vmmu2gxitaresedeozwy.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242030/cvv13nrjorakxzrybhyz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242032/uqtabdnhi87fgqj6uyrf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242033/ftso1gdl3pydfndmul3i.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242022/et5gakg3ttjrpaocdrhj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242023/zyxyuodrznijtx9htcgh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242024/nvx1b5qu71r1morqpogv.png"],"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242017/xhsyfhnh2ohy8gdo4gbx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242018/i1ek3bj6quqlyrweyav1.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242020/pmm6wzown0nvrqaxyjbf.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242037/pyutr9umxsyhqre5twwk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242035/whmjqbrlbzxqlgohzpwb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242038/ajaqgx1dp3slbquw4mqy.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242046/kuu390re0sjhgwxtdozg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242049/llti53qlpeo6he6iyepg.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242041/w3bqvag96sjkqaqt6otx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242042/wgdksgeqad5hjjwthyxh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242045/wobnjlxqye96sonmjiuh.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242050/mt1m2s4b3pmrzclsur90.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242051/yqtt3f6ddky3d1m01jor.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242055/likodamfh0tnmanutqez.png"],"steelblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242057/ppzxm4hussikf4xeodks.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242056/plecdtdxjrqwv5ogroyh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242062/o7nidfchqyxj6sv0ftsy.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242070/hz7efssob93nmyqgfops.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242072/df0oelpt8qs2qw2goqya.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242075/moplg3kedybdnoyz7jrv.png"],"deepink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242016/ollsxotjasmd3vf5bszm.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242079/ftznc2ggfw2qui01m5g4.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242016/tuj3mcerslrwctwezm8h.png"]}</t>
+  </si>
+  <si>
+    <t>orange,lime,blue,red,gray,darkred,cyan,pink,dimgray,crimson</t>
+  </si>
+  <si>
+    <t>{"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247417/fsnc76cnoyldcjrtqimf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247408/vlndzxu3t9dpp4ttozth.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247418/mctbjpwaqtslwymgbe8v.png"],"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247421/z2o1l14z6bsnzg9lwehx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247423/yqnnmwpfgjxnu3lauwlg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247426/awauj6scyqizoxckmvhc.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247120/qycbtly9j4her3konvlu.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247125/snjvyp8cmeq3pbufrxbe.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247122/yh43dsbcwebudyexc8bf.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247128/cywqxzzvjc3xec1jdofo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247131/yxure4h71vujpodaiqfz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247134/oxltg3f7klarkx3edgcn.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247138/ghfvtbboobuzylosnngg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247142/rnynzply9urpfvdjvpis.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247152/dbzo8kcdmzv1kclqkl9k.png"],"darkred":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247146/pef9xkgaen7quevt12ih.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247150/qmojaewohggfuhy4vtp0.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247157/o0c0se1fcldfzpvfvras.png"],"cyan":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247161/z5ibtetkaifmwga6xuwm.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247168/gv8mqwlsscxwqpvxmag4.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247163/xynygevq9hfbp5bfxrif.png"],"pink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247384/kxf5almctfuhrkay3b7f.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247391/tk7cqx51wm6zxtvhiwif.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247395/hyhdaibr2av6pvap3mdu.png"],"dimgray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247397/trpsmfci5nyixoti6csf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247401/f1godfk1kmhcie0ltc8f.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247405/qi0swtsd80v1qqcnekl4.png"],"crimson":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247428/zj9u9fwptpcltt6fidbs.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247432/rhhw4rtpbrxdz26hnze6.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247434/twh04ewl59cdgdtt1vf5.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247437/wfszxagudgfkkhibg64w.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247440/jzd37xntwermpav5ibes.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773247442/e3bwrrvsigcneqjtap67.png"]}</t>
+  </si>
+  <si>
+    <r>
+      <t>{"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203999/usyc6b2wrusfgxtlm2qk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203998/qqrg6ovyaygwgzo6hiut.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773203999/oygmfyylfh3myppaxvci.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204001/z7wmpqkqkmv6cftzahgt.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204001/z7wmpqkqkmv6cftzahgt.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204002/dpr85e6lpra04cm8qhvr.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204004/bjbwe0vvws465sgdsibi.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204004/mqynudrqxao2nlxmw3jc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204006/ntok0wpipovhqo8f5cgy.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204010/udiozzvwnwvydtv0wq3g.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204013/i65pypk91tpykczm7aue.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204017/wdgots0y5qxq4xapd5am.png</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"],"steelblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204007/kmygqxsbpvkk655deajr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204008/ro2gdz0vksafdl1nsgje.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204009/kchxfk2hucqvjsbiiqzm.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204015/cx6vbwbybklwqeb2rb6n.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204015/ow6wevpsxfxj7ok5uwcp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204017/qdijmtqkme1yxfsrcvyh.png"]}</t>
+    </r>
+  </si>
+  <si>
+    <t>{"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246199/i0dglyyhbcluqatrfsvo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246197/zqako0ctmghqrl6zwtzk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246198/ta1v6vfpxzaxjjwcgz5p.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246184/zbf54ys2kknf7oztx0tx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246220/dkbsjozqyjjajesardrg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246185/oirzy658durxqoleif6j.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246203/vjacif9vp8htkdysvtmt.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246206/psburg2qyrlzmn9pm0bs.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246208/u60u4ilzfe7kqsrr0pfp.png"],"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246176/mshuohmqntaoukgvfail.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246177/a5dlrfq7gacz0ivmgsza.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246180/h5ityj1muhoa5qvnt1jp.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246211/ssmizxvpulellquw0eib.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246213/zqoaptlc290prwz9nnrx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246218/czcwuvs3fgvdkireybmo.png"],"crimson":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246188/o6uxls2gicnpmpgehtd3.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246191/pmyulqx9ilktonbzjgea.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246193/zbk3k2yzdzrgzs7yem7e.png"]}</t>
+  </si>
+  <si>
+    <t>{"pink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251316/hk0jlni8wpksgof3baiq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251332/nmhl4weionvrzubg7j5a.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251296/xpukyywtqft1da538wcw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251306/fhraecid5vphrtch2dri.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251302/jjjogiovv0wzysfa9isu.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251500/jstdomn7l5y6x3ocpuym.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251495/kryxhbzdtateashb1erm.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251299/o6ffovs84oykaps9c1t8.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251340/xu3a88n0sclnadfbmhuj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251344/aleyzsp20qw7biej2p5j.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251309/b1zryqx1bsafrlyvhvyy.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251514/jgosmb2r3ko6qqn3z5hg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251491/mas362bji3q33ih5bptw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251313/feh4kaab9r6e7hwioogt.png"],"purple":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251324/lr4gpikcrov2q5qq9m8c.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251328/fjxmafrngvkbn88ejw4i.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251320/tuufe6sjelutlmr4b9ee.png"],"peru":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251582/oos8ldtacdmwveywefle.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251578/gf8eygd5san0v4ra5s98.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251336/crqclarwktlfrxomlfdu.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251567/hj9j4ikrvrgnmxcg86fx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251569/e3bnxeywesj5hdunqp54.png"],"steelblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251503/abt1o1yeybagwndpnepm.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251510/ole8ggrtozry9zg23juu.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251506/z2himy0y7khwvid8epu0.png"],"crimson":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251522/egtmqebvbs4zppoksnxt.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251526/dqnnvig8vlsdbjycqnxp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251518/j0ir1ewset7adclellzd.png"],"darkgreen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251530/kv1jdohhfd9nisq9gcaz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251534/vcawodcdldm8dik7y1ih.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251540/nkrliakvitqlsymdle50.png"],"royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251544/jwpqm6e8rgpanqdth6zo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251552/emcnouavm6pygbhoj8ka.png"],"mediumblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251558/xp2mksxivnerri6uwavf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251548/yjolwgv3hwrlidwsax9q.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251562/awzlefc0vnoikld48dox.png"]}</t>
+  </si>
+  <si>
+    <t>{"S":{"retail":34000,"wholesale":17000},"M":{"retail":34000,"wholesale":17000},"L":{"retail":34000,"wholesale":17000},"XL":{"retail":34000,"wholesale":17500},"XXL":{"retail":34000,"wholesale":18000}}</t>
+  </si>
+  <si>
+    <t>{"aqua":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243833/ag7fvcalwnwu39zfktdr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243829/fgyjb9q1tw3gba5nk2su.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243830/kcfpvzkfka3b3xeygxll.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243820/mxewjb6f6duitmjychhw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243824/inyaodlfwyqr4moex7n1.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243825/aqktqoqiifn9mbbd3rab.png"],"sienna":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243813/fdck5hyohbvrzlo7fltd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243814/aykqexydowfyzxomcc42.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243818/mh9fwgfnvevlsrvkrnkq.png"],"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243804/peuetkjhsux1ur6vyvbz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243808/cvzhjpfpasgw49dse2xq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243809/wsxn1vh94rqdgdlnmlok.png"],"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243797/onocg21ivaqcafob67ti.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243800/yfzxpij8ha9nndinetxs.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243803/yhq0apstlyxici5ytbtj.png"],"crimson":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243789/nosi8kjoigatgrzpzhzh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243794/ur41t6slq13rkfntj2i8.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243783/zxw3kndw7iivajhcx50p.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243782/lapro3zzm8mibteb1qut.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243787/pfjjtad5iy34x9scjoti.png"],"mediumblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243773/pznysna8zgrwgei7iosz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243776/pv42tv6dpex9dnxe7dyw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243777/ldegmscz37zsz8kosa7d.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243766/ihfpqly9ougd1zmqqrv4.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243771/hefdrod8dailwbehpkbo.png"],"darkgreen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243758/lxlnk73tcxxib8zmkpht.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243761/lr2e6afjdp0p5tlv2w2t.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243763/ierurivlvb08tnxyalk0.png"],"palegreen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243753/pa93tugsywvwkyglttyx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243751/dqn9os5y7gn6oprrbcct.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243756/nqkvo9rwehv61boql34y.png"]}</t>
+  </si>
+  <si>
+    <t>{"yello":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206201/btygymizhrf2lph7iqd1.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206192/klhra6geetywd6zwvjlt.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206194/c27fyoa2bpegm6jursp8.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206198/btfl3b4olt1skxbds9ao.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206221/v9ho9qfzw7ayeirao6ym.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206224/ka1gwsxjcozhoqwpulyl.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206225/l5zu2qiqapzi5xptxpwf.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206208/vgs6ehnasapqhzdtvlzy.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206206/nmuefu9vwm11mqrjxqhf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206210/ujuvzdpxtzwtkgcbijmi.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206213/adkptqxij8fmhbsen1lh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206215/zr4hck3iljojhhvaqwwv.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206237/f9lyfni15lwx0yoerfhe.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206238/nlubmnfupy0ao2vc7rdl.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206241/ebemeofhz7csmnxaik1a.png"],"mediumblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206229/e8dbtk3ozmsxnypu38h6.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206230/qzz5dknp6pav7svxox5p.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206234/oohgk5nu6hktzmfggpec.png"],"royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206245/q6tac1iumusqgree2h6t.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206249/zakhmtf84etmjjwo6pft.png"]}</t>
+  </si>
+  <si>
+    <t>{"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243265/lbckoxtgdwsbuj3irkxo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243259/usc625rcmjo8mwec5rw0.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243262/shmpwj4ypl7qgs2guhrs.png"],"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243128/kjatv1i98poykoervnke.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243134/ciuxu61cqfsassyvyjwu.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243138/qozrzjiku0vwiuqsfqky.png"],"crimson":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243138/oyassw3iejqmackln8jk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243139/eaaikz3oxhjhjdouh3ns.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243145/hbhpsfpfqnnei0z5xjba.png"],"pink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243147/pwk9iwc22ag4sjubhwp2.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243151/bt2knyzbwfv4qqmbvw4k.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243153/tyqsxzbn9lgio0hma2dg.png"],"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243235/dlbdsvf26udcmpdajexp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243241/armqf4yhv1amiomc30oq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243236/cvxzg0sj0fcoyr4fkeqs.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243244/fvxbecqdzdyt5e2hmzhh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243246/nucwf90fvyycvxmuygtc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243249/cs7nhoopwedkvpe5z4zf.png"],"royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243253/gtwlxgnawlgxpmnph7ra.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243255/ksbn4rpcltiz8vtrrcnh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243255/am09lysi4qgtmqxegfny.png"],"purple":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243267/f3w2rmrndowm8oeiywbz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243268/zumu0xzo9n9stt8prfbl.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243272/n6uzajqlx3m3iovgw7c6.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243275/xfw3x1ddikfmnin96tqx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243279/x4xb568xsqgsciwnxyck.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243280/obocuu9xt6hlckmfbov7.png"],"dimgray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243285/t72b4tjttwkblzqbl1dy.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243303/de3wdtoe9xisowovvxk2.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243304/nt62kbiluuhwrjbhygav.png"],"darkslategray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243307/mbcjrbl2mam41lb8j1dd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243312/mkaneumzcre25bofkzwg.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243313/bxbqbm3zyp4rn0v1bhlj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243318/ccjefsgxdixtpl6jltws.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773243318/d9gy2uac8ktt3mjqnaav.png"]}</t>
+  </si>
+  <si>
+    <t>{"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204338/oejbgfjjrnas7l9peyx2.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204336/k7scng21l4yann7xww1g.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204337/p7rhhrzowr2rwabaf4wq.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204340/kjystwsspe4qlwkpttbx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204343/x0wczvaf4thuo262zk1a.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204342/k6n6vrz51vbfxkp37vxw.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204332/klqdeyjspxstecn1fqng.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204334/pmpnlaeem4it8y8tnxn1.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204335/e8dw9g0qre5ydzlqlatf.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204328/bvt7ueaexvkdythpanwn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204329/aofbo59s1uffco8i2wpi.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204330/b8n7glynvblcahn4kh05.png"],"pink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204325/tjdsejcvcgfgkfquxzjn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204326/mwrayyzb1rfuvdycyddq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204327/hn8p4ckn1sozzowpziib.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204322/b16ab0jfz0etyo8jshsw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204321/ooznuwz1cpqaqu5ownul.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204323/q61r8koxk0fhvecqkrfz.png"],"darkblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204319/fkqlvntrdaq8jt793uhj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204319/a5ep6vrxclrxq3b0h6lk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204320/vckmbagb1qiehbka8qce.png"],"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204344/io3zcwbwx9oayypdxmuc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204346/shnjivk8vn0zompx1d0k.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204347/uf0mrbixslbi3i4p13qk.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204350/nhoe6gys7x7a9tr92gcv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204351/kmf8fquhpmgnpaudotr8.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204351/tvy8pbmxrxbyttnzajdn.png"],"lawngreen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204355/nmvtfz8xc6seaah6thgh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204357/wmeg6mwijy05p1hpu3kh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204358/g5nsawbiilegcqjkcsuk.png"],"mediumblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204361/y8ykrtunchadolpwmw7a.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204363/toeoq0ot4by8nx7y6dfw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204366/iy9zgfv11qm7vwguueo3.png"],"skyblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204367/b4delwnliq7h2nijhugw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204368/rxy7ecs4vyuxbllduanx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204370/bvmqdttjroiogb5zsevr.png"]}</t>
+  </si>
+  <si>
+    <t>{"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242668/fmmqv9d3abczghkogp1p.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242712/aushzmuk00uao21tcsfe.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242720/aqutgbwf8fhr0ay0et9x.png"],"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242705/gbq3blhqjey9pfsrccot.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242707/licsjuezzfbcaastvwty.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242702/y2vqiplb42ugvde6pibd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242703/xmpeiwyzm5pykzpaouuh.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242700/kbdbl8y32oyxpwtho1sg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242698/vfmx6wm7pgfdxausx0qh.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242675/vbr5qoanu6pzhtwareey.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242697/jxucutam0nuykc3cbptz.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242670/vn5zjnwmtj1ubnosan6g.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242672/ladrzy2w92giulcorc0d.png"]}</t>
+  </si>
+  <si>
+    <t>{"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205288/smm8fjw9rl4bnfqartjf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205287/xibsxjngkirncuy1yzho.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205357/io2ygjdephs2ufzv133d.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205290/r3hm9neakhl3lxyiseju.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205292/jasnol7orezj790psdxv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205294/tp3zzxyom7kg9g40bnug.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205296/lbmq4786zitdm7sqf2gh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205300/szighhczcmlvktpwcu0c.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205301/zc9grwxp77zytgruhujb.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205305/ip9ubuw7yzb1loywx9hp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205303/srdszj6njhkynu6hedrq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205303/srdszj6njhkynu6hedrq.png"],"darkblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205310/in2uykc5yibqy3ii59yd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205312/auuktvqrfwlpu4yf5zxq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205314/p8f8kh4dqcbkefuzbxv1.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205317/masdfk78uq1h1ocqnxon.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205320/ib4jb51wjac4tnbizgel.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205321/bjwnz5zmham8542llwvl.png"],"turquoise":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205323/ghweohyghfzxnp3autyo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205326/ztc53cu857yxbfpqp193.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205328/ay9h3tyk1kikgchkgh1r.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205329/hgsinisspnemzvna56cg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205332/u7f9tauhwezirlpxvghh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205335/ryi88h3pmqpwnjvruazi.png"],"darkgreen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205339/eezvjpd0anxakn1d1eir.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205366/afcwdckametvhcm2vdnk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205339/sj4x0jejmfcckjyjcgff.png"],"skyblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205340/ly5tvmjhv2exoglszokt.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205345/mbswblamqqdllr1hzulb.png"],"peru":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205349/ptzps64butp9eg2kdvn5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205354/spdvczuhihi0kmjzwygz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205353/uwy3dpacpekdc1mh1k76.png"]}</t>
+  </si>
+  <si>
+    <t>{"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246712/gotvnqbl4y3hdyauibw5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246707/yonflyqalxcl4c9if2bj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246709/xbj5qrmtoxxcqq5damdg.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246714/thwkb1zhc1xobjfnlkec.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246717/lsxqmrzz8lwomqaaua16.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246719/eq8r76oqa5gnfh9gvln8.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246722/ppj4owyqnlqcuebnxv4t.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246725/zzyif5jcihzmwccgjfkf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246730/dauki5afyvny7y19x5sp.png"],"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246732/wd38ed0dzdwcjwiwzflh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246737/swfnbkucmbke4llvpasp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246739/j9jizettng9z4ufui6mh.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246745/qjkntjcqnncozqokqdai.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246746/dici1svfsqmtnwbaxh3r.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246812/dkdxyqkjivhmzzyiqh8o.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246817/snvmvdacyeefzgztoegr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246819/llsaoy4lp3xuig0mzgkz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246824/qkhbddvmlcesobq3axsl.png"],"skyblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246828/yjyw5k38esggufh9nxoz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246832/i4h1qxhsejjbg5xnnamq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246835/wwsyptj2wb0253mmnltu.png"]}</t>
+  </si>
+  <si>
+    <t>{"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205570/nhimz97jvqd9n1anbddo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205566/eni1iwttfuwdm6kncir2.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205568/w374fboftzxgumppqjif.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205572/tdscqyvl7puxmhp803bq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205574/ww5xymmzveriylq7hrsj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205577/qev35wdfez0aydlybnss.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205560/zhfve7c7vhmi63cuxyge.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205562/odyhznfvxmlcbsbrqur3.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205564/mewqtd5fhilbuca20zfw.png"],"purple":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205557/wpiksu82a8nlxnpzrocd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205558/t4vt0vtucu51eafi7m1v.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205558/oklowlxk9rgnmv2spfbc.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205549/liik5ncoge6hhciqti90.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205553/yv2zrdnlobqntlgqune6.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205553/pvm5v9ohw0zkojlhdlbx.png"],"skyblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205580/yzmnnxuztrs4an1hdaxg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205581/hlllcf6dsxdyghn2xvkq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205585/subuoln7hcs70beqduga.png"]}</t>
+  </si>
+  <si>
+    <t>{"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944380/tutamvoy6hekufy41mzf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944392/fs1fytkfohyns82bne9c.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771942898/rijbhlwuavx9gcfg6fjw.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944379/bqaxccjfd6sr9nygvvg8.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944381/ysoyvmudfblboutmhm23.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944380/hhjqrcunr7khqfpqoumw.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944372/ldgptok98o4xkculp1vh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944220/coiapz0j73s8lapejom5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944375/sm91gmfmekdnakedgc9b.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944376/mlqjjv3lt7ao8uga1qeb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944376/cn55k0sldjbzhkbhe3u8.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771942902/dcwrxzuqhm4ccs1fhtry.png"],"darkred":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771942906/edfoqpunyti5d46l6u1x.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771942898/syeguyaosiwujnhgafnq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944220/mznurti6vuchjsbrlxjr.png"],"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944400/ygeuapeswxsjxwkvjwhe.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944406/eojts9d6cyjkf9fbg8f2.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944400/satmn0myii8g4qfq3lmc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944405/mblaxevepd4xmyl8e20x.png"],"maroon":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944399/o8b0z1y5stp7wvur1elc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944400/r1q59vlsyve7tlx6akti.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771942897/slwjdugxruduftmpj5kb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771942898/dxlnhwz77zdmqx0wchms.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944393/igdodsernfywmwpj4hgt.png"],"firebrick":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944392/rm7f2iz6gl1qefchhczq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771942911/h1gkx3ddfuqzb6puuvjt.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771942904/bunx3o1ry3mr1hix2scn.png"],"turquoise":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771942910/bya8tyhnpxlnuu0i44yj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771944387/lvlvjoyrudz5aoresntt.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771942889/kutpbrfwwxek49qzxcwi.png"],"peru":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771942889/ry5yllxtpdgyy23hhgjk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1771942891/ucy8wgnrslt6bczwablx.png"]}</t>
+  </si>
+  <si>
+    <t>{"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246413/sd8zifftkaradsu1ihxh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246405/m9uncnvd91mhscr2frjt.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246407/sdl7xnzvd5o4clqvl2kz.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246420/hfwjfdya9qvnbqrrjgoj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246416/hx9geatzcpeukodlwrgp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246423/jq1476fe7qfouhjhgaph.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246393/mwpiatyahlzpxlfztjs7.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246390/cotmmhbm8wixclxhd7m0.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246402/k0ysviylwxsylrskjkbt.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246398/zahqih859tvsnul2167z.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246400/r5n4bbavhmkkuietsujt.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246404/ziu6vn0zurqfr2zpd6gw.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246381/ivvwsdoetr8xck3yxqkl.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246384/c05ryi55fpxln4pdtogn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246387/jyoh5rpqp0txkmwgfdfo.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246428/ldtwdrargleady5som4q.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246432/ouwjlgcucmiz6ce5fijg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246434/wzqag5crymrmlpffjvbb.png"],"skyblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246507/wrmq1ij5tnjnkwneprtt.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246511/uqobbv5j1zrhxsswlf3b.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246512/dyhmm1lrkrj7nwtcrk5m.png"]}</t>
+  </si>
+  <si>
+    <t>reflectivos</t>
+  </si>
+  <si>
+    <t>Reflectiva 100% Tipo Robotica.</t>
+  </si>
+  <si>
+    <t>Reflectiva 100% Tipo Robotica(Dama)</t>
+  </si>
+  <si>
+    <t>Reflectiva 100% Tipo Robotica(Dam)</t>
+  </si>
+  <si>
+    <t>Reflectiva 100% Tipo Robotica(Caballero)</t>
+  </si>
+  <si>
+    <t>Chaqueta Tricolor Reflectiva Pecho.</t>
+  </si>
+  <si>
+    <t>Rompevientos Tipo N.F(Caballero)</t>
+  </si>
+  <si>
+    <t>Reflectiva 100% Tipo Robotica (Caballero)</t>
+  </si>
+  <si>
+    <t>Rompevientos Camuflada(Caballero)</t>
+  </si>
+  <si>
+    <t>Rompevientos Camuflada(Mujer)</t>
+  </si>
+  <si>
+    <t>Rompevientos Clásica(Caballero)</t>
+  </si>
+  <si>
+    <t>Rompevientos Clásica(Caballer.)</t>
+  </si>
+  <si>
+    <t>Rompevientos Clásica(Dama)</t>
+  </si>
+  <si>
+    <t>Chaqueta Tornasol.</t>
+  </si>
+  <si>
+    <t>Chaqueta Selección Colombia(Dama)</t>
+  </si>
+  <si>
+    <t>Reflectivo Tipo Triangulo Combinado(Hombre)</t>
+  </si>
+  <si>
+    <t>Chaleco Reflectivo.</t>
+  </si>
+  <si>
+    <t>Reflectiva con Cinta Rompevientos Cola de Pato.</t>
+  </si>
+  <si>
+    <t>Reflectiva de cremallera en Tela Galleta.</t>
+  </si>
+  <si>
+    <t>Chaqueta Tricolor Reflectiva Hombros.</t>
+  </si>
+  <si>
+    <t>Chaqueta Rompevientos Combinado Lateral.</t>
+  </si>
+  <si>
+    <t>Rompevientos SemiRobotica</t>
+  </si>
+  <si>
+    <t>ciclismo</t>
+  </si>
+  <si>
+    <t>{"M":{"retail":27000,"wholesale":21000},"L":{"retail":27000,"wholesale":21000},"XL":{"retail":27000,"wholesale":23000}}</t>
+  </si>
+  <si>
+    <t>red,orange,lime,black,green</t>
+  </si>
+  <si>
+    <t>{
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252534/kj5hpboo6rbytss7n64m.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252538/uwl3srr90j05z7vvsfaq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252526/vjbzuezxlogkzv5s6cpq.png"
+  ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252516/jqlpvxtzmkudbv2lypti.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252512/z8rbb1cwoqqem0wnmhxd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252521/tpqqguqq3vvxhqis8asq.png"
+  ],
+  "lime": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252560/xn2z7498xutogb5uyy59.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252552/ewbrxkkkjkah4eeccv9y.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252564/pcvbn30662jthl3vmdjy.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252569/u1udeunrohym2cte8w2v.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252577/gndnce5wjffvaxqh8ege.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252581/muzm2jyvy9cdwdbemdnv.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252548/shlrflbdoxhjozjehk6i.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252543/kzqt6ggjpfplbqxjjcea.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252555/kyjfquqnjh7rcksy6glw.png"
+  ]}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,8 +651,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -93,6 +670,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -124,7 +713,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -136,11 +725,36 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -448,22 +1062,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.90625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.26953125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.7265625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="1" customWidth="1"/>
-    <col min="7" max="7" width="28.1796875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="123.6328125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.26953125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.26953125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.54296875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.90625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.26953125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18" style="2" customWidth="1"/>
+    <col min="5" max="5" width="37.7265625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.7265625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15" style="2" customWidth="1"/>
+    <col min="8" max="8" width="31.54296875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="131.26953125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.26953125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.26953125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -476,106 +1091,1912 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="3" customFormat="1" ht="232" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:11" s="3" customFormat="1" ht="88.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="6">
+        <v>33000</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="6">
+        <v>49500</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="6">
+        <v>21000</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6">
+        <v>31500</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6">
+        <v>21000</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6">
+        <v>31500</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="J4" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="3" customFormat="1" ht="89.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="6">
+        <v>28000</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="6">
+        <v>42000</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="J5" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="3" customFormat="1" ht="145" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="6">
+        <v>28000</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="6">
+        <v>42000</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="118.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="6">
+        <v>21000</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6">
+        <v>33000</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="J7" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="77.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="6">
+        <v>33000</v>
+      </c>
+      <c r="E8" s="7"/>
+      <c r="F8" s="6">
+        <v>49500</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="H8" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J8" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="6">
+        <v>20000</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="6">
+        <v>30000</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="J9" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="6">
+        <v>20000</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="6">
+        <v>30000</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="J10" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="6">
+        <v>18000</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6">
+        <v>27000</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="J11" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="6">
+        <v>18000</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6">
+        <v>27000</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="J12" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="47" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="6">
+        <v>21000</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6">
+        <v>31000</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="J13" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="47" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="6">
+        <v>21000</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6">
+        <v>31000</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="J14" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="6">
+        <v>38000</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="6">
+        <v>57000</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="J15" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="6">
+        <v>38000</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="6">
+        <v>57000</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="J16" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="6">
+        <v>38000</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="6">
+        <v>57000</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="J17" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="6">
+        <v>38000</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="6">
+        <v>57000</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="J18" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="6">
+        <v>21000</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6">
+        <v>31500</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="J19" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2">
+      <c r="C20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="6">
         <v>21000</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E20" s="6"/>
+      <c r="F20" s="6">
         <v>31500</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="J20" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="6">
+        <v>22000</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6">
+        <v>28000</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="J21" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="6">
+        <v>22000</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6">
+        <v>28000</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="J22" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="54.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="6">
+        <v>21000</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6">
+        <v>31500</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="J23" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="6">
+        <v>47000</v>
+      </c>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6">
+        <v>70500</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="J24" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="6">
+        <v>25000</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6">
+        <v>37500</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="J25" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="6">
+        <v>22000</v>
+      </c>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6">
+        <v>33000</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="J26" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="6">
+        <v>22000</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6">
+        <v>33000</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="J27" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A28" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="6">
+        <v>40000</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6">
+        <v>60000</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="J28" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="6">
+        <v>12000</v>
+      </c>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6">
+        <v>18000</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="J29" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="6">
+        <v>12000</v>
+      </c>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6">
+        <v>18000</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="J30" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="6">
+        <v>20000</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F31" s="6">
+        <v>28500</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="J31" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A32" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="6">
+        <v>18000</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32" s="6">
+        <v>27000</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="J32" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="6">
+        <v>19000</v>
+      </c>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6">
+        <v>28500</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J33" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="6">
+        <v>21000</v>
+      </c>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6">
+        <v>26000</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="J34" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="6">
+        <v>17000</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F35" s="6">
+        <v>34000</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="J35" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="126.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="6">
+        <v>17000</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F36" s="6">
+        <v>34000</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="J36" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" s="6">
+        <v>17000</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F37" s="6">
+        <v>34000</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="J37" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="91" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" s="6">
+        <v>17000</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F38" s="6">
+        <v>34000</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="J38" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A39" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="6">
+        <v>20000</v>
+      </c>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6">
+        <v>30000</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="J39" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A40" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" s="6">
+        <v>20000</v>
+      </c>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6">
+        <v>30000</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="J40" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A41" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="6">
+        <v>29000</v>
+      </c>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6">
+        <v>35800</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="J41" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="98.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" s="6">
+        <v>24000</v>
+      </c>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6">
+        <v>36000</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="J42" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="6">
+        <v>24000</v>
+      </c>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6">
+        <v>36000</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I43" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="J43" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="158" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="6">
+        <v>19000</v>
+      </c>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6">
+        <v>24000</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="J44" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D45" s="6">
+        <v>10000</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F45" s="6">
+        <v>19000</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="J45" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="82" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" s="6">
+        <v>13000</v>
+      </c>
+      <c r="E46" s="7"/>
+      <c r="F46" s="6">
+        <v>20000</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="J46" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="302.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="6">
+        <v>22000</v>
+      </c>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6">
+        <v>26000</v>
+      </c>
+      <c r="G47" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H47" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="I47" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="J47" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A48" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="6">
+        <v>22000</v>
+      </c>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6">
+        <v>30000</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="J48" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="261.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" s="6">
+        <v>25000</v>
+      </c>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6">
+        <v>37500</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="J49" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A50" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="6">
+        <v>22000</v>
+      </c>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6">
+        <v>29000</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="I50" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="J50" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A51" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="6">
+        <v>18000</v>
+      </c>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6">
+        <v>24000</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="I51" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="J51" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="121.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="6">
+        <v>15000</v>
+      </c>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6">
+        <v>20000</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="3" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" s="3" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+      <c r="H52" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I52" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="J52" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A53" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" s="6">
+        <v>20000</v>
+      </c>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6">
+        <v>25000</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="I53" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="J53" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="141.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="6">
+        <v>18000</v>
+      </c>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6">
+        <v>20000</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="I54" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="J54" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="276.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="6">
+        <v>40000</v>
+      </c>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6">
+        <v>49000</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="J55" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="6">
+        <v>52000</v>
+      </c>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6">
+        <v>78000</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="J56" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="377" x14ac:dyDescent="0.35">
+      <c r="A57" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="6">
+        <v>22000</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F57" s="6">
+        <v>27000</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="I57" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="J57" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" s="6" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K1" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0526577688ca4eec/Escritorio/Proyectos developer/Diseños_Gasper/Back-end/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="148" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{658F7071-6F7C-4D44-9A7F-1A5B99463D12}"/>
+  <xr:revisionPtr revIDLastSave="201" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CFA2F24-2203-4147-B3AC-6C018103D5F3}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="197">
   <si>
     <t>name</t>
   </si>
@@ -638,6 +638,129 @@
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252543/kzqt6ggjpfplbqxjjcea.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252555/kyjfquqnjh7rcksy6glw.png"
   ]}</t>
   </si>
+  <si>
+    <t>Conjunto en Licra y Esqueleto en Maya</t>
+  </si>
+  <si>
+    <t>conjuntos</t>
+  </si>
+  <si>
+    <t>purple,orange,lime,black,green,pink,red,yellow,white,darkgreen</t>
+  </si>
+  <si>
+    <t>{
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420993/kkmdjr3zd2qzczclloqt.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420996/p37wdxl0g36hyp7kzrxk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420998/pwdjrqwgurkm56jw00fe.png"
+  ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421000/h5rp8pk5jg65fcjqr9rm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421003/ra29tkoggbizia8uhhtm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421005/c7qaqd2dm4efprhwv5jb.png"
+  ],
+  "lime": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421007/puak7fprgoicscjbr0tr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421010/wqee9mm8jcrypnunh5b5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421012/tgxqsbv36106wa5war0u.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421015/w58kqlbdis1tzhpvz8zb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421017/fiuoz4hfowekqxgrus7k.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421019/foceqllwrxjo7bh8ww7e.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421021/ztpefxjbhi1xkdowml9m.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421024/penknuwcdhp0gpuxrwoq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421029/jfaet59kswrxvlrnwm9x.png"
+  ],             "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421029/jfaet59kswrxvlrnwm9x.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421031/iabnxliciu3n6dbadzu8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421037/ocptsmfnf1gejhtu54yl.png"
+  ],  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421033/sd1imwmbs59aid8qyx8u.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421038/ybglf2hixphgayj2haky.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421040/ptbqpwcj8hsmumhidvuy.png"
+  ],"yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421042/zltgysluvinxvf8qxkyk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421046/fqm7ajd4ktdfozwx1vry.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421048/jqqmqoorekufjoexwxpz.png"
+  ], "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421051/kes6ycx3qlo4byxqpqha.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421053/qhyewlgztcdm8ypdxae4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252555/kyjfquqnjh7rcksy6glw.png"
+  ], "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421058/i3jq2rctkdfzzdm2orqa.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421058/vsqodprdycyyfna4k6xu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421060/s0cdeylzx2xswm50nb8m.png"
+  ] }</t>
+  </si>
+  <si>
+    <t>Conjunto en Licra y Esqueleto en Maya.</t>
+  </si>
+  <si>
+    <t>Conjunto en Licra y Esqueleto en May</t>
+  </si>
+  <si>
+    <t>{
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421149/qzkzole8x6gmakojrzvl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421152/a7wigb3vck0ldqo4gkdq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421154/lsnzg3x2lvlsgeu0fkgx.png"
+  ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421157/onyms9a7ib2ql3j58okw.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421162/vf5u2lagecckomov5gcb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421165/wkmnjao69u0em7pekk7d.png"
+  ],
+  "lime": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421179/qaabrem5wrnuy9df5wrj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421182/ucql2bpfgmbsghzjrknl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421184/dsrcpreqx4wyrt4dnhjo.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421189/hrffwgfiezszaru4hznp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421190/eepjpj7odzj3txsmbk0b.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421197/yldjef9vreky36smwldd.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421200/uetmtmsoopoed95pdgqp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421202/fqx9oqnbmmwgvjf4uoxh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421208/aap4wn37d7n5sesfvfig.png"
+  ],             "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421211/rl3fsc0opvecnsoq0dbv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421215/zogfpwnmphvghzgja74m.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421220/v7lhntmj7msfsaglowzc.png"
+  ],  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421223/giezr8zzha0t0qs2p4so.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421226/y5psna9plddpjowaqyop.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421229/dx2cvxtz7dy31gailnts.png"
+  ] }</t>
+  </si>
+  <si>
+    <t>{
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421065/yj3ltanlgtde7kf354ha.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421069/xppnolztpe5iopc6xbkp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421071/hf4fxifemsuajfyi9bjp.png"
+  ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421075/pk7xuh67sticdkbbjlqq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421077/n8jzd8sbfpkfnhe37wif.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421081/bmp99f8ifcol5jcm3yzo.png"
+  ],
+  "lime": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421082/ffzphlzfqhlxjypaihzf.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421084/wchtso75tjdmnsfgx3jh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421087/c4vrnk5smub9uxvtfxr6.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421090/meksjjymc1pe8iyb0umv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421094/hby8kz1bzjtxmbaoj0wn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421096/g3w5sobu0kvwo8qpj0is.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421097/t0duwqdnqv2c4nzayrbj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421103/pv1fgx8tqplhbidapm6p.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421103/pv1fgx8tqplhbidapm6p.png"
+  ],             "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421105/kmegyf5j6babw43idtbj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421110/jkz6grsiwrdf4todbkii.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421112/ydvvbukdm01b8hf52sv5.png"
+  ],  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421115/la4bjtyyijuyw8olqfsj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421118/igvdjts0mnd6m8izkypf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421118/igvdjts0mnd6m8izkypf.png"
+  ],"yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421124/ub2pugvw9etn87ylol6j.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421125/zduqpt4wip8kecctw0o7.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421130/n6hkbquijsy0tvp5ac03.png"
+  ], "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421134/fnmjdvoxdlqhnvkxx2pb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421136/o4k7rnqdgif34xfmim0q.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421136/o4k7rnqdgif34xfmim0q.png"
+  ], "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421141/kh8vh0ukdb8unavjz9vm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421144/yikhayfjat3dbnyyphhn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421147/jjrdbrrdauzbtkiavamr.png"
+  ] }</t>
+  </si>
 </sst>
 </file>
 
@@ -660,7 +783,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -682,6 +805,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -713,7 +842,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -755,6 +884,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1062,7 +1197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}">
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="57.54296875" style="2" customWidth="1"/>
@@ -2995,6 +3130,102 @@
         <v>0</v>
       </c>
     </row>
+    <row r="58" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D58" s="2">
+        <v>17000</v>
+      </c>
+      <c r="F58" s="2">
+        <v>25000</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H58" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="I58" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="J58" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D59" s="2">
+        <v>17000</v>
+      </c>
+      <c r="F59" s="2">
+        <v>25000</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="I59" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="J59" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D60" s="2">
+        <v>17000</v>
+      </c>
+      <c r="F60" s="2">
+        <v>25000</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H60" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="I60" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="J60" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0526577688ca4eec/Escritorio/Proyectos developer/Diseños_Gasper/Back-end/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="201" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CFA2F24-2203-4147-B3AC-6C018103D5F3}"/>
+  <xr:revisionPtr revIDLastSave="230" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7721A7CE-E70E-4E76-AD0A-627A2EF1A243}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="201">
   <si>
     <t>name</t>
   </si>
@@ -639,58 +639,10 @@
   ]}</t>
   </si>
   <si>
-    <t>Conjunto en Licra y Esqueleto en Maya</t>
-  </si>
-  <si>
     <t>conjuntos</t>
   </si>
   <si>
     <t>purple,orange,lime,black,green,pink,red,yellow,white,darkgreen</t>
-  </si>
-  <si>
-    <t>{
-  "purple": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420993/kkmdjr3zd2qzczclloqt.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420996/p37wdxl0g36hyp7kzrxk.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420998/pwdjrqwgurkm56jw00fe.png"
-  ],
-  "orange": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421000/h5rp8pk5jg65fcjqr9rm.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421003/ra29tkoggbizia8uhhtm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421005/c7qaqd2dm4efprhwv5jb.png"
-  ],
-  "lime": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421007/puak7fprgoicscjbr0tr.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421010/wqee9mm8jcrypnunh5b5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421012/tgxqsbv36106wa5war0u.png"
-  ],
-  "black": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421015/w58kqlbdis1tzhpvz8zb.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421017/fiuoz4hfowekqxgrus7k.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421019/foceqllwrxjo7bh8ww7e.png"
-  ],
-  "green": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421021/ztpefxjbhi1xkdowml9m.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421024/penknuwcdhp0gpuxrwoq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421029/jfaet59kswrxvlrnwm9x.png"
-  ],             "pink": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421029/jfaet59kswrxvlrnwm9x.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421031/iabnxliciu3n6dbadzu8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421037/ocptsmfnf1gejhtu54yl.png"
-  ],  "red": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421033/sd1imwmbs59aid8qyx8u.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421038/ybglf2hixphgayj2haky.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421040/ptbqpwcj8hsmumhidvuy.png"
-  ],"yellow": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421042/zltgysluvinxvf8qxkyk.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421046/fqm7ajd4ktdfozwx1vry.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421048/jqqmqoorekufjoexwxpz.png"
-  ], "white": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421051/kes6ycx3qlo4byxqpqha.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421053/qhyewlgztcdm8ypdxae4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252555/kyjfquqnjh7rcksy6glw.png"
-  ], "darkgreen": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421058/i3jq2rctkdfzzdm2orqa.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421058/vsqodprdycyyfna4k6xu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421060/s0cdeylzx2xswm50nb8m.png"
-  ] }</t>
-  </si>
-  <si>
-    <t>Conjunto en Licra y Esqueleto en Maya.</t>
-  </si>
-  <si>
-    <t>Conjunto en Licra y Esqueleto en May</t>
   </si>
   <si>
     <t>{
@@ -723,6 +675,54 @@
   ] }</t>
   </si>
   <si>
+    <t>Conjunto en Licra y Esqueleto en Mal</t>
+  </si>
+  <si>
+    <t>Conjunto en Licra y Esqueleto en Malla.</t>
+  </si>
+  <si>
+    <t>Conjunto en Licra y Esqueleto en Malla</t>
+  </si>
+  <si>
+    <t>{
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420993/kkmdjr3zd2qzczclloqt.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420996/p37wdxl0g36hyp7kzrxk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420998/pwdjrqwgurkm56jw00fe.png"
+  ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421000/h5rp8pk5jg65fcjqr9rm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421003/ra29tkoggbizia8uhhtm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421005/c7qaqd2dm4efprhwv5jb.png"
+  ],
+  "lime": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421007/puak7fprgoicscjbr0tr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421010/wqee9mm8jcrypnunh5b5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421012/tgxqsbv36106wa5war0u.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421015/w58kqlbdis1tzhpvz8zb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421017/fiuoz4hfowekqxgrus7k.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421019/foceqllwrxjo7bh8ww7e.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421021/ztpefxjbhi1xkdowml9m.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421024/penknuwcdhp0gpuxrwoq.png"
+  ],             "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421029/jfaet59kswrxvlrnwm9x.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421031/iabnxliciu3n6dbadzu8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421037/ocptsmfnf1gejhtu54yl.png"
+  ],  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421033/sd1imwmbs59aid8qyx8u.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421038/ybglf2hixphgayj2haky.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421040/ptbqpwcj8hsmumhidvuy.png"
+  ],"yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421042/zltgysluvinxvf8qxkyk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421046/fqm7ajd4ktdfozwx1vry.png"
+  ], "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421051/kes6ycx3qlo4byxqpqha.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421053/qhyewlgztcdm8ypdxae4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252555/kyjfquqnjh7rcksy6glw.png"
+  ], "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421058/i3jq2rctkdfzzdm2orqa.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421058/vsqodprdycyyfna4k6xu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421060/s0cdeylzx2xswm50nb8m.png"
+  ] }</t>
+  </si>
+  <si>
     <t>{
   "purple": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421065/yj3ltanlgtde7kf354ha.png",
@@ -743,23 +743,58 @@
   ],
   "green": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421097/t0duwqdnqv2c4nzayrbj.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421103/pv1fgx8tqplhbidapm6p.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421103/pv1fgx8tqplhbidapm6p.png"
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421103/pv1fgx8tqplhbidapm6p.png"
   ],             "pink": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421105/kmegyf5j6babw43idtbj.png",
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421110/jkz6grsiwrdf4todbkii.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421112/ydvvbukdm01b8hf52sv5.png"
   ],  "red": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421115/la4bjtyyijuyw8olqfsj.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421118/igvdjts0mnd6m8izkypf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421118/igvdjts0mnd6m8izkypf.png"
-  ],"yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421118/igvdjts0mnd6m8izkypf.png"  ],"yellow": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421124/ub2pugvw9etn87ylol6j.png",
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421125/zduqpt4wip8kecctw0o7.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421130/n6hkbquijsy0tvp5ac03.png"
   ], "white": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421134/fnmjdvoxdlqhnvkxx2pb.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421136/o4k7rnqdgif34xfmim0q.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421136/o4k7rnqdgif34xfmim0q.png"
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421136/o4k7rnqdgif34xfmim0q.png"
   ], "darkgreen": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421141/kh8vh0ukdb8unavjz9vm.png",
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421144/yikhayfjat3dbnyyphhn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421147/jjrdbrrdauzbtkiavamr.png"
   ] }</t>
+  </si>
+  <si>
+    <t>Conjunto Braga y Top</t>
+  </si>
+  <si>
+    <t>{
+  "lime": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420354/neutotxkhgbreztiwqr5.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420600/vnxlff5q98k3y6pcgb1h.png"
+  ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420350/bewhfsaqrepryemkso7k.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420908/gec1mfgswg1zw1pmraoy.png"
+  ],
+  "lime": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420491/ukcjzzpmydyraeejnekm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420610/sl97lgu2yjrfq8afd1cd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420916/oupndaoakbhwc2cvtefa.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420349/gzikyahqgzyvviligkjy.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420898/wk5y9brgelaa1mccxj3o.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420352/rffqebx5orlr6mfo5ix1.png"
+  ],             "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420483/xhq4i3vjnhluwwzt5k8u.png"
+  ],  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420489/ns2whdudtdrgpqo1g7p2.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420597/bcqhqa5iqvcr223ewo9f.png"
+  ] }</t>
+  </si>
+  <si>
+    <t>lime,orange,lime,black,green,pink,red</t>
+  </si>
+  <si>
+    <t>purple,orange,lime,black,green,pink,red</t>
   </si>
 </sst>
 </file>
@@ -783,7 +818,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -811,6 +846,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -842,7 +883,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -890,6 +931,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1197,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}">
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="57.54296875" style="2" customWidth="1"/>
@@ -3132,10 +3176,10 @@
     </row>
     <row r="58" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>27</v>
@@ -3150,10 +3194,10 @@
         <v>14</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I58" s="16" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="J58" s="1" t="b">
         <v>0</v>
@@ -3167,7 +3211,7 @@
         <v>193</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>27</v>
@@ -3182,7 +3226,7 @@
         <v>14</v>
       </c>
       <c r="H59" s="17" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I59" s="16" t="s">
         <v>196</v>
@@ -3196,10 +3240,10 @@
     </row>
     <row r="60" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>27</v>
@@ -3214,17 +3258,53 @@
         <v>14</v>
       </c>
       <c r="H60" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="I60" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="I60" s="16" t="s">
-        <v>195</v>
-      </c>
       <c r="J60" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K60" s="1" t="b">
         <v>0</v>
       </c>
+    </row>
+    <row r="61" spans="1:11" ht="377" x14ac:dyDescent="0.35">
+      <c r="A61" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D61" s="2">
+        <v>21000</v>
+      </c>
+      <c r="F61" s="2">
+        <v>31500</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H61" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="I61" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="J61" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H62" s="17"/>
+      <c r="I62" s="18"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}"/>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0526577688ca4eec/Escritorio/Proyectos developer/Diseños_Gasper/Back-end/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="230" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7721A7CE-E70E-4E76-AD0A-627A2EF1A243}"/>
+  <xr:revisionPtr revIDLastSave="348" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F63A0D3E-3ED3-45E7-A943-9138FB7A96FD}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="209">
   <si>
     <t>name</t>
   </si>
@@ -682,45 +682,6 @@
   </si>
   <si>
     <t>Conjunto en Licra y Esqueleto en Malla</t>
-  </si>
-  <si>
-    <t>{
-  "purple": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420993/kkmdjr3zd2qzczclloqt.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420996/p37wdxl0g36hyp7kzrxk.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420998/pwdjrqwgurkm56jw00fe.png"
-  ],
-  "orange": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421000/h5rp8pk5jg65fcjqr9rm.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421003/ra29tkoggbizia8uhhtm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421005/c7qaqd2dm4efprhwv5jb.png"
-  ],
-  "lime": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421007/puak7fprgoicscjbr0tr.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421010/wqee9mm8jcrypnunh5b5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421012/tgxqsbv36106wa5war0u.png"
-  ],
-  "black": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421015/w58kqlbdis1tzhpvz8zb.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421017/fiuoz4hfowekqxgrus7k.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421019/foceqllwrxjo7bh8ww7e.png"
-  ],
-  "green": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421021/ztpefxjbhi1xkdowml9m.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421024/penknuwcdhp0gpuxrwoq.png"
-  ],             "pink": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421029/jfaet59kswrxvlrnwm9x.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421031/iabnxliciu3n6dbadzu8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421037/ocptsmfnf1gejhtu54yl.png"
-  ],  "red": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421033/sd1imwmbs59aid8qyx8u.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421038/ybglf2hixphgayj2haky.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421040/ptbqpwcj8hsmumhidvuy.png"
-  ],"yellow": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421042/zltgysluvinxvf8qxkyk.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421046/fqm7ajd4ktdfozwx1vry.png"
-  ], "white": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421051/kes6ycx3qlo4byxqpqha.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421053/qhyewlgztcdm8ypdxae4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252555/kyjfquqnjh7rcksy6glw.png"
-  ], "darkgreen": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421058/i3jq2rctkdfzzdm2orqa.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421058/vsqodprdycyyfna4k6xu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421060/s0cdeylzx2xswm50nb8m.png"
-  ] }</t>
   </si>
   <si>
     <t>{
@@ -764,37 +725,266 @@
     <t>Conjunto Braga y Top</t>
   </si>
   <si>
+    <t>purple,orange,lime,black,green,pink,red</t>
+  </si>
+  <si>
+    <t>{
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420993/kkmdjr3zd2qzczclloqt.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420996/p37wdxl0g36hyp7kzrxk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420998/pwdjrqwgurkm56jw00fe.png"
+  ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421000/h5rp8pk5jg65fcjqr9rm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421003/ra29tkoggbizia8uhhtm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421005/c7qaqd2dm4efprhwv5jb.png"
+  ],
+  "lime": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421007/puak7fprgoicscjbr0tr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421010/wqee9mm8jcrypnunh5b5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421012/tgxqsbv36106wa5war0u.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421015/w58kqlbdis1tzhpvz8zb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421017/fiuoz4hfowekqxgrus7k.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421019/foceqllwrxjo7bh8ww7e.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421021/ztpefxjbhi1xkdowml9m.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421024/penknuwcdhp0gpuxrwoq.png"
+  ],             "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421029/jfaet59kswrxvlrnwm9x.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421031/iabnxliciu3n6dbadzu8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421037/ocptsmfnf1gejhtu54yl.png"
+  ],  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421033/sd1imwmbs59aid8qyx8u.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421038/ybglf2hixphgayj2haky.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421040/ptbqpwcj8hsmumhidvuy.png"
+  ],"yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421042/zltgysluvinxvf8qxkyk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421046/fqm7ajd4ktdfozwx1vry.png"
+  ], "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421051/kes6ycx3qlo4byxqpqha.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252555/kyjfquqnjh7rcksy6glw.png"
+  ], "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421058/i3jq2rctkdfzzdm2orqa.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421058/vsqodprdycyyfna4k6xu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421060/s0cdeylzx2xswm50nb8m.png"
+  ] }</t>
+  </si>
+  <si>
+    <t>lime,orange,yellow,black,green,pink,black, gray,blue, gray</t>
+  </si>
+  <si>
+    <t>Vestidos Short Interno</t>
+  </si>
+  <si>
+    <t>shorts</t>
+  </si>
+  <si>
+    <t>pink,blue, gray,purple,green,black,red,gray,green,black,gray,blackgreen,lime,aqua</t>
+  </si>
+  <si>
+    <t>Top Clásico</t>
+  </si>
+  <si>
+    <t>blusas</t>
+  </si>
+  <si>
     <t>{
   "lime": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420354/neutotxkhgbreztiwqr5.png",
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420600/vnxlff5q98k3y6pcgb1h.png"
   ],
   "orange": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420350/bewhfsaqrepryemkso7k.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420908/gec1mfgswg1zw1pmraoy.png"
-  ],
-  "lime": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420491/ukcjzzpmydyraeejnekm.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420610/sl97lgu2yjrfq8afd1cd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420916/oupndaoakbhwc2cvtefa.png"
-  ],
-  "black": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420349/gzikyahqgzyvviligkjy.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420898/wk5y9brgelaa1mccxj3o.png"
-  ],
-  "green": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420352/rffqebx5orlr6mfo5ix1.png"
-  ],             "pink": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420483/xhq4i3vjnhluwwzt5k8u.png"
-  ],  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420493/rgssmdtdukgcfnquw6bc.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420901/gxlqrunmta6rllyxxwra.png"
+  ],
+  "yellow": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420489/ns2whdudtdrgpqo1g7p2.png",
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420597/bcqhqa5iqvcr223ewo9f.png"
-  ] }</t>
-  </si>
-  <si>
-    <t>lime,orange,lime,black,green,pink,red</t>
-  </si>
-  <si>
-    <t>purple,orange,lime,black,green,pink,red</t>
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420894/trr8bz3jtpx5it5wwxvp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420607/p0muzrbs4h88fosmlhoo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420596/t9vpxkruz38w9mm3mcdg.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420586/gwxpwemnouoqmmzmxsi2.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420611/zag8p4prgencg4v7gb92.png"
+  ],             "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420591/bubuqygxitdekxw5tgyb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420615/ktjcll08g5cx3jk8puap.png"
+  ],  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420916/oupndaoakbhwc2cvtefa.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420610/sl97lgu2yjrfq8afd1cd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420491/ukcjzzpmydyraeejnekm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420485/uawcp6zs2gtdqyxeoykp.png"
+  ], "pink": [ "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420621/retbnyq9lvjwnlrpnuvc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420483/xhq4i3vjnhluwwzt5k8u.png" ], "gray": ["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420908/gec1mfgswg1zw1pmraoy.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420350/bewhfsaqrepryemkso7k.png"], "blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420349/gzikyahqgzyvviligkjy.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420898/wk5y9brgelaa1mccxj3o.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420891/itvtz1l7pvrpl6kyj3wd.png"], "gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420594/dkt4rid2cxvhzbb0xuot.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420602/zcrabmnewqo582puof4u.png"] }</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415216/we06xpomlovjuwtsqccl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415596/up4cjn2fcsefjdxztuzg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415594/rxddosoufbm36d2mpnoy.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415216/yzzivjhq7zizy3cx6woc.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415297/rox1ecupp73twsij3pso.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415296/y0emipldhrkmrfdg22nl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415902/en2a4yhri1sxekh9fuxd.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415295/xzzhoiod97echxzakued.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415295/hfvnucxihutzbutojecn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415588/my7frcxwdjffwkmav0kz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415907/xsixsbegznsvq4aezxpq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415907/y8pcamgmsq5ydddsw9xg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415302/m34efgayxjdqijyhlnrm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415305/olhenrdjnzy9ba1mhrwq.png"
+  ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415589/cjl9fultnxravelkg1ub.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415592/tzk3kpowq0746izdicyx.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415215/efpg1modoagqdq2fsuey.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415597/hf3z6610qz3jvzcjpppk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415218/xyfwe929j8xsub2s9b7m.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415626/uc3hxv7miy65kfu2gdjk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415902/skbtgp8gbjhaloyaalfx.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415290/v2mqsskcutskulpq9etr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415293/ooi0wnd9iyjnapqej12t.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415301/oujtaq1bq5tgvow7r1pd.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415589/hfieefqx9d8rkk24jhiz.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415313/xnkogrzhcs8vkpl3jg8n.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415311/dg1713rlfnw8fiabuqhu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415300/yz9mxbz6x9wuxqgqlfcw.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415302/qjwkrzu87uth0zulfs6a.png"
+  ],
+  "blackgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415308/fzvsqfuydbkxjcty5fpm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415311/in7rx8nvxviqcfcwxiev.png"
+  ],
+  "lime": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415901/dpawiurwyn1vorut7a3u.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415306/vsp5lctpzji6zwmphr4g.png"
+  ],
+  "aqua": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415307/xcbj08b9gtyukvtwstnr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415293/ls0hdduvkgrgugovojgj.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414853/yfdkmyhn5keiujc6ddtb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414861/yl2bxsm11finlrndpxbx.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414852/ujdfeda800rgt190rynw.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415136/axcroj0gkmsmmirsnvzk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414796/pzvlcupjmgw095bbup2k.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414868/iw8n8muamoqt0kd2mzuy.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414792/efu3do0v19xmx3thuyjx.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415096/vxmfmxzxgkkastehhu77.png"
+  ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415041/wnhowthtaronwtpo5to0.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415041/sh7y2dwg4kwmaxxe442e.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414857/fuxinggav1f9nr8heypw.png"
+  ],
+  "skyblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414860/whml8mbbdjavv2ap2fli.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415122/rd9amtkkvtdchwyzwtf7.png"
+  ],
+  "aqua": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415036/svhyitq90q7lhtqjhwap.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415042/jiq5xsyez2fw9lr2jxwn.png"
+  ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414867/arpfnzd0azn7bzyu84f0.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415078/obxkfqxtms97miucug3e.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415083/wnebxhzw1p2ndo405i9b.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415094/tqmkamkvukmxsy2w5pw7.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414778/wjujvnoeujjtelsfgscw.png"
+  ],
+  "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414856/ncrtui5dzrgr5t06pc6v.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415143/ze6yqvfphcrj8axtgsqk.png"
+  ],
+  "hotpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415118/oibruwqbgwcuomzyfs5z.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414856/s4wayqlpyxjxgwifo9ck.png"
+  ],
+  "violet": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414853/gplwd1d5yajvnbauw9ye.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415098/azocxpflw3jd8ngubn7k.png"
+  ],
+  "steelblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415107/y8knpru3bkqk9iy6hih8.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414826/iu5khytrsdiugxeswhd8.png"
+  ],
+  "deeppurple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414797/uuxtr38hq2g1ci78rhi2.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415135/l1bcoseyvrmitzfevegx.png"
+  ],
+  "lightskyblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415098/f1wogjma7ddwwkdkalr6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414787/q2hbwuxo519xhiuxwfov.png"
+  ],
+  "slategray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414785/ohr6o581qrdc7lurna2k.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415155/cjnvkohbuewpgnfjgq3k.png"
+  ],
+  "royalblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415155/pnfjrznwccbmtedhbaej.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414786/igsmog5qmwvfc6lu3m96.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414781/fnt3bb2wrgyz9uiqjxut.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414865/ej1ehaxzxhkn14u57kx8.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415062/qfw8ptxzu3sorxv200em.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415076/g9jyjb6uoabjjrx7fibr.png"
+  ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414781/x3urvoooqv4lllzmwudc.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415148/wvbetssef5bxiy9hz7xw.png"
+  ],
+  "charcoal": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414780/nmnixvfqnriglvgoszrk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415116/blmlmnfanmifpkwp5wkb.png"
+  ],
+  "navyblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414778/w84cqacplq6aqufoowkj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414777/wmyyavcnfzrse3gxk8a6.png"
+  ],
+  "forestgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415143/fkccj9oiukxewotej11y.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415179/fvwujf9kyyzobbcnhxfg.png"
+  ],
+  "turquoise": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415179/naxtpc6455zsfycfisaw.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415061/h9omz3wenqkmme8l5wuq.png"
+  ],
+  "obsidian": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414874/czklsfcuwbqgyljx6vso.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414790/kscmdvzihiv7opfi4l6l.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415178/lt0njqng02ahsetfuyif.png"
+  ],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415178/aukzkpz2fucsqn8i5c3t.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414783/nv4hocphgbdvc8qjtijn.png"
+  ],
+  "rosepink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415161/izm1qjaw1gylhuhkwtox.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415172/eie2t1xnta0jasxn7d6o.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>pink,blue,gray,purple,skyblue,aqua,darkblue,green,darkgreen,hotpink,violet,steelblue,deeppurple,ligthskyblue,slategray,royalblue,black,red,orange,charcoal,navyblue,forestgreen,turquoise,obsidian,white,rosepink</t>
   </si>
 </sst>
 </file>
@@ -818,7 +1008,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -855,6 +1045,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -883,7 +1079,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -933,6 +1129,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1241,7 +1440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}">
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="57.54296875" style="2" customWidth="1"/>
@@ -3197,7 +3396,7 @@
         <v>190</v>
       </c>
       <c r="I58" s="16" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J58" s="1" t="b">
         <v>0</v>
@@ -3229,7 +3428,7 @@
         <v>190</v>
       </c>
       <c r="I59" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J59" s="1" t="b">
         <v>0</v>
@@ -3258,7 +3457,7 @@
         <v>14</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I60" s="16" t="s">
         <v>191</v>
@@ -3270,9 +3469,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="377" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>189</v>
@@ -3293,7 +3492,7 @@
         <v>199</v>
       </c>
       <c r="I61" s="18" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="J61" s="1" t="b">
         <v>0</v>
@@ -3302,9 +3501,63 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="H62" s="17"/>
-      <c r="I62" s="18"/>
+    <row r="62" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D62" s="2">
+        <v>22000</v>
+      </c>
+      <c r="F62" s="2">
+        <v>28000</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H62" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="I62" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="J62" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" s="2">
+        <v>5000</v>
+      </c>
+      <c r="F63" s="2">
+        <v>7000</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H63" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="I63" s="18" t="s">
+        <v>207</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}"/>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0526577688ca4eec/Escritorio/Proyectos developer/Diseños_Gasper/Back-end/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="348" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F63A0D3E-3ED3-45E7-A943-9138FB7A96FD}"/>
+  <xr:revisionPtr revIDLastSave="398" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{441170B5-D974-42A3-9B84-74B5E05FE727}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="216">
   <si>
     <t>name</t>
   </si>
@@ -779,9 +779,6 @@
     <t>pink,blue, gray,purple,green,black,red,gray,green,black,gray,blackgreen,lime,aqua</t>
   </si>
   <si>
-    <t>Top Clásico</t>
-  </si>
-  <si>
     <t>blusas</t>
   </si>
   <si>
@@ -985,6 +982,133 @@
   </si>
   <si>
     <t>pink,blue,gray,purple,skyblue,aqua,darkblue,green,darkgreen,hotpink,violet,steelblue,deeppurple,ligthskyblue,slategray,royalblue,black,red,orange,charcoal,navyblue,forestgreen,turquoise,obsidian,white,rosepink</t>
+  </si>
+  <si>
+    <t>Top Clásico con Estampado</t>
+  </si>
+  <si>
+    <t>Top Clásico con Estampado.</t>
+  </si>
+  <si>
+    <t>blue, black,pink,skyblue,red,aqua,green,darkblue,hotpink,steelblue</t>
+  </si>
+  <si>
+    <t>Leguis con Bolsillo Secreto</t>
+  </si>
+  <si>
+    <t>leguis</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414294/lalfn7mpxyrfn61cr2ui.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414079/uuyymhtjebpnzieha46s.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413936/q3vffhwxc966kznn6g6l.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413796/zhrihfxtjxtbh2ap5okx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414110/adb360lld4u3wfl30bhn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414111/l81pfolseshvhlyiqhmm.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413797/vpi6ojnecgpdykoi8pna.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414120/oill26ouut0zr1o9oqom.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414288/aku1blvuagnm3qg2s5tq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414252/dbpuxgerfccbsrxh45dl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413798/iilut58aa5sgrl9rcay5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413807/ohmahl5wmzpzu2eujwwx.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413921/jicruqkcffnnblnrskyz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413923/hamcnqlv1nknjnznd6h6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413933/zspfcqoqps5jogvl4mic.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414122/sa2xpbziy81plcdrxjg0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413944/dfedjzcsvqkuf4yah3w9.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413915/by3xpktfzvomhmdnsqaa.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>pink,blue,gray</t>
+  </si>
+  <si>
+    <t>{
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415173/ehbtjxpqigtrjexprq1e.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415038/yedvzvv3q68xraht3jsx.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415109/v3odslhbq858qgjstliq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415166/dtggf63ii76rhbrfljns.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415108/gjz61wre9kywk9tpoqfw.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415056/ejxd0rl7hlbiyfbziksr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415057/kqmtkeyqhc2bdubq99yp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415046/rrjlobxsbfexfhfezjm8.png"
+  ],
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415168/xkjtrme9qbjk6exr5rcg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415036/jjq2ulppyznowg4sqbag.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415039/rykzli2ujeb8aqz2rtur.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414793/wxhgeznzedlvj2qsf7ul.png"
+  ],
+  "skyblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414789/q6s0hd6qlhtve5oqve2m.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414873/dgaicodicvxyeodcojyw.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415103/av5ntpkna0td5o0sqofy.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415137/o46stih89fs9l5wl9d1p.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415045/knkzhzen944uh64dux5k.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415065/eugarofesxglemsrgus3.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415129/df6y3tu98qbhtk9za3o7.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414862/rekfrano7tohivkpaxsq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415071/vz9tfwlztrcvfygx0ws3.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415072/mmdq7gmn8ksqemkfapqn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415162/xnranzdmgindyl8kdjhe.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415046/oeiuyakakm8tjuxthc5y.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415130/cruzgtrkkrmdubjoq7iu.png"
+  ],
+  "aqua": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415050/y3ulrhvmdj8ozm7j7shr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414795/tbxyymwyvtwhddexastb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415055/jzm6avbnsoebygrer2nz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415077/zaxcnkgtvcktta5zqo1u.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415068/lvl16yschn5i369ajgsw.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415050/vtz4u8bw5nqpwryoggsa.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415088/yci9thxy2qlmmijymiyl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415141/jrarb8m23ukeihtxryef.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415123/nfpd6alsvyic6f2te49k.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415066/w8k6z6dqmbimtxaomztw.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415149/ers5wlsck3ptjhisv56t.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415066/hqhrntdhgo4xxc5zhi0b.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415088/jihvmjs3ypg0gwhznfbe.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415173/frdmj0otsbitniu4xxnp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415102/ieyr2fookfvrzst4ow8k.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414867/mcsvtvf34tzjum7wpe74.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415073/zvaubje9c1uqwk6gwgly.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415107/ryeohsddja6nxygg7qnd.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414861/jwext9wxavh6vzqxzjqy.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414791/lulm7l9pfeau0yly08bt.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415061/lfuhwqxtaz4s3j7hha3f.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415165/brwjqthq7xw248dz9qib.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414779/tyovchmfwcg98m9mvl71.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415092/cvcqvekasklwdzedtd3c.png"
+  ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415115/j7r3ssqzeju3hfxw4fio.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414869/dgep04ackkpjzao8mhlu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415138/yopy3iqz4fjzglekrmt1.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415169/pg0qzfdr7hcjynsimiqu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415149/a7tn1cfqlpx1etvzim38.png"
+  ],
+  "hotpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415054/cjl2nfcozxguf0spqhtm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415087/al3rlm4iukbkgxaeodea.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415098/h7n7w64pxtlozzjndyee.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415102/dk1zxnwmudvgpj35y0gp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415123/j3fej715ue1jiuxq25i5.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415115/r2odusg85zzecxpbcnsd.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415156/jkp8p7nfwetobtwkgdvh.png"
+  ],
+  "steelblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415109/gzintwkxzs3fy0aztqws.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415145/bufzacscqijnirzsamvm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415125/jpvuamrupevzvuccmf8s.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415130/qthqtbojm7vhohh4wkgo.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415156/z58um5lqnxlnd8pp0grd.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415129/odclfkwhom4d9u1wijnb.png"
+  ]
+}</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1132,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1035,19 +1159,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1079,7 +1197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1122,18 +1240,22 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1440,7 +1562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}">
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="57.54296875" style="2" customWidth="1"/>
@@ -3374,189 +3496,260 @@
       </c>
     </row>
     <row r="58" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="18">
         <v>17000</v>
       </c>
-      <c r="F58" s="2">
+      <c r="E58" s="18"/>
+      <c r="F58" s="18">
         <v>25000</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="G58" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H58" s="17" t="s">
+      <c r="H58" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="I58" s="16" t="s">
+      <c r="I58" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="J58" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="K58" s="1" t="b">
+      <c r="J58" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" s="21" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="18">
         <v>17000</v>
       </c>
-      <c r="F59" s="2">
+      <c r="E59" s="18"/>
+      <c r="F59" s="18">
         <v>25000</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="G59" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H59" s="17" t="s">
+      <c r="H59" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="I59" s="16" t="s">
+      <c r="I59" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="J59" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" s="1" t="b">
+      <c r="J59" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" s="21" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="18">
         <v>17000</v>
       </c>
-      <c r="F60" s="2">
+      <c r="E60" s="18"/>
+      <c r="F60" s="18">
         <v>25000</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="G60" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H60" s="17" t="s">
+      <c r="H60" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="I60" s="16" t="s">
+      <c r="I60" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="J60" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="K60" s="1" t="b">
+      <c r="J60" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" s="21" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="18">
         <v>21000</v>
       </c>
-      <c r="F61" s="2">
+      <c r="E61" s="18"/>
+      <c r="F61" s="18">
         <v>31500</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H61" s="17" t="s">
+      <c r="H61" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="I61" s="18" t="s">
+      <c r="I61" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="J61" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" s="21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D62" s="18">
+        <v>22000</v>
+      </c>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18">
+        <v>28000</v>
+      </c>
+      <c r="G62" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H62" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="I62" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="J61" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="K61" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A62" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C62" s="2" t="s">
+      <c r="J62" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" s="21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="C63" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D62" s="2">
-        <v>22000</v>
-      </c>
-      <c r="F62" s="2">
-        <v>28000</v>
-      </c>
-      <c r="G62" s="2" t="s">
+      <c r="D63" s="18">
+        <v>5000</v>
+      </c>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18">
+        <v>7000</v>
+      </c>
+      <c r="G63" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H62" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="I62" s="19" t="s">
+      <c r="H63" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="I63" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="J62" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="K62" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A63" s="2" t="s">
+      <c r="J63" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" s="21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="B64" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C63" s="2" t="s">
+      <c r="C64" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D64" s="18">
         <v>5000</v>
       </c>
-      <c r="F63" s="2">
+      <c r="E64" s="18"/>
+      <c r="F64" s="18">
         <v>7000</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="G64" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H63" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="I63" s="18" t="s">
-        <v>207</v>
+      <c r="H64" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="I64" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="J64" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" s="21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="377" x14ac:dyDescent="0.35">
+      <c r="A65" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" s="2">
+        <v>15000</v>
+      </c>
+      <c r="F65" s="2">
+        <v>22500</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H65" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="I65" s="17" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0526577688ca4eec/Escritorio/Proyectos developer/Diseños_Gasper/Back-end/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="398" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{441170B5-D974-42A3-9B84-74B5E05FE727}"/>
+  <xr:revisionPtr revIDLastSave="520" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E8FE5CB-D456-48F3-8194-AB91FFB47B84}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="233">
   <si>
     <t>name</t>
   </si>
@@ -993,33 +993,6 @@
     <t>blue, black,pink,skyblue,red,aqua,green,darkblue,hotpink,steelblue</t>
   </si>
   <si>
-    <t>Leguis con Bolsillo Secreto</t>
-  </si>
-  <si>
-    <t>leguis</t>
-  </si>
-  <si>
-    <t>{
-  "pink": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414294/lalfn7mpxyrfn61cr2ui.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414079/uuyymhtjebpnzieha46s.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413936/q3vffhwxc966kznn6g6l.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413796/zhrihfxtjxtbh2ap5okx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414110/adb360lld4u3wfl30bhn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414111/l81pfolseshvhlyiqhmm.png"
-  ],
-  "blue": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413797/vpi6ojnecgpdykoi8pna.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414120/oill26ouut0zr1o9oqom.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414288/aku1blvuagnm3qg2s5tq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414252/dbpuxgerfccbsrxh45dl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413798/iilut58aa5sgrl9rcay5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413807/ohmahl5wmzpzu2eujwwx.png"
-  ],
-  "gray": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413921/jicruqkcffnnblnrskyz.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413923/hamcnqlv1nknjnznd6h6.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413933/zspfcqoqps5jogvl4mic.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414122/sa2xpbziy81plcdrxjg0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413944/dfedjzcsvqkuf4yah3w9.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413915/by3xpktfzvomhmdnsqaa.png"
-  ]
-}</t>
-  </si>
-  <si>
-    <t>pink,blue,gray</t>
-  </si>
-  <si>
     <t>{
   "blue": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415173/ehbtjxpqigtrjexprq1e.png",
@@ -1107,6 +1080,491 @@
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415130/qthqtbojm7vhohh4wkgo.png",
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415156/z58um5lqnxlnd8pp0grd.png",
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415129/odclfkwhom4d9u1wijnb.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>Leggins con Bolsillo Secreto</t>
+  </si>
+  <si>
+    <t>pink,blue,gray,green,darkblue</t>
+  </si>
+  <si>
+    <t>pink,blue,gray,green,darkblue,hotpink,steelblue</t>
+  </si>
+  <si>
+    <t>pink,blue,gray,green,darkblue,hotpink,steelblue,purple,skyblue,aqua,darkgreen,violet</t>
+  </si>
+  <si>
+    <t>pink,blue,gray,green,darkblue,hotpink,steelblue,purple,skyblue,aqua,darkgreen,violet,deeppurple,lightskyblue</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414294/lalfn7mpxyrfn61cr2ui.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414079/uuyymhtjebpnzieha46s.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413936/q3vffhwxc966kznn6g6l.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413796/zhrihfxtjxtbh2ap5okx.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414110/adb360lld4u3wfl30bhn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414111/l81pfolseshvhlyiqhmm.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413797/vpi6ojnecgpdykoi8pna.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414120/oill26ouut0zr1o9oqom.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414288/aku1blvuagnm3qg2s5tq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414252/dbpuxgerfccbsrxh45dl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413798/iilut58aa5sgrl9rcay5.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413807/ohmahl5wmzpzu2eujwwx.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413921/jicruqkcffnnblnrskyz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414243/np3dt1zaylqh15fw7rbk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413933/zspfcqoqps5jogvl4mic.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414122/sa2xpbziy81plcdrxjg0.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413944/dfedjzcsvqkuf4yah3w9.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413915/by3xpktfzvomhmdnsqaa.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413971/qat6mj1veao9waxi3dug.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414285/nsg7o9xxyhou5rrqwyc6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414276/dxoq2m6lopkmc32iasdx.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414093/maysungclt1pr5qh23zk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413813/xegn4yxow51syknrcux5.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413799/cgvmflkvcl75bblngevz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413970/jxkhcqeoxu9ubyumw8xz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414080/qh1whzgzth6j4npfdqbr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413923/bwx35scullsw9d0hzunj.png"
+  ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413921/erbbholegvoeoww9sfva.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414082/skfz752sglsreduj9uqu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413960/e78025escua3bomuhysg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413819/jexzjpljjcdch0idbtbh.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414279/bcdx5y316kj3lvvljqts.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413943/ahstkcubkyeyv7it1wqk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413970/nxydq4quupplfznmvdtu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413961/xcyoxbh38zgpoq6boq2o.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413944/k9fnpmko2zg6qrr4avn8.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414268/z2qio7du85famxzrgskx.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413951/htgn6kwq1yglbjmegupu.png"
+  ],
+  "hotpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413945/hn18jeg1plsyxgt01ypw.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413796/puajc3hhd5es3bcofika.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413934/byroocndccwiufzw1h1w.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413961/k60uvpxjz5yojr6mexqd.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413970/wloyiqp4upgkkyjjrx4e.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414292/tipguffasprqb1euwktl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413970/fvluwv2mau8covsnqqpt.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413933/wjdimdl17x1zataiym9l.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413934/s1fnhndobocoiekuh40g.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414111/oo72s59lyyxa16shoby9.png"
+  ],
+  "steelblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414287/qbbwkjc3dztcaynt3cup.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413995/v9fliydr7goulntxrsme.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413925/e86p8xxnjna9z6zksw02.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413814/iibfiai0axxewkr6loxn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413813/guulmf6zy7hx3cmtqkyw.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413906/t7ptujlwwj9vbde3vr96.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414276/cuh4mdl33uuvbswriin8.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414297/esyt4ivemvht9gcws5ss.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413951/escjilx65z3oi8fqlxpv.png"
+  ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413971/qum5h88wwuj2yga29ti3.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414110/uzxuuxnfbbkym0zhxn6o.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414268/ftd23ai5xnreoi0wnsgn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413912/yrc0s5ikhhwapgkiomfj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414099/ertnzfzfwshveynqgepp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414245/bzkgudmxuvxc5kmnnbph.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413914/cgl04vamfoackf4dpkvi.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414091/y1irenz6seklkzgj9whb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413922/hqdl51ch65zr1sty3fiu.png"
+  ],
+  "skyblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414103/k8t62vurbbfirimqvgua.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414261/wahmvwrxxlozfrtyueyc.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414268/u7rw6l1taqxh6u9tghk9.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413801/tj4oldr3c34hzv2kjudt.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413906/t7ptujlwwj9vbde3vr96.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413921/w5dd4jokysajgridrgfd.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414259/xaio62leb5cbqjmbhaav.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413809/pidpzhsaebyls4cqtjsc.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413907/x722bmd2nabfvuai2mvf.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413913/d6aeph3rplasv85jmayf.png"
+  ],
+  "aqua": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414079/yfpdc9yp3omt9aiknavz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413933/cvae0gmekgyrsoodel2d.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414243/np3dt1zaylqh15fw7rbk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414283/oqhru4pfdrttafkjumg6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414285/sohjo6ntim5puzsrsa5m.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414295/d8tz8bfvpexblqh97anv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414292/wrqo7rgojzap4j96ijzg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413799/i2icv3theu4wpxqn3wpc.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413800/xh3108truulqgmdzdiom.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413801/tfmgfq7dtjc7of2cjwx9.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413804/a0ocnoipqhxzg0hasw6d.png"
+  ],
+  "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413804/a0ocnoipqhxzg0hasw6d.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413803/eprpxhpbgxqjc4vvvy3t.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413805/sreucdflm6hrrhkrmi0n.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413804/nqzgrvtnjg45bgsyvml7.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413810/eq43rkacal3unvd8rcmg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413812/q9ahjg5gyty29gsnr6ob.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413816/xehs55jojxbwjyuu6xl8.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413818/z2if1njq0ctkcugbouwp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413821/bdrumc8onx6d3wbdqqnc.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413822/mszs4aphn0dprgy2xwdl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413824/bxhqyayed8aoej7bq7rb.png"
+  ],
+  "violet": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413906/lkqxmjl6vzahqidgjt1z.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413907/f5usxmf6puiwjl1nx1xt.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413952/va7xuesuquxzkiunavqo.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413953/lsmuo4voxvqlfqeenwvo.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413959/qnfl27o9lg2w4m0erx00.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414081/wjyo8mnfysvdgystsuso.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414089/enhp8mka5elynaddchqh.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414090/fk1nmktnmsfarspqpyza.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414091/vmrksuonyklfc68hosxv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414100/iof19urc3kapsfqt7ybu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414100/qfyhlwzv2obyyb0rarhz.png"
+  ],
+  "deeppurple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414101/zjd2vnacrtduxeokxffa.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414111/v6rujhegeirvscgqi95v.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414120/lgqapwrhxmjoy3ti0ix1.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414300/gr59yiegdqrtdqceiebs.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414303/hjqgtrs9jll2rg9xdajt.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414122/lpu3oz7wi302kqsm48cl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414123/izlq4nlf3f33ih75csye.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414122/x0onp1njrzmbr5yvlogm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414244/kzmov0nqen15otlejyvj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414242/zz03zjc2ub9dev9flyvk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414245/gllmzbrktbxcpvrd42fm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414251/urib84rdjzvuxpjjyheu.png"
+  ],
+  "lightskyblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414252/t7jqvkqgvjdsd9wm24zl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414252/fxzaghi3cny9v43zz4kj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414252/t7jqvkqgvjdsd9wm24zl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414260/q4q8oc5aolqxxy4yasol.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414253/zrzgguswc614lryohh5a.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414260/lk16bnutw9z8fla6fvfe.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414261/cvswxwgriktvsbcc6ygr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414269/wurzomnlp7ndc1satefq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414276/igk27krghj8sgf1nhaoe.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414269/tnslxisl1oukwdivaupd.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773414277/fl8sochhdcgbeftze2ny.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>leggins</t>
+  </si>
+  <si>
+    <t>Leggins con Pretina Sencilla</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413128/xwvzllehqzsvr7b43uta.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412989/w8ro1xngsmrawoqilowz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412988/dcozhihvr6jff5zw8xyw.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412997/xw8av7jg53sactclszxs.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412990/efml364h7hixcdky94h3.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412721/yvbcsw1qfdx6zcgldygl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412723/wvirs4u1hwe0khmqs5cd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412722/jqqtegsmzv0oxvle2ghw.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413729/ou4mhrq2mgztqxyjzq34.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412988/t2vu1ixfxw9u1pvbk1ol.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412788/o3t9tytmuhcwttyoisxi.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412721/dlpkge27t8pdhz0arkzy.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413728/mi0dolknthiris9gruhz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412989/sxflme4v7capemjpt1j7.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412722/uiiodxgvasxia4z3hgf9.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412720/e4ixev84t9li4k3mzbxd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413749/dwafekbl181c3gzcblq6.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413200/e0lrwup80dxnlanezdqr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412703/hjkxxfkcizjlmxqcwrnd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412680/pr5mcu44rg0aehi0ye18.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413729/qtcdh1vf8pw269usqcqq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413741/snherujfbuvwjildvx8m.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413045/cj37n4ix4044vrna3roq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413025/atpumvelqrj3mfigayaq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413015/luvjisqckhs6hdgpbuvm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412997/wtq21x7j7dbrh55jagej.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413052/q1wrmhncjt4mrqfrclzy.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412687/dau0cgts3bznbotwyt1n.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413016/hpijor2iuoaiz0juebeo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413741/zrmmxrx7okpe5sycz3di.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413131/w5ap4rzzlkne7caorbhm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412710/ausfcty9staqu9evldhj.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412709/deyqciaphppiwnghzojr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412687/tkxz6eeyda6vicehhgog.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413105/uv5lm0n34ngu8wxvyno1.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413105/tnqjiohshytnerq2ib7a.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413015/cgu5y9zdnolf08hraqt4.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413063/dbr7dma20cahwubtjvyd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412688/p7xwrtrna0jloyy6hjyr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413062/wxyv83yinsbty3iwtwte.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413092/rv5swqanjv7mq025wujg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412673/biaoza8fms4luxlqpqji.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412695/myeeekz6ucjimcjyksui.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413728/slh2aywbmxbhfgomnhk2.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413016/s8cxd6mkrgfqui9a0gqt.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412995/uwr5dfks6zun1st7wzow.png"
+  ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412696/nrbadvmcgsodhmsccpau.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413147/m8qynnfwbfho4rluh0w4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412673/sr5yhpkxrchu98vluoby.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413045/twdcct0hpu3hgvxektot.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413092/wxzywezyxm4zuxg2tbwj.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412686/ffn97zmic00cc4dca1ot.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412688/talfaj45am5rai0boiap.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413062/jsyh6nyd9oxxc9iox8bo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413080/mvfbiob4g6orercbwa8e.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412696/pp9vbe1lqhxrik3c4ztv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413035/poqt4b7amhya7oyjxeoh.png"
+  ],
+  "hotpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413075/iruznckcimhnqzkurn8h.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413044/dorfybq7xb2i8jkpymlp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412673/duzszulirpe0z3rp0agp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413063/rovi8jfjn7mo2k0nezit.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413077/w8hmunrbvk7rogafjchr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412709/kvbfhhnzxjzeapdfusnv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413096/xnctg77tgaz9t39ltekk.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412687/blvlzea33jhlktruinan.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413018/ftgb5jy79ijeuyz9wi5n.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413053/phrqytufktzylgannasv.png"
+  ],
+  "steelblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412680/iuhfmwrbm5tvtrc6orj2.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413007/jazz6ajvok5clqpqab5e.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413106/apnkybsakwce06h3vhlc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413052/f9ae3ug575w7nqjwf9jd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413043/u4np20az54qvxd6pblzi.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413728/qzehio1sj7dxavfvf5qt.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413077/dhpodajuylhnrqsa52p5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413060/uozmvznqy5gylewhlu1x.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412681/njyvjjevillmou3d644a.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412681/uhnvrixfu27wdagbew05.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413147/ukcj9ubv2gew0ouwerc4.png"
+  ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413006/gtp5nrurslxwxitbvzef.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413742/d8qncnmdu9ttrgxrhovg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413141/u9uujcka3l9huq27lwt8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412681/soa5i0xs1ts83uletzem.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412673/onxvccho1m78xrcxk8ux.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412686/ohpdqdpxjpva6xaguai3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412695/ored1hhq9ullz0fw9rwq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413053/abrlnfse81jebdtn13rb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413065/kuz2chrvq9bipckbcok5.png"
+   ],
+  "skyblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412721/c63tgukbrg6cqs1gficx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412710/pbanonkbtsj6eeaqdkun.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413055/o0i6direpybjdnd3w8sa.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413025/idnas1lwq54mpnixzxiz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413008/wvte9zfdlha80k1oxshx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413014/crkwjgfbyp8kvia6vgx3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413024/cnqx1ocgwweifxawcjqq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413035/wf42zg8gmlt5afe9qvr0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413034/zqdut3nofz3w4bbg0fub.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413027/ycqjv3v4lvtx7fz7vz5l.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413091/t5gcp7iwputgsa7aexws.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413748/u9i2qtq0gxep7ahxobbj.png"
+   ],
+  "aqua": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413147/yc5encpilujjyyizwivn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413106/m8nb0rnhragafhk2yuus.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413006/gagqvido5y9ovkpwf30l.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413148/ud6sk9uodpgdzelpa9uf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413063/ppuafrcekeqorlmrfz3g.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413063/ne7m6pzcviauyr6w2nuc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413146/o2fm6sikpvzsidzvezdx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413051/zkir9twfrshownwre4ef.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413037/rvjybrz608gd9pq8o8sr.png"
+  ],
+  "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412673/znhlnj0qncvpoixuozb8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412701/yu1l0ig8yyrc3pymn1q0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412997/yrlq6cchhjjf43wpliwt.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773412709/bhmjyfmaj9qzl1m9kumj.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413007/obvr7z3vayhwi0543wuw.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413024/kgdabg8ha2kacwpca9bf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413034/iucewbiujasakwse7nxv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413035/dddroxh3rcbzhatnsufg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413106/xyx76hbia71s8wokq43i.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413117/udbmvby1ennw0tdmihaa.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413127/qxpxlhkatdn2fn4luhja.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413110/bdmuhwbq1c8jjkwmouym.png"
+     ],
+  "violet": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413128/vpzw4qjro0v8tjc32o3i.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773413127/bwdfkuzlapwtsldwpjzx.png"
+      ]}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falda Short </t>
+  </si>
+  <si>
+    <t>Enterizo Short</t>
+  </si>
+  <si>
+    <t>enterizos</t>
+  </si>
+  <si>
+    <t>Crop Top Traslucido</t>
+  </si>
+  <si>
+    <t>{
+  "green": [
+  "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773418473/rx5rq2svozhutyqy8pnm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773417581/uqweodwpc6iz0ie1aapq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773417568/hibvcyc3mipsw3ialfxl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773418394/wfpoq8pfnbdnis8ijimk.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773417567/np9bfvp6gcqt2poyfe9q.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773417569/ydqchnpzqlwlfoubnyqv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773417579/optc5w25bmcgia78krhk.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773417574/fztzozdoacbk6h2xs8co.png"
+    ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773417576/sncaajlj5aifkyx9viwp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773418472/u08ycofebclm6hxz70vs.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773418477/kflfcxmrbino4nky66ao.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773418398/yyx7k2por800im82rdil.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773418399/z4ga76ewwhjzu8xyoeqk.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773417572/jfrru3nwkxsbataorlyb.png"
+   ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773418396/q2dvc7jmub8dtig29lun.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773418468/ch36hjfbm0whxm6izoj6.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773418474/ir124fjbormlex3k1evg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773418399/z4ga76ewwhjzu8xyoeqk.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773418398/yyx7k2por800im82rdil.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773418395/vpuyoylif7jhmmxbybg1.png"
+    ]}</t>
+  </si>
+  <si>
+    <t>green,blue,gray,darkblue</t>
+  </si>
+  <si>
+    <t>Conjunto Deportivo Buso y Leggins</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420046/o4phycvt82wjz8kplszr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420265/twvchekif2zodyxanc1i.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420049/db3k6djx5iehvdk5tzsb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420266/s8wejcy8ethxjhvwfim1.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420039/zy4nsioggmxibakgkmnq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420258/befqhobvwpandubpdwnx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420208/nsi9nfrc9iwjh549x27f.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420041/oscbxkl0amqrovmxdl96.png"
+    ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420271/emoayd31qpmmzq1e3cow.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420209/grarwuvkojfsxp3zkkea.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420219/iej9eryy6zmsqpxbtren.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420269/ssqsptxxtzk5242meapv.png"
+   ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420212/dwppw1yttgi1glfoirjp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420261/tsukkdewe1ssc9fx1xyf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420213/nslqbwrpsalmznectkju.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420205/tjubdm4z489rrllcpjae.png"
+    ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420050/a3sah9k0vso0yczkejjp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420217/qqxejrn7vafzp7mxinpd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420203/tjmfayvfgtfwvotp3w7b.png" ],
+  "hotpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420202/mllthenng41x09edlbhz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420045/a2ajlcckgz0jrgzkc5ym.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420259/rpf0na4o552r5leox8lp.png"  ],
+  "steelblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420215/ctwopprmeqldjrqo7ore.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420277/vme2qfi6m8fkbpuuwwmw.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420273/eigh1jdqa5mypkwg9lf9.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420043/hgp1p2lxyof2jxtglg7u.png"
+  ]}</t>
+  </si>
+  <si>
+    <t>Conjunto Bicicletero y Top Combinado</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421306/yrvmtvck1id2esghyj3v.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421299/wlh3qogjom1mdp5waxmc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421291/xnrzh5l6kyrs9y5h2tts.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421287/hf9r0snzw6ll2p2vgzhz.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421308/dgh6cpxztpqvxvq0mmrv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421311/is9xnlsigmtvb7ry1vna.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421278/cosbfglwgxwgyepsrqts.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421280/hwx4llrzbwy0gllfhpmz.png"
+    ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421288/utbf1cys5etqed74vujo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421296/zyukc0d8ooypv4asz6cl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421292/oglskua7nktxdn78lwxp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421304/is6bwzgumdyjcxiddnpb.png"
+   ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421316/vkrx4xtqfpvx1rxhhjaw.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421313/dbjj7jtvep3awsdoisjt.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421301/fe4my2vqlrxj1ogorji3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421284/cos85vncc1vbhbuy528v.png"
+    ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421319/d9qqgtc0yluoaqb2nhss.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421294/hniugnmmmcgs8gfc3kyq.png"]}</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072753/dsppjvpwowbghyyabeog.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072754/iufnbxgh8v2t6nun4m8f.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072791/lycg5baqgojxovlk3klq.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072764/q9ui9mat04sqcn7jpqb8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072753/vaefzvoqosvza2tjc04h.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072751/tktrkjoftskg81kjytab.png"
+    ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072762/oxepi3ridavl6iaquioe.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072768/jibcdv8zdbbnl2shknx5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415974/zlvlfegmwgwtj3uegmf6.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072784/lkxruusxffwbja8pvoem.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072794/htikpbl3pq2mpqp2ps8r.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072753/egdi0tylliek1qyjso6x.png"
+   ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072758/tfir7j2qcftiffz8aca6.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072757/schvcegqk9teituzut2v.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072772/fuhllgv2gcygjv5uvhqx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072786/iulimynpkmgyp1lrfyca.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072787/fhvdbb22uf43y6a8y3pz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072763/xjzgglbt4ryzsr1dvjul.png"
+    ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072771/ocuhg6y7bx3q4k6qswwm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072761/to6r3iw5czbnugwicbyo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072755/njj3ykdg4wphlwueohpp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072772/smojgyyxywm1ppopmhac.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072766/ehfpqr0onlnnfcmxkw6g.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072765/aijvgan44bsdlarde9hu.png"],
+  "hotpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072776/xy0oq8u2z354b9irwdi0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072760/f7qv7ihynasmahakerzr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072759/khvijabocbvnua4rq4vt.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072778/mey8d1cqjigzohe2kfsh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072791/pglujdgbvmqn12el2igs.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072752/lud7tphmwdzz98gq2bkm.png"  ],
+  "steelblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072778/rt8jsbd8g77dtmflde6n.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072783/qzzslyqihjzfteprnqu3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072756/nrlasih250wtk3djzpne.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072781/ecdvpj1gcs5bf219hskg.png"
+  ]}</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416290/qrlowbtwfkpfypavclt5.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416053/k746fugxvqwjknpiychz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416262/wqdfvzcho2lfxta4gzgz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416311/ooa4txwpixsa1zktiz0o.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416190/nf2325leitsuv0tua7lf.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416250/ets5y8x1rkziuisz27vd.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416286/bn9euxkqhrbqlmvuhxiz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416207/bmecxkohc2lcciefvprm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416302/fc0pvuenvqudhe0ry818.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416195/kqzwt4sp5q0ge1hh8dwq.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416294/pmshoq3tjgafq6gpcbt9.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416273/uogfsfsucmmsnyepdtbb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416220/jdzz1cc3iaizq4j4dz6e.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416183/filmlgbtdgt2pd2pjeuo.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416323/qmthfapue8mwtsxurtfz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416244/vxyttjxduexjvje1lvm6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416215/snrk8fldawf0oirrvquv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416178/pr4qhmhhxtvt0d5apipa.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415980/gzezgzr4ue2yp3mu5rzo.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416196/f9jdzglnonjv9mrqmrea.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415970/j0emdwlkpwvkwyofrxkv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416208/jksbv56emig4qz94gmu9.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415974/zlvlfegmwgwtj3uegmf6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416294/gom3hdiys0lpegiucrfa.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416262/hqptcmqk7le05zjivb2k.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416312/tbaamx57e76vf6gpb7wz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416316/yvchju9wkaf9elfxm2w6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416263/xdmzoozc7dhxq6cuze6i.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416320/iq8yndysogkwqyeie3t1.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415991/t796xjnfo98lb7bhmvsq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416310/ohb69dmxvobxucufp8fz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416289/hycllrw7ygufhch0nysq.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416166/qrqgdfj7kqlb9zfng6og.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415990/j3al7u3gj7mkaku0qoby.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415980/cnnqftkwrshlexyjlapl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415959/kjxny6jnzipqvk91ok2x.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415995/na8186pgdaqwniyxhose.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416176/s1w9mmdlhvuqb2avrrad.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415984/dpccybijitpf8ji3iteu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416285/ybuu7gx8wzf3jejflzts.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416187/vioijghseh9sdqf2nkal.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416300/divgdwrvstqluscll2lf.png"
+  ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416299/fpqonbmnz6qfdppdzmsl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416295/cwxjgbndrpebrw4dya7c.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416272/yutx8qm1vkjeggh99ew7.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416177/gsen39sqfogt42jmlpez.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415973/voeon9pukrdqtvq128kv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416211/ubqgbda3rjout3urkw09.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416168/se1krtmrlk6epe6mmqzz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416242/wtlrtruu93kuzt61p55z.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416243/fcuvs7v55a66f46l0jed.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416310/bjypkov8tqc4gvms7tod.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415965/cvx3oyygwzfxfgj3mgof.png"
+  ],
+  "hotpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415987/iuyjozzwro18snorgkaz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416003/vou1uotpawlgvdow6blj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416228/grpnayzcsu7pwysdpm9l.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416336/so117psdpsxbfxn86aa4.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416212/clo6omrpdsqacmfbyx2e.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416003/nal0y1aousnydel9c9bh.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416167/wh3yinojxhalhz4qe3rg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416180/yariiiyggalcawpthysm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416317/eonvxsrpzrhn2vlcjatj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416203/lv6d9y5cicybrhhqsa95.png"
+  ],
+  "steelblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416197/amqyro3gix08x6shrfse.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416249/zunvoy8vibbzqefqfkg0.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416255/whzbzzogzo5d9u1s3oym.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416307/sxqy71iwrzngraaqy41z.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416257/zx2rocsa6yo0hlfr6g3f.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416172/ufxqq1uylrgqzklew8dx.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416227/sstrutfjlgnriihaeiqr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416304/saebaj98hfibjsrxh6pe.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416282/n7j0vwkpwaw9gdh5yqh6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416270/cujzcybg3letrklfedyq.png"
+  ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415976/c49c6b4ghcascmn4xfsm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416276/zar1mfht0oqihxq7ciek.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416204/qknnwtey3qjb5madflre.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416330/khsiuv0wjbulqncixkxh.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416326/lvofqnvvvshtuacbat9c.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416217/bdwtuvpgbhbx7gjwlteb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416280/t9udoglicwhgict1zcxf.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416218/kstch50r1aejy5lnqm8p.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416281/z2abttmsbynsnumwlqg3.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416257/nilon24mjwuwkewq0gae.png"
+  ],
+  "skyblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416235/kpslv6ns5dpnneniazhg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416170/sfzqob28zvb9uw2sftum.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415967/cr1iwmrjopvh4oiz6tdg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416202/r5vobz5we7aegrustg9y.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415983/fpryq4gkkdmkuoldsy7p.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415979/y9pwxvqyhqqiupsxoo78.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415960/i5ifavyrvgy1ay4u1isg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416230/uydhjaphwoaowfm0sxzu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416331/dqozvw2bjohcfo3zrwko.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416249/chdorgyrnfbpq49xgxew.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415998/i4wzvtqzfymknwyfuyc6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416182/ztobiv6hgdafne2jw3s7.png"
+  ],
+  "aqua": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416340/h1kuqgcqpjzwu0ljgjzl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416321/dzi2zp9sztzqtw9uee7r.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416174/ud2uehcqq1qyghq0utcp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415964/ksisxgqdtz2vjyxxf0h5.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415963/op7g9sppryp1h2szkawc.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416330/odo3lr9n9qslrpelpf17.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416341/qq7aqw8a1tbjnzua5ofy.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416237/rlj8h5vqatrvid2htupx.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415962/lc02levu16k5xkcsdkqw.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416239/gnttl90pitpt5isdqvxb.png"
+  ],
+  "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416264/hgfibbhawru3agvmqhmp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416251/neqrvs4qgeumrv4vfmwp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416234/dgzqkw1d2n6ndcit4wnb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416188/ug26ujte97hoqtgj8gxt.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416232/woljjv2lj53ioyvydv6b.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415972/apqgw44r8kjxf6wpevyl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415968/mzxgjg1w67lfns5fcbsq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416222/yoloxsbdp4fsergeernp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416268/cjwpdaow3vxkyxv3n5pn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415996/yczrjb9sqy1e1nhwcmq1.png"
+  ],
+  "violet": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416223/umysgecl2lxao9ujbupq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416187/gn4k5mcwnhft4suls5r8.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416275/aj6ismbfekdqh41mffaa.png"
   ]
 }</t>
   </si>
@@ -1132,7 +1590,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1154,12 +1612,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1197,7 +1649,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1240,22 +1692,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1562,7 +2008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}">
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="57.54296875" style="2" customWidth="1"/>
@@ -3496,260 +3942,465 @@
       </c>
     </row>
     <row r="58" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A58" s="18" t="s">
+      <c r="A58" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="B58" s="18" t="s">
+      <c r="B58" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C58" s="18" t="s">
+      <c r="C58" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D58" s="18">
+      <c r="D58" s="16">
         <v>17000</v>
       </c>
-      <c r="E58" s="18"/>
-      <c r="F58" s="18">
+      <c r="E58" s="16"/>
+      <c r="F58" s="16">
         <v>25000</v>
       </c>
-      <c r="G58" s="18" t="s">
+      <c r="G58" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H58" s="19" t="s">
+      <c r="H58" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="I58" s="20" t="s">
+      <c r="I58" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="J58" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K58" s="21" t="b">
+      <c r="J58" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" s="19" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A59" s="18" t="s">
+      <c r="A59" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="B59" s="18" t="s">
+      <c r="B59" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C59" s="18" t="s">
+      <c r="C59" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D59" s="18">
+      <c r="D59" s="16">
         <v>17000</v>
       </c>
-      <c r="E59" s="18"/>
-      <c r="F59" s="18">
+      <c r="E59" s="16"/>
+      <c r="F59" s="16">
         <v>25000</v>
       </c>
-      <c r="G59" s="18" t="s">
+      <c r="G59" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H59" s="19" t="s">
+      <c r="H59" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="I59" s="20" t="s">
+      <c r="I59" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="J59" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" s="21" t="b">
+      <c r="J59" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" s="19" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="18" t="s">
+      <c r="A60" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="B60" s="18" t="s">
+      <c r="B60" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C60" s="18" t="s">
+      <c r="C60" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D60" s="18">
+      <c r="D60" s="16">
         <v>17000</v>
       </c>
-      <c r="E60" s="18"/>
-      <c r="F60" s="18">
+      <c r="E60" s="16"/>
+      <c r="F60" s="16">
         <v>25000</v>
       </c>
-      <c r="G60" s="18" t="s">
+      <c r="G60" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H60" s="19" t="s">
+      <c r="H60" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="I60" s="20" t="s">
+      <c r="I60" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="J60" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K60" s="21" t="b">
+      <c r="J60" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" s="19" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="18" t="s">
+      <c r="A61" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="B61" s="18" t="s">
+      <c r="B61" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C61" s="18" t="s">
+      <c r="C61" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D61" s="18">
+      <c r="D61" s="16">
         <v>21000</v>
       </c>
-      <c r="E61" s="18"/>
-      <c r="F61" s="18">
+      <c r="E61" s="16"/>
+      <c r="F61" s="16">
         <v>31500</v>
       </c>
-      <c r="G61" s="18" t="s">
+      <c r="G61" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H61" s="19" t="s">
+      <c r="H61" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="I61" s="20" t="s">
+      <c r="I61" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="J61" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K61" s="21" t="b">
+      <c r="J61" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" s="19" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A62" s="18" t="s">
+      <c r="A62" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="B62" s="18" t="s">
+      <c r="B62" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="C62" s="18" t="s">
+      <c r="C62" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D62" s="18">
+      <c r="D62" s="16">
         <v>22000</v>
       </c>
-      <c r="E62" s="18"/>
-      <c r="F62" s="18">
+      <c r="E62" s="16"/>
+      <c r="F62" s="16">
         <v>28000</v>
       </c>
-      <c r="G62" s="18" t="s">
+      <c r="G62" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H62" s="19" t="s">
+      <c r="H62" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="I62" s="20" t="s">
+      <c r="I62" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="J62" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K62" s="21" t="b">
+      <c r="J62" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" s="19" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A63" s="18" t="s">
+      <c r="A63" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="B63" s="18" t="s">
+      <c r="B63" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="C63" s="18" t="s">
+      <c r="C63" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D63" s="18">
+      <c r="D63" s="16">
         <v>5000</v>
       </c>
-      <c r="E63" s="18"/>
-      <c r="F63" s="18">
+      <c r="E63" s="16"/>
+      <c r="F63" s="16">
         <v>7000</v>
       </c>
-      <c r="G63" s="18" t="s">
+      <c r="G63" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H63" s="19" t="s">
+      <c r="H63" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="I63" s="20" t="s">
+      <c r="I63" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="J63" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K63" s="21" t="b">
+      <c r="J63" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" s="19" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A64" s="18" t="s">
+      <c r="A64" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="B64" s="18" t="s">
+      <c r="B64" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="C64" s="18" t="s">
+      <c r="C64" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D64" s="18">
+      <c r="D64" s="16">
         <v>5000</v>
       </c>
-      <c r="E64" s="18"/>
-      <c r="F64" s="18">
+      <c r="E64" s="16"/>
+      <c r="F64" s="16">
         <v>7000</v>
       </c>
-      <c r="G64" s="18" t="s">
+      <c r="G64" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H64" s="19" t="s">
+      <c r="H64" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="I64" s="20" t="s">
+      <c r="I64" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="J64" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A65" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" s="16">
+        <v>15000</v>
+      </c>
+      <c r="E65" s="16"/>
+      <c r="F65" s="16">
+        <v>22500</v>
+      </c>
+      <c r="G65" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H65" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="I65" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="J65" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="B66" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D66" s="16">
+        <v>12000</v>
+      </c>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16">
+        <v>18000</v>
+      </c>
+      <c r="G66" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H66" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="J64" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K64" s="21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="377" x14ac:dyDescent="0.35">
-      <c r="A65" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C65" s="2" t="s">
+      <c r="I66" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="J66" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="B67" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="C67" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D67" s="16">
         <v>15000</v>
       </c>
-      <c r="F65" s="2">
-        <v>22500</v>
-      </c>
-      <c r="G65" s="2" t="s">
+      <c r="E67" s="16"/>
+      <c r="F67" s="16">
+        <v>19000</v>
+      </c>
+      <c r="G67" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H65" s="16" t="s">
+      <c r="H67" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="I67" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="J67" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D68" s="16">
+        <v>22000</v>
+      </c>
+      <c r="E68" s="16"/>
+      <c r="F68" s="16">
+        <v>34500</v>
+      </c>
+      <c r="G68" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H68" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="I65" s="17" t="s">
+      <c r="I68" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="J68" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="B69" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D69" s="16">
+        <v>12000</v>
+      </c>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16">
+        <v>15000</v>
+      </c>
+      <c r="G69" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H69" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="I69" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="J69" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D70" s="16">
+        <v>29000</v>
+      </c>
+      <c r="E70" s="16"/>
+      <c r="F70" s="16">
+        <v>43500</v>
+      </c>
+      <c r="G70" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H70" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="I70" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="J70" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="406" x14ac:dyDescent="0.35">
+      <c r="A71" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B71" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" s="16">
+        <v>18000</v>
+      </c>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16">
+        <v>27000</v>
+      </c>
+      <c r="G71" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H71" s="17" t="s">
         <v>213</v>
+      </c>
+      <c r="I71" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="J71" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" s="19" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0526577688ca4eec/Escritorio/Proyectos developer/Diseños_Gasper/Back-end/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="520" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E8FE5CB-D456-48F3-8194-AB91FFB47B84}"/>
+  <xr:revisionPtr revIDLastSave="580" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05BC9152-A612-4427-9C22-BE0904F86F93}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="productos" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">productos!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">productos!$A$1:$K$71</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="238">
   <si>
     <t>name</t>
   </si>
@@ -645,126 +645,10 @@
     <t>purple,orange,lime,black,green,pink,red,yellow,white,darkgreen</t>
   </si>
   <si>
-    <t>{
-  "purple": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421149/qzkzole8x6gmakojrzvl.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421152/a7wigb3vck0ldqo4gkdq.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421154/lsnzg3x2lvlsgeu0fkgx.png"
-  ],
-  "orange": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421157/onyms9a7ib2ql3j58okw.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421162/vf5u2lagecckomov5gcb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421165/wkmnjao69u0em7pekk7d.png"
-  ],
-  "lime": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421179/qaabrem5wrnuy9df5wrj.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421182/ucql2bpfgmbsghzjrknl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421184/dsrcpreqx4wyrt4dnhjo.png"
-  ],
-  "black": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421189/hrffwgfiezszaru4hznp.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421190/eepjpj7odzj3txsmbk0b.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421197/yldjef9vreky36smwldd.png"
-  ],
-  "green": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421200/uetmtmsoopoed95pdgqp.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421202/fqx9oqnbmmwgvjf4uoxh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421208/aap4wn37d7n5sesfvfig.png"
-  ],             "pink": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421211/rl3fsc0opvecnsoq0dbv.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421215/zogfpwnmphvghzgja74m.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421220/v7lhntmj7msfsaglowzc.png"
-  ],  "red": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421223/giezr8zzha0t0qs2p4so.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421226/y5psna9plddpjowaqyop.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421229/dx2cvxtz7dy31gailnts.png"
-  ] }</t>
-  </si>
-  <si>
-    <t>Conjunto en Licra y Esqueleto en Mal</t>
-  </si>
-  <si>
-    <t>Conjunto en Licra y Esqueleto en Malla.</t>
-  </si>
-  <si>
     <t>Conjunto en Licra y Esqueleto en Malla</t>
   </si>
   <si>
-    <t>{
-  "purple": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421065/yj3ltanlgtde7kf354ha.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421069/xppnolztpe5iopc6xbkp.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421071/hf4fxifemsuajfyi9bjp.png"
-  ],
-  "orange": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421075/pk7xuh67sticdkbbjlqq.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421077/n8jzd8sbfpkfnhe37wif.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421081/bmp99f8ifcol5jcm3yzo.png"
-  ],
-  "lime": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421082/ffzphlzfqhlxjypaihzf.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421084/wchtso75tjdmnsfgx3jh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421087/c4vrnk5smub9uxvtfxr6.png"
-  ],
-  "black": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421090/meksjjymc1pe8iyb0umv.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421094/hby8kz1bzjtxmbaoj0wn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421096/g3w5sobu0kvwo8qpj0is.png"
-  ],
-  "green": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421097/t0duwqdnqv2c4nzayrbj.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421103/pv1fgx8tqplhbidapm6p.png"
-  ],             "pink": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421105/kmegyf5j6babw43idtbj.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421110/jkz6grsiwrdf4todbkii.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421112/ydvvbukdm01b8hf52sv5.png"
-  ],  "red": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421115/la4bjtyyijuyw8olqfsj.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421118/igvdjts0mnd6m8izkypf.png"  ],"yellow": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421124/ub2pugvw9etn87ylol6j.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421125/zduqpt4wip8kecctw0o7.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421130/n6hkbquijsy0tvp5ac03.png"
-  ], "white": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421134/fnmjdvoxdlqhnvkxx2pb.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421136/o4k7rnqdgif34xfmim0q.png"
-  ], "darkgreen": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421141/kh8vh0ukdb8unavjz9vm.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421144/yikhayfjat3dbnyyphhn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421147/jjrdbrrdauzbtkiavamr.png"
-  ] }</t>
-  </si>
-  <si>
     <t>Conjunto Braga y Top</t>
-  </si>
-  <si>
-    <t>purple,orange,lime,black,green,pink,red</t>
-  </si>
-  <si>
-    <t>{
-  "purple": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420993/kkmdjr3zd2qzczclloqt.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420996/p37wdxl0g36hyp7kzrxk.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420998/pwdjrqwgurkm56jw00fe.png"
-  ],
-  "orange": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421000/h5rp8pk5jg65fcjqr9rm.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421003/ra29tkoggbizia8uhhtm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421005/c7qaqd2dm4efprhwv5jb.png"
-  ],
-  "lime": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421007/puak7fprgoicscjbr0tr.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421010/wqee9mm8jcrypnunh5b5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421012/tgxqsbv36106wa5war0u.png"
-  ],
-  "black": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421015/w58kqlbdis1tzhpvz8zb.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421017/fiuoz4hfowekqxgrus7k.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421019/foceqllwrxjo7bh8ww7e.png"
-  ],
-  "green": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421021/ztpefxjbhi1xkdowml9m.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421024/penknuwcdhp0gpuxrwoq.png"
-  ],             "pink": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421029/jfaet59kswrxvlrnwm9x.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421031/iabnxliciu3n6dbadzu8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421037/ocptsmfnf1gejhtu54yl.png"
-  ],  "red": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421033/sd1imwmbs59aid8qyx8u.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421038/ybglf2hixphgayj2haky.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421040/ptbqpwcj8hsmumhidvuy.png"
-  ],"yellow": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421042/zltgysluvinxvf8qxkyk.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421046/fqm7ajd4ktdfozwx1vry.png"
-  ], "white": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421051/kes6ycx3qlo4byxqpqha.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252555/kyjfquqnjh7rcksy6glw.png"
-  ], "darkgreen": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421058/i3jq2rctkdfzzdm2orqa.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421058/vsqodprdycyyfna4k6xu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421060/s0cdeylzx2xswm50nb8m.png"
-  ] }</t>
   </si>
   <si>
     <t>lime,orange,yellow,black,green,pink,black, gray,blue, gray</t>
@@ -1567,6 +1451,195 @@
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416275/aj6ismbfekdqh41mffaa.png"
   ]
 }</t>
+  </si>
+  <si>
+    <t>Chaqueta Yoga en licra</t>
+  </si>
+  <si>
+    <t>pink,blue,gray,green</t>
+  </si>
+  <si>
+    <t>Capri</t>
+  </si>
+  <si>
+    <t>{
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420993/kkmdjr3zd2qzczclloqt.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420996/p37wdxl0g36hyp7kzrxk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420998/pwdjrqwgurkm56jw00fe.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421065/yj3ltanlgtde7kf354ha.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421069/xppnolztpe5iopc6xbkp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421071/hf4fxifemsuajfyi9bjp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421149/qzkzole8x6gmakojrzvl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421152/a7wigb3vck0ldqo4gkdq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421154/lsnzg3x2lvlsgeu0fkgx.png"
+  ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421000/h5rp8pk5jg65fcjqr9rm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421003/ra29tkoggbizia8uhhtm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421005/c7qaqd2dm4efprhwv5jb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421075/pk7xuh67sticdkbbjlqq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421077/n8jzd8sbfpkfnhe37wif.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421081/bmp99f8ifcol5jcm3yzo.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421157/onyms9a7ib2ql3j58okw.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421162/vf5u2lagecckomov5gcb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421165/wkmnjao69u0em7pekk7d.png"
+  ],
+  "lime": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421007/puak7fprgoicscjbr0tr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421010/wqee9mm8jcrypnunh5b5.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421012/tgxqsbv36106wa5war0u.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421082/ffzphlzfqhlxjypaihzf.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421084/wchtso75tjdmnsfgx3jh.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421087/c4vrnk5smub9uxvtfxr6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421179/qaabrem5wrnuy9df5wrj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421182/ucql2bpfgmbsghzjrknl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421184/dsrcpreqx4wyrt4dnhjo.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421015/w58kqlbdis1tzhpvz8zb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421017/fiuoz4hfowekqxgrus7k.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421019/foceqllwrxjo7bh8ww7e.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421090/meksjjymc1pe8iyb0umv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421094/hby8kz1bzjtxmbaoj0wn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421096/g3w5sobu0kvwo8qpj0is.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421189/hrffwgfiezszaru4hznp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421190/eepjpj7odzj3txsmbk0b.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421197/yldjef9vreky36smwldd.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421021/ztpefxjbhi1xkdowml9m.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421024/penknuwcdhp0gpuxrwoq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421097/t0duwqdnqv2c4nzayrbj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421103/pv1fgx8tqplhbidapm6p.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421200/uetmtmsoopoed95pdgqp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421202/fqx9oqnbmmwgvjf4uoxh.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421208/aap4wn37d7n5sesfvfig.png"
+  ],
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421029/jfaet59kswrxvlrnwm9x.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421031/iabnxliciu3n6dbadzu8.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421037/ocptsmfnf1gejhtu54yl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421105/kmegyf5j6babw43idtbj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421110/jkz6grsiwrdf4todbkii.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421112/ydvvbukdm01b8hf52sv5.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421211/rl3fsc0opvecnsoq0dbv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421215/zogfpwnmphvghzgja74m.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421220/v7lhntmj7msfsaglowzc.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421033/sd1imwmbs59aid8qyx8u.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421038/ybglf2hixphgayj2haky.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421040/ptbqpwcj8hsmumhidvuy.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421115/la4bjtyyijuyw8olqfsj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421118/igvdjts0mnd6m8izkypf.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421223/giezr8zzha0t0qs2p4so.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421226/y5psna9plddpjowaqyop.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421229/dx2cvxtz7dy31gailnts.png"
+  ],
+  "yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421042/zltgysluvinxvf8qxkyk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421046/fqm7ajd4ktdfozwx1vry.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421124/ub2pugvw9etn87ylol6j.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421125/zduqpt4wip8kecctw0o7.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421130/n6hkbquijsy0tvp5ac03.png"
+  ],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252555/kyjfquqnjh7rcksy6glw.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421051/kes6ycx3qlo4byxqpqha.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421134/fnmjdvoxdlqhnvkxx2pb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421136/o4k7rnqdgif34xfmim0q.png"
+  ],
+  "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421058/i3jq2rctkdfzzdm2orqa.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421058/vsqodprdycyyfna4k6xu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421060/s0cdeylzx2xswm50nb8m.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421141/kh8vh0ukdb8unavjz9vm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421144/yikhayfjat3dbnyyphhn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421147/jjrdbrrdauzbtkiavamr.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421385/mc15sce3x5kjl4k04pxx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421387/jc7zh0vg6um00gbqpmdl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421382/cx5prkld0tbgkkqc1tpr.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421370/sr6ns57ipdlidvtg2rw1.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421379/gdlxnnzxfwdqzjkcq1jg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421374/ddl5ykerqck4ypbtad6i.png"
+    ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421377/lusovt3ujiztlfblbkxx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421372/tf5s8ckywreeedmjrsz6.png"
+   ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421390/mrwelbzu8tbtcxe6fwm2.png"
+    ]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421450/dcoqsuto00vnbfwemync.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421432/bdhkzfds0ladlujtvjx4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421430/ccm5gso9rnbgfxlkzjjb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421443/cddujfgzaptpt849ow36.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421495/v0bo4tc0s34qrfco06h7.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421509/rtfmfyodyhmt9w3tfqgx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421476/pwuykhyj0iv4ix2imvlt.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421487/qbodgwsbfjqh44yzvxjm.png" 
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421428/xevwqdwp6tsunpv2f3cd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421435/ba3l1ykzsadhgyub3xpa.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421438/zf3lev8zd9bokor3uv63.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421440/jimqoxsfberln9fofyah.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421458/kkbe5xzgji91jwhq3d7z.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421466/tnezuu2ucry58jy3pzhr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421478/d2nj8tygr6gnmhrlhgst.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421503/ihqmjctjzzadtqj10hhn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421512/fphvd7t7ap15yrnaf1yf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421517/rfmv4gj00jhwywnjdhkh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421539/bgzoyctutpnsu7fvbsla.png" 
+    ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421425/pscv6e2pp6ucdiol6lif.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421446/uqfhzdkxpf8wy0imibbc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421452/qx1gnoqrilzhm0po8t8k.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421455/yedudgvyhlhovqx834op.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421460/b7vognsc3lcnhuluxszn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421463/gkolqby1jxhxeg9ht8ed.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421474/brix4hta7x7hmnwu0x0e.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421481/mpjbsw6cow7rv2bk0urn.png"
+   ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421484/jk0bz2bvtiz28ngl8kwv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421490/xyroo1a5iviltsxomhlc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421492/ow6eqs2kc6vr2ouq00dt.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421498/czlcomet321g3kysrmnf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421501/smxszsujlefwjkcsa3so.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421506/na72xvxklirdy9t6yry1.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421517/wmqsnndpowvw4d9zhdgk.png",  "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421522/l98y7nhq69odpnv6vnov.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421526/ws7wqt2z6zuxlju6gptd.png"
+    ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421528/rix4mqto3dupuneeypns.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421532/ksuvg54m8srx0ncmo2hc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421536/mfstpv4zhyihhdifrfkv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421542/rscv80x76qkijpimlhl7.png" ]
+  }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blusa Esqueleto Clásica </t>
+  </si>
+  <si>
+    <t>pink,blue,gray,green,darkblue,hotpink</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421759/mlmvi3jnzyhxlnyewlbk.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421767/u6zm7fv3yqf00zbvmsn3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421763/xuwm5s3u8qmdiquukubf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421754/d6umd8wh6xgmrgadq869.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421752/wpdoeixdy2lc3lmj7sun.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421747/fkzjz0btvy4gllakr0xt.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421744/ctukwvgnoeqg7uzhivqw.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421740/zafhbbx93n2un3tmp6qq.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421735/jgtxo9lmh190cykyh8ri.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421732/qmu42iapveqoalxutrqw.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421728/g1ikvtnvuwkbwpyvkxwj.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421725/wga0nj1yk7xg3wmotehp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421719/cic1tozvedpqzfonrywk.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421718/kozpjgel4b7m9mt63mht.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421713/wyubj859amltkk5h0r75.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421708/pkq4znz2bkqxhjaarxh4.png"
+    ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421704/klyfswnpzo5ivsupk7tv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421701/ptbfgd8f7ufy2h7qmcdh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421697/nx2kexhbryydca9nqekf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421690/mcmf1q8w9iwhmot3s9p8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421693/witd52ycl8qxyxqfqofa.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421686/b4elsguxa76wbo79jfm1.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421686/b4elsguxa76wbo79jfm1.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421683/mxyqwrefjnz2alpglzei.png"
+   ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421679/or8jcfenboiuwtl0aa7z.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421676/g48kznva6lgjvjosyowa.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421672/numyuslbdxsylekyidos.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421665/gfx1jy48eiruzfdohx8p.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421669/hg7i8u0npyp6icknqtix.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421662/dyxhir08lvx6d5bawiut.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421658/an4qfteyqmset8lsz5so.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421655/xxn6xkrvsnorrcqtgrom.png"
+    ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421651/svtc5undwsl67g1zdxis.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421648/lj4yfwsuxcx94u5n9klp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421645/vkesfdijaaragk8r1iwi.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421642/goureyp5ogodyktsukpe.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421638/f4xxvyukcpb74m5jivwu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421636/c4lak3zkgks3qbgbtcup.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421632/q23lmkdpayoejmvnsxfw.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421628/hxwwpquwnsnw9kirpenz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421627/yfjbkfhual6tznu5vjsn.png"  ],
+  "hotpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421619/zgi3wgwcbgb4tcgwcyex.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421613/it6nqmtgm8cltenbn8b3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421616/enbi23nehvjwlf5odikv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421601/eb2zr5faolhmdfwoc3sl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421607/hoqllm8mcqtuou4ep46q.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421604/fdsnetnbvfvypfcr3bfb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421587/nyo7olgzyj9p95dmqt8k.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421598/djxmxypelqgaxqivja8a.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421590/ogn6ahr4j2pablegtzst.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421584/t3fznd72wgcbqbsgvyc0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421581/kw0enir4epm9scfmsked.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421578/ojgadv34fdw3b0xbykms.png"  ]}</t>
+  </si>
+  <si>
+    <t>Bicicletero Licra</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421877/zjbkuhzhim2dpfe6gkf8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421908/qvd99rxvytxcrg1fyldl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421921/aqdbkkktufe3uc9kw1xk.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421865/f0f4kahsbnpi8famqj6m.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421861/ejr2siy3za6ay5quvuyt.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421825/hbhx6907d3xrkx57koj5.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421831/vrmvqspbh9r3tur05qcr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421904/sgkcy6ex8a82r5xpinbv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421917/nuopzrgqnuplnjhegpll.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421925/a3imk4wecaqdmi1hgaee.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421851/gulwymrtnshy0fs5sw6h.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421935/jhv9ny3hrhxn7isgyfzj.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421833/krxzotphyvivybvjus3b.png"
+    ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421828/ke0cpxal9ibwqkmc1lvq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421970/tdfsfytupxej42kw7uuz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421992/j1bats7o9bwtxm23o4zz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421943/k6ojzqoa7juwvtsyuvtt.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421975/fkcwtb62b8pk35qhvshp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421894/iaxouaulokci0aqb5w9d.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421867/gvruxaavisnfvyzotlou.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421845/vbi5lsovyoekcxcmdedi.png"
+   ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421857/uwsrpiqvvv0b0ani4tdn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421939/lqhcujt7klifb8w7ku2j.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421900/k9fvjvo23qpccrzna6wh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421881/agsntbsm4oq9w2tq8pme.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421870/r4chc7bdhoameg9axkem.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421979/yjdgpyufle9ytvb7rv1p.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421958/n0udjnukfcx8rdzlfmg9.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421884/scm7xax408nfgtfplnfd.png"
+    ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421890/s6aqfmvqvxzxbrea9o6m.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421845/vbi5lsovyoekcxcmdedi.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421982/wsanluxtsjfru3qedb6i.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421995/l7d62rcgfwbdhch3exdo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421897/eetddm28orkox7hoyivc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421842/sswalmqkan70tvt5xbb5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421987/axmuavtqpl5qzkfbifns.png" ],
+  "hotpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773422004/ybytqypmgep2zvvafglf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421915/b4pr9artbraayulde8qo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421836/zqp4tqcz5p3yqok4yz1a.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421839/nbewqlcmyzgwkgckqqqg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421822/cyjggxc3enonwvqb70se.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421854/gcim37vumhuin6espkxf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421947/op6q7fj0zfvej8zz7jfm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773422006/njr7jg5mujkmadzle1gz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421951/rzxqpkwtzyttbwocwuaj.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421966/aypwbrl04yespk7dat5r.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421962/l4mtufoby7nwglrfueng.png"   ]}</t>
   </si>
 </sst>
 </file>
@@ -2008,7 +2081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}">
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="57.54296875" style="2" customWidth="1"/>
@@ -3943,7 +4016,7 @@
     </row>
     <row r="58" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A58" s="16" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B58" s="16" t="s">
         <v>189</v>
@@ -3965,7 +4038,7 @@
         <v>190</v>
       </c>
       <c r="I58" s="18" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="J58" s="19" t="b">
         <v>0</v>
@@ -3976,29 +4049,29 @@
     </row>
     <row r="59" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A59" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B59" s="16" t="s">
         <v>189</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D59" s="16">
-        <v>17000</v>
+        <v>21000</v>
       </c>
       <c r="E59" s="16"/>
       <c r="F59" s="16">
-        <v>25000</v>
+        <v>31500</v>
       </c>
       <c r="G59" s="16" t="s">
         <v>14</v>
       </c>
       <c r="H59" s="17" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I59" s="18" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J59" s="19" t="b">
         <v>0</v>
@@ -4009,29 +4082,29 @@
     </row>
     <row r="60" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A60" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D60" s="16">
-        <v>17000</v>
+        <v>22000</v>
       </c>
       <c r="E60" s="16"/>
       <c r="F60" s="16">
-        <v>25000</v>
+        <v>28000</v>
       </c>
       <c r="G60" s="16" t="s">
         <v>14</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I60" s="18" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="J60" s="19" t="b">
         <v>0</v>
@@ -4042,29 +4115,29 @@
     </row>
     <row r="61" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A61" s="16" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C61" s="16" t="s">
         <v>20</v>
       </c>
       <c r="D61" s="16">
-        <v>21000</v>
+        <v>5000</v>
       </c>
       <c r="E61" s="16"/>
       <c r="F61" s="16">
-        <v>31500</v>
+        <v>7000</v>
       </c>
       <c r="G61" s="16" t="s">
         <v>14</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I61" s="18" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="J61" s="19" t="b">
         <v>0</v>
@@ -4075,26 +4148,26 @@
     </row>
     <row r="62" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A62" s="16" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C62" s="16" t="s">
         <v>20</v>
       </c>
       <c r="D62" s="16">
-        <v>22000</v>
+        <v>5000</v>
       </c>
       <c r="E62" s="16"/>
       <c r="F62" s="16">
-        <v>28000</v>
+        <v>7000</v>
       </c>
       <c r="G62" s="16" t="s">
         <v>14</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I62" s="18" t="s">
         <v>205</v>
@@ -4108,29 +4181,29 @@
     </row>
     <row r="63" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A63" s="16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C63" s="16" t="s">
         <v>20</v>
       </c>
       <c r="D63" s="16">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="E63" s="16"/>
       <c r="F63" s="16">
-        <v>7000</v>
+        <v>22500</v>
       </c>
       <c r="G63" s="16" t="s">
         <v>14</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I63" s="18" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="J63" s="19" t="b">
         <v>0</v>
@@ -4141,29 +4214,29 @@
     </row>
     <row r="64" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A64" s="16" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C64" s="16" t="s">
         <v>20</v>
       </c>
       <c r="D64" s="16">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="E64" s="16"/>
       <c r="F64" s="16">
-        <v>7000</v>
+        <v>18000</v>
       </c>
       <c r="G64" s="16" t="s">
         <v>14</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I64" s="18" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J64" s="19" t="b">
         <v>0</v>
@@ -4174,10 +4247,10 @@
     </row>
     <row r="65" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A65" s="16" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="C65" s="16" t="s">
         <v>20</v>
@@ -4187,16 +4260,16 @@
       </c>
       <c r="E65" s="16"/>
       <c r="F65" s="16">
-        <v>22500</v>
+        <v>19000</v>
       </c>
       <c r="G65" s="16" t="s">
         <v>14</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="I65" s="18" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="J65" s="19" t="b">
         <v>0</v>
@@ -4207,29 +4280,29 @@
     </row>
     <row r="66" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A66" s="16" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C66" s="16" t="s">
         <v>20</v>
       </c>
       <c r="D66" s="16">
-        <v>12000</v>
+        <v>22000</v>
       </c>
       <c r="E66" s="16"/>
       <c r="F66" s="16">
-        <v>18000</v>
+        <v>34500</v>
       </c>
       <c r="G66" s="16" t="s">
         <v>14</v>
       </c>
       <c r="H66" s="17" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="I66" s="18" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="J66" s="19" t="b">
         <v>0</v>
@@ -4240,29 +4313,29 @@
     </row>
     <row r="67" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A67" s="16" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C67" s="16" t="s">
         <v>20</v>
       </c>
       <c r="D67" s="16">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="E67" s="16"/>
       <c r="F67" s="16">
-        <v>19000</v>
+        <v>15000</v>
       </c>
       <c r="G67" s="16" t="s">
         <v>14</v>
       </c>
       <c r="H67" s="17" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="I67" s="18" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="J67" s="19" t="b">
         <v>0</v>
@@ -4273,29 +4346,29 @@
     </row>
     <row r="68" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A68" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>223</v>
+        <v>189</v>
       </c>
       <c r="C68" s="16" t="s">
         <v>20</v>
       </c>
       <c r="D68" s="16">
-        <v>22000</v>
+        <v>29000</v>
       </c>
       <c r="E68" s="16"/>
       <c r="F68" s="16">
-        <v>34500</v>
+        <v>43500</v>
       </c>
       <c r="G68" s="16" t="s">
         <v>14</v>
       </c>
       <c r="H68" s="17" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="I68" s="18" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="J68" s="19" t="b">
         <v>0</v>
@@ -4304,31 +4377,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" ht="406" x14ac:dyDescent="0.35">
       <c r="A69" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B69" s="16" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="C69" s="16" t="s">
         <v>20</v>
       </c>
       <c r="D69" s="16">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="E69" s="16"/>
       <c r="F69" s="16">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="G69" s="16" t="s">
         <v>14</v>
       </c>
       <c r="H69" s="17" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="I69" s="18" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J69" s="19" t="b">
         <v>0</v>
@@ -4337,32 +4410,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A70" s="16" t="s">
         <v>227</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>189</v>
+        <v>10</v>
       </c>
       <c r="C70" s="16" t="s">
         <v>20</v>
       </c>
       <c r="D70" s="16">
-        <v>29000</v>
+        <v>20000</v>
       </c>
       <c r="E70" s="16"/>
       <c r="F70" s="16">
-        <v>43500</v>
+        <v>30000</v>
       </c>
       <c r="G70" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H70" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="I70" s="18" t="s">
+      <c r="H70" s="16" t="s">
         <v>228</v>
       </c>
+      <c r="I70" s="17" t="s">
+        <v>231</v>
+      </c>
       <c r="J70" s="19" t="b">
         <v>0</v>
       </c>
@@ -4370,31 +4443,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="406" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A71" s="16" t="s">
         <v>229</v>
       </c>
       <c r="B71" s="16" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="C71" s="16" t="s">
         <v>20</v>
       </c>
       <c r="D71" s="16">
-        <v>18000</v>
+        <v>13000</v>
       </c>
       <c r="E71" s="16"/>
       <c r="F71" s="16">
-        <v>27000</v>
+        <v>19500</v>
       </c>
       <c r="G71" s="16" t="s">
         <v>14</v>
       </c>
       <c r="H71" s="17" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="I71" s="18" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J71" s="19" t="b">
         <v>0</v>
@@ -4403,8 +4476,74 @@
         <v>0</v>
       </c>
     </row>
+    <row r="72" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B72" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D72" s="16">
+        <v>8000</v>
+      </c>
+      <c r="E72" s="16"/>
+      <c r="F72" s="16">
+        <v>11000</v>
+      </c>
+      <c r="G72" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H72" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="I72" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="J72" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A73" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="B73" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="C73" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D73" s="16">
+        <v>9000</v>
+      </c>
+      <c r="E73" s="16"/>
+      <c r="F73" s="16">
+        <v>9000</v>
+      </c>
+      <c r="G73" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H73" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="I73" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="J73" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}"/>
+  <autoFilter ref="A1:K71" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0526577688ca4eec/Escritorio/Proyectos developer/Diseños_Gasper/Back-end/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="580" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05BC9152-A612-4427-9C22-BE0904F86F93}"/>
+  <xr:revisionPtr revIDLastSave="603" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96655D59-78B5-465D-9B25-EE346B63AC3C}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -332,12 +332,6 @@
   </si>
   <si>
     <t>{"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270323/p6k7eqjzznst2bxrg2vz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270317/t5cdbjnctbumlg675bnh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270319/lggiyj7ykumexocgdg3w.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270300/dph8v8zxcw4oobwmchp6.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270300/wheagvkqjkcca47yvhlb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270301/fo3oopc2w4gguhsxbwky.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270308/gtl37zjvfml3vmuv2o9l.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270313/z5kuunpfvxclcend8okq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270310/kk0wsleipwg1z2mbcqku.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270304/hl9fado9nquhxaicselq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270305/ru5vmxdsif5kt61snx2u.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270306/vodvrpkiopfd6onb91ix.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270311/ku0bx9n4tm9yljlo0wf7.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270321/ojw3mz6n6hix4ube3qne.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270316/fg6dnjtwpxwm4hoghz91.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270325/eduy6ep0xxc17tqusqq2.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270329/gvwagkni5jgyouq7z2oc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270326/r9qvdtgbdeyir30bac22.png"],"royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270330/z2mavjespmfokq9blbck.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270335/amahc57ashuhn1en1uus.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270333/uqc0lg7dkqsbpk9lul2p.png"],"mediumblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270341/fmj9dftl1oejpyyv9f5e.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270341/nc1781x31vupdepm9piz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270343/kh5eadc7awmjbgrychhh.png"]}</t>
-  </si>
-  <si>
-    <t>black,white,blue,royalblue,mediumblue,green,darkgreen,palegreen,red,crimson</t>
-  </si>
-  <si>
-    <t>{"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251884/ec6qea5mjwajn6nk0dln.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251877/hkcop8xbp6padhtnueg5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251881/u3sf21qmczzhmkc9chvn.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252051/kklwfmuzcbmquhjwr1le.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252055/gj58jpkwmgolvaueqotb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252059/txlffqcfnjip066ftd8k.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251911/jsswfj3yfpgbp0fneaot.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251916/jnbw9puupo8igk8ff0lv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251920/zkn50gnfqb1ab9knzrtr.png"],"royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252003/arjirrtfe28hrruk98by.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252007/aeprferwkxtmejtmbnt4.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252011/o5ppb5ekeva72tecdsb6.png"],"mediumblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251888/cnlog1ryadij1b1nfw4o.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251892/rbhc0i968a6azm11l6kd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251896/dmpmycsic51qpiehjzze.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252026/lu0evxujmcpajk0alk78.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252030/p1jsjnd3p5sah6f8yzfd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252039/m9pzvfpixsmhbu9hmv6n.png"],"darkgreen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252062/fmoab07kdfbqnzoh0cfe.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252066/gcx3hzyojzuimxllhakv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252071/jotsfswaol54s09fbfsm.png"],"palegreen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252034/nnvtss7oi7g69wu0jljp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252042/cm0q4cexpjve8e1m8quj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252047/gogphkry0pzgvwsbz7q5.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252015/p1arccwljiinxatuwq2z.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252018/iafldqth4txewfsqgm3h.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252022/ndnjgaf5il8pc2oos882.png"],"crimson":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251899/tvxqa3edphyb1hdrtmsh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251903/o9hsbfufrpx0n2n2budn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251907/hgknyxcfxcewldkkz0a2.png"]}</t>
   </si>
   <si>
     <t>olive,red,green,blue,crimson,purple,yellow</t>
@@ -1640,6 +1634,58 @@
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421890/s6aqfmvqvxzxbrea9o6m.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421845/vbi5lsovyoekcxcmdedi.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421982/wsanluxtsjfru3qedb6i.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421995/l7d62rcgfwbdhch3exdo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421897/eetddm28orkox7hoyivc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421842/sswalmqkan70tvt5xbb5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421987/axmuavtqpl5qzkfbifns.png" ],
   "hotpink": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773422004/ybytqypmgep2zvvafglf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421915/b4pr9artbraayulde8qo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421836/zqp4tqcz5p3yqok4yz1a.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421839/nbewqlcmyzgwkgckqqqg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421822/cyjggxc3enonwvqb70se.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421854/gcim37vumhuin6espkxf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421947/op6q7fj0zfvej8zz7jfm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773422006/njr7jg5mujkmadzle1gz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421951/rzxqpkwtzyttbwocwuaj.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421966/aypwbrl04yespk7dat5r.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421962/l4mtufoby7nwglrfueng.png"   ]}</t>
+  </si>
+  <si>
+    <t>{
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773874935/obukza5vd0lbczqa3jmj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773874935/xieyxnibupu7gyqbottu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251916/jnbw9puupo8igk8ff0lv.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773874935/vut0fklpq9iq9pgvq0qu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251903/o9hsbfufrpx0n2n2budn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773874936/nnnnksosglnwfxheeugo.png"
+  ],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773874937/ekjfmubhng4unim5sk2n.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252055/gj58jpkwmgolvaueqotb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252059/txlffqcfnjip066ftd8k.png"
+  ],
+  "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252026/lu0evxujmcpajk0alk78.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252030/p1jsjnd3p5sah6f8yzfd.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252039/m9pzvfpixsmhbu9hmv6n.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773874935/xhdaskfvjrjb2gdztdvl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251892/rbhc0i968a6azm11l6kd.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773874935/p1qxnyky6zo2pxzhwxil.png"
+  ],
+  "darkred": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773874936/vepamtjmc71hnjdflqq0.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773251881/u3sf21qmczzhmkc9chvn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773874934/mxp2otdhyeefdiccxrml.png"
+  ],
+  "palegreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773874938/oyyrvqngbzkjcd4nx1gp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252042/cm0q4cexpjve8e1m8quj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252047/gogphkry0pzgvwsbz7q5.png"
+  ],
+  "crimson": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252062/fmoab07kdfbqnzoh0cfe.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252066/gcx3hzyojzuimxllhakv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252071/jotsfswaol54s09fbfsm.png"
+  ],
+   "mediumblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252003/arjirrtfe28hrruk98by.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252007/aeprferwkxtmejtmbnt4.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252011/o5ppb5ekeva72tecdsb6.png"
+  ],  "olive": ["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773874936/gepqc6gvitwzvgsxy2ok.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773874937/qavzumaav2irbqpfkhha.png" ]
+}</t>
+  </si>
+  <si>
+    <t>blue,red,white,darkgreen,black,darkred,palegreen,crimson,mediumblue,olive</t>
   </si>
 </sst>
 </file>
@@ -2137,7 +2183,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>11</v>
@@ -2169,10 +2215,10 @@
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>18</v>
+        <v>177</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>11</v>
@@ -2200,31 +2246,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" s="3" customFormat="1" ht="89.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="6">
-        <v>21000</v>
-      </c>
-      <c r="E4" s="6"/>
+        <v>28000</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>35</v>
+      </c>
       <c r="F4" s="6">
-        <v>31500</v>
+        <v>42000</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>72</v>
+        <v>17</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>74</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J4" s="6" t="b">
         <v>0</v>
@@ -2233,15 +2281,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="3" customFormat="1" ht="89.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" s="3" customFormat="1" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>178</v>
+        <v>19</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D5" s="6">
         <v>28000</v>
@@ -2256,10 +2304,10 @@
         <v>17</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J5" s="6" t="b">
         <v>0</v>
@@ -2268,33 +2316,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="3" customFormat="1" ht="145" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="118.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D6" s="6">
-        <v>28000</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>35</v>
-      </c>
+        <v>21000</v>
+      </c>
+      <c r="E6" s="6"/>
       <c r="F6" s="6">
-        <v>42000</v>
+        <v>33000</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="J6" s="6" t="b">
         <v>0</v>
@@ -2303,31 +2349,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="118.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="77.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="6">
-        <v>21000</v>
-      </c>
-      <c r="E7" s="6"/>
+        <v>33000</v>
+      </c>
+      <c r="E7" s="7"/>
       <c r="F7" s="6">
-        <v>33000</v>
+        <v>49500</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>141</v>
+        <v>78</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="J7" s="6" t="b">
         <v>0</v>
@@ -2336,31 +2382,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="77.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="6">
-        <v>33000</v>
-      </c>
-      <c r="E8" s="7"/>
+        <v>20000</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="F8" s="6">
-        <v>49500</v>
+        <v>30000</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J8" s="6" t="b">
         <v>0</v>
@@ -2371,10 +2419,10 @@
     </row>
     <row r="9" spans="1:11" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>23</v>
+        <v>178</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>11</v>
@@ -2404,33 +2452,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>180</v>
+        <v>24</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="6">
-        <v>20000</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="E10" s="6"/>
       <c r="F10" s="6">
-        <v>30000</v>
+        <v>27000</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>82</v>
+        <v>14</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="J10" s="6" t="b">
         <v>0</v>
@@ -2441,10 +2487,10 @@
     </row>
     <row r="11" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>11</v>
@@ -2472,31 +2518,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="47" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>181</v>
+        <v>85</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="6">
-        <v>18000</v>
+        <v>21000</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6">
-        <v>27000</v>
+        <v>31000</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>140</v>
       </c>
       <c r="J12" s="6" t="b">
         <v>0</v>
@@ -2507,10 +2553,10 @@
     </row>
     <row r="13" spans="1:11" ht="47" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>11</v>
@@ -2529,7 +2575,7 @@
         <v>86</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J13" s="6" t="b">
         <v>0</v>
@@ -2538,31 +2584,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="47" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D14" s="6">
-        <v>21000</v>
-      </c>
-      <c r="E14" s="6"/>
+        <v>38000</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="F14" s="6">
-        <v>31000</v>
+        <v>57000</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>142</v>
+        <v>87</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>141</v>
       </c>
       <c r="J14" s="6" t="b">
         <v>0</v>
@@ -2573,10 +2621,10 @@
     </row>
     <row r="15" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>27</v>
@@ -2597,7 +2645,7 @@
         <v>87</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J15" s="6" t="b">
         <v>0</v>
@@ -2608,13 +2656,13 @@
     </row>
     <row r="16" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D16" s="6">
         <v>38000</v>
@@ -2632,7 +2680,7 @@
         <v>87</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J16" s="6" t="b">
         <v>0</v>
@@ -2643,10 +2691,10 @@
     </row>
     <row r="17" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>11</v>
@@ -2667,7 +2715,7 @@
         <v>87</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J17" s="6" t="b">
         <v>0</v>
@@ -2676,33 +2724,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
-        <v>167</v>
+        <v>25</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D18" s="6">
-        <v>38000</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>37</v>
-      </c>
+        <v>21000</v>
+      </c>
+      <c r="E18" s="6"/>
       <c r="F18" s="6">
-        <v>57000</v>
+        <v>31500</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J18" s="6" t="b">
         <v>0</v>
@@ -2713,10 +2759,10 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
-        <v>25</v>
+        <v>162</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>30</v>
@@ -2735,7 +2781,7 @@
         <v>88</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J19" s="6" t="b">
         <v>0</v>
@@ -2744,31 +2790,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>10</v>
+        <v>161</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D20" s="6">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6">
-        <v>31500</v>
+        <v>28000</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>88</v>
+        <v>14</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J20" s="6" t="b">
         <v>0</v>
@@ -2779,10 +2825,10 @@
     </row>
     <row r="21" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
-        <v>168</v>
+        <v>29</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>11</v>
@@ -2801,7 +2847,7 @@
         <v>89</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J21" s="6" t="b">
         <v>0</v>
@@ -2810,28 +2856,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" ht="54.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D22" s="6">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6">
-        <v>28000</v>
+        <v>31500</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="I22" s="12" t="s">
         <v>146</v>
@@ -2843,31 +2889,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="54.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D23" s="6">
-        <v>21000</v>
+        <v>47000</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6">
-        <v>31500</v>
+        <v>70500</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I23" s="12" t="s">
         <v>147</v>
-      </c>
-      <c r="I23" s="12" t="s">
-        <v>148</v>
       </c>
       <c r="J23" s="6" t="b">
         <v>0</v>
@@ -2878,29 +2924,29 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="6">
-        <v>47000</v>
+        <v>25000</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6">
-        <v>70500</v>
+        <v>37500</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J24" s="6" t="b">
         <v>0</v>
@@ -2911,29 +2957,29 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D25" s="6">
-        <v>25000</v>
+        <v>22000</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6">
-        <v>37500</v>
+        <v>33000</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>150</v>
+        <v>93</v>
       </c>
       <c r="J25" s="6" t="b">
         <v>0</v>
@@ -2944,10 +2990,10 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>39</v>
+        <v>167</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>185</v>
+        <v>10</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>11</v>
@@ -2975,31 +3021,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
-        <v>169</v>
+        <v>18</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>10</v>
+        <v>183</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D27" s="6">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6">
-        <v>33000</v>
+        <v>31500</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H27" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>93</v>
+      <c r="H27" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="J27" s="6" t="b">
         <v>0</v>
@@ -3013,7 +3059,7 @@
         <v>40</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>11</v>
@@ -3043,7 +3089,7 @@
     </row>
     <row r="29" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>10</v>
@@ -3065,7 +3111,7 @@
         <v>96</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J29" s="6" t="b">
         <v>0</v>
@@ -3076,7 +3122,7 @@
     </row>
     <row r="30" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>10</v>
@@ -3177,7 +3223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>47</v>
       </c>
@@ -3198,10 +3244,10 @@
         <v>14</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="I33" s="12" t="s">
-        <v>104</v>
+        <v>237</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>236</v>
       </c>
       <c r="J33" s="6" t="b">
         <v>0</v>
@@ -3231,10 +3277,10 @@
         <v>14</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J34" s="6" t="b">
         <v>0</v>
@@ -3245,7 +3291,7 @@
     </row>
     <row r="35" spans="1:11" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>10</v>
@@ -3257,7 +3303,7 @@
         <v>17000</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F35" s="6">
         <v>34000</v>
@@ -3266,10 +3312,10 @@
         <v>41</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J35" s="6" t="b">
         <v>0</v>
@@ -3280,7 +3326,7 @@
     </row>
     <row r="36" spans="1:11" ht="126.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>10</v>
@@ -3292,7 +3338,7 @@
         <v>17000</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F36" s="6">
         <v>34000</v>
@@ -3301,10 +3347,10 @@
         <v>41</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J36" s="6" t="b">
         <v>0</v>
@@ -3315,7 +3361,7 @@
     </row>
     <row r="37" spans="1:11" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>10</v>
@@ -3327,7 +3373,7 @@
         <v>17000</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F37" s="6">
         <v>34000</v>
@@ -3336,10 +3382,10 @@
         <v>41</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J37" s="6" t="b">
         <v>0</v>
@@ -3350,7 +3396,7 @@
     </row>
     <row r="38" spans="1:11" ht="91" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>10</v>
@@ -3362,7 +3408,7 @@
         <v>17000</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F38" s="6">
         <v>34000</v>
@@ -3371,10 +3417,10 @@
         <v>41</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J38" s="6" t="b">
         <v>0</v>
@@ -3385,7 +3431,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>10</v>
@@ -3404,10 +3450,10 @@
         <v>52</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J39" s="6" t="b">
         <v>0</v>
@@ -3437,10 +3483,10 @@
         <v>52</v>
       </c>
       <c r="H40" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I40" s="13" t="s">
         <v>114</v>
-      </c>
-      <c r="I40" s="13" t="s">
-        <v>116</v>
       </c>
       <c r="J40" s="6" t="b">
         <v>0</v>
@@ -3470,10 +3516,10 @@
         <v>14</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I41" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J41" s="6" t="b">
         <v>0</v>
@@ -3484,7 +3530,7 @@
     </row>
     <row r="42" spans="1:11" ht="98.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>10</v>
@@ -3503,10 +3549,10 @@
         <v>45</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I42" s="15" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J42" s="6" t="b">
         <v>0</v>
@@ -3536,10 +3582,10 @@
         <v>45</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J43" s="6" t="b">
         <v>0</v>
@@ -3569,10 +3615,10 @@
         <v>14</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J44" s="6" t="b">
         <v>0</v>
@@ -3604,10 +3650,10 @@
         <v>56</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J45" s="6" t="b">
         <v>0</v>
@@ -3637,10 +3683,10 @@
         <v>59</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J46" s="6" t="b">
         <v>0</v>
@@ -3670,10 +3716,10 @@
         <v>13</v>
       </c>
       <c r="H47" s="15" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J47" s="6" t="b">
         <v>0</v>
@@ -3684,7 +3730,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>10</v>
@@ -3703,10 +3749,10 @@
         <v>61</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I48" s="14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J48" s="6" t="b">
         <v>0</v>
@@ -3736,10 +3782,10 @@
         <v>12</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J49" s="6" t="b">
         <v>0</v>
@@ -3753,7 +3799,7 @@
         <v>63</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>11</v>
@@ -3769,10 +3815,10 @@
         <v>12</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I50" s="14" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J50" s="6" t="b">
         <v>0</v>
@@ -3802,10 +3848,10 @@
         <v>12</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J51" s="6" t="b">
         <v>0</v>
@@ -3835,10 +3881,10 @@
         <v>14</v>
       </c>
       <c r="H52" s="15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J52" s="6" t="b">
         <v>0</v>
@@ -3852,7 +3898,7 @@
         <v>66</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>11</v>
@@ -3868,10 +3914,10 @@
         <v>14</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J53" s="6" t="b">
         <v>0</v>
@@ -3885,7 +3931,7 @@
         <v>67</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>11</v>
@@ -3901,10 +3947,10 @@
         <v>14</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J54" s="6" t="b">
         <v>0</v>
@@ -3918,7 +3964,7 @@
         <v>68</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>11</v>
@@ -3934,10 +3980,10 @@
         <v>14</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J55" s="6" t="b">
         <v>0</v>
@@ -3951,7 +3997,7 @@
         <v>69</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>11</v>
@@ -3967,10 +4013,10 @@
         <v>32</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J56" s="6" t="b">
         <v>0</v>
@@ -3981,10 +4027,10 @@
     </row>
     <row r="57" spans="1:11" ht="377" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>11</v>
@@ -3993,7 +4039,7 @@
         <v>22000</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F57" s="6">
         <v>27000</v>
@@ -4002,10 +4048,10 @@
         <v>17</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I57" s="15" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J57" s="6" t="b">
         <v>0</v>
@@ -4016,10 +4062,10 @@
     </row>
     <row r="58" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A58" s="16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C58" s="16" t="s">
         <v>27</v>
@@ -4035,10 +4081,10 @@
         <v>14</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I58" s="18" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J58" s="19" t="b">
         <v>0</v>
@@ -4049,10 +4095,10 @@
     </row>
     <row r="59" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A59" s="16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C59" s="16" t="s">
         <v>20</v>
@@ -4068,10 +4114,10 @@
         <v>14</v>
       </c>
       <c r="H59" s="17" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I59" s="18" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J59" s="19" t="b">
         <v>0</v>
@@ -4082,10 +4128,10 @@
     </row>
     <row r="60" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A60" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C60" s="16" t="s">
         <v>20</v>
@@ -4101,10 +4147,10 @@
         <v>14</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I60" s="18" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J60" s="19" t="b">
         <v>0</v>
@@ -4115,10 +4161,10 @@
     </row>
     <row r="61" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A61" s="16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C61" s="16" t="s">
         <v>20</v>
@@ -4134,10 +4180,10 @@
         <v>14</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I61" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J61" s="19" t="b">
         <v>0</v>
@@ -4148,10 +4194,10 @@
     </row>
     <row r="62" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A62" s="16" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C62" s="16" t="s">
         <v>20</v>
@@ -4167,10 +4213,10 @@
         <v>14</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I62" s="18" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J62" s="19" t="b">
         <v>0</v>
@@ -4181,10 +4227,10 @@
     </row>
     <row r="63" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A63" s="16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C63" s="16" t="s">
         <v>20</v>
@@ -4200,10 +4246,10 @@
         <v>14</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I63" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J63" s="19" t="b">
         <v>0</v>
@@ -4214,10 +4260,10 @@
     </row>
     <row r="64" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A64" s="16" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C64" s="16" t="s">
         <v>20</v>
@@ -4233,10 +4279,10 @@
         <v>14</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I64" s="18" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J64" s="19" t="b">
         <v>0</v>
@@ -4247,10 +4293,10 @@
     </row>
     <row r="65" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A65" s="16" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C65" s="16" t="s">
         <v>20</v>
@@ -4266,10 +4312,10 @@
         <v>14</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I65" s="18" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J65" s="19" t="b">
         <v>0</v>
@@ -4280,10 +4326,10 @@
     </row>
     <row r="66" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A66" s="16" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C66" s="16" t="s">
         <v>20</v>
@@ -4299,10 +4345,10 @@
         <v>14</v>
       </c>
       <c r="H66" s="17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I66" s="18" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J66" s="19" t="b">
         <v>0</v>
@@ -4313,10 +4359,10 @@
     </row>
     <row r="67" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A67" s="16" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C67" s="16" t="s">
         <v>20</v>
@@ -4332,10 +4378,10 @@
         <v>14</v>
       </c>
       <c r="H67" s="17" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I67" s="18" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J67" s="19" t="b">
         <v>0</v>
@@ -4346,10 +4392,10 @@
     </row>
     <row r="68" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A68" s="16" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C68" s="16" t="s">
         <v>20</v>
@@ -4365,10 +4411,10 @@
         <v>14</v>
       </c>
       <c r="H68" s="17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I68" s="18" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J68" s="19" t="b">
         <v>0</v>
@@ -4379,10 +4425,10 @@
     </row>
     <row r="69" spans="1:11" ht="406" x14ac:dyDescent="0.35">
       <c r="A69" s="16" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B69" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C69" s="16" t="s">
         <v>20</v>
@@ -4398,10 +4444,10 @@
         <v>14</v>
       </c>
       <c r="H69" s="17" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I69" s="18" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J69" s="19" t="b">
         <v>0</v>
@@ -4412,7 +4458,7 @@
     </row>
     <row r="70" spans="1:11" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A70" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B70" s="16" t="s">
         <v>10</v>
@@ -4431,10 +4477,10 @@
         <v>14</v>
       </c>
       <c r="H70" s="16" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J70" s="19" t="b">
         <v>0</v>
@@ -4445,10 +4491,10 @@
     </row>
     <row r="71" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A71" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B71" s="16" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C71" s="16" t="s">
         <v>20</v>
@@ -4464,10 +4510,10 @@
         <v>14</v>
       </c>
       <c r="H71" s="17" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I71" s="18" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J71" s="19" t="b">
         <v>0</v>
@@ -4478,10 +4524,10 @@
     </row>
     <row r="72" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A72" s="16" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C72" s="16" t="s">
         <v>20</v>
@@ -4497,10 +4543,10 @@
         <v>14</v>
       </c>
       <c r="H72" s="17" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I72" s="18" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J72" s="19" t="b">
         <v>0</v>
@@ -4511,10 +4557,10 @@
     </row>
     <row r="73" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A73" s="16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C73" s="16" t="s">
         <v>20</v>
@@ -4530,10 +4576,10 @@
         <v>14</v>
       </c>
       <c r="H73" s="17" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I73" s="18" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J73" s="19" t="b">
         <v>0</v>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0526577688ca4eec/Escritorio/Proyectos developer/Diseños_Gasper/Back-end/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="603" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96655D59-78B5-465D-9B25-EE346B63AC3C}"/>
+  <xr:revisionPtr revIDLastSave="620" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51DF0282-5D04-46C1-B851-385A0E1E8518}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="243">
   <si>
     <t>name</t>
   </si>
@@ -1686,6 +1686,33 @@
   </si>
   <si>
     <t>blue,red,white,darkgreen,black,darkred,palegreen,crimson,mediumblue,olive</t>
+  </si>
+  <si>
+    <t>Chaqueta Publicidad</t>
+  </si>
+  <si>
+    <t>publicidad</t>
+  </si>
+  <si>
+    <t>{
+  "green": [
+  "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774395922/zebgi2cvqlhgxaav0zmi.jpg", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774395923/rqp9dj0761msqqaekqyz.png"
+  ],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774395922/sbkh9hf1obzqjtbxxwh1.jpg", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774395922/gcffbqz9psi69c6brfsb.jpg"
+    ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774395922/bsh7ab1mqmmiooyzxoyl.jpg", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774395923/uxfvmse8dalcupvoblws.png"
+   ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774396861/p0ek3kuirzlgcrstgddr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774396861/xrxzbn70xvrj8mpntflf.png"
+    ]}</t>
+  </si>
+  <si>
+    <t>green,white,red,gray</t>
+  </si>
+  <si>
+    <t>*Consultar</t>
   </si>
 </sst>
 </file>
@@ -2127,7 +2154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}">
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="57.54296875" style="2" customWidth="1"/>
@@ -4588,6 +4615,39 @@
         <v>0</v>
       </c>
     </row>
+    <row r="74" spans="1:11" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="B74" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74" s="16">
+        <v>17000</v>
+      </c>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16">
+        <v>34000</v>
+      </c>
+      <c r="G74" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="H74" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="I74" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="J74" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K71" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0526577688ca4eec/Escritorio/Proyectos developer/Diseños_Gasper/Back-end/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="620" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51DF0282-5D04-46C1-B851-385A0E1E8518}"/>
+  <xr:revisionPtr revIDLastSave="632" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABD973EF-F20D-47B4-BAB1-C1E9DB290B63}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="productos" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">productos!$A$1:$K$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">productos!$A$1:$L$71</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="247">
   <si>
     <t>name</t>
   </si>
@@ -1713,6 +1713,18 @@
   </si>
   <si>
     <t>*Consultar</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>Chaqueta rompevientos semireflectiva con colores laterales y material reflectivo</t>
+  </si>
+  <si>
+    <t>Maya lateral de diferentes colores y material reflectivo</t>
+  </si>
+  <si>
+    <t>Chaqueta rompevientos semireflectiva con color tipo triangulo y material reflectivo</t>
   </si>
 </sst>
 </file>
@@ -1736,7 +1748,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1764,6 +1776,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1795,7 +1813,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1848,6 +1866,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2154,2502 +2175,2586 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}">
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="57.54296875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="24.90625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.26953125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18" style="2" customWidth="1"/>
-    <col min="5" max="5" width="37.7265625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.7265625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="15" style="2" customWidth="1"/>
-    <col min="8" max="8" width="31.54296875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="131.26953125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.26953125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.26953125" style="1" customWidth="1"/>
+    <col min="1" max="2" width="57.54296875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="24.90625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.26953125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.7265625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.7265625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15" style="2" customWidth="1"/>
+    <col min="9" max="9" width="31.54296875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="131.26953125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="15.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.26953125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="3" customFormat="1" ht="88.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" s="3" customFormat="1" ht="88.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="6">
+      <c r="E2" s="6">
         <v>33000</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="6">
+      <c r="G2" s="6">
         <v>49500</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K2" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L2" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>177</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="6">
+      <c r="E3" s="6">
         <v>21000</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6">
+      <c r="F3" s="6"/>
+      <c r="G3" s="6">
         <v>31500</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="J3" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K3" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" s="3" customFormat="1" ht="89.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L3" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="3" customFormat="1" ht="89.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="6">
+      <c r="E4" s="6">
         <v>28000</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="6">
+      <c r="G4" s="6">
         <v>42000</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="I4" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="J4" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K4" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" s="3" customFormat="1" ht="145" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L4" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="3" customFormat="1" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="6">
+      <c r="E5" s="6">
         <v>28000</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="6">
+      <c r="G5" s="6">
         <v>42000</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="I5" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="J5" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="J5" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K5" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="118.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L5" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="118.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="6">
+      <c r="E6" s="6">
         <v>21000</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6">
+      <c r="F6" s="6"/>
+      <c r="G6" s="6">
         <v>33000</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="I6" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="J6" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="J6" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K6" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="77.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L6" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="77.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="6">
+      <c r="E7" s="6">
         <v>33000</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="6">
+      <c r="F7" s="7"/>
+      <c r="G7" s="6">
         <v>49500</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="I7" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="J7" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="J7" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K7" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L7" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="6"/>
+      <c r="C8" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="6">
+      <c r="E8" s="6">
         <v>20000</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="6">
+      <c r="G8" s="6">
         <v>30000</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="H8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="I8" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="J8" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="J8" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K8" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L8" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="6"/>
+      <c r="C9" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="6">
+      <c r="E9" s="6">
         <v>20000</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="6">
+      <c r="G9" s="6">
         <v>30000</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="H9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="I9" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="J9" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="J9" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K9" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L9" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="6"/>
+      <c r="C10" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="6">
+      <c r="E10" s="6">
         <v>18000</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6">
+      <c r="F10" s="6"/>
+      <c r="G10" s="6">
         <v>27000</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="H10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="I10" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="J10" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="J10" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K10" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L10" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="6"/>
+      <c r="C11" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="D11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="6">
+      <c r="E11" s="6">
         <v>18000</v>
       </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6">
+      <c r="F11" s="6"/>
+      <c r="G11" s="6">
         <v>27000</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="H11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="I11" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="J11" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="J11" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K11" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="47" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L11" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="47" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="6"/>
+      <c r="C12" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="6">
+      <c r="E12" s="6">
         <v>21000</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6">
+      <c r="F12" s="6"/>
+      <c r="G12" s="6">
         <v>31000</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="I12" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="J12" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="J12" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K12" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="47" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L12" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="47" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="D13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="6">
+      <c r="E13" s="6">
         <v>21000</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6">
+      <c r="F13" s="6"/>
+      <c r="G13" s="6">
         <v>31000</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="H13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="I13" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="J13" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="J13" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K13" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="L13" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="6"/>
+      <c r="C14" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="6">
+      <c r="E14" s="6">
         <v>38000</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="F14" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="6">
+      <c r="G14" s="6">
         <v>57000</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="H14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="I14" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="J14" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="J14" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K14" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="L14" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="6"/>
+      <c r="C15" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="D15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="6">
+      <c r="E15" s="6">
         <v>38000</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="6">
+      <c r="G15" s="6">
         <v>57000</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="H15" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="I15" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="J15" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="J15" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K15" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="L15" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="6"/>
+      <c r="C16" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="6">
+      <c r="E16" s="6">
         <v>38000</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="F16" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F16" s="6">
+      <c r="G16" s="6">
         <v>57000</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="H16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="I16" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="J16" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="J16" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K16" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="L16" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="6"/>
+      <c r="C17" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="D17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="6">
+      <c r="E17" s="6">
         <v>38000</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="F17" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="6">
+      <c r="G17" s="6">
         <v>57000</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="H17" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="I17" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="J17" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="J17" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K17" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L17" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="6"/>
+      <c r="C18" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="D18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="6">
+      <c r="E18" s="6">
         <v>21000</v>
       </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6">
+      <c r="F18" s="6"/>
+      <c r="G18" s="6">
         <v>31500</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="I18" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="J18" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="J18" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K18" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L18" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="6"/>
+      <c r="C19" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="D19" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="6">
+      <c r="E19" s="6">
         <v>21000</v>
       </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6">
+      <c r="F19" s="6"/>
+      <c r="G19" s="6">
         <v>31500</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="H19" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="I19" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="J19" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="J19" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K19" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="L19" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="6"/>
+      <c r="C20" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="D20" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="6">
+      <c r="E20" s="6">
         <v>22000</v>
       </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6">
+      <c r="F20" s="6"/>
+      <c r="G20" s="6">
         <v>28000</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="H20" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="I20" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="J20" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="J20" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K20" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="L20" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="6"/>
+      <c r="C21" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="D21" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="6">
+      <c r="E21" s="6">
         <v>22000</v>
       </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6">
+      <c r="F21" s="6"/>
+      <c r="G21" s="6">
         <v>28000</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="H21" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="I21" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="J21" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="J21" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K21" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="54.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L21" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="54.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="6"/>
+      <c r="C22" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="D22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="6">
+      <c r="E22" s="6">
         <v>21000</v>
       </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6">
+      <c r="F22" s="6"/>
+      <c r="G22" s="6">
         <v>31500</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="H22" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="I22" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="J22" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="J22" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K22" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L22" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="6"/>
+      <c r="C23" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="6">
+      <c r="E23" s="6">
         <v>47000</v>
       </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6">
+      <c r="F23" s="6"/>
+      <c r="G23" s="6">
         <v>70500</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="H23" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="I23" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="I23" s="12" t="s">
+      <c r="J23" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="J23" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K23" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L23" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="6"/>
+      <c r="C24" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="D24" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="6">
+      <c r="E24" s="6">
         <v>25000</v>
       </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6">
+      <c r="F24" s="6"/>
+      <c r="G24" s="6">
         <v>37500</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="H24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="I24" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="I24" s="12" t="s">
+      <c r="J24" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="J24" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K24" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L24" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="6"/>
+      <c r="C25" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="D25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="6">
+      <c r="E25" s="6">
         <v>22000</v>
       </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6">
+      <c r="F25" s="6"/>
+      <c r="G25" s="6">
         <v>33000</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="H25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="I25" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="I25" s="12" t="s">
+      <c r="J25" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J25" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K25" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L25" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="6"/>
+      <c r="C26" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="D26" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="6">
+      <c r="E26" s="6">
         <v>22000</v>
       </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6">
+      <c r="F26" s="6"/>
+      <c r="G26" s="6">
         <v>33000</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="I26" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="I26" s="12" t="s">
+      <c r="J26" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J26" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K26" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="L26" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="6"/>
+      <c r="C27" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="D27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="6">
+      <c r="E27" s="6">
         <v>21000</v>
       </c>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6">
+      <c r="F27" s="6"/>
+      <c r="G27" s="6">
         <v>31500</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="H27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="I27" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="J27" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="J27" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K27" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="L27" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="6"/>
+      <c r="C28" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="D28" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D28" s="6">
+      <c r="E28" s="6">
         <v>40000</v>
       </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6">
+      <c r="F28" s="6"/>
+      <c r="G28" s="6">
         <v>60000</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="H28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="I28" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="I28" s="12" t="s">
+      <c r="J28" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="J28" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K28" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="L28" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="6"/>
+      <c r="C29" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="D29" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="6">
+      <c r="E29" s="6">
         <v>12000</v>
       </c>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6">
+      <c r="F29" s="6"/>
+      <c r="G29" s="6">
         <v>18000</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="H29" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="I29" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="I29" s="12" t="s">
+      <c r="J29" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="J29" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K29" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="L29" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="6"/>
+      <c r="C30" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="D30" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D30" s="6">
+      <c r="E30" s="6">
         <v>12000</v>
       </c>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6">
+      <c r="F30" s="6"/>
+      <c r="G30" s="6">
         <v>18000</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="H30" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="I30" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="I30" s="12" t="s">
+      <c r="J30" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="J30" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K30" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="L30" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="6"/>
+      <c r="C31" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="D31" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="6">
+      <c r="E31" s="6">
         <v>20000</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F31" s="6">
+      <c r="G31" s="6">
         <v>28500</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="H31" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="I31" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I31" s="12" t="s">
+      <c r="J31" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="J31" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K31" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="L31" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="6"/>
+      <c r="C32" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="D32" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="6">
+      <c r="E32" s="6">
         <v>18000</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="F32" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F32" s="6">
+      <c r="G32" s="6">
         <v>27000</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="H32" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="I32" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="I32" s="12" t="s">
+      <c r="J32" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="J32" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K32" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L32" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="6"/>
+      <c r="C33" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="D33" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D33" s="6">
+      <c r="E33" s="6">
         <v>19000</v>
       </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6">
+      <c r="F33" s="6"/>
+      <c r="G33" s="6">
         <v>28500</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="H33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="8" t="s">
+      <c r="I33" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="I33" s="11" t="s">
+      <c r="J33" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="J33" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K33" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L33" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="6"/>
+      <c r="C34" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="D34" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D34" s="6">
+      <c r="E34" s="6">
         <v>21000</v>
       </c>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6">
+      <c r="F34" s="6"/>
+      <c r="G34" s="6">
         <v>26000</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H34" s="12" t="s">
+      <c r="I34" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="I34" s="12" t="s">
+      <c r="J34" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="J34" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K34" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L34" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="6"/>
+      <c r="C35" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="D35" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D35" s="6">
+      <c r="E35" s="6">
         <v>17000</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="F35" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F35" s="6">
+      <c r="G35" s="6">
         <v>34000</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="H35" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H35" s="11" t="s">
+      <c r="I35" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I35" s="8" t="s">
+      <c r="J35" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="J35" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K35" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" ht="126.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L35" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="126.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="6"/>
+      <c r="C36" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="D36" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D36" s="6">
+      <c r="E36" s="6">
         <v>17000</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="F36" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F36" s="6">
+      <c r="G36" s="6">
         <v>34000</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="H36" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H36" s="11" t="s">
+      <c r="I36" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="I36" s="8" t="s">
+      <c r="J36" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="J36" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K36" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L36" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="6"/>
+      <c r="C37" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="D37" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D37" s="6">
+      <c r="E37" s="6">
         <v>17000</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="F37" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F37" s="6">
+      <c r="G37" s="6">
         <v>34000</v>
       </c>
-      <c r="G37" s="6" t="s">
+      <c r="H37" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H37" s="7" t="s">
+      <c r="I37" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="I37" s="8" t="s">
+      <c r="J37" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="J37" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K37" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" ht="91" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L37" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="91" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="6"/>
+      <c r="C38" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="D38" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D38" s="6">
+      <c r="E38" s="6">
         <v>17000</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="F38" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F38" s="6">
+      <c r="G38" s="6">
         <v>34000</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="I38" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="I38" s="8" t="s">
+      <c r="J38" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="J38" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K38" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L38" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="6"/>
+      <c r="C39" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="D39" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D39" s="6">
+      <c r="E39" s="6">
         <v>20000</v>
       </c>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6">
+      <c r="F39" s="6"/>
+      <c r="G39" s="6">
         <v>30000</v>
       </c>
-      <c r="G39" s="6" t="s">
+      <c r="H39" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H39" s="6" t="s">
+      <c r="I39" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="I39" s="12" t="s">
+      <c r="J39" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="J39" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K39" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L39" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="6"/>
+      <c r="C40" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="D40" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D40" s="6">
+      <c r="E40" s="6">
         <v>20000</v>
       </c>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6">
+      <c r="F40" s="6"/>
+      <c r="G40" s="6">
         <v>30000</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H40" s="6" t="s">
+      <c r="I40" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="I40" s="13" t="s">
+      <c r="J40" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="J40" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K40" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L40" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="6"/>
+      <c r="C41" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="D41" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D41" s="6">
+      <c r="E41" s="6">
         <v>29000</v>
       </c>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6">
+      <c r="F41" s="6"/>
+      <c r="G41" s="6">
         <v>35800</v>
       </c>
-      <c r="G41" s="6" t="s">
+      <c r="H41" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H41" s="6" t="s">
+      <c r="I41" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="I41" s="14" t="s">
+      <c r="J41" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="J41" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K41" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" ht="98.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L41" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="98.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="6"/>
+      <c r="C42" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="D42" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D42" s="6">
+      <c r="E42" s="6">
         <v>24000</v>
       </c>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6">
+      <c r="F42" s="6"/>
+      <c r="G42" s="6">
         <v>36000</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H42" s="7" t="s">
+      <c r="I42" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="I42" s="15" t="s">
+      <c r="J42" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="J42" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K42" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" ht="95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L42" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="6"/>
+      <c r="C43" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="D43" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D43" s="6">
+      <c r="E43" s="6">
         <v>24000</v>
       </c>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6">
+      <c r="F43" s="6"/>
+      <c r="G43" s="6">
         <v>36000</v>
       </c>
-      <c r="G43" s="6" t="s">
+      <c r="H43" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H43" s="7" t="s">
+      <c r="I43" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="I43" s="15" t="s">
+      <c r="J43" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="J43" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K43" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" ht="158" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L43" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="158" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="6"/>
+      <c r="C44" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="D44" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D44" s="6">
+      <c r="E44" s="6">
         <v>19000</v>
       </c>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6">
+      <c r="F44" s="6"/>
+      <c r="G44" s="6">
         <v>24000</v>
       </c>
-      <c r="G44" s="6" t="s">
+      <c r="H44" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="I44" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="I44" s="8" t="s">
+      <c r="J44" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="J44" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K44" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L44" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="6"/>
+      <c r="C45" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="D45" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D45" s="6">
+      <c r="E45" s="6">
         <v>10000</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="F45" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F45" s="6">
+      <c r="G45" s="6">
         <v>19000</v>
       </c>
-      <c r="G45" s="7" t="s">
+      <c r="H45" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H45" s="7" t="s">
+      <c r="I45" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="I45" s="8" t="s">
+      <c r="J45" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="J45" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K45" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" ht="82" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L45" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="82" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="6"/>
+      <c r="C46" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="D46" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D46" s="6">
+      <c r="E46" s="6">
         <v>13000</v>
       </c>
-      <c r="E46" s="7"/>
-      <c r="F46" s="6">
+      <c r="F46" s="7"/>
+      <c r="G46" s="6">
         <v>20000</v>
       </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="H46" s="6" t="s">
+      <c r="I46" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="I46" s="8" t="s">
+      <c r="J46" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="J46" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K46" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" ht="302.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L46" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="302.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="6"/>
+      <c r="C47" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="D47" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D47" s="6">
+      <c r="E47" s="6">
         <v>22000</v>
       </c>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6">
+      <c r="F47" s="6"/>
+      <c r="G47" s="6">
         <v>26000</v>
       </c>
-      <c r="G47" s="6" t="s">
+      <c r="H47" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H47" s="15" t="s">
+      <c r="I47" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="I47" s="15" t="s">
+      <c r="J47" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="J47" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K47" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L47" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="6"/>
+      <c r="C48" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="D48" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D48" s="6">
+      <c r="E48" s="6">
         <v>22000</v>
       </c>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6">
+      <c r="F48" s="6"/>
+      <c r="G48" s="6">
         <v>30000</v>
       </c>
-      <c r="G48" s="6" t="s">
+      <c r="H48" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H48" s="6" t="s">
+      <c r="I48" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="I48" s="14" t="s">
+      <c r="J48" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="J48" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K48" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" ht="261.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L48" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="261.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="6"/>
+      <c r="C49" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="D49" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D49" s="6">
+      <c r="E49" s="6">
         <v>25000</v>
       </c>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6">
+      <c r="F49" s="6"/>
+      <c r="G49" s="6">
         <v>37500</v>
       </c>
-      <c r="G49" s="6" t="s">
+      <c r="H49" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H49" s="7" t="s">
+      <c r="I49" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="I49" s="8" t="s">
+      <c r="J49" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="J49" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K49" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L49" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="6"/>
+      <c r="C50" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="D50" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D50" s="6">
+      <c r="E50" s="6">
         <v>22000</v>
       </c>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6">
+      <c r="F50" s="6"/>
+      <c r="G50" s="6">
         <v>29000</v>
       </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H50" s="6" t="s">
+      <c r="I50" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="I50" s="14" t="s">
+      <c r="J50" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="J50" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K50" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L50" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="6"/>
+      <c r="C51" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="D51" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D51" s="6">
+      <c r="E51" s="6">
         <v>18000</v>
       </c>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6">
+      <c r="F51" s="6"/>
+      <c r="G51" s="6">
         <v>24000</v>
       </c>
-      <c r="G51" s="6" t="s">
+      <c r="H51" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H51" s="6" t="s">
+      <c r="I51" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="I51" s="14" t="s">
+      <c r="J51" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="J51" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K51" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" ht="121.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L51" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="121.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="6"/>
+      <c r="C52" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="D52" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D52" s="6">
+      <c r="E52" s="6">
         <v>15000</v>
       </c>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6">
+      <c r="F52" s="6"/>
+      <c r="G52" s="6">
         <v>20000</v>
       </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H52" s="15" t="s">
+      <c r="I52" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="I52" s="15" t="s">
+      <c r="J52" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="J52" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K52" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L52" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="6"/>
+      <c r="C53" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="D53" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D53" s="6">
+      <c r="E53" s="6">
         <v>20000</v>
       </c>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6">
+      <c r="F53" s="6"/>
+      <c r="G53" s="6">
         <v>25000</v>
       </c>
-      <c r="G53" s="6" t="s">
+      <c r="H53" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H53" s="6" t="s">
+      <c r="I53" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="I53" s="12" t="s">
+      <c r="J53" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="J53" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K53" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" ht="141.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L53" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="141.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="6"/>
+      <c r="C54" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="D54" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D54" s="6">
+      <c r="E54" s="6">
         <v>18000</v>
       </c>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6">
+      <c r="F54" s="6"/>
+      <c r="G54" s="6">
         <v>20000</v>
       </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H54" s="6" t="s">
+      <c r="I54" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="I54" s="11" t="s">
+      <c r="J54" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="J54" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K54" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" ht="276.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L54" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="276.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="6"/>
+      <c r="C55" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="D55" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D55" s="6">
+      <c r="E55" s="6">
         <v>40000</v>
       </c>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6">
+      <c r="F55" s="6"/>
+      <c r="G55" s="6">
         <v>49000</v>
       </c>
-      <c r="G55" s="6" t="s">
+      <c r="H55" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H55" s="6" t="s">
+      <c r="I55" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="I55" s="11" t="s">
+      <c r="J55" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="J55" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K55" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L55" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="6"/>
+      <c r="C56" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="D56" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D56" s="6">
+      <c r="E56" s="6">
         <v>52000</v>
       </c>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6">
+      <c r="F56" s="6"/>
+      <c r="G56" s="6">
         <v>78000</v>
       </c>
-      <c r="G56" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H56" s="6" t="s">
+      <c r="I56" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="I56" s="6" t="s">
+      <c r="J56" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="J56" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K56" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" ht="377" x14ac:dyDescent="0.35">
+      <c r="L56" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="377" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="6"/>
+      <c r="C57" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="D57" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D57" s="6">
+      <c r="E57" s="6">
         <v>22000</v>
       </c>
-      <c r="E57" s="6" t="s">
+      <c r="F57" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F57" s="6">
+      <c r="G57" s="6">
         <v>27000</v>
       </c>
-      <c r="G57" s="6" t="s">
+      <c r="H57" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H57" s="7" t="s">
+      <c r="I57" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="I57" s="15" t="s">
+      <c r="J57" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="J57" s="6" t="b">
-        <v>0</v>
-      </c>
       <c r="K57" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="L57" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A58" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B58" s="16"/>
+      <c r="C58" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="D58" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D58" s="16">
+      <c r="E58" s="16">
         <v>17000</v>
       </c>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16">
+      <c r="F58" s="16"/>
+      <c r="G58" s="16">
         <v>25000</v>
       </c>
-      <c r="G58" s="16" t="s">
+      <c r="H58" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H58" s="17" t="s">
+      <c r="I58" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="I58" s="18" t="s">
+      <c r="J58" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="J58" s="19" t="b">
-        <v>0</v>
-      </c>
       <c r="K58" s="19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="L58" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A59" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="B59" s="16" t="s">
+      <c r="B59" s="16"/>
+      <c r="C59" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="C59" s="16" t="s">
+      <c r="D59" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D59" s="16">
+      <c r="E59" s="16">
         <v>21000</v>
       </c>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16">
+      <c r="F59" s="16"/>
+      <c r="G59" s="16">
         <v>31500</v>
       </c>
-      <c r="G59" s="16" t="s">
+      <c r="H59" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H59" s="17" t="s">
+      <c r="I59" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="I59" s="18" t="s">
+      <c r="J59" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="J59" s="19" t="b">
-        <v>0</v>
-      </c>
       <c r="K59" s="19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="L59" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A60" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="B60" s="16" t="s">
+      <c r="B60" s="16"/>
+      <c r="C60" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="C60" s="16" t="s">
+      <c r="D60" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D60" s="16">
+      <c r="E60" s="16">
         <v>22000</v>
       </c>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16">
+      <c r="F60" s="16"/>
+      <c r="G60" s="16">
         <v>28000</v>
       </c>
-      <c r="G60" s="16" t="s">
+      <c r="H60" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H60" s="17" t="s">
+      <c r="I60" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="I60" s="18" t="s">
+      <c r="J60" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="J60" s="19" t="b">
-        <v>0</v>
-      </c>
       <c r="K60" s="19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="L60" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A61" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="B61" s="16"/>
+      <c r="C61" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="16" t="s">
+      <c r="D61" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D61" s="16">
+      <c r="E61" s="16">
         <v>5000</v>
       </c>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16">
+      <c r="F61" s="16"/>
+      <c r="G61" s="16">
         <v>7000</v>
       </c>
-      <c r="G61" s="16" t="s">
+      <c r="H61" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H61" s="17" t="s">
+      <c r="I61" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="I61" s="18" t="s">
+      <c r="J61" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="J61" s="19" t="b">
-        <v>0</v>
-      </c>
       <c r="K61" s="19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="L61" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A62" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="B62" s="16" t="s">
+      <c r="B62" s="16"/>
+      <c r="C62" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="C62" s="16" t="s">
+      <c r="D62" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D62" s="16">
+      <c r="E62" s="16">
         <v>5000</v>
       </c>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16">
+      <c r="F62" s="16"/>
+      <c r="G62" s="16">
         <v>7000</v>
       </c>
-      <c r="G62" s="16" t="s">
+      <c r="H62" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H62" s="17" t="s">
+      <c r="I62" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="I62" s="18" t="s">
+      <c r="J62" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="J62" s="19" t="b">
-        <v>0</v>
-      </c>
       <c r="K62" s="19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="L62" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A63" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="B63" s="16"/>
+      <c r="C63" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="C63" s="16" t="s">
+      <c r="D63" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D63" s="16">
+      <c r="E63" s="16">
         <v>15000</v>
       </c>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16">
+      <c r="F63" s="16"/>
+      <c r="G63" s="16">
         <v>22500</v>
       </c>
-      <c r="G63" s="16" t="s">
+      <c r="H63" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H63" s="17" t="s">
+      <c r="I63" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="I63" s="18" t="s">
+      <c r="J63" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="J63" s="19" t="b">
-        <v>0</v>
-      </c>
       <c r="K63" s="19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="L63" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A64" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="B64" s="16"/>
+      <c r="C64" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="C64" s="16" t="s">
+      <c r="D64" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D64" s="16">
+      <c r="E64" s="16">
         <v>12000</v>
       </c>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16">
+      <c r="F64" s="16"/>
+      <c r="G64" s="16">
         <v>18000</v>
       </c>
-      <c r="G64" s="16" t="s">
+      <c r="H64" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H64" s="17" t="s">
+      <c r="I64" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="I64" s="18" t="s">
+      <c r="J64" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="J64" s="19" t="b">
-        <v>0</v>
-      </c>
       <c r="K64" s="19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="L64" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A65" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="B65" s="16"/>
+      <c r="C65" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="C65" s="16" t="s">
+      <c r="D65" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D65" s="16">
+      <c r="E65" s="16">
         <v>15000</v>
       </c>
-      <c r="E65" s="16"/>
-      <c r="F65" s="16">
+      <c r="F65" s="16"/>
+      <c r="G65" s="16">
         <v>19000</v>
       </c>
-      <c r="G65" s="16" t="s">
+      <c r="H65" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H65" s="17" t="s">
+      <c r="I65" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="I65" s="18" t="s">
+      <c r="J65" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="J65" s="19" t="b">
-        <v>0</v>
-      </c>
       <c r="K65" s="19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="L65" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A66" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="B66" s="16" t="s">
+      <c r="B66" s="16"/>
+      <c r="C66" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="C66" s="16" t="s">
+      <c r="D66" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D66" s="16">
+      <c r="E66" s="16">
         <v>22000</v>
       </c>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16">
+      <c r="F66" s="16"/>
+      <c r="G66" s="16">
         <v>34500</v>
       </c>
-      <c r="G66" s="16" t="s">
+      <c r="H66" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H66" s="17" t="s">
+      <c r="I66" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="I66" s="18" t="s">
+      <c r="J66" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="J66" s="19" t="b">
-        <v>0</v>
-      </c>
       <c r="K66" s="19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="L66" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A67" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="B67" s="16" t="s">
+      <c r="B67" s="16"/>
+      <c r="C67" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="C67" s="16" t="s">
+      <c r="D67" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D67" s="16">
+      <c r="E67" s="16">
         <v>12000</v>
       </c>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16">
+      <c r="F67" s="16"/>
+      <c r="G67" s="16">
         <v>15000</v>
       </c>
-      <c r="G67" s="16" t="s">
+      <c r="H67" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H67" s="17" t="s">
+      <c r="I67" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="I67" s="18" t="s">
+      <c r="J67" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="J67" s="19" t="b">
-        <v>0</v>
-      </c>
       <c r="K67" s="19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="L67" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A68" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="B68" s="16"/>
+      <c r="C68" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="C68" s="16" t="s">
+      <c r="D68" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D68" s="16">
+      <c r="E68" s="16">
         <v>29000</v>
       </c>
-      <c r="E68" s="16"/>
-      <c r="F68" s="16">
+      <c r="F68" s="16"/>
+      <c r="G68" s="16">
         <v>43500</v>
       </c>
-      <c r="G68" s="16" t="s">
+      <c r="H68" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H68" s="17" t="s">
+      <c r="I68" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="I68" s="18" t="s">
+      <c r="J68" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="J68" s="19" t="b">
-        <v>0</v>
-      </c>
       <c r="K68" s="19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" ht="406" x14ac:dyDescent="0.35">
+      <c r="L68" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="406" x14ac:dyDescent="0.35">
       <c r="A69" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="B69" s="16" t="s">
+      <c r="B69" s="16"/>
+      <c r="C69" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="C69" s="16" t="s">
+      <c r="D69" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D69" s="16">
+      <c r="E69" s="16">
         <v>18000</v>
       </c>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16">
+      <c r="F69" s="16"/>
+      <c r="G69" s="16">
         <v>27000</v>
       </c>
-      <c r="G69" s="16" t="s">
+      <c r="H69" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H69" s="17" t="s">
+      <c r="I69" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="I69" s="18" t="s">
+      <c r="J69" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="J69" s="19" t="b">
-        <v>0</v>
-      </c>
       <c r="K69" s="19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="L69" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A70" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="B70" s="16" t="s">
+      <c r="B70" s="16"/>
+      <c r="C70" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="16" t="s">
+      <c r="D70" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D70" s="16">
+      <c r="E70" s="16">
         <v>20000</v>
       </c>
-      <c r="E70" s="16"/>
-      <c r="F70" s="16">
+      <c r="F70" s="16"/>
+      <c r="G70" s="16">
         <v>30000</v>
       </c>
-      <c r="G70" s="16" t="s">
+      <c r="H70" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H70" s="16" t="s">
+      <c r="I70" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="I70" s="17" t="s">
+      <c r="J70" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="J70" s="19" t="b">
-        <v>0</v>
-      </c>
       <c r="K70" s="19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="L70" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A71" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="B71" s="16" t="s">
+      <c r="B71" s="16"/>
+      <c r="C71" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="C71" s="16" t="s">
+      <c r="D71" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D71" s="16">
+      <c r="E71" s="16">
         <v>13000</v>
       </c>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16">
+      <c r="F71" s="16"/>
+      <c r="G71" s="16">
         <v>19500</v>
       </c>
-      <c r="G71" s="16" t="s">
+      <c r="H71" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H71" s="17" t="s">
+      <c r="I71" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="I71" s="18" t="s">
+      <c r="J71" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="J71" s="19" t="b">
-        <v>0</v>
-      </c>
       <c r="K71" s="19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="L71" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A72" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="B72" s="16" t="s">
+      <c r="B72" s="16"/>
+      <c r="C72" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="C72" s="16" t="s">
+      <c r="D72" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D72" s="16">
+      <c r="E72" s="16">
         <v>8000</v>
       </c>
-      <c r="E72" s="16"/>
-      <c r="F72" s="16">
+      <c r="F72" s="16"/>
+      <c r="G72" s="16">
         <v>11000</v>
       </c>
-      <c r="G72" s="16" t="s">
+      <c r="H72" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H72" s="17" t="s">
+      <c r="I72" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="I72" s="18" t="s">
+      <c r="J72" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="J72" s="19" t="b">
-        <v>0</v>
-      </c>
       <c r="K72" s="19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="L72" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A73" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="B73" s="16" t="s">
+      <c r="B73" s="16"/>
+      <c r="C73" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="C73" s="16" t="s">
+      <c r="D73" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D73" s="16">
+      <c r="E73" s="16">
         <v>9000</v>
       </c>
-      <c r="E73" s="16"/>
-      <c r="F73" s="16">
+      <c r="F73" s="16"/>
+      <c r="G73" s="16">
         <v>9000</v>
       </c>
-      <c r="G73" s="16" t="s">
+      <c r="H73" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H73" s="17" t="s">
+      <c r="I73" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="I73" s="18" t="s">
+      <c r="J73" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="J73" s="19" t="b">
-        <v>0</v>
-      </c>
       <c r="K73" s="19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="L73" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A74" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="B74" s="16" t="s">
+      <c r="B74" s="16"/>
+      <c r="C74" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="C74" s="16" t="s">
+      <c r="D74" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D74" s="16">
+      <c r="E74" s="16">
         <v>17000</v>
       </c>
-      <c r="E74" s="16"/>
-      <c r="F74" s="16">
+      <c r="F74" s="16"/>
+      <c r="G74" s="16">
         <v>34000</v>
       </c>
-      <c r="G74" s="16" t="s">
+      <c r="H74" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="H74" s="16" t="s">
+      <c r="I74" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="I74" s="18" t="s">
+      <c r="J74" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="J74" s="19" t="b">
-        <v>0</v>
-      </c>
       <c r="K74" s="19" t="b">
         <v>0</v>
       </c>
+      <c r="L74" s="19" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K71" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}"/>
+  <autoFilter ref="A1:L71" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0526577688ca4eec/Escritorio/Proyectos developer/Diseños_Gasper/Back-end/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="632" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABD973EF-F20D-47B4-BAB1-C1E9DB290B63}"/>
+  <xr:revisionPtr revIDLastSave="684" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2F653BC-69AE-426E-90DC-F6A4E30EF892}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="257">
   <si>
     <t>name</t>
   </si>
@@ -1694,37 +1694,84 @@
     <t>publicidad</t>
   </si>
   <si>
+    <t>green,white,red,gray</t>
+  </si>
+  <si>
+    <t>*Consultar</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>Chaqueta rompevientos semireflectiva con colores laterales y material reflectivo</t>
+  </si>
+  <si>
+    <t>Maya lateral de diferentes colores y material reflectivo</t>
+  </si>
+  <si>
+    <t>Chaqueta rompevientos semireflectiva con color tipo triangulo y material reflectivo</t>
+  </si>
+  <si>
+    <t>Enterizo Karina</t>
+  </si>
+  <si>
+    <t>black</t>
+  </si>
+  <si>
+    <t>{
+  "black": [
+  "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488365/simzx5yophjj5bzlt38h.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488365/sttnowhg0zuzwcbmwbcv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488365/lohxko8kkxiee7vsdnnv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488365/jeumh9wadcod22wezj7d.png"
+  ]}</t>
+  </si>
+  <si>
+    <t>Enterizo Cruzado Espalda</t>
+  </si>
+  <si>
+    <t>black,blue,gray,green,darkblue,hotpink,steelblue,white,red</t>
+  </si>
+  <si>
+    <t>{
+  "black": [
+  "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488766/apmmsg14df0qqitgfbyg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488768/ruyj7szm3l5zda8pizyi.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488767/fnkstkajn7yynmraijyv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488766/yyjs5sws4apvnq2jhzsh.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488770/udgrhjmakmo4hljixja3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488770/lolgdf4sors13wje1ve1.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488774/jpw0t4re3quqerugt7qe.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488772/nioqupqnhwgtlv6vmq3h.png"
+    ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488778/rfmecuoa39dds3x5fwqw.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488775/ykjjgszbxe44uygenk0v.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488779/jtgsnpgf8izc1bqppzvk.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488778/qlzlgtfjvm9vyhqpapyh.png"
+   ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488784/b3qvdrnrbzykbq36dgez.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488783/lyhzjkbx7rsarpkgjzos.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488789/zklx3njnqbesbrjqvlai.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488784/vwihwfa48w53cl2rqz6s.png"
+    ], "darkblue": ["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488789/ojpyflc9ntnybgokxc2a.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488790/eo7davsllqb8mu4sdwzy.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488790/b6reb7jkkovtiixx3pof.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488916/ijyb77fwtreuq46gkkjv.png"], "hotpink": ["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488916/jb3h7kidcn542pww1u9c.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488917/zyqtzcos0cjjz7btea4y.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488921/bxipc0oih4gnzdbpmhjj.png"], "steelblue": ["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488917/aj9musqfkp7i9ltknmkk.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488922/qzpbohd30ajclgrusomx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488924/gibfvvawnpbcchshhnqy.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488926/afmyyt8s5gupp4pu1cdp.png"], "white": ["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488925/q8aapomyacgvblbufuxf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488928/gvwrkleilzae36myixuk.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488930/fecvn2etsv9qskb7yzq0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488929/ikg7fxkho9a7ergns8ah.png"], "red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488934/enmkz396r5axth3unw87.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488933/zwmtel4kdajg5rme2qqx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488938/dhl5z4kixf8oci0qoqqo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488934/gdieezr6h4tuk6jumcbi.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488938/edpdzvmgymln8jvchioz.png"] }</t>
+  </si>
+  <si>
+    <t>Enterizo Manga Larga</t>
+  </si>
+  <si>
+    <t>white,black</t>
+  </si>
+  <si>
+    <t>{
+  "white": [
+  "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488994/w7ysb9ust7edzqm4vjh4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488995/eclb86z4n4xscrvpyj0y.png"], "black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488998/vxu8x6ri3veykfp6tf0x.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488997/mpnrqzrzjthuvvn1kvly.png"]}</t>
+  </si>
+  <si>
     <t>{
   "green": [
-  "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774395922/zebgi2cvqlhgxaav0zmi.jpg", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774395923/rqp9dj0761msqqaekqyz.png"
+  "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488505/vevqjxm3okxbrcvky5bp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488504/lniljfi7wj22xuv9htog.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488506/zhjadjoytjpxv1q2amxj.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488504/pfxgwmtfrmcygsal4kct.png"
   ],
   "white": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774395922/sbkh9hf1obzqjtbxxwh1.jpg", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774395922/gcffbqz9psi69c6brfsb.jpg"
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488507/rpxdhrt2eroal8geqf22.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488508/kprxk4he3v3br81pgfw0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488509/ixccmctwit5qbxuvnyku.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488510/ijuylk1ln2mu9bcze5bi.png"
     ],
   "red": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774395922/bsh7ab1mqmmiooyzxoyl.jpg", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774395923/uxfvmse8dalcupvoblws.png"
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488512/amixdcgn7jd12pdnpnoq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488511/fxlisnnunattjkity87v.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774488513/nzcujy59hqzick5ahobo.png"
    ],
   "gray": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774396861/p0ek3kuirzlgcrstgddr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774396861/xrxzbn70xvrj8mpntflf.png"
     ]}</t>
   </si>
   <si>
-    <t>green,white,red,gray</t>
-  </si>
-  <si>
-    <t>*Consultar</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>Chaqueta rompevientos semireflectiva con colores laterales y material reflectivo</t>
-  </si>
-  <si>
-    <t>Maya lateral de diferentes colores y material reflectivo</t>
-  </si>
-  <si>
-    <t>Chaqueta rompevientos semireflectiva con color tipo triangulo y material reflectivo</t>
+    <t>Creamos chaquetas personalizadas para tu negocio, adaptadas a tu estilo, marca y necesidades. Si deseas realizar un pedido, dirígete a la sección ‘Contacto’ al final de la página y completa el formulario para recibir más información.</t>
   </si>
 </sst>
 </file>
@@ -2175,7 +2222,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}">
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="57.54296875" style="2" customWidth="1"/>
@@ -2196,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>1</v>
@@ -2234,7 +2281,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>161</v>
@@ -2272,7 +2319,7 @@
         <v>177</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>161</v>
@@ -2308,7 +2355,7 @@
         <v>176</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>161</v>
@@ -2346,7 +2393,7 @@
         <v>19</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>161</v>
@@ -4719,11 +4766,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:12" ht="319" x14ac:dyDescent="0.35">
       <c r="A74" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="B74" s="16"/>
+      <c r="B74" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="C74" s="16" t="s">
         <v>239</v>
       </c>
@@ -4738,18 +4787,120 @@
         <v>34000</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I74" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J74" s="18" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="K74" s="19" t="b">
         <v>0</v>
       </c>
       <c r="L74" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A75" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="B75" s="16"/>
+      <c r="C75" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="D75" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E75" s="16">
+        <v>28000</v>
+      </c>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16">
+        <v>42000</v>
+      </c>
+      <c r="H75" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I75" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="J75" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="K75" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A76" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="B76" s="16"/>
+      <c r="C76" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="D76" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E76" s="16">
+        <v>23000</v>
+      </c>
+      <c r="F76" s="16"/>
+      <c r="G76" s="16">
+        <v>34500</v>
+      </c>
+      <c r="H76" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I76" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="J76" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="K76" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="87" x14ac:dyDescent="0.35">
+      <c r="A77" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="B77" s="16"/>
+      <c r="C77" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="D77" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E77" s="16">
+        <v>28000</v>
+      </c>
+      <c r="F77" s="16"/>
+      <c r="G77" s="16">
+        <v>35000</v>
+      </c>
+      <c r="H77" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I77" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="J77" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="K77" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L77" s="19" t="b">
         <v>0</v>
       </c>
     </row>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0526577688ca4eec/Escritorio/Proyectos developer/Diseños_Gasper/Back-end/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="684" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2F653BC-69AE-426E-90DC-F6A4E30EF892}"/>
+  <xr:revisionPtr revIDLastSave="691" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA653A74-019D-4A7D-B15C-A0D3D58A0D3C}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="258">
   <si>
     <t>name</t>
   </si>
@@ -233,12 +233,6 @@
   </si>
   <si>
     <t>Chaqueta Robótica con forro Interno</t>
-  </si>
-  <si>
-    <t>blue,red,black, darkred</t>
-  </si>
-  <si>
-    <t>{ "blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253382/k5shc79l7qjtrz6ci2u8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253382/g6vshxggogiqr9sohubg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253382/i1rxwb30h6txzqwls9a9.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/bnlvhnp5unrky6m3hrq9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253384/nibqhcfcluku6e2sjuf3.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253384/fa3gtcxcbbujpmz1q32y.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/gt8labiuzvzqteqiuki9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/pllztvi8ue5dtb9xd26j.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/dxofsgljvhppxhvxcf9q.png"],"darkred":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/uqqd6kygifncoygwvzfk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253382/kiy5vdzzlhglrhntyfpf.png"]}</t>
   </si>
   <si>
     <t>red,blue</t>
@@ -1772,6 +1766,28 @@
   </si>
   <si>
     <t>Creamos chaquetas personalizadas para tu negocio, adaptadas a tu estilo, marca y necesidades. Si deseas realizar un pedido, dirígete a la sección ‘Contacto’ al final de la página y completa el formulario para recibir más información.</t>
+  </si>
+  <si>
+    <t>blue,red,black, darkred, royalblue</t>
+  </si>
+  <si>
+    <t>{ "blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253382/k5shc79l7qjtrz6ci2u8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662299/g4llyutemrjvlpsyhbjl.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662300/qtwerqw10yv6wxqpb1cl.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662299/scdqmabiuqxkreow7u6c.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662302/wghzvjuaajuwpbfddzvk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253384/fa3gtcxcbbujpmz1q32y.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662299/ys0v7pwpkcommwyjadtf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662310/tbrnns244roeseqtkxrr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/dxofsgljvhppxhvxcf9q.png"],"darkred":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/uqqd6kygifncoygwvzfk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253382/kiy5vdzzlhglrhntyfpf.png"], "royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662300/t7f9xsg5ij4gmjrmoyso.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662304/k5128obkwuopjaualtol.png"]}</t>
+  </si>
+  <si>
+    <r>
+      <t>{"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242437/dmbpdy0o8zo774yg0esp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242493/phwa4ghsnghxaad8rs0s.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242496/z0ckuych5747dbdjbblh.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242497/mllydvsxp8bsmjxtudpf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242438/gbxh6ouluwykgpjacnn5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242440/jbincqszbskytgzid1xr.png"],"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242442/rjagdaxpyr2ekyatvpnc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242443/omnxdetafnsovhyqsrrk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242445/tfuorgusbozzg5qangpa.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242446/vrqh5h2ds6suivfhxsg9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242448/arvjdgaypjnno56lfvbk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242450/yzbjosqrehdwxvwhcyfo.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242452/mzxqsxz8cz3pfkwggyzv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242454/xburffuwfdwwt6917fav.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242455/qgkevnsapc7o43ad0bq7.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774664553/ckjrrp0qrdw6vn6yqjmf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774664554/neg0acxwxh0mhhfynsh6.png</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242498/c9jctj0oy5awxkw7qhps.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242456/lqgzodgnyvwdgdski6al.png"],"deepink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242501/dzn9seysibv5yjlylqkz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242464/lxs8m7ci4bwqqyfbrjz5.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242485/t4lvqrs96uqcbrzscv68.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242488/c7sam295q1wiuiiakyt7.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242489/n1csydhjwtdmhlpf30te.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242479/ony3dvs6kvxistz3fxic.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242481/mmu22qpkw9rz2ecm79rk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242484/afwxcc8qacktmzbo5pcn.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242473/h5jrcvlasfsfetqinrzi.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242473/dfhfnav2renc5azvzicn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242474/dcsjwceh9gzre70xl9n7.png"],"aqua":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242466/wxbkzpewkatvhqphl8vc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242469/zlrfrhmdw24co5sql2xg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242469/oxccamqqxqe81hbdryqd.png"]}</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2243,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>1</v>
@@ -2281,10 +2297,10 @@
         <v>16</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>11</v>
@@ -2302,10 +2318,10 @@
         <v>17</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>70</v>
+        <v>255</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>71</v>
+        <v>256</v>
       </c>
       <c r="K2" s="6" t="b">
         <v>0</v>
@@ -2314,15 +2330,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" s="3" customFormat="1" ht="86.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>11</v>
@@ -2338,10 +2354,10 @@
         <v>14</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K3" s="6" t="b">
         <v>0</v>
@@ -2352,13 +2368,13 @@
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="89.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>11</v>
@@ -2376,10 +2392,10 @@
         <v>17</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K4" s="6" t="b">
         <v>0</v>
@@ -2393,10 +2409,10 @@
         <v>19</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>20</v>
@@ -2414,10 +2430,10 @@
         <v>17</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K5" s="6" t="b">
         <v>0</v>
@@ -2432,7 +2448,7 @@
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>11</v>
@@ -2448,10 +2464,10 @@
         <v>14</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K6" s="6" t="b">
         <v>0</v>
@@ -2466,7 +2482,7 @@
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>11</v>
@@ -2482,10 +2498,10 @@
         <v>12</v>
       </c>
       <c r="I7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>78</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>80</v>
       </c>
       <c r="K7" s="6" t="b">
         <v>0</v>
@@ -2500,7 +2516,7 @@
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>11</v>
@@ -2518,10 +2534,10 @@
         <v>13</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K8" s="6" t="b">
         <v>0</v>
@@ -2532,11 +2548,11 @@
     </row>
     <row r="9" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>11</v>
@@ -2554,10 +2570,10 @@
         <v>13</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K9" s="6" t="b">
         <v>0</v>
@@ -2572,7 +2588,7 @@
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>11</v>
@@ -2588,10 +2604,10 @@
         <v>14</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K10" s="6" t="b">
         <v>0</v>
@@ -2602,11 +2618,11 @@
     </row>
     <row r="11" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>11</v>
@@ -2622,10 +2638,10 @@
         <v>14</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K11" s="6" t="b">
         <v>0</v>
@@ -2636,11 +2652,11 @@
     </row>
     <row r="12" spans="1:12" ht="47" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>11</v>
@@ -2656,10 +2672,10 @@
         <v>14</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K12" s="6" t="b">
         <v>0</v>
@@ -2670,11 +2686,11 @@
     </row>
     <row r="13" spans="1:12" ht="47" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>11</v>
@@ -2690,10 +2706,10 @@
         <v>14</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>140</v>
+        <v>257</v>
       </c>
       <c r="K13" s="6" t="b">
         <v>0</v>
@@ -2704,11 +2720,11 @@
     </row>
     <row r="14" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>27</v>
@@ -2726,10 +2742,10 @@
         <v>26</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K14" s="6" t="b">
         <v>0</v>
@@ -2740,11 +2756,11 @@
     </row>
     <row r="15" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>27</v>
@@ -2762,10 +2778,10 @@
         <v>26</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K15" s="6" t="b">
         <v>0</v>
@@ -2776,11 +2792,11 @@
     </row>
     <row r="16" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>11</v>
@@ -2798,10 +2814,10 @@
         <v>26</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K16" s="6" t="b">
         <v>0</v>
@@ -2812,11 +2828,11 @@
     </row>
     <row r="17" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>11</v>
@@ -2834,10 +2850,10 @@
         <v>26</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K17" s="6" t="b">
         <v>0</v>
@@ -2852,7 +2868,7 @@
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>30</v>
@@ -2868,10 +2884,10 @@
         <v>28</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K18" s="6" t="b">
         <v>0</v>
@@ -2882,7 +2898,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6" t="s">
@@ -2902,10 +2918,10 @@
         <v>28</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K19" s="6" t="b">
         <v>0</v>
@@ -2916,11 +2932,11 @@
     </row>
     <row r="20" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>11</v>
@@ -2936,10 +2952,10 @@
         <v>14</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K20" s="6" t="b">
         <v>0</v>
@@ -2954,7 +2970,7 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>11</v>
@@ -2970,10 +2986,10 @@
         <v>14</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K21" s="6" t="b">
         <v>0</v>
@@ -2988,7 +3004,7 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>11</v>
@@ -3004,10 +3020,10 @@
         <v>32</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K22" s="6" t="b">
         <v>0</v>
@@ -3022,7 +3038,7 @@
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>11</v>
@@ -3038,10 +3054,10 @@
         <v>14</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K23" s="6" t="b">
         <v>0</v>
@@ -3056,7 +3072,7 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>11</v>
@@ -3072,10 +3088,10 @@
         <v>14</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K24" s="6" t="b">
         <v>0</v>
@@ -3090,7 +3106,7 @@
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>11</v>
@@ -3106,10 +3122,10 @@
         <v>14</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K25" s="6" t="b">
         <v>0</v>
@@ -3120,7 +3136,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
@@ -3140,10 +3156,10 @@
         <v>14</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K26" s="6" t="b">
         <v>0</v>
@@ -3158,7 +3174,7 @@
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>11</v>
@@ -3174,10 +3190,10 @@
         <v>14</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K27" s="6" t="b">
         <v>0</v>
@@ -3192,7 +3208,7 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>11</v>
@@ -3208,10 +3224,10 @@
         <v>14</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K28" s="6" t="b">
         <v>0</v>
@@ -3222,7 +3238,7 @@
     </row>
     <row r="29" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
@@ -3242,10 +3258,10 @@
         <v>41</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K29" s="6" t="b">
         <v>0</v>
@@ -3256,7 +3272,7 @@
     </row>
     <row r="30" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6" t="s">
@@ -3276,10 +3292,10 @@
         <v>41</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K30" s="6" t="b">
         <v>0</v>
@@ -3312,10 +3328,10 @@
         <v>44</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K31" s="6" t="b">
         <v>0</v>
@@ -3348,10 +3364,10 @@
         <v>45</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K32" s="6" t="b">
         <v>0</v>
@@ -3382,10 +3398,10 @@
         <v>14</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K33" s="6" t="b">
         <v>0</v>
@@ -3416,10 +3432,10 @@
         <v>14</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K34" s="6" t="b">
         <v>0</v>
@@ -3430,7 +3446,7 @@
     </row>
     <row r="35" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6" t="s">
@@ -3443,7 +3459,7 @@
         <v>17000</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G35" s="6">
         <v>34000</v>
@@ -3452,10 +3468,10 @@
         <v>41</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K35" s="6" t="b">
         <v>0</v>
@@ -3466,7 +3482,7 @@
     </row>
     <row r="36" spans="1:12" ht="126.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6" t="s">
@@ -3479,7 +3495,7 @@
         <v>17000</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G36" s="6">
         <v>34000</v>
@@ -3488,10 +3504,10 @@
         <v>41</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K36" s="6" t="b">
         <v>0</v>
@@ -3502,7 +3518,7 @@
     </row>
     <row r="37" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6" t="s">
@@ -3515,7 +3531,7 @@
         <v>17000</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G37" s="6">
         <v>34000</v>
@@ -3524,10 +3540,10 @@
         <v>41</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="K37" s="6" t="b">
         <v>0</v>
@@ -3538,7 +3554,7 @@
     </row>
     <row r="38" spans="1:12" ht="91" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6" t="s">
@@ -3551,7 +3567,7 @@
         <v>17000</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G38" s="6">
         <v>34000</v>
@@ -3560,10 +3576,10 @@
         <v>41</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K38" s="6" t="b">
         <v>0</v>
@@ -3574,7 +3590,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
@@ -3594,10 +3610,10 @@
         <v>52</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K39" s="6" t="b">
         <v>0</v>
@@ -3628,10 +3644,10 @@
         <v>52</v>
       </c>
       <c r="I40" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="J40" s="13" t="s">
         <v>112</v>
-      </c>
-      <c r="J40" s="13" t="s">
-        <v>114</v>
       </c>
       <c r="K40" s="6" t="b">
         <v>0</v>
@@ -3662,10 +3678,10 @@
         <v>14</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J41" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K41" s="6" t="b">
         <v>0</v>
@@ -3676,7 +3692,7 @@
     </row>
     <row r="42" spans="1:12" ht="98.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
@@ -3696,10 +3712,10 @@
         <v>45</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J42" s="15" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K42" s="6" t="b">
         <v>0</v>
@@ -3730,10 +3746,10 @@
         <v>45</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="K43" s="6" t="b">
         <v>0</v>
@@ -3764,10 +3780,10 @@
         <v>14</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="K44" s="6" t="b">
         <v>0</v>
@@ -3800,10 +3816,10 @@
         <v>56</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K45" s="6" t="b">
         <v>0</v>
@@ -3834,10 +3850,10 @@
         <v>59</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K46" s="6" t="b">
         <v>0</v>
@@ -3868,10 +3884,10 @@
         <v>13</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K47" s="6" t="b">
         <v>0</v>
@@ -3882,7 +3898,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6" t="s">
@@ -3902,10 +3918,10 @@
         <v>61</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K48" s="6" t="b">
         <v>0</v>
@@ -3936,10 +3952,10 @@
         <v>12</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K49" s="6" t="b">
         <v>0</v>
@@ -3954,7 +3970,7 @@
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>11</v>
@@ -3970,10 +3986,10 @@
         <v>12</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K50" s="6" t="b">
         <v>0</v>
@@ -4004,10 +4020,10 @@
         <v>12</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J51" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K51" s="6" t="b">
         <v>0</v>
@@ -4038,10 +4054,10 @@
         <v>14</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J52" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K52" s="6" t="b">
         <v>0</v>
@@ -4056,7 +4072,7 @@
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>11</v>
@@ -4072,10 +4088,10 @@
         <v>14</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K53" s="6" t="b">
         <v>0</v>
@@ -4090,7 +4106,7 @@
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>11</v>
@@ -4106,10 +4122,10 @@
         <v>14</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K54" s="6" t="b">
         <v>0</v>
@@ -4124,7 +4140,7 @@
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>11</v>
@@ -4140,10 +4156,10 @@
         <v>14</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K55" s="6" t="b">
         <v>0</v>
@@ -4158,7 +4174,7 @@
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>11</v>
@@ -4174,10 +4190,10 @@
         <v>32</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K56" s="6" t="b">
         <v>0</v>
@@ -4188,11 +4204,11 @@
     </row>
     <row r="57" spans="1:12" ht="377" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>11</v>
@@ -4201,7 +4217,7 @@
         <v>22000</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G57" s="6">
         <v>27000</v>
@@ -4210,10 +4226,10 @@
         <v>17</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K57" s="6" t="b">
         <v>0</v>
@@ -4224,11 +4240,11 @@
     </row>
     <row r="58" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A58" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B58" s="16"/>
       <c r="C58" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D58" s="16" t="s">
         <v>27</v>
@@ -4244,10 +4260,10 @@
         <v>14</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J58" s="18" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K58" s="19" t="b">
         <v>0</v>
@@ -4258,11 +4274,11 @@
     </row>
     <row r="59" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A59" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B59" s="16"/>
       <c r="C59" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D59" s="16" t="s">
         <v>20</v>
@@ -4278,10 +4294,10 @@
         <v>14</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J59" s="18" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K59" s="19" t="b">
         <v>0</v>
@@ -4292,11 +4308,11 @@
     </row>
     <row r="60" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A60" s="16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B60" s="16"/>
       <c r="C60" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D60" s="16" t="s">
         <v>20</v>
@@ -4312,10 +4328,10 @@
         <v>14</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J60" s="18" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K60" s="19" t="b">
         <v>0</v>
@@ -4326,11 +4342,11 @@
     </row>
     <row r="61" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A61" s="16" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B61" s="16"/>
       <c r="C61" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D61" s="16" t="s">
         <v>20</v>
@@ -4346,10 +4362,10 @@
         <v>14</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J61" s="18" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K61" s="19" t="b">
         <v>0</v>
@@ -4360,11 +4376,11 @@
     </row>
     <row r="62" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A62" s="16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B62" s="16"/>
       <c r="C62" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D62" s="16" t="s">
         <v>20</v>
@@ -4380,10 +4396,10 @@
         <v>14</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J62" s="18" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K62" s="19" t="b">
         <v>0</v>
@@ -4394,11 +4410,11 @@
     </row>
     <row r="63" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A63" s="16" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B63" s="16"/>
       <c r="C63" s="16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D63" s="16" t="s">
         <v>20</v>
@@ -4414,10 +4430,10 @@
         <v>14</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J63" s="18" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K63" s="19" t="b">
         <v>0</v>
@@ -4428,11 +4444,11 @@
     </row>
     <row r="64" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A64" s="16" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B64" s="16"/>
       <c r="C64" s="16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D64" s="16" t="s">
         <v>20</v>
@@ -4448,10 +4464,10 @@
         <v>14</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J64" s="18" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K64" s="19" t="b">
         <v>0</v>
@@ -4462,11 +4478,11 @@
     </row>
     <row r="65" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A65" s="16" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B65" s="16"/>
       <c r="C65" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D65" s="16" t="s">
         <v>20</v>
@@ -4482,10 +4498,10 @@
         <v>14</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J65" s="18" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K65" s="19" t="b">
         <v>0</v>
@@ -4496,11 +4512,11 @@
     </row>
     <row r="66" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A66" s="16" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B66" s="16"/>
       <c r="C66" s="16" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D66" s="16" t="s">
         <v>20</v>
@@ -4516,10 +4532,10 @@
         <v>14</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J66" s="18" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K66" s="19" t="b">
         <v>0</v>
@@ -4530,11 +4546,11 @@
     </row>
     <row r="67" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A67" s="16" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B67" s="16"/>
       <c r="C67" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D67" s="16" t="s">
         <v>20</v>
@@ -4550,10 +4566,10 @@
         <v>14</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J67" s="18" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K67" s="19" t="b">
         <v>0</v>
@@ -4564,11 +4580,11 @@
     </row>
     <row r="68" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A68" s="16" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B68" s="16"/>
       <c r="C68" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D68" s="16" t="s">
         <v>20</v>
@@ -4584,10 +4600,10 @@
         <v>14</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J68" s="18" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K68" s="19" t="b">
         <v>0</v>
@@ -4598,11 +4614,11 @@
     </row>
     <row r="69" spans="1:12" ht="406" x14ac:dyDescent="0.35">
       <c r="A69" s="16" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B69" s="16"/>
       <c r="C69" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D69" s="16" t="s">
         <v>20</v>
@@ -4618,10 +4634,10 @@
         <v>14</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J69" s="18" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K69" s="19" t="b">
         <v>0</v>
@@ -4632,7 +4648,7 @@
     </row>
     <row r="70" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A70" s="16" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B70" s="16"/>
       <c r="C70" s="16" t="s">
@@ -4652,10 +4668,10 @@
         <v>14</v>
       </c>
       <c r="I70" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K70" s="19" t="b">
         <v>0</v>
@@ -4666,11 +4682,11 @@
     </row>
     <row r="71" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A71" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B71" s="16"/>
       <c r="C71" s="16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D71" s="16" t="s">
         <v>20</v>
@@ -4686,10 +4702,10 @@
         <v>14</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J71" s="18" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K71" s="19" t="b">
         <v>0</v>
@@ -4700,11 +4716,11 @@
     </row>
     <row r="72" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A72" s="16" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B72" s="16"/>
       <c r="C72" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D72" s="16" t="s">
         <v>20</v>
@@ -4720,10 +4736,10 @@
         <v>14</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J72" s="18" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K72" s="19" t="b">
         <v>0</v>
@@ -4734,11 +4750,11 @@
     </row>
     <row r="73" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A73" s="16" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B73" s="16"/>
       <c r="C73" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D73" s="16" t="s">
         <v>20</v>
@@ -4754,10 +4770,10 @@
         <v>14</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J73" s="18" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K73" s="19" t="b">
         <v>0</v>
@@ -4768,13 +4784,13 @@
     </row>
     <row r="74" spans="1:12" ht="319" x14ac:dyDescent="0.35">
       <c r="A74" s="16" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D74" s="16" t="s">
         <v>11</v>
@@ -4787,13 +4803,13 @@
         <v>34000</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I74" s="16" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="J74" s="18" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K74" s="19" t="b">
         <v>0</v>
@@ -4804,11 +4820,11 @@
     </row>
     <row r="75" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A75" s="16" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B75" s="16"/>
       <c r="C75" s="16" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D75" s="16" t="s">
         <v>20</v>
@@ -4824,10 +4840,10 @@
         <v>14</v>
       </c>
       <c r="I75" s="16" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J75" s="18" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="K75" s="19" t="b">
         <v>0</v>
@@ -4838,11 +4854,11 @@
     </row>
     <row r="76" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A76" s="16" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B76" s="16"/>
       <c r="C76" s="16" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D76" s="16" t="s">
         <v>20</v>
@@ -4858,10 +4874,10 @@
         <v>14</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K76" s="19" t="b">
         <v>0</v>
@@ -4872,11 +4888,11 @@
     </row>
     <row r="77" spans="1:12" ht="87" x14ac:dyDescent="0.35">
       <c r="A77" s="16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B77" s="16"/>
       <c r="C77" s="16" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D77" s="16" t="s">
         <v>20</v>
@@ -4892,10 +4908,10 @@
         <v>14</v>
       </c>
       <c r="I77" s="16" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J77" s="18" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K77" s="19" t="b">
         <v>0</v>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0526577688ca4eec/Escritorio/Proyectos developer/Diseños_Gasper/Back-end/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="691" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA653A74-019D-4A7D-B15C-A0D3D58A0D3C}"/>
+  <xr:revisionPtr revIDLastSave="851" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B09FC64-0D1D-4C56-8422-2F2F565BFC65}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="productos" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">productos!$A$1:$L$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">productos!$A$1:$L$80</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="292">
   <si>
     <t>name</t>
   </si>
@@ -413,9 +413,6 @@
   </si>
   <si>
     <t>{"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205963/iqugy93ruijx2qs6albr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205963/q6ouylsvbgqejbwf7ylc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205962/kwzacjzqbafzsjs5fixy.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072968/riy6rimanvqxwxzlay7x.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072970/dsfskf4hd98akspwscqp.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072961/bkqyk3gc00ddzqxykogc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072962/nowuvxkhdkur9vgrobql.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072962/lhnh9ojgrwatsvbsdzeg.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072966/ghqmghlhv83i5vvcas7y.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072968/xcsewhi1ixqg5zsl7ooo.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072964/nbkvbujd0eextzgqc2qu.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072965/pn8avdaq3ufr5vtacwpb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072966/ditkur6no6op4lvydks4.png"]}</t>
-  </si>
-  <si>
-    <t>white,lime,gray,olive,green,black</t>
   </si>
   <si>
     <t>lime,blue,green,red,darkblue,orange,turquoise,gray,darkgreen,skyblue,peru</t>
@@ -508,9 +505,6 @@
   </si>
   <si>
     <t>{"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204338/oejbgfjjrnas7l9peyx2.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204336/k7scng21l4yann7xww1g.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204337/p7rhhrzowr2rwabaf4wq.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204340/kjystwsspe4qlwkpttbx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204343/x0wczvaf4thuo262zk1a.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204342/k6n6vrz51vbfxkp37vxw.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204332/klqdeyjspxstecn1fqng.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204334/pmpnlaeem4it8y8tnxn1.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204335/e8dw9g0qre5ydzlqlatf.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204328/bvt7ueaexvkdythpanwn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204329/aofbo59s1uffco8i2wpi.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204330/b8n7glynvblcahn4kh05.png"],"pink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204325/tjdsejcvcgfgkfquxzjn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204326/mwrayyzb1rfuvdycyddq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204327/hn8p4ckn1sozzowpziib.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204322/b16ab0jfz0etyo8jshsw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204321/ooznuwz1cpqaqu5ownul.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204323/q61r8koxk0fhvecqkrfz.png"],"darkblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204319/fkqlvntrdaq8jt793uhj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204319/a5ep6vrxclrxq3b0h6lk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204320/vckmbagb1qiehbka8qce.png"],"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204344/io3zcwbwx9oayypdxmuc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204346/shnjivk8vn0zompx1d0k.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204347/uf0mrbixslbi3i4p13qk.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204350/nhoe6gys7x7a9tr92gcv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204351/kmf8fquhpmgnpaudotr8.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204351/tvy8pbmxrxbyttnzajdn.png"],"lawngreen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204355/nmvtfz8xc6seaah6thgh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204357/wmeg6mwijy05p1hpu3kh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204358/g5nsawbiilegcqjkcsuk.png"],"mediumblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204361/y8ykrtunchadolpwmw7a.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204363/toeoq0ot4by8nx7y6dfw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204366/iy9zgfv11qm7vwguueo3.png"],"skyblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204367/b4delwnliq7h2nijhugw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204368/rxy7ecs4vyuxbllduanx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204370/bvmqdttjroiogb5zsevr.png"]}</t>
-  </si>
-  <si>
-    <t>{"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242668/fmmqv9d3abczghkogp1p.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242712/aushzmuk00uao21tcsfe.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242720/aqutgbwf8fhr0ay0et9x.png"],"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242705/gbq3blhqjey9pfsrccot.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242707/licsjuezzfbcaastvwty.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242702/y2vqiplb42ugvde6pibd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242703/xmpeiwyzm5pykzpaouuh.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242700/kbdbl8y32oyxpwtho1sg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242698/vfmx6wm7pgfdxausx0qh.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242675/vbr5qoanu6pzhtwareey.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242697/jxucutam0nuykc3cbptz.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242670/vn5zjnwmtj1ubnosan6g.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242672/ladrzy2w92giulcorc0d.png"]}</t>
   </si>
   <si>
     <t>{"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205288/smm8fjw9rl4bnfqartjf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205287/xibsxjngkirncuy1yzho.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205357/io2ygjdephs2ufzv133d.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205290/r3hm9neakhl3lxyiseju.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205292/jasnol7orezj790psdxv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205294/tp3zzxyom7kg9g40bnug.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205296/lbmq4786zitdm7sqf2gh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205300/szighhczcmlvktpwcu0c.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205301/zc9grwxp77zytgruhujb.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205305/ip9ubuw7yzb1loywx9hp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205303/srdszj6njhkynu6hedrq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205303/srdszj6njhkynu6hedrq.png"],"darkblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205310/in2uykc5yibqy3ii59yd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205312/auuktvqrfwlpu4yf5zxq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205314/p8f8kh4dqcbkefuzbxv1.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205317/masdfk78uq1h1ocqnxon.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205320/ib4jb51wjac4tnbizgel.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205321/bjwnz5zmham8542llwvl.png"],"turquoise":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205323/ghweohyghfzxnp3autyo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205326/ztc53cu857yxbfpqp193.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205328/ay9h3tyk1kikgchkgh1r.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205329/hgsinisspnemzvna56cg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205332/u7f9tauhwezirlpxvghh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205335/ryi88h3pmqpwnjvruazi.png"],"darkgreen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205339/eezvjpd0anxakn1d1eir.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205366/afcwdckametvhcm2vdnk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205339/sj4x0jejmfcckjyjcgff.png"],"skyblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205340/ly5tvmjhv2exoglszokt.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205345/mbswblamqqdllr1hzulb.png"],"peru":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205349/ptzps64butp9eg2kdvn5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205354/spdvczuhihi0kmjzwygz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205353/uwy3dpacpekdc1mh1k76.png"]}</t>
@@ -1788,6 +1782,343 @@
       </rPr>
       <t>"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242498/c9jctj0oy5awxkw7qhps.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242456/lqgzodgnyvwdgdski6al.png"],"deepink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242501/dzn9seysibv5yjlylqkz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242464/lxs8m7ci4bwqqyfbrjz5.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242485/t4lvqrs96uqcbrzscv68.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242488/c7sam295q1wiuiiakyt7.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242489/n1csydhjwtdmhlpf30te.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242479/ony3dvs6kvxistz3fxic.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242481/mmu22qpkw9rz2ecm79rk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242484/afwxcc8qacktmzbo5pcn.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242473/h5jrcvlasfsfetqinrzi.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242473/dfhfnav2renc5azvzicn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242474/dcsjwceh9gzre70xl9n7.png"],"aqua":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242466/wxbkzpewkatvhqphl8vc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242469/zlrfrhmdw24co5sql2xg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242469/oxccamqqxqe81hbdryqd.png"]}</t>
     </r>
+  </si>
+  <si>
+    <t>Enterizo para Ciclismo</t>
+  </si>
+  <si>
+    <t>Enterizo para dama en licra power con badana importada.</t>
+  </si>
+  <si>
+    <t>black,blue,gray,green,darkblue,hotpink,steelblue,purple,skyblue,aqua,darkgreen,violet</t>
+  </si>
+  <si>
+    <t>Enterizo para dama en licra power con badana importada</t>
+  </si>
+  <si>
+    <t>{  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713897/rdzrfclycuoxgmyreeze.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713897/afomfdojro2mhwvypkgj.png"
+     ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713897/cugq2lvmwyz9bi7npxf3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713899/x63gl1wxbacukmeubgke.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713896/yflvlmlgpkmyzugmtpgj.png"
+   ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713897/qlczppqlobtbultcufsr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713897/rsdudxrmezxpk1axfrda.png"
+   ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713898/atoyj3guosnz0c3b6jq4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713898/movs1zimr7ycctqpawnw.png"
+    ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713898/hlkivss4lzb0cye2wwr9.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713902/uonr2ryfjyoogktkhi8a.png"
+  ],
+  "hotpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713901/kgk3aheja7hfgcjuui2m.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713903/h60xprkt2tcgermuh5wr.png"
+     ],
+  "steelblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713904/mk7ohtto0i0sics8huvs.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713906/gpab15hqatq2h0a91le2.png"
+   ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713905/ylz6a4rwejcndqcm3z8t.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713908/zcgkyg8jj0rkso0gn2de.png"     
+  ],
+  "skyblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713904/efqguvlqfzpyc5xcnvja.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713906/yz7gtw4ryqxmfb4kfxdq.png"
+      ],
+  "aqua": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713914/h9nlnpyuk1zfpzhwqj9l.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713906/wgdeevxdknw5mm6vr6so.png"   
+  ],
+  "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713914/hwv60nzmq0hajfc3qtv0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713916/sag26em2eadwa00wkdaj.png"
+  ],
+  "violet": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713915/qxqdb2gk2mrqbmqgcudb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713916/kgchxcjilzfj5smw6wtl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713915/djfglisdjgkhkdvwvbex.png"  
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713897/cugq2lvmwyz9bi7npxf3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713899/x63gl1wxbacukmeubgke.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713896/yflvlmlgpkmyzugmtpgj.png"
+   ],   "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713897/rdzrfclycuoxgmyreeze.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713897/afomfdojro2mhwvypkgj.png"
+     ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713897/qlczppqlobtbultcufsr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713897/rsdudxrmezxpk1axfrda.png"
+   ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713898/atoyj3guosnz0c3b6jq4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713898/movs1zimr7ycctqpawnw.png"
+    ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713898/hlkivss4lzb0cye2wwr9.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713902/uonr2ryfjyoogktkhi8a.png"
+  ],
+  "hotpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713901/kgk3aheja7hfgcjuui2m.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713903/h60xprkt2tcgermuh5wr.png"
+     ],
+  "steelblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713904/mk7ohtto0i0sics8huvs.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713906/gpab15hqatq2h0a91le2.png"
+   ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713905/ylz6a4rwejcndqcm3z8t.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713908/zcgkyg8jj0rkso0gn2de.png"     
+  ],
+  "skyblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713904/efqguvlqfzpyc5xcnvja.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713906/yz7gtw4ryqxmfb4kfxdq.png"
+      ],
+  "aqua": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713914/h9nlnpyuk1zfpzhwqj9l.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713906/wgdeevxdknw5mm6vr6so.png"   
+  ],
+  "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713914/hwv60nzmq0hajfc3qtv0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713916/sag26em2eadwa00wkdaj.png"
+  ],
+  "violet": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713915/qxqdb2gk2mrqbmqgcudb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713916/kgchxcjilzfj5smw6wtl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774713915/djfglisdjgkhkdvwvbex.png"  
+  ]
+}</t>
+  </si>
+  <si>
+    <t>Top Texturizado</t>
+  </si>
+  <si>
+    <t>{"black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714018/b9xqqndx2f6nnu1r5frp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714021/ngnrdffmeyhiipe1djmg.png"
+     ] }</t>
+  </si>
+  <si>
+    <t>Top Suplex Energy Pro</t>
+  </si>
+  <si>
+    <t>{"blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714137/iiqmphaqbr1flgemubgn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714137/ra2rgjcylnmdksoc1jgu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714138/xz0vgbqgjeno5ih6rdfw.png"
+     ] }</t>
+  </si>
+  <si>
+    <t>blue</t>
+  </si>
+  <si>
+    <t>Conjuto un solo hombro</t>
+  </si>
+  <si>
+    <t>blue,black,gray,green,darkblue,hotpink,steelblue,purple,skyblue,aqua,darkgreen,violet</t>
+  </si>
+  <si>
+    <t>{  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714509/lajy5yzvekp3usc8gxhh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714509/eknz97qnryoxychursgz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714509/yf4booicnc3eivr8nqoi.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714510/mddh9ymk1oe2wipnhqnt.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714510/et5iqdf5lnbckgeu63cx.png"
+     ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714513/uzrfltewqefrem1eq33j.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714514/wl0n2qbsgjaildmgmshx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714514/i4cs5a8seetzbjnupnji.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714516/bv3vdgjzu4fb185zg4gb.png"
+   ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714520/dy41ds9uj6lxkfskto2d.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714521/pbc5fdafy4jcvs8l2xgr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714524/w7bsl2pcoxl2q2zoitjl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714527/efkrvrqntltot3t6nqsi.png"
+   ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714525/ider9pgwbwowsumhmdtg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714530/qrj8nc6x8mrm2olm5jzj.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714530/xb9urtpzezp0fzeljv83.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714532/wrdv1xpbifgg127coqo7.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714546/bnj6nqfxwqlh8cbbuieu.png"
+    ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714579/ko775atq8sufbrw96jlv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714579/fsjsvsv5fftbesko2wu8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714580/jzenuxko3lclog6ev5ki.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714581/g3sz7wojdfpo7xvkrqun.png"
+  ],
+  "hotpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714584/nffylufuberfwvd73gik.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714585/hcx1ahu5kmwxlvyixdis.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714587/o6curpdnnr7xnhj0c6bd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714586/i9tvkqpxif5ukwnkipd3.png"
+     ],
+  "steelblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714591/ydkznuqmmeny9dfg5h0l.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714592/libyrxbgxadqngtqz1vk.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714592/r36nybgk5griozbkm3ge.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714592/uzjly8c0d58gvevbtcsv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714594/ekpoxw3kunkpeblekte1.png"
+   ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714598/g3ql7omhiekcfaprg1um.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714601/r3s2h7hyydu8wcpkxkk6.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714599/lybq7oe8tgy4mc3bcmio.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714600/jmwjmoej73c0lr3muhhm.png"     
+  ],
+  "skyblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714602/bpjzgkxfdzkmbxvrnuli.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714606/mpsvuuxowoqkhid039u3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714607/ushxwasjogdcsqht0yuu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714608/jubzjqf9n5d8zpmqlcen.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714610/mmwxzikaxzrixlrlaf2a.png"
+      ]}</t>
+  </si>
+  <si>
+    <t>black,blue,gray,green,darkblue,hotpink,steelblue,purple,skyblue</t>
+  </si>
+  <si>
+    <t>Top un solo hombro</t>
+  </si>
+  <si>
+    <t>{  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714859/hewrryb07ejjdtevkloi.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714860/dwfhjuikoiz3tcal5uyq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714860/wcakb3xriax3bpfdkjxk.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714861/fzlybe8yxbew46jb6pjb.png"
+     ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714863/swjr5q5xzuaayjgynqnl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714864/khneiu8dloyuq7rcfson.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714865/uuorxyl3wc7ydnnotfdg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714867/kr7rirn2pfbs6apdbmjf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714868/uah3ayfhpuxwpqzftd6s.png"
+   ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714869/f5kb8vzmzm5bjbfcmfzo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714872/jsnhovnqix5xd8rhgjnq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714875/meq9cyrn0d78xpxtg0gs.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714876/sr2edccvsbpwupobthtz.png"
+   ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714879/tccsxgr2najc1aecmfxd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714880/qspl0qnovkj0uuxo8f5v.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714883/tgfibvuefkwpuegmwwtp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714884/k2kef5ccg70a8dgulton.png"
+    ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714902/lzhuirsrlhjvkk596xl3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714903/dwexwhnyczect6xt8foz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714904/w9abnurff6gwgxudhpi5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714907/rjjvxhmkoz3ugsgmbtv8.png"
+  ],
+  "hotpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714908/v48b2msoplxpcsjowws5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714908/efjr4hduya3zg8a53ur4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714912/ijv56mgb8u6hztj7vzfz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714914/zhqeidho1rlohk2jtk5j.png"
+     ],
+  "steelblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714913/ftfmcv2wumpfjrqttgoy.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714916/srkbdsivxx8mchhptm4l.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714917/vqridi2h2nzogrtcz7ro.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714918/shitt6l5w5kzilw4mdnm.png"
+   ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714921/xi3u17hbsvexzltvkyiu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714922/yss0o9ipsbjevh9ayljg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714927/w87yj6wphofpqdtns9jj.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714929/bhdlqud5qmjt8opeldlq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714933/tjtiwf2swymjqwam0csg.png"
+  ],
+  "skyblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714937/zb06mil8puch3yxvgetq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714938/ihnf8vpsaf6kfhv6tczb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714939/omk4mxlswarpyvfpcpbn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714948/btar9aoderjhodl3pdax.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714948/tqxq8gqerqbyhkpkyx66.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714950/ebcudttebohdgnr9jcbj.png"
+      ], "red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714958/w7ljbkfrrh1xiklno1l1.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714959/odfimspvi65onsrsdtaq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714960/nrni9r0bhudr0olbnsm2.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714960/od8ijqimlshqzs8ccsda.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714974/ydfwvstyrhlr2ttnvtrc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714973/osnfglktn6vlv2pxurkh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774714976/pbv04p4lnraxyxyvfdhn.png"]}</t>
+  </si>
+  <si>
+    <t>black,blue,gray,green,darkblue,hotpink,steelblue,purple,skyblue,red</t>
+  </si>
+  <si>
+    <t>Conjunto Leggins Suplex</t>
+  </si>
+  <si>
+    <t>{  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715054/obdim5wxps2rmhad5jye.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715056/gi95mdzimlmkwfw9cxuh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715054/d5ssuobvxyzqs0aip7bu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715056/pky3elmrbs9hnhhl7syy.png"
+     ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715058/p3ei6oadeehtbdr3gvwe.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715059/n95j9sacvi2h2commmv7.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715060/o0mresfwwapl5xhdbkup.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715063/zir74pmtou4en2tdtlzl.png"
+   ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715065/gjcqr8dhxffnee28u7um.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715066/qk6eodn98pyi7imjeeyh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715069/dmcj29lxosvyqalkploc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715071/xecaq8wg8uo3gmfbm2qk.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715074/rgkhwukae8eqxngcu3dr.png"]}</t>
+  </si>
+  <si>
+    <t>black,blue,gray</t>
+  </si>
+  <si>
+    <t>Leggins Suplex</t>
+  </si>
+  <si>
+    <t>{"L":{"retail":36000,"wholesale":25000},"XL":{"retail":36000,"wholesale":26000}}</t>
+  </si>
+  <si>
+    <t>{    "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715058/p3ei6oadeehtbdr3gvwe.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715059/n95j9sacvi2h2commmv7.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715060/o0mresfwwapl5xhdbkup.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715063/zir74pmtou4en2tdtlzl.png"
+   ], "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715054/obdim5wxps2rmhad5jye.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715056/gi95mdzimlmkwfw9cxuh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715054/d5ssuobvxyzqs0aip7bu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715056/pky3elmrbs9hnhhl7syy.png"
+     ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715065/gjcqr8dhxffnee28u7um.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715066/qk6eodn98pyi7imjeeyh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715069/dmcj29lxosvyqalkploc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715071/xecaq8wg8uo3gmfbm2qk.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715074/rgkhwukae8eqxngcu3dr.png"]}</t>
+  </si>
+  <si>
+    <t>blue,black,gray</t>
+  </si>
+  <si>
+    <t>Short recogido Lateral</t>
+  </si>
+  <si>
+    <t>Enterizo para Ciclismo.</t>
+  </si>
+  <si>
+    <t>{
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715391/agiednmodeb5yfpahlp1.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715392/tofa7d0ks3nqok7en9j6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715395/cdbcpgyhms197nffsus0.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715394/jpithdawvqp2tmmz4sbr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715398/aonotdgo3ttkxg3vxife.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715399/ga18nxoi4pcosvxkgd6x.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715402/u2jtujngu7yuuqdbfo7r.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715403/q1bwntcbzvnilh5xyumu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715406/nbo3egml3xzqqkgj2yqk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715407/zdjxkw4a53r0j2kjn5zi.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715412/fpyfapenk9fxym7eewmu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715410/z4kcqsfgasg1z53yarur.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715414/m23amhh21mpotdp88sjn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715416/ydmz1uralgltpdeevcbc.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715418/x2rtdwfrfwecvxs84i7l.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715421/ebbezh68fixgh6o84qli.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715423/a7wjeymergff40uhpykt.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715427/oq9maqfvtwrz5cfpmnnw.png"
+  ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715428/espsoggmadkxd6weqeb8.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715429/drdkltcampvjzfzc0ifn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715434/ufwqg1cmoeslcqafsaw9.png"
+  ],
+  "hotpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715436/fn4lbigoobdn5xjbm8jh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715440/ddhq5u6ubbdbbw1no78m.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715441/vb5pyt9y9flu8fh0f45c.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715447/cksicv1hldfrcxgapuug.png"
+  ],
+  "steelblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715449/zhcwcrbc5dkixpezz70b.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715445/koyfabdm2bhnjhkcamu4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715453/rrada8pae4w27xmxzimc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715453/ee4ronykxwaebzdtzx8c.png"
+      ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715458/uc7n4i1rqltsbblh1ftl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715460/on3p22rgtcgnqndozwu3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715460/on3p22rgtcgnqndozwu3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715465/xxg2fwuxia77qn9dxqtv.png"
+  ],
+  "skyblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715467/bni8lwrz38khcg0wjqss.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715469/zds8ckdyanvwacjut2if.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715475/i3us2trdde2od7imi4yp.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>black,blue,gray,green,darkblue,hotpink,steelblue</t>
+  </si>
+  <si>
+    <t>Reflectivo Seme-Impermeable en Conjunto.</t>
+  </si>
+  <si>
+    <t>Buso Combinado.</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>black,blue,gray,green,darkblue</t>
+  </si>
+  <si>
+    <t>black,gray,green,lime,olive,white</t>
+  </si>
+  <si>
+    <t>{
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242668/fmmqv9d3abczghkogp1p.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242712/aushzmuk00uao21tcsfe.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242720/aqutgbwf8fhr0ay0et9x.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774739758/o1kam9otlhetqvskjme1.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242703/xmpeiwyzm5pykzpaouuh.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774739761/mquvckpggvlpeh1plhp9.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242707/licsjuezzfbcaastvwty.png"
+  ],
+  "lime": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242670/vn5zjnwmtj1ubnosan6g.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242672/ladrzy2w92giulcorc0d.png"
+  ],
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242675/vbr5qoanu6pzhtwareey.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242697/jxucutam0nuykc3cbptz.png"
+  ],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242700/kbdbl8y32oyxpwtho1sg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242698/vfmx6wm7pgfdxausx0qh.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774730098/elsyao9pkpiqsjcdvypa.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774730120/jtqoxvlbtnkthgqs3o1o.png"],
+     "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774730099/stm0oyw9de4wmos1kfrv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774730102/zfskg7mb72bzns8kezen.png"
+     ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774730106/pw6s1ybyiqpifwttonmk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774730104/hls8zybrz7ppkdzcdf7g.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774730113/wdadzficzzj9divaockh.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774730109/sx6ffskqrr7wjarcx7td.png"
+     ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774730113/llqkj3dh8c0omjedlwrs.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774730116/kmdru7pnltmq5zzwxyed.png"
+  ]
+}</t>
   </si>
 </sst>
 </file>
@@ -1876,7 +2207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1931,6 +2262,12 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2238,7 +2575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}">
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="57.54296875" style="2" customWidth="1"/>
@@ -2259,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>1</v>
@@ -2297,10 +2634,10 @@
         <v>16</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>11</v>
@@ -2318,10 +2655,10 @@
         <v>17</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K2" s="6" t="b">
         <v>0</v>
@@ -2332,13 +2669,13 @@
     </row>
     <row r="3" spans="1:12" s="3" customFormat="1" ht="86.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>11</v>
@@ -2368,13 +2705,13 @@
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="89.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>11</v>
@@ -2409,10 +2746,10 @@
         <v>19</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>20</v>
@@ -2448,7 +2785,7 @@
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>11</v>
@@ -2467,7 +2804,7 @@
         <v>77</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K6" s="6" t="b">
         <v>0</v>
@@ -2482,7 +2819,7 @@
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>11</v>
@@ -2516,7 +2853,7 @@
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>11</v>
@@ -2548,11 +2885,11 @@
     </row>
     <row r="9" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>11</v>
@@ -2588,7 +2925,7 @@
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>11</v>
@@ -2618,11 +2955,11 @@
     </row>
     <row r="11" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>11</v>
@@ -2656,7 +2993,7 @@
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>11</v>
@@ -2675,7 +3012,7 @@
         <v>84</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K12" s="6" t="b">
         <v>0</v>
@@ -2686,11 +3023,11 @@
     </row>
     <row r="13" spans="1:12" ht="47" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>11</v>
@@ -2709,7 +3046,7 @@
         <v>84</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K13" s="6" t="b">
         <v>0</v>
@@ -2720,11 +3057,11 @@
     </row>
     <row r="14" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>27</v>
@@ -2745,7 +3082,7 @@
         <v>85</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K14" s="6" t="b">
         <v>0</v>
@@ -2756,11 +3093,11 @@
     </row>
     <row r="15" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>27</v>
@@ -2781,7 +3118,7 @@
         <v>85</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K15" s="6" t="b">
         <v>0</v>
@@ -2792,11 +3129,11 @@
     </row>
     <row r="16" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>11</v>
@@ -2817,7 +3154,7 @@
         <v>85</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K16" s="6" t="b">
         <v>0</v>
@@ -2828,11 +3165,11 @@
     </row>
     <row r="17" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>11</v>
@@ -2853,7 +3190,7 @@
         <v>85</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K17" s="6" t="b">
         <v>0</v>
@@ -2868,7 +3205,7 @@
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>30</v>
@@ -2887,7 +3224,7 @@
         <v>86</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K18" s="6" t="b">
         <v>0</v>
@@ -2898,7 +3235,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6" t="s">
@@ -2921,7 +3258,7 @@
         <v>86</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K19" s="6" t="b">
         <v>0</v>
@@ -2932,11 +3269,11 @@
     </row>
     <row r="20" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>11</v>
@@ -2955,7 +3292,7 @@
         <v>87</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K20" s="6" t="b">
         <v>0</v>
@@ -2970,7 +3307,7 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>11</v>
@@ -2989,7 +3326,7 @@
         <v>87</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K21" s="6" t="b">
         <v>0</v>
@@ -3004,7 +3341,7 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>11</v>
@@ -3020,10 +3357,10 @@
         <v>32</v>
       </c>
       <c r="I22" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="J22" s="12" t="s">
         <v>143</v>
-      </c>
-      <c r="J22" s="12" t="s">
-        <v>144</v>
       </c>
       <c r="K22" s="6" t="b">
         <v>0</v>
@@ -3038,7 +3375,7 @@
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>11</v>
@@ -3057,7 +3394,7 @@
         <v>88</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K23" s="6" t="b">
         <v>0</v>
@@ -3072,7 +3409,7 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>11</v>
@@ -3091,7 +3428,7 @@
         <v>89</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K24" s="6" t="b">
         <v>0</v>
@@ -3106,7 +3443,7 @@
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>11</v>
@@ -3136,7 +3473,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
@@ -3174,7 +3511,7 @@
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>11</v>
@@ -3208,7 +3545,7 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>11</v>
@@ -3238,7 +3575,7 @@
     </row>
     <row r="29" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
@@ -3261,7 +3598,7 @@
         <v>94</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K29" s="6" t="b">
         <v>0</v>
@@ -3272,7 +3609,7 @@
     </row>
     <row r="30" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6" t="s">
@@ -3398,10 +3735,10 @@
         <v>14</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="K33" s="6" t="b">
         <v>0</v>
@@ -3446,7 +3783,7 @@
     </row>
     <row r="35" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6" t="s">
@@ -3459,7 +3796,7 @@
         <v>17000</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G35" s="6">
         <v>34000</v>
@@ -3482,7 +3819,7 @@
     </row>
     <row r="36" spans="1:12" ht="126.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6" t="s">
@@ -3495,7 +3832,7 @@
         <v>17000</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G36" s="6">
         <v>34000</v>
@@ -3507,7 +3844,7 @@
         <v>106</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K36" s="6" t="b">
         <v>0</v>
@@ -3531,7 +3868,7 @@
         <v>17000</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G37" s="6">
         <v>34000</v>
@@ -3543,7 +3880,7 @@
         <v>107</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K37" s="6" t="b">
         <v>0</v>
@@ -3554,7 +3891,7 @@
     </row>
     <row r="38" spans="1:12" ht="91" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6" t="s">
@@ -3567,7 +3904,7 @@
         <v>17000</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G38" s="6">
         <v>34000</v>
@@ -3590,7 +3927,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
@@ -3692,7 +4029,7 @@
     </row>
     <row r="42" spans="1:12" ht="98.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
@@ -3715,7 +4052,7 @@
         <v>115</v>
       </c>
       <c r="J42" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K42" s="6" t="b">
         <v>0</v>
@@ -3887,7 +4224,7 @@
         <v>124</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K47" s="6" t="b">
         <v>0</v>
@@ -3898,7 +4235,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6" t="s">
@@ -3955,7 +4292,7 @@
         <v>127</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K49" s="6" t="b">
         <v>0</v>
@@ -3970,7 +4307,7 @@
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>11</v>
@@ -3998,7 +4335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" ht="406" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
         <v>64</v>
       </c>
@@ -4020,10 +4357,10 @@
         <v>12</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="J51" s="14" t="s">
-        <v>153</v>
+        <v>289</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>290</v>
       </c>
       <c r="K51" s="6" t="b">
         <v>0</v>
@@ -4054,10 +4391,10 @@
         <v>14</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J52" s="15" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K52" s="6" t="b">
         <v>0</v>
@@ -4072,7 +4409,7 @@
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>11</v>
@@ -4088,10 +4425,10 @@
         <v>14</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K53" s="6" t="b">
         <v>0</v>
@@ -4106,7 +4443,7 @@
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>11</v>
@@ -4122,10 +4459,10 @@
         <v>14</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K54" s="6" t="b">
         <v>0</v>
@@ -4140,7 +4477,7 @@
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>11</v>
@@ -4156,10 +4493,10 @@
         <v>14</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K55" s="6" t="b">
         <v>0</v>
@@ -4174,7 +4511,7 @@
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>11</v>
@@ -4190,10 +4527,10 @@
         <v>32</v>
       </c>
       <c r="I56" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="J56" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="K56" s="6" t="b">
         <v>0</v>
@@ -4204,11 +4541,11 @@
     </row>
     <row r="57" spans="1:12" ht="377" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>11</v>
@@ -4217,7 +4554,7 @@
         <v>22000</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G57" s="6">
         <v>27000</v>
@@ -4226,10 +4563,10 @@
         <v>17</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K57" s="6" t="b">
         <v>0</v>
@@ -4240,11 +4577,11 @@
     </row>
     <row r="58" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A58" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B58" s="16"/>
       <c r="C58" s="16" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D58" s="16" t="s">
         <v>27</v>
@@ -4260,10 +4597,10 @@
         <v>14</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J58" s="18" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K58" s="19" t="b">
         <v>0</v>
@@ -4274,11 +4611,11 @@
     </row>
     <row r="59" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A59" s="16" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B59" s="16"/>
       <c r="C59" s="16" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D59" s="16" t="s">
         <v>20</v>
@@ -4294,10 +4631,10 @@
         <v>14</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J59" s="18" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K59" s="19" t="b">
         <v>0</v>
@@ -4308,11 +4645,11 @@
     </row>
     <row r="60" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A60" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B60" s="16"/>
       <c r="C60" s="16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D60" s="16" t="s">
         <v>20</v>
@@ -4328,10 +4665,10 @@
         <v>14</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J60" s="18" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K60" s="19" t="b">
         <v>0</v>
@@ -4342,11 +4679,11 @@
     </row>
     <row r="61" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A61" s="16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B61" s="16"/>
       <c r="C61" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D61" s="16" t="s">
         <v>20</v>
@@ -4362,10 +4699,10 @@
         <v>14</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J61" s="18" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K61" s="19" t="b">
         <v>0</v>
@@ -4376,11 +4713,11 @@
     </row>
     <row r="62" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A62" s="16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B62" s="16"/>
       <c r="C62" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D62" s="16" t="s">
         <v>20</v>
@@ -4396,10 +4733,10 @@
         <v>14</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J62" s="18" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K62" s="19" t="b">
         <v>0</v>
@@ -4410,11 +4747,11 @@
     </row>
     <row r="63" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A63" s="16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B63" s="16"/>
       <c r="C63" s="16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D63" s="16" t="s">
         <v>20</v>
@@ -4430,10 +4767,10 @@
         <v>14</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J63" s="18" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="K63" s="19" t="b">
         <v>0</v>
@@ -4444,11 +4781,11 @@
     </row>
     <row r="64" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A64" s="16" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B64" s="16"/>
       <c r="C64" s="16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D64" s="16" t="s">
         <v>20</v>
@@ -4464,10 +4801,10 @@
         <v>14</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J64" s="18" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K64" s="19" t="b">
         <v>0</v>
@@ -4478,11 +4815,11 @@
     </row>
     <row r="65" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A65" s="16" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B65" s="16"/>
       <c r="C65" s="16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D65" s="16" t="s">
         <v>20</v>
@@ -4498,10 +4835,10 @@
         <v>14</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J65" s="18" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K65" s="19" t="b">
         <v>0</v>
@@ -4512,11 +4849,11 @@
     </row>
     <row r="66" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A66" s="16" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B66" s="16"/>
       <c r="C66" s="16" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D66" s="16" t="s">
         <v>20</v>
@@ -4532,10 +4869,10 @@
         <v>14</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J66" s="18" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K66" s="19" t="b">
         <v>0</v>
@@ -4546,11 +4883,11 @@
     </row>
     <row r="67" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A67" s="16" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B67" s="16"/>
       <c r="C67" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D67" s="16" t="s">
         <v>20</v>
@@ -4566,10 +4903,10 @@
         <v>14</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J67" s="18" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K67" s="19" t="b">
         <v>0</v>
@@ -4580,11 +4917,11 @@
     </row>
     <row r="68" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A68" s="16" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B68" s="16"/>
       <c r="C68" s="16" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D68" s="16" t="s">
         <v>20</v>
@@ -4600,10 +4937,10 @@
         <v>14</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J68" s="18" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K68" s="19" t="b">
         <v>0</v>
@@ -4614,11 +4951,11 @@
     </row>
     <row r="69" spans="1:12" ht="406" x14ac:dyDescent="0.35">
       <c r="A69" s="16" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B69" s="16"/>
       <c r="C69" s="16" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D69" s="16" t="s">
         <v>20</v>
@@ -4634,10 +4971,10 @@
         <v>14</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J69" s="18" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K69" s="19" t="b">
         <v>0</v>
@@ -4648,7 +4985,7 @@
     </row>
     <row r="70" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A70" s="16" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B70" s="16"/>
       <c r="C70" s="16" t="s">
@@ -4668,10 +5005,10 @@
         <v>14</v>
       </c>
       <c r="I70" s="16" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K70" s="19" t="b">
         <v>0</v>
@@ -4682,11 +5019,11 @@
     </row>
     <row r="71" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A71" s="16" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B71" s="16"/>
       <c r="C71" s="16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D71" s="16" t="s">
         <v>20</v>
@@ -4702,10 +5039,10 @@
         <v>14</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J71" s="18" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K71" s="19" t="b">
         <v>0</v>
@@ -4716,11 +5053,11 @@
     </row>
     <row r="72" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A72" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B72" s="16"/>
       <c r="C72" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D72" s="16" t="s">
         <v>20</v>
@@ -4736,10 +5073,10 @@
         <v>14</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J72" s="18" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K72" s="19" t="b">
         <v>0</v>
@@ -4750,11 +5087,11 @@
     </row>
     <row r="73" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A73" s="16" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B73" s="16"/>
       <c r="C73" s="16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D73" s="16" t="s">
         <v>20</v>
@@ -4770,10 +5107,10 @@
         <v>14</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J73" s="18" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K73" s="19" t="b">
         <v>0</v>
@@ -4784,13 +5121,13 @@
     </row>
     <row r="74" spans="1:12" ht="319" x14ac:dyDescent="0.35">
       <c r="A74" s="16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D74" s="16" t="s">
         <v>11</v>
@@ -4803,13 +5140,13 @@
         <v>34000</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I74" s="16" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J74" s="18" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K74" s="19" t="b">
         <v>0</v>
@@ -4820,11 +5157,11 @@
     </row>
     <row r="75" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A75" s="16" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B75" s="16"/>
       <c r="C75" s="16" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D75" s="16" t="s">
         <v>20</v>
@@ -4840,10 +5177,10 @@
         <v>14</v>
       </c>
       <c r="I75" s="16" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="J75" s="18" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K75" s="19" t="b">
         <v>0</v>
@@ -4854,11 +5191,11 @@
     </row>
     <row r="76" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A76" s="16" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B76" s="16"/>
       <c r="C76" s="16" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D76" s="16" t="s">
         <v>20</v>
@@ -4874,10 +5211,10 @@
         <v>14</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K76" s="19" t="b">
         <v>0</v>
@@ -4888,11 +5225,11 @@
     </row>
     <row r="77" spans="1:12" ht="87" x14ac:dyDescent="0.35">
       <c r="A77" s="16" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B77" s="16"/>
       <c r="C77" s="16" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D77" s="16" t="s">
         <v>20</v>
@@ -4908,10 +5245,10 @@
         <v>14</v>
       </c>
       <c r="I77" s="16" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J77" s="18" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="K77" s="19" t="b">
         <v>0</v>
@@ -4920,8 +5257,388 @@
         <v>0</v>
       </c>
     </row>
+    <row r="78" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A78" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="B78" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="C78" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="D78" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" s="16">
+        <v>49000</v>
+      </c>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16">
+        <v>63000</v>
+      </c>
+      <c r="H78" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I78" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="J78" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="K78" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A79" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="B79" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="C79" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="D79" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E79" s="16">
+        <v>49000</v>
+      </c>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16">
+        <v>63000</v>
+      </c>
+      <c r="H79" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I79" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="J79" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="K79" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="58" x14ac:dyDescent="0.35">
+      <c r="A80" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="B80" s="16"/>
+      <c r="C80" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="D80" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E80" s="16">
+        <v>9000</v>
+      </c>
+      <c r="F80" s="16"/>
+      <c r="G80" s="16">
+        <v>14000</v>
+      </c>
+      <c r="H80" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I80" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="J80" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="K80" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L80" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A81" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="B81" s="16"/>
+      <c r="C81" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="D81" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E81" s="16">
+        <v>21000</v>
+      </c>
+      <c r="F81" s="16"/>
+      <c r="G81" s="16">
+        <v>31500</v>
+      </c>
+      <c r="H81" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I81" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="J81" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="K81" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L81" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A82" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="B82" s="16"/>
+      <c r="C82" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="D82" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E82" s="16">
+        <v>17000</v>
+      </c>
+      <c r="F82" s="16"/>
+      <c r="G82" s="16">
+        <v>22000</v>
+      </c>
+      <c r="H82" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I82" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="J82" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="K82" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L82" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A83" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="B83" s="16"/>
+      <c r="C83" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="D83" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E83" s="16">
+        <v>5000</v>
+      </c>
+      <c r="F83" s="16"/>
+      <c r="G83" s="16">
+        <v>7000</v>
+      </c>
+      <c r="H83" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I83" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="J83" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="K83" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L83" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="261" x14ac:dyDescent="0.35">
+      <c r="A84" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="B84" s="16"/>
+      <c r="C84" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="D84" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E84" s="16">
+        <v>23000</v>
+      </c>
+      <c r="F84" s="16"/>
+      <c r="G84" s="16">
+        <v>34500</v>
+      </c>
+      <c r="H84" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I84" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="J84" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="K84" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L84" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A85" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="B85" s="16"/>
+      <c r="C85" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="D85" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E85" s="16">
+        <v>25000</v>
+      </c>
+      <c r="F85" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="G85" s="16">
+        <v>36000</v>
+      </c>
+      <c r="H85" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I85" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="J85" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="K85" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L85" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A86" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="B86" s="16"/>
+      <c r="C86" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="D86" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E86" s="16">
+        <v>14000</v>
+      </c>
+      <c r="F86" s="16"/>
+      <c r="G86" s="16">
+        <v>18000</v>
+      </c>
+      <c r="H86" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I86" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="J86" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="K86" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L86" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A87" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="B87" s="6"/>
+      <c r="C87" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="6">
+        <v>33000</v>
+      </c>
+      <c r="F87" s="7"/>
+      <c r="G87" s="6">
+        <v>49500</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I87" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="J87" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="K87" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L87" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="304.5" x14ac:dyDescent="0.35">
+      <c r="A88" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E88" s="6">
+        <v>18000</v>
+      </c>
+      <c r="F88" s="6"/>
+      <c r="G88" s="6">
+        <v>27000</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="I88" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="J88" s="22" t="s">
+        <v>291</v>
+      </c>
+      <c r="K88" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L88" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L71" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}"/>
+  <autoFilter ref="A1:L80" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/productos.xlsx
+++ b/productos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0526577688ca4eec/Escritorio/Proyectos developer/Diseños_Gasper/Back-end/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="851" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B09FC64-0D1D-4C56-8422-2F2F565BFC65}"/>
+  <xr:revisionPtr revIDLastSave="884" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01004DC4-E4DC-44DA-8E81-0DB028C4A5BB}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="300">
   <si>
     <t>name</t>
   </si>
@@ -1679,9 +1679,6 @@
     <t>Chaqueta Publicidad</t>
   </si>
   <si>
-    <t>publicidad</t>
-  </si>
-  <si>
     <t>green,white,red,gray</t>
   </si>
   <si>
@@ -1893,9 +1890,6 @@
     <t>blue</t>
   </si>
   <si>
-    <t>Conjuto un solo hombro</t>
-  </si>
-  <si>
     <t>blue,black,gray,green,darkblue,hotpink,steelblue,purple,skyblue,aqua,darkgreen,violet</t>
   </si>
   <si>
@@ -2119,6 +2113,75 @@
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774730116/kmdru7pnltmq5zzwxyed.png"
   ]
 }</t>
+  </si>
+  <si>
+    <t>Rompevientos Tipo Chamarra</t>
+  </si>
+  <si>
+    <t>black,blue,gray,green,darkblue,pink,white</t>
+  </si>
+  <si>
+    <t>{
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774743821/fxbehwvioldhp0cu3jul.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774743822/zxo956tqz7j0wkygdquo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774743827/ggopc6wvbkzfgqqit2ta.png"],
+     "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774743820/vo0m7q2mp1spwumxpr0m.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774743819/xnyozkxjfuykiegethwa.png"
+     ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774743819/suqhltanck83u98uvkz6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774743820/n7cfreaeswehtqdjie03.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774743821/mqapir8airohi0svikqf.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774743821/c47pfijjyqwv8jtq9wzp.png"
+     ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774743821/ngluonalmvoyng50zqvf.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774743822/xlyuek5an3mx0yt4a8b6.png"
+  ], "pink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774743822/yl17mxyq7tge01x1abqu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774743822/ukx6hlz8ovxbynk72ivy.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774743823/dzunxhz2ohbeom7uzv4f.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774743825/vduyinixt4gu6jgqgdyx.png"]
+}</t>
+  </si>
+  <si>
+    <t>chaquetas</t>
+  </si>
+  <si>
+    <t>Chaqueta en Tela Antifluido.</t>
+  </si>
+  <si>
+    <t>Conjunto un solo hombro</t>
+  </si>
+  <si>
+    <t>Chaqueta en Algodón Perchado</t>
+  </si>
+  <si>
+    <t>L.XL</t>
+  </si>
+  <si>
+    <t>{
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774748523/smnesemts5z58wtxoouy.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774748524/pused7jvglwombreo3o4.png"],
+     "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774748531/hibcuhc7hlf4awilhozf.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774748523/rvfwbofnusbokv0h1j6d.png"
+     ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774748531/e1r3vw3cimi6jx5eq0as.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774748525/sxpuworwx5xtaeblrtrs.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774748536/njck6gi9spshpx0wdkbc.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774748524/bqkpmlrg0ie2ylbgshka.png"
+     ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774748532/xtsybhtzrd4zks8fk4dt.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774748524/jwafxedbkduq6c7zxkw1.png"
+  ], "pink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774748535/jyn2b9mqvjnem1ln8wrv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774748525/tdy4bblkeeocypv3mloy.png"]
+}</t>
+  </si>
+  <si>
+    <t>black,blue,gray,green,darkblue,pink</t>
   </si>
 </sst>
 </file>
@@ -2142,7 +2205,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2179,6 +2242,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2207,7 +2276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2268,6 +2337,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2575,7 +2647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}">
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="57.54296875" style="2" customWidth="1"/>
@@ -2596,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>1</v>
@@ -2634,7 +2706,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>157</v>
@@ -2655,10 +2727,10 @@
         <v>17</v>
       </c>
       <c r="I2" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>253</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>254</v>
       </c>
       <c r="K2" s="6" t="b">
         <v>0</v>
@@ -2672,7 +2744,7 @@
         <v>173</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>157</v>
@@ -2708,7 +2780,7 @@
         <v>172</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>157</v>
@@ -2746,7 +2818,7 @@
         <v>19</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>157</v>
@@ -3046,7 +3118,7 @@
         <v>84</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K13" s="6" t="b">
         <v>0</v>
@@ -4357,10 +4429,10 @@
         <v>12</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K51" s="6" t="b">
         <v>0</v>
@@ -4989,7 +5061,7 @@
       </c>
       <c r="B70" s="16"/>
       <c r="C70" s="16" t="s">
-        <v>10</v>
+        <v>293</v>
       </c>
       <c r="D70" s="16" t="s">
         <v>20</v>
@@ -5124,10 +5196,10 @@
         <v>234</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>235</v>
+        <v>293</v>
       </c>
       <c r="D74" s="16" t="s">
         <v>11</v>
@@ -5140,13 +5212,13 @@
         <v>34000</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I74" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J74" s="18" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K74" s="19" t="b">
         <v>0</v>
@@ -5157,7 +5229,7 @@
     </row>
     <row r="75" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A75" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B75" s="16"/>
       <c r="C75" s="16" t="s">
@@ -5177,10 +5249,10 @@
         <v>14</v>
       </c>
       <c r="I75" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J75" s="18" t="s">
         <v>243</v>
-      </c>
-      <c r="J75" s="18" t="s">
-        <v>244</v>
       </c>
       <c r="K75" s="19" t="b">
         <v>0</v>
@@ -5191,7 +5263,7 @@
     </row>
     <row r="76" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A76" s="16" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B76" s="16"/>
       <c r="C76" s="16" t="s">
@@ -5211,10 +5283,10 @@
         <v>14</v>
       </c>
       <c r="I76" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="J76" s="17" t="s">
         <v>246</v>
-      </c>
-      <c r="J76" s="17" t="s">
-        <v>247</v>
       </c>
       <c r="K76" s="19" t="b">
         <v>0</v>
@@ -5225,7 +5297,7 @@
     </row>
     <row r="77" spans="1:12" ht="87" x14ac:dyDescent="0.35">
       <c r="A77" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B77" s="16"/>
       <c r="C77" s="16" t="s">
@@ -5245,10 +5317,10 @@
         <v>14</v>
       </c>
       <c r="I77" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="J77" s="18" t="s">
         <v>249</v>
-      </c>
-      <c r="J77" s="18" t="s">
-        <v>250</v>
       </c>
       <c r="K77" s="19" t="b">
         <v>0</v>
@@ -5259,10 +5331,10 @@
     </row>
     <row r="78" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A78" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="B78" s="16" t="s">
         <v>256</v>
-      </c>
-      <c r="B78" s="16" t="s">
-        <v>257</v>
       </c>
       <c r="C78" s="16" t="s">
         <v>211</v>
@@ -5281,10 +5353,10 @@
         <v>14</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J78" s="18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K78" s="19" t="b">
         <v>0</v>
@@ -5295,10 +5367,10 @@
     </row>
     <row r="79" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A79" s="16" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C79" s="16" t="s">
         <v>179</v>
@@ -5317,10 +5389,10 @@
         <v>14</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J79" s="18" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K79" s="19" t="b">
         <v>0</v>
@@ -5331,7 +5403,7 @@
     </row>
     <row r="80" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A80" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B80" s="16"/>
       <c r="C80" s="16" t="s">
@@ -5351,10 +5423,10 @@
         <v>14</v>
       </c>
       <c r="I80" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K80" s="19" t="b">
         <v>0</v>
@@ -5365,7 +5437,7 @@
     </row>
     <row r="81" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A81" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B81" s="16"/>
       <c r="C81" s="16" t="s">
@@ -5385,10 +5457,10 @@
         <v>14</v>
       </c>
       <c r="I81" s="16" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J81" s="17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K81" s="19" t="b">
         <v>0</v>
@@ -5399,7 +5471,7 @@
     </row>
     <row r="82" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A82" s="16" t="s">
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="B82" s="16"/>
       <c r="C82" s="16" t="s">
@@ -5419,10 +5491,10 @@
         <v>14</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="J82" s="18" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="K82" s="19" t="b">
         <v>0</v>
@@ -5433,7 +5505,7 @@
     </row>
     <row r="83" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A83" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B83" s="16"/>
       <c r="C83" s="16" t="s">
@@ -5453,10 +5525,10 @@
         <v>14</v>
       </c>
       <c r="I83" s="17" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J83" s="21" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K83" s="19" t="b">
         <v>0</v>
@@ -5467,7 +5539,7 @@
     </row>
     <row r="84" spans="1:12" ht="261" x14ac:dyDescent="0.35">
       <c r="A84" s="16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B84" s="16"/>
       <c r="C84" s="16" t="s">
@@ -5487,10 +5559,10 @@
         <v>14</v>
       </c>
       <c r="I84" s="16" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="J84" s="21" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K84" s="19" t="b">
         <v>0</v>
@@ -5501,7 +5573,7 @@
     </row>
     <row r="85" spans="1:12" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A85" s="16" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B85" s="16"/>
       <c r="C85" s="16" t="s">
@@ -5514,7 +5586,7 @@
         <v>25000</v>
       </c>
       <c r="F85" s="17" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G85" s="16">
         <v>36000</v>
@@ -5523,10 +5595,10 @@
         <v>13</v>
       </c>
       <c r="I85" s="16" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J85" s="21" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="K85" s="19" t="b">
         <v>0</v>
@@ -5537,7 +5609,7 @@
     </row>
     <row r="86" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A86" s="16" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B86" s="16"/>
       <c r="C86" s="16" t="s">
@@ -5557,10 +5629,10 @@
         <v>14</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J86" s="21" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="K86" s="19" t="b">
         <v>0</v>
@@ -5571,7 +5643,7 @@
     </row>
     <row r="87" spans="1:12" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6" t="s">
@@ -5605,7 +5677,7 @@
     </row>
     <row r="88" spans="1:12" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A88" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6" t="s">
@@ -5622,20 +5694,132 @@
         <v>27000</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="I88" s="7" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="J88" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="K88" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L88" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="362.5" x14ac:dyDescent="0.35">
+      <c r="A89" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E89" s="6">
+        <v>20000</v>
+      </c>
+      <c r="F89" s="6"/>
+      <c r="G89" s="6">
+        <v>40000</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I89" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="K88" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L88" s="6" t="b">
-        <v>0</v>
-      </c>
+      <c r="J89" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="K89" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L89" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="319" x14ac:dyDescent="0.35">
+      <c r="A90" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B90" s="6"/>
+      <c r="C90" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" s="6">
+        <v>25000</v>
+      </c>
+      <c r="F90" s="6"/>
+      <c r="G90" s="6">
+        <v>37500</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I90" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="J90" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="K90" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L90" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="319" x14ac:dyDescent="0.35">
+      <c r="A91" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="B91" s="23"/>
+      <c r="C91" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="D91" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" s="23">
+        <v>30000</v>
+      </c>
+      <c r="F91" s="23"/>
+      <c r="G91" s="23">
+        <v>45000</v>
+      </c>
+      <c r="H91" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="I91" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="J91" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="K91" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L91" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A92" s="23"/>
+      <c r="B92" s="23"/>
+      <c r="C92" s="23"/>
+      <c r="D92" s="23"/>
+      <c r="E92" s="23"/>
+      <c r="F92" s="23"/>
+      <c r="G92" s="23"/>
+      <c r="H92" s="23"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L80" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}"/>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0526577688ca4eec/Escritorio/Proyectos developer/Diseños_Gasper/Back-end/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="884" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01004DC4-E4DC-44DA-8E81-0DB028C4A5BB}"/>
+  <xr:revisionPtr revIDLastSave="1082" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD197DE3-9C6B-4378-9E80-462B24D23981}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="335">
   <si>
     <t>name</t>
   </si>
@@ -238,9 +238,6 @@
     <t>red,blue</t>
   </si>
   <si>
-    <t>{ "red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204994/ciz9eayk0ncioycgi6md.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204989/kbdzejtejhebqpcgfq9h.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204991/vmjyoodcogoisj569jqi.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204990/te1ar1hzxwpa63bosi7y.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204996/jysdhm98z84oslidk3of.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204993/gtced3dtobo1xhsfddog.png"]}</t>
-  </si>
-  <si>
     <t>green,red,blue,orange,darkred,cyan,royalblue</t>
   </si>
   <si>
@@ -256,9 +253,6 @@
     <t xml:space="preserve">	deepink,orange,blue,yellow,red,black,steelblue,olive</t>
   </si>
   <si>
-    <t xml:space="preserve">	deepink,orange,blue,yellow,red,black,steelblue,olive,gray</t>
-  </si>
-  <si>
     <t>{"deepink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250668/wr3birigvcczhipu6f6b.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250661/bwrwnlrrzbemqhwezjs3.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250664/kf7cxffjt9v8rnivdpjq.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250674/m0zgh5r2w9jrsupizmlr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250677/h0axfsbqji10ikh93gro.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250681/j3pfgwp8lbn2uwblfgkk.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250591/neflcst2k6ca3z50sqmw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250595/d9wnhi8wolybvyze5bhf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250598/l8zk3dfpfi6mus9dugpt.png"],"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250583/cla7lli8tpekp0vagslg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250583/trbe9ncnkutck5dwtaej.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250587/ufparkeluojp5mno5qyg.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250557/hjrgzqbdqgif5qjv6ubg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250560/h99wigyd1eyaeliptbgx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250578/yuujfqysnlb9zd1usu7m.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250547/h4rswumx0oekhu5bdsvl.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250550/wxle71udpbzovfk16lql.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250553/vvvcrtyf235mjgnz402s.png"],"steelblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250537/kol5crynodqpe9xfhrka.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250540/ald94s4ire08qmvov9hf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250544/o2ckxwtxoewp8ufxto0q.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250528/cq8rviwowjfbqpsd1mht.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250531/hyed4wj9doos3g2leqjf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250534/pfeghmv1cewqmzjahztt.png"]}</t>
   </si>
   <si>
@@ -295,12 +289,6 @@
     <t>green,black,red,lime,blue,crimson</t>
   </si>
   <si>
-    <t>green,red,blue,black,steelblue</t>
-  </si>
-  <si>
-    <t>{"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252333/osa3ymwwye7jeb8ildet.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252325/doe9jefe7loznqbux6da.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252330/x01eyusrbndxewf4jkxz.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252301/jbgk24ihrhe9nvxumrnf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252305/nyytgo9oyln4gpwxhqh0.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252309/veirdgpkm636ujmcuwcb.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252345/qdjjvejzjoofpdmbmzk9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252341/orcp3gqvyekxk4u2rwk2.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252345/gro4dkgj8mxfvmdc55fu.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252349/v6dvkfe0kq1azslvqszg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252353/pcd9tspgvfaisqybm5lc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252357/yn04pl8chvwoqitpatvt.png"],"steelblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252313/nqlunqt2il4ivgdntmkc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252317/nalieq2cp4rfuduhdgmw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252321/slepxzqdf4hzpgfwbj8t.png"]}</t>
-  </si>
-  <si>
     <t>blue,black,red,gray,olive,steelblue,green</t>
   </si>
   <si>
@@ -328,12 +316,6 @@
     <t>{"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270323/p6k7eqjzznst2bxrg2vz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270317/t5cdbjnctbumlg675bnh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270319/lggiyj7ykumexocgdg3w.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270300/dph8v8zxcw4oobwmchp6.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270300/wheagvkqjkcca47yvhlb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270301/fo3oopc2w4gguhsxbwky.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270308/gtl37zjvfml3vmuv2o9l.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270313/z5kuunpfvxclcend8okq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270310/kk0wsleipwg1z2mbcqku.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270304/hl9fado9nquhxaicselq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270305/ru5vmxdsif5kt61snx2u.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270306/vodvrpkiopfd6onb91ix.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270311/ku0bx9n4tm9yljlo0wf7.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270321/ojw3mz6n6hix4ube3qne.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270316/fg6dnjtwpxwm4hoghz91.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270325/eduy6ep0xxc17tqusqq2.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270329/gvwagkni5jgyouq7z2oc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270326/r9qvdtgbdeyir30bac22.png"],"royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270330/z2mavjespmfokq9blbck.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270335/amahc57ashuhn1en1uus.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270333/uqc0lg7dkqsbpk9lul2p.png"],"mediumblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270341/fmj9dftl1oejpyyv9f5e.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270341/nc1781x31vupdepm9piz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773270343/kh5eadc7awmjbgrychhh.png"]}</t>
   </si>
   <si>
-    <t>olive,red,green,blue,crimson,purple,yellow</t>
-  </si>
-  <si>
-    <t>{"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252930/hbihvyjdkb8dxbqi74t8.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252843/qd84u0bkum5jcn3bvq7c.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252844/maugsjv6quoobzfjppfd.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252938/phsxzm7ep4futpsiaqfn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252943/i07ow5pr2c7f4dr4vspg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252988/ldk3mkqfk7ujpqax1zyj.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252828/mq1rp9spdu64l9xdgndo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252834/ncwp3pociq94agob9dui.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252836/jtnk3zok8seesgoiany4.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252798/tnp7j6yaab4gbw7otzib.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252803/ivfco3xf0tlsj3hraeoq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252806/xja0nunxmuk8e7eswxem.png"],"crimson":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252784/uxqckf6soklrbzlpxive.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252788/rqpzcxnhpqndorf3tbez.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252793/c1hlcxr1blya15vl4jkg.png"],"purple":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252772/x0xkb8qhi69mkgbztqvj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252775/hmaeweoghycujhmevatq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252779/cbtiwseig4xigz1wburo.png"],"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252759/ixpuoagsxmh3kocrh0ya.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252763/kgpljnb5krrqagxy1bei.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252767/qonnjw4i4dzwbmhfcqbj.png"]}</t>
-  </si>
-  <si>
     <t>Rompevientos Clásica.</t>
   </si>
   <si>
@@ -379,12 +361,6 @@
     <t>{"mediumblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240533/n60eaikcezvynntuau0v.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240528/zyo9kzojtxho9wvesmrp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240531/ooyr3pz6uhvfsm77ejvk.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240532/bz2psdzgpyuyvjzjsdel.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240534/ub1joafbr0olhdtmbw0i.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240535/lwawv9dqvmiu5lxu728m.png"],"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240515/p9y8b9e5niqyywlk9sui.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240516/jp1rmju1wb5fxw9bxn3n.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240517/aafn2qd9tgpmekskj9vh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240517/mudhcxxp6flsivis2qbr.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240522/zfl1xwdjcwzcxpwwbqdw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240523/vgozlwbmddque7ctdpxu.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240525/ypie8z5xidufdlcheiso.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240520/gsfb4nwft4oko0lkclv1.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240519/xurbgbhtwpunfux4x3tq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240520/vyqamob8xq85rfqkr6q1.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240526/cxrgavd3mfsemkwkyatd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240527/zdq90d5lcagyjfdkjji5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240526/nqsgpezieko4rfklfth6.png"],"royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240540/ytouuhvitxe4wl7xmgcz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240541/geo8emnkqncogehf5qxb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240540/risndn1ndpkwnagacnsn.png"]}</t>
   </si>
   <si>
-    <t>sienna,red,green,blue,pink,purple,gray,darkblue,aqua</t>
-  </si>
-  <si>
-    <t>{"sienna":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204571/rkcauwdzs6jgeratl9ec.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204568/ioxhqy5xy0oq1wrhcehu.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204569/oan5nrqbfsqypbeqhidt.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204561/duwq6qi8wfrgp89mpbjs.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204559/ighobxv0gxjbzoumdgwk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204563/wmvhsdj73gzsnleekcpg.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204562/rt4qwaidcxlpqw6cwrzv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204566/k2ua1gohhgtkercwdprk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204566/k2ua1gohhgtkercwdprk.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204601/fyv4gkv15lax7lkjfnv4.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204605/e7jhnqd8biahfavjhslb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204605/lcvfgcxmp4g1ebktlowf.png"],"pink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204572/wgz1hj8fbajhl7tqdmkj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204574/ugaqohzi2jyghldh16jd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204575/wuewltpzlrn9adwlqi4r.png"],"purple":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204578/nexkekptxpmwl9q8xbxr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204579/rudlg0lfwojkamq3j5r9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204581/bgnzj1fc2szshj73adbd.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204583/kgqpcl63triyw4gbq666.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204585/vkhr8xo08dv8kecffzzj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204589/vbhopcissflqgso8ti1c.png"],"darkblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204563/ovbge4jhaovvni5tbm8o.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204594/hwjqfa14rugvedj5pzny.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204595/fvw0ygqxpslajts5lyei.png"],"aqua":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204594/jg4rp3seg4qdctunm5iz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204600/e5w5h2dbbth6byeel0zx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204600/ermpdq0pnvgsdeh1lwfx.png"]}</t>
-  </si>
-  <si>
     <t>aqua,white,orange,lime,red,blue,black,darkblue,pink</t>
   </si>
   <si>
@@ -431,9 +407,6 @@
   </si>
   <si>
     <t>{"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205752/mfwiprr6tvgovwpuue2v.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205755/cnpmodwwbutausd84kzo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205754/vuzoeqyobfg2u01bmwry.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205752/m1pbnbpak4qv1eurewfs.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205758/yii0fqmgiqr2vcn6jobs.png"]}</t>
-  </si>
-  <si>
-    <t>{"deepink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253062/zptpktvgxg3f8kktmdoc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253054/lgmv12q6kdnnihthu2c5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253058/esrhz9htyzmbtw8lprlb.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253066/cu60ygho9ju8nhgs9u0i.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253071/yxibzfzbdieldwpk4rj6.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253075/pzfosnwlpivkyqw3spua.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253175/wy1mdakj1rgi8npqbnes.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253179/j1pocuccycfwko4n1lvc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253183/us4odbmjtwnoosljrf4i.png"],"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253188/mxfmivtle98ap5ucsrqh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253192/unqydmy6xqan8ns2c8w9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253196/uoy5ksbucjxis24dmvjg.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253201/ayeeoh6cxmydwakscp1e.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253205/za5icspaghp6ejbvcv0f.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253210/amsnseat5x3qul0ced8w.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253214/kxwpnvvjy9srtea3vnjo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253218/lxluzyp8ltavizaho5kh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253223/meumpynjfc5fiidbslqz.png"],"steelblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253228/hhj9g92uudrv9rka6fsq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253232/xjvbxl1bpa8jjedw0pg5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253237/pte8vrflbtvl8mami0jk.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253242/wvcutbu8mdpijx9ue7uq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253246/mqiabyzb4qz1d6andsuz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253251/muflvb9qdzympgejtlam.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253256/bvykxavqeornwqnln7qo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253260/dmhygcjblo6xnn6yhclc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253265/k2adwky6ak2i5jdiobl5.png"]}</t>
   </si>
   <si>
     <r>
@@ -1676,9 +1649,6 @@
     <t>blue,red,white,darkgreen,black,darkred,palegreen,crimson,mediumblue,olive</t>
   </si>
   <si>
-    <t>Chaqueta Publicidad</t>
-  </si>
-  <si>
     <t>green,white,red,gray</t>
   </si>
   <si>
@@ -2182,6 +2152,455 @@
   </si>
   <si>
     <t>black,blue,gray,green,darkblue,pink</t>
+  </si>
+  <si>
+    <t>Chaqueta para Publicidad</t>
+  </si>
+  <si>
+    <t>olive,red,green,blue,crimson,purple,yellow,lime,darkblue,darkgreen,black,gray</t>
+  </si>
+  <si>
+    <t>{
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252930/hbihvyjdkb8dxbqi74t8.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252843/qd84u0bkum5jcn3bvq7c.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252844/maugsjv6quoobzfjppfd.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252938/phsxzm7ep4futpsiaqfn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252943/i07ow5pr2c7f4dr4vspg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252988/ldk3mkqfk7ujpqax1zyj.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252828/mq1rp9spdu64l9xdgndo.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252834/ncwp3pociq94agob9dui.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252836/jtnk3zok8seesgoiany4.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252798/tnp7j6yaab4gbw7otzib.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252803/ivfco3xf0tlsj3hraeoq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252806/xja0nunxmuk8e7eswxem.png"
+  ],
+  "crimson": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252784/uxqckf6soklrbzlpxive.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252788/rqpzcxnhpqndorf3tbez.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252793/c1hlcxr1blya15vl4jkg.png"
+  ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252772/x0xkb8qhi69mkgbztqvj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252775/hmaeweoghycujhmevatq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252779/cbtiwseig4xigz1wburo.png"
+  ],
+  "yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252759/ixpuoagsxmh3kocrh0ya.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252763/kgpljnb5krrqagxy1bei.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252767/qonnjw4i4dzwbmhfcqbj.png"
+  ], "lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774897688/wv06bsrronrpwqxzr22w.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774897683/llswxh9qbif94sf9wjfk.png"], "darkblue": ["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774897683/edqokqjugekbz9jnuwvj.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774897682/nrlon8hupqywjq8ngnxg.png"], "darkgreen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774897682/x5fpmvk8m0psgnliqmuk.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774897682/blhhswsy0xb9ub1slbry.png"], "black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774897682/lmd2c9igwnevxewfppbf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774897682/ff82df29ylhfuxkposql.png"], "gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774897683/bwa7mpvesmxiewqty3yu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774897683/jqtier0gqdukwlmqb2ly.png"]
+}</t>
+  </si>
+  <si>
+    <t>Rompevientos Crop Top</t>
+  </si>
+  <si>
+    <t>pink,darkpink,purple,black,gray,blue,darkblue,red</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774920092/tldq99qpyn1ra73nwahh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774920093/ywmbj8wp2yzwbswtfy9x.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774920095/fyqllkbzbbkr4nt6pucr.png"],
+     "darkpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774920093/riju7ocfjr0g0wpcgr07.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774920092/nzxdvnhx0lwsttmlxl0u.png"
+     ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774920095/nc6khea38p1tixaofliz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774920092/emjqzbx9wnokkaqhglt3.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774920094/ra8f39fnfuputhnheuba.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774920092/hc8xsvfc2j0cgxljrama.png"
+     ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774920095/s5iri3trqnge8rc1crqz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774920096/vol9monxrip7w8cebynp.png"
+  ], "blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774920093/ut885acsr0hzisy2zvh2.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774920094/gll7jo37wo5efr2hzyus.png"], "darkblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774920093/jbvfvhn0o1ygolrevook.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774920093/owgsleg1049gchu4x0sd.png"], "red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774920092/q2aobrjsvhllgnyuhwka.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774920092/obrwyduezm41xqthxiai.png"]
+}</t>
+  </si>
+  <si>
+    <t>green,red,blue,black,steelblue,darkgreen,gray,darkblue</t>
+  </si>
+  <si>
+    <t>{
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252333/osa3ymwwye7jeb8ildet.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252325/doe9jefe7loznqbux6da.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252330/x01eyusrbndxewf4jkxz.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252301/jbgk24ihrhe9nvxumrnf.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252305/nyytgo9oyln4gpwxhqh0.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252309/veirdgpkm636ujmcuwcb.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252345/qdjjvejzjoofpdmbmzk9.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252341/orcp3gqvyekxk4u2rwk2.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252345/gro4dkgj8mxfvmdc55fu.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252349/v6dvkfe0kq1azslvqszg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252353/pcd9tspgvfaisqybm5lc.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252357/yn04pl8chvwoqitpatvt.png"
+  ],
+  "steelblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252313/nqlunqt2il4ivgdntmkc.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252317/nalieq2cp4rfuduhdgmw.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773252321/slepxzqdf4hzpgfwbj8t.png"
+  ],
+  "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774925500/h9vw82zugdp4bxbsdvsr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774925500/tsqxkzhztmqqtpr1scta.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774925499/ouzel6uee1bak2duq5ln.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774925500/xujjkm37o2dphullecsp.png"
+  ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774925499/vy6qtyipn9urwyqaj1ff.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774925499/wzkcnun8bbhuuz1uwmza.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>Conjunto Crop Top Manga Larga</t>
+  </si>
+  <si>
+    <t>gray,red,yellow,blue,orange,darkblue,olive,deepink,white,black</t>
+  </si>
+  <si>
+    <t>pink,red,green,blue,sienna,purple,gray,darkblue,aqua</t>
+  </si>
+  <si>
+    <t>{ "red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775016547/zx4ehulzrf1wsxwctbiy.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775016545/lcsfzgejsyq8zgyjqm7n.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775016547/ox1jq4rlg4ge3givbnix.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775016548/gr9awglqvtmkogejavsj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775016550/a3ukiv2vhnyvaeseale9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775016547/ngmu88yvr4m1vemuw1t4.png"]}</t>
+  </si>
+  <si>
+    <t>blue,red</t>
+  </si>
+  <si>
+    <t>{ "blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775016548/gr9awglqvtmkogejavsj.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775016550/a3ukiv2vhnyvaeseale9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775016547/ngmu88yvr4m1vemuw1t4.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775016547/zx4ehulzrf1wsxwctbiy.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775016545/lcsfzgejsyq8zgyjqm7n.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775016547/ox1jq4rlg4ge3givbnix.png"]}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	orange,deepink,blue,yellow,red,black,steelblue,olive,gray</t>
+  </si>
+  <si>
+    <t>{
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253075/pzfosnwlpivkyqw3spua.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775018475/frph6lulhfimuqc1ivva.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775018477/t0qaz0uwoufzx43evrbs.png"
+  ],
+  "deepink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775018474/rinouati6vh8r1tpypgk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775018476/i7rawyyhhmtclkyyg4pr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253062/zptpktvgxg3f8kktmdoc.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775018488/c6tsd3ry8txrwsvqkgq0.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775018490/vwaeojsti3u8zgwhtzoq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253237/pte8vrflbtvl8mami0jk.png"
+  ],
+  "yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775018480/nou01x9t5adjjx3apfqr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775018482/xtn0xpseaybqkykxdlnv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253196/uoy5ksbucjxis24dmvjg.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775018483/nuelgvdqalzcerelmsk0.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775018484/mnwd4w6mmqlb9hk6quoq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253210/amsnseat5x3qul0ced8w.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775018487/tlyzwwowmwhow60sc9hk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775018486/qurjg2xrzen2bl8zgma4.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253223/meumpynjfc5fiidbslqz.png"
+  ],
+  "steelblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775018478/icrxqjahytam7kvjvzj4.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775018479/tlekfgyriwaey5ddokt7.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253183/us4odbmjtwnoosljrf4i.png"
+  ],
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775018491/glmei5jektv1g9kvtwdk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775018492/whp6ujuvkilyqzykpdzs.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253251/muflvb9qdzympgejtlam.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775018494/msd4ck8j8hb3p7uuycrk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775018495/t2zp9wfkbdvnubyjl1sv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253265/k2adwky6ak2i5jdiobl5.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015430/upsts48vi2vjofjkyqe3.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015430/ubmscx2cl2dgj9m1un0v.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015430/z7wpam9ayxdog1hn1qsi.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015424/epartcwsim98fumy6jdt.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015423/jwqpjjqtx4ljtgw5npda.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015423/li2pvltkoghpn5krwylu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015423/ekopyrdijx6uk6lugu9r.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015425/szt2kwqc2jajiuyirxsm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015425/x7jbhaeozuhfr2uemrjw.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015425/lfnhkn0e8j1p8n8hwhfn.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015428/msmwgaxiresszmzxpzyl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015428/aeeuqlql8z9q5dtjzgas.png"
+  ],
+  "sienna": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015423/r4txxmcsax1tlczaobyl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015423/twwbpxmv2m2jhrigkvay.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015425/eqvgoex8pwbumacb3xuy.png"
+  ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204581/bgnzj1fc2szshj73adbd.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015427/teylkkhe4kpcouyjmpvh.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015427/xrnajzemlo2vglwbqtyl.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015429/yubjk5a3be4re6ceywu9.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015429/wdzfi2gqo03bfxpdroim.png"
+  ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015425/mwifkie2wkev8hrepynw.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015426/qrqozlfhyyhirnnhmoel.png"   
+  ],
+  "aqua": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015428/smkdydhg3roqwpug4rit.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015428/lzvs5vzarezvzflc87ir.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775015429/zivf0wr34aceyaagpfyf.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995787/wuvmoa4ksbruvc4ailaz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995711/n5gzkrb8xzjocbmyffmj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995711/pe4y3nj8h3n3xnbsujev.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995711/m8tqe26wf4kjz3w7ocmm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995711/afxjvc9nqshvbuu1yhih.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995715/bbixvjzygoh9rugbvkoi.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995716/m46vbm5ej3hbygcqrv78.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995717/izgpolmeh9uvxh2s4iit.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995717/wxzds7vk4ygb7faxuq6d.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995718/bd38cnsrjpm5tds2aevv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995720/szfetzctilo9clyobbd6.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995721/pyal0sycg965kvflvzjd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995721/s3dbmqqgipb4ef1fisfr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995722/mxeyd8llnzu8z7ctqtwy.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995724/icew7lwyapqpvndqoyoj.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995725/r95makzahzvxp1zlmfhp.png"  ],
+  "yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995726/jbwyjdzuifitnpw9lert.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995728/fmt0y3cdn1irvipubvov.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995728/qcxnz6fxg6qd8hywadas.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995731/sdyx0b3iqt1zect5wak2.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995731/mnd9kmvhmmda2ndfhznn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995787/j5wjlyufv1vtolxcdcuq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775019775/xxyhkbfptdrz7nyvgll8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775019773/cdr3qqjmbxrdn91pnwlv.png"  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995732/lpvknac48pvzwhuosx3e.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995733/eze6zp6pi0g5j8c5qvtx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995738/ifrhpbm3ntvd4jsrf7pp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995737/lvrtiqdot2z4hu4xe7kp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995738/oqe7evjxldl21fqtzeoa.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995738/kcqo8qq4nlduquln3d3p.png"  ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995742/cluftg1h32ocrcdsx6cy.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995784/oileum8mispfc5qknht8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995739/tzmlrscvim9aygur65ps.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995746/dimk4o68v8hyx71agbkg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995745/gyvw3ujrq9day6hhjyms.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995745/oh2dsdvyofqkbg3ayxs6.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995746/nl2iwksvpafeei2kzivr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995746/gvk1sxa2cgbo2yhadzff.png"  ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995746/uoystymn9kgyvpke4api.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995754/jvpqutvswrfa8qxtk3oc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995752/aaicezjsldyce6hhd8e2.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995752/hkiusogui3xb2l78zwvb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995754/lrixm2k76gehujzvhycs.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995794/aoghjspaxv1vmkgag0go.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995756/z0myv21wf2vvd628qai7.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995754/mo5ch782fmeveqeu8gof.png"  ],
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995755/cyrfiqmigtszzxzui1xr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995760/nmhvc2bww8idxlj5mczm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995761/pm0wqbf7uy7oulv67z8t.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995762/r50tpijdg8ubav5gbkwn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995761/lleonfl52ocr2goz72tc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995799/bij8u59zq58is46ku6ai.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995787/xofnsjyuxasr5tg7bnve.png"  ],
+  "deepink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995795/vbhzasn4rzf58jd7b7gv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995761/ig1rhdj0it6e8t47unlg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995762/chjs9bhxoesmdc8fhjwz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995761/gjmyrfudsqvxwmxovcfg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995764/jafusylfx4zttqvgx1nn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995779/xarefpesghacsro02jud.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995768/cgremjm0isscj1cbzkcs.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995770/efxzumnfvzqk7jqaduaz.png"
+  ],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995800/a9tpw8rldaftaqzfqetf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995787/jgj2scgnzrphj9gupqfu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995769/dnyx3yj7n8fvimtvt8xu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995770/h2vv5bo73e0foqkmki8a.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995783/rz5npxw0em5fepprd384.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995797/eydeuvjrc02o6a4dcuib.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995785/c0hx1v05grvxzypu2bay.png"  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995797/vkamzgu2klcz95wcgdzt.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995769/cpapuw1vmn0s2zwdcbjk.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995770/nlt5legcyz7pccodl9di.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995774/vjizkqkw98tn5kkdtffs.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995776/wbf8tblyewiv64qlrz5q.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995778/nb3peywg1hbgzcrbvx9y.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995778/v4ejg7m0wqtaiqd01rbq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995778/edjf8fsatvxhpn3uwcd4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774995790/mibq5hfupsdip1ajk3mn.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>Crop Top con Descote</t>
+  </si>
+  <si>
+    <t>{
+  "lime": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058960/j4hwfg39omrmsgbumnsu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058964/mhync674o585blxwvdyc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058961/yyq7jk4irlchravr3dev.png" ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058962/vdp3howvwlyax6ohv8vd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058964/rsv7rs2wo6p8ld5mcvkk.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058962/nzsrrfrppow5psf7lvbq.png"  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058967/b280yr0frxsovle0u9g5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058965/t9aesv79twou2al2ncy4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058965/w8oglz4lb95uizfdl6ne.png"  ] }</t>
+  </si>
+  <si>
+    <t>lime,black,blue</t>
+  </si>
+  <si>
+    <t>Conjunto Crop Top Abierto</t>
+  </si>
+  <si>
+    <t>{
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059026/onmifetpko1b0gjndapp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059023/wenm9z2fipfewla60ron.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059031/koczsufhszk3drk7jx56.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059027/briqhfrefkcmalx1pyku.png"  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059015/txgflb5clf5vnyjf3mzr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059018/bo3d6f2ipt9ekkp15l2l.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059017/nnyygi4b82dapllc1bdw.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059016/ssdunqdsgjuvgqb1dszt.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059017/ajfzjcqafjx1hpvce7zd.png"  ],
+  "yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059037/s6lunk8xa8httsr1hxw4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059028/xeyoqvolcjjmpxoqrvmf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059021/ci3vxyg9kcefo0qw7lcy.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059031/ugx25bdxsi1mk7n4vqqr.png"  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059035/jr4haifmwcji8qsj5xme.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059029/gboetpjgjylvqgocgzpp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059034/rdzisumreuqgjscci9jq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059024/obskluivg6hjgstlaulu.png"  ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059032/vhcmv456aprgiy446dn6.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059025/e5nxl4qir5yhaed9yqdo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059019/a5g55illcbsffxhfvqnb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059029/kavoqqwjmy9yafoi12mc.png" ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059037/ijccwehjouwytx9pgkeq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059022/oq7wpevcmhvzjiaz74be.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059036/yoku1o7zbrdxv0jnybz9.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059034/u6fuktgwiosi7sxcudfi.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059020/uthzsfqgnu3f8imaxr8v.png"  ],
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059020/flkyahjswijj3lk88l13.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059024/iazxo0xthehnbqugdhkk.png"  ]
+}</t>
+  </si>
+  <si>
+    <t>Crop Top Manga larga Cerrado</t>
+  </si>
+  <si>
+    <t>pink,white,black,blue</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059128/pjlkyjern1y1zwvg2vga.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059135/s0k0eqemtnn0fvbukqyq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059128/sywbky1n3x7blx6ok4dd.png"   ],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059132/lictcvqszim5lkoix4pf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059126/yibq2hprzw3nb1qjgpin.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059132/riufsul5qtfewfsmjivr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059125/uehn07ssalshhlpt15n0.png" ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059130/cweuywulssi1g21qjlha.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059135/yyejdtpl3wyxebuyjypr.png"  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059130/rzbrauywd5fom7yl3qei.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059134/jghb6wimluapnj1q2eyc.png" ]
+}</t>
+  </si>
+  <si>
+    <t>Enterizo 3 huecos</t>
+  </si>
+  <si>
+    <t>blue,white,black</t>
+  </si>
+  <si>
+    <t>{
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059268/evuncxtmygm5csyptekt.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059272/liqkbvjwflzhb2koa34z.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059272/lei3fbrgsctcpt29dfho.png"   ],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059269/ghhmljfs6kudpouvncqj.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059267/moa5vufxs1ijbwigu0n0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059265/j5fwcfnifqcph2jmatvk.png" ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059270/wngrneg7oeu9g89qzn9n.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059274/x7t0b9orxnupxauhhsev.png"  ]}</t>
+  </si>
+  <si>
+    <t>Licra de Pecho (Dama)</t>
+  </si>
+  <si>
+    <t>blue,darkblue,pink,darkred</t>
+  </si>
+  <si>
+    <t>Blusa Traslucida Transpirable</t>
+  </si>
+  <si>
+    <t>green,red,yellow,blue,orange,darkblue,olive</t>
+  </si>
+  <si>
+    <t>{
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059429/mmg65lklgg3e9dtydyhl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059443/zfw6llireyhaajk5a6kq.png"  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059438/psljapk9sp7qdph0cqah.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059433/uwjwjx8yswu3hsyb0qn1.png" ],
+  "yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059442/wpvvjozcxafsud2kkll1.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059430/m0brjd6an7shouebgb0c.png"  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059439/fvdgfb1gwrlr8sm1ntis.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059427/iksrgfaxysxf99aizh1b.png" ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059445/ipmmjkfsz6swiw7c8ogg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059436/gy3pavkl3s1h17ukw6us.png" ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059441/qr9lbfd1zbxxqpnfzoxt.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059431/gmw50w8nsoxpqevpc1qi.png" ],
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059433/srzvpsd68bgrjmy9gkqo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059435/nneim7k9n6eknnwhkjeh.png"  ]}</t>
+  </si>
+  <si>
+    <t>Pantaloneta Rompevientos Dama</t>
+  </si>
+  <si>
+    <t>Conjunto Top de Transparencia</t>
+  </si>
+  <si>
+    <t>{
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058812/wpybvhkk9ugsy6gnxkkm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058811/d8lzuacyktsdlepm9qcd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058811/jdmi9kwuwllmglwhhcbc.png"  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058814/buq9q1wtddmrrkg6iakf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058812/b7emupdqe6witatlqvq4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058814/mkbq6zncote7su95rhag.png" ],
+  "yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058812/d6j3vnuq23pr3pvlqrrc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058813/sldsj7nnpogk2gxufpxz.png", " https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058814/dmsndzjcdeiql1crljdb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058814/etvlgtogg1be4ui79eux.png" ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058814/pwpefqqs0ay3xfzyqep5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058815/vfq45emabazi47rx4wd0.png" ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058815/esequ0cwic5ues3kyrck.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058817/yikzlztavx3gaci9xpfr.png"],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058816/bg7eetec0kwqfntlzhdu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058817/hel3nql1dp0vfvjpieyk.png" ],
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058817/xnmxv2e9memmagybowsd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058816/s6zbit7x8tejpcfnv3s0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058817/wqonc9kcviofhs7qiatn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058818/ht4eo6wpkw58c3zsjttb.png" ]}</t>
+  </si>
+  <si>
+    <t>{
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059351/ms0pfrg6qexy7pvp2b2d.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059359/knvhre2v1jzwh6slg2m7.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059355/hgbv0fwafwvnznmhyojl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059363/gsrwyckhl9luqezcaslx.png"  ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059350/xtdyi9p6tofiwtkhloqe.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059348/j3f4rodcddpddj3kfwxh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059354/lw12cgerhos7zaw30skq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059349/zagwghsa2hsa0waq4pas.png" ],
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059362/yyvtsrgqe5hpel6inc21.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059356/uh9kvnso9qrdufg8tw89.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059361/enrhz3zn92xkzp2rr8vr.png"   ],
+  "darkred": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059353/ab7frk5zgvmu08zhgoge.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059347/npzsyb4l37cwbn5nq01b.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059358/fif9ctysdwwvrvjwn6rc.png"  ]}</t>
+  </si>
+  <si>
+    <t>{
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059497/f1x4zujftw78jgbewye9.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059519/lnjhlfn58bonoblhdrc0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059485/wizkhym3yfsekcfzdbfh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059515/afo8brdibkag4ehazdqi.png"  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059493/psoy8csvowjeuzfi1vmp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059515/gnchbo4jin3ivucaurjg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059481/mrajgjd0gtkgxorklouf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059502/npq8yofij59wrsrkwklx.png" ],
+  "yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059484/stghnytqc2a9fhevuxun.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059506/jeai9uqvfeuh0faglpi7.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059509/cy43cqh1th1lv5fhr2vi.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059511/emejoynhewsuwa7npbpx.png"  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059487/hmxdg8dku1qr0wlivxua.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059503/zvdrdlz8aewey8jjwptw.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059494/y4qnl4ulthtqga5jwx6g.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059520/rojixcboispgqhueym3l.png" ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059488/kspgrbkejuwd3juyctvp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059518/momddqb5tz7g52mpslw6.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059499/q5zxx4tzcnyfzzlrqv5e.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059508/epclqybzhzvkzougb0sm.png" ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059490/ic9xzebgimyoaxqhyzix.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059512/vqecdhjsvu8cuyx9xrfo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059500/hggx6z04ffidgef5skab.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059480/lnu8cs2erpxorsptpuyd.png" ],
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059505/oxvkmenwdhkhzt6qgp9s.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059496/jy8f1zadflmv5d5jwfsp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059482/lafdvqjlenoslzbsx2z0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059491/anzhzbtehfwbipcy2evd.png" ]}</t>
+  </si>
+  <si>
+    <t>Blusa Espalda Cruzada</t>
+  </si>
+  <si>
+    <t>{
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080346/hl5jotv2jpgxcoilqi3i.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080383/sb8mdjgful2vdrharx5b.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080368/mghibebgk0wm3evstryg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080343/tnl1sikyzo71rxkjhxvd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080381/xjdjoxjuftfp3gd6juvk.png" ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080309/tnaay1xy1xyeqr530hrn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080371/utoavvccx2udohqxtb3q.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080377/zwbccwtwwpviyrlgxnfr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080349/nyarlfidpmpkn9fke4b8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080313/qvg6zagtsbegm7hwihil.png" ],
+  "yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080365/lun2yv8wwhu7dbwrzsmh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080386/rmqcplamsazrt3svojnb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080315/jjo4pum6c4fac7ha0apl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080337/jjznbh0csokyayg8cvkc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080318/ncio4pxlchcx93ic6uiw.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080335/z1pc2kw3n44tuqnvwojs.png" ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080321/fc5mkgtpg2byw3frgotx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080374/stv6xhitzhorpnsneyda.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080307/og6n27fkckazv6o2pcmx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080357/sisvdcjwfwck063xllhu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080323/iinxyglqkkefn0worohd.png" ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080329/ff8oh5dryuf55kehjanf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080326/sbuh78xzsjunsdeavte3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080341/ypj4nzcjfo0uhwg97iwn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080332/w9g67kinud0b5rkuii5m.png"],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080354/ljf6tbcc6g9owpatbjz4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080351/fxthor7ohopmqbqfi3tm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080377/zwbccwtwwpviyrlgxnfr.png" ]}</t>
+  </si>
+  <si>
+    <t>green,red,yellow,blue,orange,darkblue</t>
+  </si>
+  <si>
+    <t>Jogger en Algodón</t>
+  </si>
+  <si>
+    <t>gray,black,darkblue,olive</t>
+  </si>
+  <si>
+    <t>{
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080255/czlfuvutd72atp0ojhqh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080247/xpw55vkz1revjayfz3zz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080238/itypiaz7qmh7ralcuari.png" ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080241/h3g6polr1fdcf8ygdklb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080252/yzndprsrmahdoeruuzlt.png" ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080244/mlvuk1yzzwhccuyxm6hn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080250/xigvnqz7go87woirjlvb.png" ],
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080236/pxianovllar2lhhacceh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080258/jravrpw6pis8ehszhslp.png" ]}</t>
   </si>
 </sst>
 </file>
@@ -2205,7 +2624,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2248,6 +2667,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2276,7 +2707,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2341,6 +2772,24 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2356,10 +2805,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2647,7 +3092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}">
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="57.54296875" style="2" customWidth="1"/>
@@ -2668,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>1</v>
@@ -2706,10 +3151,10 @@
         <v>16</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>11</v>
@@ -2727,10 +3172,10 @@
         <v>17</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="K2" s="6" t="b">
         <v>0</v>
@@ -2739,15 +3184,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="3" customFormat="1" ht="86.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" s="3" customFormat="1" ht="99.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>11</v>
@@ -2766,7 +3211,7 @@
         <v>70</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>71</v>
+        <v>301</v>
       </c>
       <c r="K3" s="6" t="b">
         <v>0</v>
@@ -2777,13 +3222,13 @@
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="89.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>11</v>
@@ -2801,10 +3246,10 @@
         <v>17</v>
       </c>
       <c r="I4" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>73</v>
       </c>
       <c r="K4" s="6" t="b">
         <v>0</v>
@@ -2818,10 +3263,10 @@
         <v>19</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>20</v>
@@ -2839,11 +3284,11 @@
         <v>17</v>
       </c>
       <c r="I5" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="J5" s="8" t="s">
-        <v>75</v>
-      </c>
       <c r="K5" s="6" t="b">
         <v>0</v>
       </c>
@@ -2851,13 +3296,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="118.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="148.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>11</v>
@@ -2873,10 +3318,10 @@
         <v>14</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>77</v>
+        <v>304</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>136</v>
+        <v>305</v>
       </c>
       <c r="K6" s="6" t="b">
         <v>0</v>
@@ -2891,7 +3336,7 @@
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>11</v>
@@ -2907,10 +3352,10 @@
         <v>12</v>
       </c>
       <c r="I7" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>76</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>78</v>
       </c>
       <c r="K7" s="6" t="b">
         <v>0</v>
@@ -2925,7 +3370,7 @@
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>11</v>
@@ -2943,10 +3388,10 @@
         <v>13</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K8" s="6" t="b">
         <v>0</v>
@@ -2957,11 +3402,11 @@
     </row>
     <row r="9" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>11</v>
@@ -2979,10 +3424,10 @@
         <v>13</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K9" s="6" t="b">
         <v>0</v>
@@ -2997,7 +3442,7 @@
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>11</v>
@@ -3013,10 +3458,10 @@
         <v>14</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K10" s="6" t="b">
         <v>0</v>
@@ -3027,11 +3472,11 @@
     </row>
     <row r="11" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>11</v>
@@ -3047,10 +3492,10 @@
         <v>14</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K11" s="6" t="b">
         <v>0</v>
@@ -3061,11 +3506,11 @@
     </row>
     <row r="12" spans="1:12" ht="47" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>11</v>
@@ -3081,10 +3526,10 @@
         <v>14</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="K12" s="6" t="b">
         <v>0</v>
@@ -3095,11 +3540,11 @@
     </row>
     <row r="13" spans="1:12" ht="47" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>11</v>
@@ -3115,10 +3560,10 @@
         <v>14</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="K13" s="6" t="b">
         <v>0</v>
@@ -3129,11 +3574,11 @@
     </row>
     <row r="14" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>27</v>
@@ -3151,10 +3596,10 @@
         <v>26</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="K14" s="6" t="b">
         <v>0</v>
@@ -3165,11 +3610,11 @@
     </row>
     <row r="15" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>27</v>
@@ -3187,10 +3632,10 @@
         <v>26</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="K15" s="6" t="b">
         <v>0</v>
@@ -3201,11 +3646,11 @@
     </row>
     <row r="16" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>11</v>
@@ -3223,10 +3668,10 @@
         <v>26</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="K16" s="6" t="b">
         <v>0</v>
@@ -3237,11 +3682,11 @@
     </row>
     <row r="17" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>11</v>
@@ -3259,10 +3704,10 @@
         <v>26</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="K17" s="6" t="b">
         <v>0</v>
@@ -3277,7 +3722,7 @@
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>30</v>
@@ -3293,10 +3738,10 @@
         <v>28</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="K18" s="6" t="b">
         <v>0</v>
@@ -3307,7 +3752,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6" t="s">
@@ -3327,10 +3772,10 @@
         <v>28</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="K19" s="6" t="b">
         <v>0</v>
@@ -3341,11 +3786,11 @@
     </row>
     <row r="20" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>11</v>
@@ -3361,10 +3806,10 @@
         <v>14</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="K20" s="6" t="b">
         <v>0</v>
@@ -3379,7 +3824,7 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>11</v>
@@ -3395,10 +3840,10 @@
         <v>14</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="K21" s="6" t="b">
         <v>0</v>
@@ -3413,7 +3858,7 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>11</v>
@@ -3429,10 +3874,10 @@
         <v>32</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="K22" s="6" t="b">
         <v>0</v>
@@ -3447,7 +3892,7 @@
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>11</v>
@@ -3463,10 +3908,10 @@
         <v>14</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="K23" s="6" t="b">
         <v>0</v>
@@ -3481,7 +3926,7 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>11</v>
@@ -3497,10 +3942,10 @@
         <v>14</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="K24" s="6" t="b">
         <v>0</v>
@@ -3509,13 +3954,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>11</v>
@@ -3530,11 +3975,11 @@
       <c r="H25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I25" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="J25" s="12" t="s">
-        <v>91</v>
+      <c r="I25" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>297</v>
       </c>
       <c r="K25" s="6" t="b">
         <v>0</v>
@@ -3543,9 +3988,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
@@ -3565,10 +4010,10 @@
         <v>14</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="J26" s="12" t="s">
-        <v>91</v>
+        <v>296</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>297</v>
       </c>
       <c r="K26" s="6" t="b">
         <v>0</v>
@@ -3583,7 +4028,7 @@
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>11</v>
@@ -3599,10 +4044,10 @@
         <v>14</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>70</v>
+        <v>302</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>71</v>
+        <v>303</v>
       </c>
       <c r="K27" s="6" t="b">
         <v>0</v>
@@ -3617,7 +4062,7 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>11</v>
@@ -3633,10 +4078,10 @@
         <v>14</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="K28" s="6" t="b">
         <v>0</v>
@@ -3647,7 +4092,7 @@
     </row>
     <row r="29" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
@@ -3667,10 +4112,10 @@
         <v>41</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="K29" s="6" t="b">
         <v>0</v>
@@ -3681,7 +4126,7 @@
     </row>
     <row r="30" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6" t="s">
@@ -3701,10 +4146,10 @@
         <v>41</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K30" s="6" t="b">
         <v>0</v>
@@ -3737,10 +4182,10 @@
         <v>44</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="K31" s="6" t="b">
         <v>0</v>
@@ -3773,10 +4218,10 @@
         <v>45</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K32" s="6" t="b">
         <v>0</v>
@@ -3807,10 +4252,10 @@
         <v>14</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="K33" s="6" t="b">
         <v>0</v>
@@ -3819,7 +4264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>48</v>
       </c>
@@ -3840,11 +4285,11 @@
       <c r="H34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I34" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="J34" s="12" t="s">
-        <v>102</v>
+      <c r="I34" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>292</v>
       </c>
       <c r="K34" s="6" t="b">
         <v>0</v>
@@ -3855,7 +4300,7 @@
     </row>
     <row r="35" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6" t="s">
@@ -3868,7 +4313,7 @@
         <v>17000</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G35" s="6">
         <v>34000</v>
@@ -3877,10 +4322,10 @@
         <v>41</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="K35" s="6" t="b">
         <v>0</v>
@@ -3891,7 +4336,7 @@
     </row>
     <row r="36" spans="1:12" ht="126.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6" t="s">
@@ -3904,7 +4349,7 @@
         <v>17000</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G36" s="6">
         <v>34000</v>
@@ -3913,10 +4358,10 @@
         <v>41</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="K36" s="6" t="b">
         <v>0</v>
@@ -3927,7 +4372,7 @@
     </row>
     <row r="37" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6" t="s">
@@ -3940,7 +4385,7 @@
         <v>17000</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G37" s="6">
         <v>34000</v>
@@ -3949,10 +4394,10 @@
         <v>41</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="K37" s="6" t="b">
         <v>0</v>
@@ -3963,7 +4408,7 @@
     </row>
     <row r="38" spans="1:12" ht="91" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6" t="s">
@@ -3976,7 +4421,7 @@
         <v>17000</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G38" s="6">
         <v>34000</v>
@@ -3985,10 +4430,10 @@
         <v>41</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K38" s="6" t="b">
         <v>0</v>
@@ -3999,7 +4444,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
@@ -4019,10 +4464,10 @@
         <v>52</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="K39" s="6" t="b">
         <v>0</v>
@@ -4053,10 +4498,10 @@
         <v>52</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="K40" s="6" t="b">
         <v>0</v>
@@ -4087,10 +4532,10 @@
         <v>14</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="J41" s="14" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K41" s="6" t="b">
         <v>0</v>
@@ -4101,7 +4546,7 @@
     </row>
     <row r="42" spans="1:12" ht="98.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
@@ -4121,10 +4566,10 @@
         <v>45</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="J42" s="15" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="K42" s="6" t="b">
         <v>0</v>
@@ -4155,10 +4600,10 @@
         <v>45</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="K43" s="6" t="b">
         <v>0</v>
@@ -4189,10 +4634,10 @@
         <v>14</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>118</v>
+        <v>300</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>119</v>
+        <v>306</v>
       </c>
       <c r="K44" s="6" t="b">
         <v>0</v>
@@ -4225,10 +4670,10 @@
         <v>56</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="K45" s="6" t="b">
         <v>0</v>
@@ -4259,10 +4704,10 @@
         <v>59</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="K46" s="6" t="b">
         <v>0</v>
@@ -4293,10 +4738,10 @@
         <v>13</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="K47" s="6" t="b">
         <v>0</v>
@@ -4307,7 +4752,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6" t="s">
@@ -4327,10 +4772,10 @@
         <v>61</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K48" s="6" t="b">
         <v>0</v>
@@ -4361,10 +4806,10 @@
         <v>12</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="K49" s="6" t="b">
         <v>0</v>
@@ -4379,7 +4824,7 @@
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>11</v>
@@ -4395,10 +4840,10 @@
         <v>12</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="K50" s="6" t="b">
         <v>0</v>
@@ -4429,10 +4874,10 @@
         <v>12</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="K51" s="6" t="b">
         <v>0</v>
@@ -4463,10 +4908,10 @@
         <v>14</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="J52" s="15" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="K52" s="6" t="b">
         <v>0</v>
@@ -4481,7 +4926,7 @@
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>11</v>
@@ -4497,10 +4942,10 @@
         <v>14</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="K53" s="6" t="b">
         <v>0</v>
@@ -4515,7 +4960,7 @@
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>11</v>
@@ -4531,10 +4976,10 @@
         <v>14</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="K54" s="6" t="b">
         <v>0</v>
@@ -4549,7 +4994,7 @@
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>11</v>
@@ -4565,10 +5010,10 @@
         <v>14</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="K55" s="6" t="b">
         <v>0</v>
@@ -4583,7 +5028,7 @@
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>11</v>
@@ -4599,10 +5044,10 @@
         <v>32</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="K56" s="6" t="b">
         <v>0</v>
@@ -4613,11 +5058,11 @@
     </row>
     <row r="57" spans="1:12" ht="377" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>11</v>
@@ -4626,7 +5071,7 @@
         <v>22000</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="G57" s="6">
         <v>27000</v>
@@ -4635,10 +5080,10 @@
         <v>17</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="K57" s="6" t="b">
         <v>0</v>
@@ -4649,11 +5094,11 @@
     </row>
     <row r="58" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A58" s="16" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B58" s="16"/>
       <c r="C58" s="16" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D58" s="16" t="s">
         <v>27</v>
@@ -4669,10 +5114,10 @@
         <v>14</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="J58" s="18" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="K58" s="19" t="b">
         <v>0</v>
@@ -4683,11 +5128,11 @@
     </row>
     <row r="59" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A59" s="16" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="B59" s="16"/>
       <c r="C59" s="16" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D59" s="16" t="s">
         <v>20</v>
@@ -4703,10 +5148,10 @@
         <v>14</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="J59" s="18" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="K59" s="19" t="b">
         <v>0</v>
@@ -4717,11 +5162,11 @@
     </row>
     <row r="60" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A60" s="16" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="B60" s="16"/>
       <c r="C60" s="16" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D60" s="16" t="s">
         <v>20</v>
@@ -4737,10 +5182,10 @@
         <v>14</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="J60" s="18" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="K60" s="19" t="b">
         <v>0</v>
@@ -4751,11 +5196,11 @@
     </row>
     <row r="61" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A61" s="16" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="B61" s="16"/>
       <c r="C61" s="16" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D61" s="16" t="s">
         <v>20</v>
@@ -4771,10 +5216,10 @@
         <v>14</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="J61" s="18" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="K61" s="19" t="b">
         <v>0</v>
@@ -4785,11 +5230,11 @@
     </row>
     <row r="62" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A62" s="16" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B62" s="16"/>
       <c r="C62" s="16" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D62" s="16" t="s">
         <v>20</v>
@@ -4805,10 +5250,10 @@
         <v>14</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="J62" s="18" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="K62" s="19" t="b">
         <v>0</v>
@@ -4819,11 +5264,11 @@
     </row>
     <row r="63" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A63" s="16" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="B63" s="16"/>
       <c r="C63" s="16" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="D63" s="16" t="s">
         <v>20</v>
@@ -4839,10 +5284,10 @@
         <v>14</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="J63" s="18" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="K63" s="19" t="b">
         <v>0</v>
@@ -4853,11 +5298,11 @@
     </row>
     <row r="64" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A64" s="16" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B64" s="16"/>
       <c r="C64" s="16" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="D64" s="16" t="s">
         <v>20</v>
@@ -4873,10 +5318,10 @@
         <v>14</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="J64" s="18" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="K64" s="19" t="b">
         <v>0</v>
@@ -4887,11 +5332,11 @@
     </row>
     <row r="65" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A65" s="16" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B65" s="16"/>
       <c r="C65" s="16" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D65" s="16" t="s">
         <v>20</v>
@@ -4907,10 +5352,10 @@
         <v>14</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="J65" s="18" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K65" s="19" t="b">
         <v>0</v>
@@ -4921,11 +5366,11 @@
     </row>
     <row r="66" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A66" s="16" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B66" s="16"/>
       <c r="C66" s="16" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D66" s="16" t="s">
         <v>20</v>
@@ -4941,10 +5386,10 @@
         <v>14</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="J66" s="18" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="K66" s="19" t="b">
         <v>0</v>
@@ -4955,11 +5400,11 @@
     </row>
     <row r="67" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A67" s="16" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B67" s="16"/>
       <c r="C67" s="16" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D67" s="16" t="s">
         <v>20</v>
@@ -4975,10 +5420,10 @@
         <v>14</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="J67" s="18" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="K67" s="19" t="b">
         <v>0</v>
@@ -4989,11 +5434,11 @@
     </row>
     <row r="68" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A68" s="16" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B68" s="16"/>
       <c r="C68" s="16" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D68" s="16" t="s">
         <v>20</v>
@@ -5009,10 +5454,10 @@
         <v>14</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="J68" s="18" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="K68" s="19" t="b">
         <v>0</v>
@@ -5023,11 +5468,11 @@
     </row>
     <row r="69" spans="1:12" ht="406" x14ac:dyDescent="0.35">
       <c r="A69" s="16" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="B69" s="16"/>
       <c r="C69" s="16" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D69" s="16" t="s">
         <v>20</v>
@@ -5043,10 +5488,10 @@
         <v>14</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="J69" s="18" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="K69" s="19" t="b">
         <v>0</v>
@@ -5057,11 +5502,11 @@
     </row>
     <row r="70" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A70" s="16" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="B70" s="16"/>
       <c r="C70" s="16" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="D70" s="16" t="s">
         <v>20</v>
@@ -5077,10 +5522,10 @@
         <v>14</v>
       </c>
       <c r="I70" s="16" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="K70" s="19" t="b">
         <v>0</v>
@@ -5091,11 +5536,11 @@
     </row>
     <row r="71" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A71" s="16" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="B71" s="16"/>
       <c r="C71" s="16" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="D71" s="16" t="s">
         <v>20</v>
@@ -5111,10 +5556,10 @@
         <v>14</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="J71" s="18" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="K71" s="19" t="b">
         <v>0</v>
@@ -5125,11 +5570,11 @@
     </row>
     <row r="72" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A72" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B72" s="16"/>
       <c r="C72" s="16" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D72" s="16" t="s">
         <v>20</v>
@@ -5145,10 +5590,10 @@
         <v>14</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="J72" s="18" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="K72" s="19" t="b">
         <v>0</v>
@@ -5159,11 +5604,11 @@
     </row>
     <row r="73" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A73" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B73" s="16"/>
       <c r="C73" s="16" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D73" s="16" t="s">
         <v>20</v>
@@ -5179,10 +5624,10 @@
         <v>14</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="J73" s="18" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="K73" s="19" t="b">
         <v>0</v>
@@ -5193,13 +5638,13 @@
     </row>
     <row r="74" spans="1:12" ht="319" x14ac:dyDescent="0.35">
       <c r="A74" s="16" t="s">
-        <v>234</v>
+        <v>290</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="D74" s="16" t="s">
         <v>11</v>
@@ -5212,13 +5657,13 @@
         <v>34000</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="I74" s="16" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="J74" s="18" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="K74" s="19" t="b">
         <v>0</v>
@@ -5229,11 +5674,11 @@
     </row>
     <row r="75" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A75" s="16" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B75" s="16"/>
       <c r="C75" s="16" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D75" s="16" t="s">
         <v>20</v>
@@ -5249,10 +5694,10 @@
         <v>14</v>
       </c>
       <c r="I75" s="16" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="J75" s="18" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="K75" s="19" t="b">
         <v>0</v>
@@ -5263,11 +5708,11 @@
     </row>
     <row r="76" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A76" s="16" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="B76" s="16"/>
       <c r="C76" s="16" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D76" s="16" t="s">
         <v>20</v>
@@ -5283,10 +5728,10 @@
         <v>14</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="K76" s="19" t="b">
         <v>0</v>
@@ -5297,11 +5742,11 @@
     </row>
     <row r="77" spans="1:12" ht="87" x14ac:dyDescent="0.35">
       <c r="A77" s="16" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="B77" s="16"/>
       <c r="C77" s="16" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D77" s="16" t="s">
         <v>20</v>
@@ -5317,10 +5762,10 @@
         <v>14</v>
       </c>
       <c r="I77" s="16" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="J77" s="18" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="K77" s="19" t="b">
         <v>0</v>
@@ -5331,13 +5776,13 @@
     </row>
     <row r="78" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A78" s="16" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D78" s="16" t="s">
         <v>20</v>
@@ -5353,10 +5798,10 @@
         <v>14</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="J78" s="18" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="K78" s="19" t="b">
         <v>0</v>
@@ -5367,13 +5812,13 @@
     </row>
     <row r="79" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A79" s="16" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D79" s="16" t="s">
         <v>20</v>
@@ -5389,10 +5834,10 @@
         <v>14</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="J79" s="18" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="K79" s="19" t="b">
         <v>0</v>
@@ -5403,11 +5848,11 @@
     </row>
     <row r="80" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A80" s="16" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="B80" s="16"/>
       <c r="C80" s="16" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D80" s="16" t="s">
         <v>20</v>
@@ -5423,10 +5868,10 @@
         <v>14</v>
       </c>
       <c r="I80" s="16" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="K80" s="19" t="b">
         <v>0</v>
@@ -5437,11 +5882,11 @@
     </row>
     <row r="81" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A81" s="16" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="B81" s="16"/>
       <c r="C81" s="16" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D81" s="16" t="s">
         <v>20</v>
@@ -5457,10 +5902,10 @@
         <v>14</v>
       </c>
       <c r="I81" s="16" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="J81" s="17" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="K81" s="19" t="b">
         <v>0</v>
@@ -5471,11 +5916,11 @@
     </row>
     <row r="82" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A82" s="16" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="B82" s="16"/>
       <c r="C82" s="16" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D82" s="16" t="s">
         <v>20</v>
@@ -5491,10 +5936,10 @@
         <v>14</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="J82" s="18" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="K82" s="19" t="b">
         <v>0</v>
@@ -5505,11 +5950,11 @@
     </row>
     <row r="83" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A83" s="16" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="B83" s="16"/>
       <c r="C83" s="16" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D83" s="16" t="s">
         <v>20</v>
@@ -5525,10 +5970,10 @@
         <v>14</v>
       </c>
       <c r="I83" s="17" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="J83" s="21" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="K83" s="19" t="b">
         <v>0</v>
@@ -5539,11 +5984,11 @@
     </row>
     <row r="84" spans="1:12" ht="261" x14ac:dyDescent="0.35">
       <c r="A84" s="16" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="B84" s="16"/>
       <c r="C84" s="16" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D84" s="16" t="s">
         <v>20</v>
@@ -5559,10 +6004,10 @@
         <v>14</v>
       </c>
       <c r="I84" s="16" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="J84" s="21" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="K84" s="19" t="b">
         <v>0</v>
@@ -5573,11 +6018,11 @@
     </row>
     <row r="85" spans="1:12" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A85" s="16" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="B85" s="16"/>
       <c r="C85" s="16" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="D85" s="16" t="s">
         <v>20</v>
@@ -5586,7 +6031,7 @@
         <v>25000</v>
       </c>
       <c r="F85" s="17" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="G85" s="16">
         <v>36000</v>
@@ -5595,10 +6040,10 @@
         <v>13</v>
       </c>
       <c r="I85" s="16" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="J85" s="21" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="K85" s="19" t="b">
         <v>0</v>
@@ -5609,11 +6054,11 @@
     </row>
     <row r="86" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A86" s="16" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="B86" s="16"/>
       <c r="C86" s="16" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D86" s="16" t="s">
         <v>20</v>
@@ -5629,10 +6074,10 @@
         <v>14</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="J86" s="21" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="K86" s="19" t="b">
         <v>0</v>
@@ -5643,11 +6088,11 @@
     </row>
     <row r="87" spans="1:12" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>11</v>
@@ -5663,10 +6108,10 @@
         <v>12</v>
       </c>
       <c r="I87" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J87" s="11" t="s">
         <v>76</v>
-      </c>
-      <c r="J87" s="11" t="s">
-        <v>78</v>
       </c>
       <c r="K87" s="6" t="b">
         <v>0</v>
@@ -5677,7 +6122,7 @@
     </row>
     <row r="88" spans="1:12" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A88" s="6" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6" t="s">
@@ -5694,13 +6139,13 @@
         <v>27000</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="I88" s="7" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="J88" s="22" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="K88" s="6" t="b">
         <v>0</v>
@@ -5711,7 +6156,7 @@
     </row>
     <row r="89" spans="1:12" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A89" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6" t="s">
@@ -5731,10 +6176,10 @@
         <v>14</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="J89" s="22" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="K89" s="6" t="b">
         <v>0</v>
@@ -5745,11 +6190,11 @@
     </row>
     <row r="90" spans="1:12" ht="319" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>11</v>
@@ -5765,10 +6210,10 @@
         <v>12</v>
       </c>
       <c r="I90" s="7" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="J90" s="8" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="K90" s="6" t="b">
         <v>0</v>
@@ -5779,11 +6224,11 @@
     </row>
     <row r="91" spans="1:12" ht="319" x14ac:dyDescent="0.35">
       <c r="A91" s="23" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="B91" s="23"/>
       <c r="C91" s="23" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="D91" s="23" t="s">
         <v>11</v>
@@ -5796,30 +6241,428 @@
         <v>45000</v>
       </c>
       <c r="H91" s="23" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="I91" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="J91" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="K91" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L91" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="391.5" x14ac:dyDescent="0.35">
+      <c r="A92" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="B92" s="23"/>
+      <c r="C92" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E92" s="23">
+        <v>18000</v>
+      </c>
+      <c r="F92" s="23"/>
+      <c r="G92" s="23">
+        <v>27500</v>
+      </c>
+      <c r="H92" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I92" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="J92" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="K92" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L92" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A93" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="B93" s="23"/>
+      <c r="C93" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="D93" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E93" s="23">
+        <v>29000</v>
+      </c>
+      <c r="F93" s="23"/>
+      <c r="G93" s="23">
+        <v>43500</v>
+      </c>
+      <c r="H93" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I93" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="J91" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="K91" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L91" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A92" s="23"/>
-      <c r="B92" s="23"/>
-      <c r="C92" s="23"/>
-      <c r="D92" s="23"/>
-      <c r="E92" s="23"/>
-      <c r="F92" s="23"/>
-      <c r="G92" s="23"/>
-      <c r="H92" s="23"/>
+      <c r="J93" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="K93" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L93" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A94" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="B94" s="25"/>
+      <c r="C94" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="D94" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E94" s="25">
+        <v>14000</v>
+      </c>
+      <c r="F94" s="25"/>
+      <c r="G94" s="25">
+        <v>18000</v>
+      </c>
+      <c r="H94" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I94" s="25" t="s">
+        <v>310</v>
+      </c>
+      <c r="J94" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="K94" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L94" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A95" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="B95" s="25"/>
+      <c r="C95" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="D95" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E95" s="25">
+        <v>15000</v>
+      </c>
+      <c r="F95" s="25"/>
+      <c r="G95" s="25">
+        <v>15000</v>
+      </c>
+      <c r="H95" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="I95" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="J95" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="K95" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L95" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="261" x14ac:dyDescent="0.35">
+      <c r="A96" s="25" t="s">
+        <v>313</v>
+      </c>
+      <c r="B96" s="25"/>
+      <c r="C96" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="D96" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E96" s="25">
+        <v>15000</v>
+      </c>
+      <c r="F96" s="25"/>
+      <c r="G96" s="25">
+        <v>20000</v>
+      </c>
+      <c r="H96" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I96" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="J96" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="K96" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L96" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="174" x14ac:dyDescent="0.35">
+      <c r="A97" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="B97" s="25"/>
+      <c r="C97" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="D97" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E97" s="25">
+        <v>24000</v>
+      </c>
+      <c r="F97" s="25"/>
+      <c r="G97" s="25">
+        <v>36000</v>
+      </c>
+      <c r="H97" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I97" s="25" t="s">
+        <v>317</v>
+      </c>
+      <c r="J97" s="26" t="s">
+        <v>318</v>
+      </c>
+      <c r="K97" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L97" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A98" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="B98" s="25"/>
+      <c r="C98" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="D98" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E98" s="25">
+        <v>19000</v>
+      </c>
+      <c r="F98" s="25"/>
+      <c r="G98" s="25">
+        <v>19000</v>
+      </c>
+      <c r="H98" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I98" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="J98" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="K98" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L98" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="319" x14ac:dyDescent="0.35">
+      <c r="A99" s="25" t="s">
+        <v>321</v>
+      </c>
+      <c r="B99" s="25"/>
+      <c r="C99" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="D99" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E99" s="25">
+        <v>12000</v>
+      </c>
+      <c r="F99" s="25"/>
+      <c r="G99" s="25">
+        <v>16000</v>
+      </c>
+      <c r="H99" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I99" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="J99" s="26" t="s">
+        <v>323</v>
+      </c>
+      <c r="K99" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L99" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A100" s="25" t="s">
+        <v>324</v>
+      </c>
+      <c r="B100" s="25"/>
+      <c r="C100" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="D100" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E100" s="25">
+        <v>10000</v>
+      </c>
+      <c r="F100" s="25"/>
+      <c r="G100" s="25">
+        <v>13000</v>
+      </c>
+      <c r="H100" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I100" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="J100" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="K100" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L100" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="406" x14ac:dyDescent="0.35">
+      <c r="A101" s="28" t="s">
+        <v>325</v>
+      </c>
+      <c r="B101" s="28"/>
+      <c r="C101" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="D101" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E101" s="28">
+        <v>22000</v>
+      </c>
+      <c r="F101" s="28"/>
+      <c r="G101" s="28">
+        <v>33000</v>
+      </c>
+      <c r="H101" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I101" s="29" t="s">
+        <v>322</v>
+      </c>
+      <c r="J101" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="K101" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L101" s="28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A102" s="25" t="s">
+        <v>329</v>
+      </c>
+      <c r="B102" s="25"/>
+      <c r="C102" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="D102" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E102" s="25">
+        <v>12000</v>
+      </c>
+      <c r="F102" s="25"/>
+      <c r="G102" s="25">
+        <v>18000</v>
+      </c>
+      <c r="H102" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I102" s="26" t="s">
+        <v>331</v>
+      </c>
+      <c r="J102" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="K102" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L102" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="203" x14ac:dyDescent="0.35">
+      <c r="A103" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="B103" s="28"/>
+      <c r="C103" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="D103" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="28">
+        <v>38000</v>
+      </c>
+      <c r="F103" s="28"/>
+      <c r="G103" s="28">
+        <v>47000</v>
+      </c>
+      <c r="H103" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I103" s="28" t="s">
+        <v>333</v>
+      </c>
+      <c r="J103" s="29" t="s">
+        <v>334</v>
+      </c>
+      <c r="K103" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L103" s="28" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L80" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}"/>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0526577688ca4eec/Escritorio/Proyectos developer/Diseños_Gasper/Back-end/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1082" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD197DE3-9C6B-4378-9E80-462B24D23981}"/>
+  <xr:revisionPtr revIDLastSave="1224" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{475A7107-F44D-4D35-AFB3-5531D56FB622}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="356">
   <si>
     <t>name</t>
   </si>
@@ -247,9 +247,6 @@
     <t xml:space="preserve">	deepink,red,blue,orange,darkred,cyan,royalblue,green,olive</t>
   </si>
   <si>
-    <t>{ "deeppink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250982/dvmu9dgiwvufb7191usm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250955/slshdhn4kio9xddrtrmq.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250918/fqhuo4tjpp4yczwzdshf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250921/ahlr0dgh0r98xw4wqud5.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250911/indvbpbsahhllbr2demt.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250914/cx8wavuzsrrfeqgehwan.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250940/hi9axizusckhejfco5s0.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250943/raziqm5ewrpzzjidxqim.png"],"darkred":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250891/zcfxokfughsvu67yjcdh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250897/gtzajz8mpqk30anhwnhq.png"],"cyan":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250901/nndijkiq3dplak0kmfwk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250904/wh8ugd1vd4yfscmrb8mr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250907/onk3n4ptbomthsd5ycfk.png"],"royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250924/ur5hr32mcpowkradyc1d.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250928/xhpn1wpn0hhufkbbxbci.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250947/ypiwxkfwgbloipv08r3c.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250951/l9xl1h9afd08rzvpze3v.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250932/hwq3ugjjcdq3xshspdyf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250936/ima8bakxaxo6mvsch85s.png"]}</t>
-  </si>
-  <si>
     <t xml:space="preserve">	deepink,orange,blue,yellow,red,black,steelblue,olive</t>
   </si>
   <si>
@@ -407,22 +404,6 @@
   </si>
   <si>
     <t>{"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205752/mfwiprr6tvgovwpuue2v.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205755/cnpmodwwbutausd84kzo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205754/vuzoeqyobfg2u01bmwry.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205752/m1pbnbpak4qv1eurewfs.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205758/yii0fqmgiqr2vcn6jobs.png"]}</t>
-  </si>
-  <si>
-    <r>
-      <t>{"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242437/dmbpdy0o8zo774yg0esp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242493/phwa4ghsnghxaad8rs0s.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242496/z0ckuych5747dbdjbblh.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242497/mllydvsxp8bsmjxtudpf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242438/gbxh6ouluwykgpjacnn5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242440/jbincqszbskytgzid1xr.png"],"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242442/rjagdaxpyr2ekyatvpnc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242443/omnxdetafnsovhyqsrrk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242445/tfuorgusbozzg5qangpa.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242446/vrqh5h2ds6suivfhxsg9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242448/arvjdgaypjnno56lfvbk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242450/yzbjosqrehdwxvwhcyfo.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242452/mzxqsxz8cz3pfkwggyzv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242454/xburffuwfdwwt6917fav.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242455/qgkevnsapc7o43ad0bq7.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242460/burfwilllus1qaxskiqw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242460/yspgkvybbozucaqc9ap1.png</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242462/ngof4yshn3cjaat7tglk.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242498/c9jctj0oy5awxkw7qhps.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242456/lqgzodgnyvwdgdski6al.png"],"deepink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242501/dzn9seysibv5yjlylqkz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242464/lxs8m7ci4bwqqyfbrjz5.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242485/t4lvqrs96uqcbrzscv68.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242488/c7sam295q1wiuiiakyt7.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242489/n1csydhjwtdmhlpf30te.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242479/ony3dvs6kvxistz3fxic.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242481/mmu22qpkw9rz2ecm79rk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242484/afwxcc8qacktmzbo5pcn.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242473/h5jrcvlasfsfetqinrzi.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242473/dfhfnav2renc5azvzicn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242474/dcsjwceh9gzre70xl9n7.png"],"aqua":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242466/wxbkzpewkatvhqphl8vc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242469/zlrfrhmdw24co5sql2xg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242469/oxccamqqxqe81hbdryqd.png"]}</t>
-    </r>
   </si>
   <si>
     <t>{"steelblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206521/lgdrcsg1bhg9kh7qjnhs.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206518/hzeq19gaqctil3pzrsi7.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206525/u9vdtg7rq4zp8awiwcvk.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206510/q3vtqnmiruti86ckrgbu.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206515/me4zdvq6donb2neznfwx.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206507/nrjilgz3harir9vbblte.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773206512/sgr2zgufvyugwtetnfwq.png"]}</t>
@@ -478,9 +459,6 @@
   </si>
   <si>
     <t>{"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204338/oejbgfjjrnas7l9peyx2.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204336/k7scng21l4yann7xww1g.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204337/p7rhhrzowr2rwabaf4wq.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204340/kjystwsspe4qlwkpttbx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204343/x0wczvaf4thuo262zk1a.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204342/k6n6vrz51vbfxkp37vxw.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204332/klqdeyjspxstecn1fqng.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204334/pmpnlaeem4it8y8tnxn1.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204335/e8dw9g0qre5ydzlqlatf.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204328/bvt7ueaexvkdythpanwn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204329/aofbo59s1uffco8i2wpi.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204330/b8n7glynvblcahn4kh05.png"],"pink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204325/tjdsejcvcgfgkfquxzjn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204326/mwrayyzb1rfuvdycyddq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204327/hn8p4ckn1sozzowpziib.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204322/b16ab0jfz0etyo8jshsw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204321/ooznuwz1cpqaqu5ownul.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204323/q61r8koxk0fhvecqkrfz.png"],"darkblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204319/fkqlvntrdaq8jt793uhj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204319/a5ep6vrxclrxq3b0h6lk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204320/vckmbagb1qiehbka8qce.png"],"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204344/io3zcwbwx9oayypdxmuc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204346/shnjivk8vn0zompx1d0k.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204347/uf0mrbixslbi3i4p13qk.png"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204350/nhoe6gys7x7a9tr92gcv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204351/kmf8fquhpmgnpaudotr8.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204351/tvy8pbmxrxbyttnzajdn.png"],"lawngreen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204355/nmvtfz8xc6seaah6thgh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204357/wmeg6mwijy05p1hpu3kh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204358/g5nsawbiilegcqjkcsuk.png"],"mediumblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204361/y8ykrtunchadolpwmw7a.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204363/toeoq0ot4by8nx7y6dfw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204366/iy9zgfv11qm7vwguueo3.png"],"skyblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204367/b4delwnliq7h2nijhugw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204368/rxy7ecs4vyuxbllduanx.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773204370/bvmqdttjroiogb5zsevr.png"]}</t>
-  </si>
-  <si>
-    <t>{"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205288/smm8fjw9rl4bnfqartjf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205287/xibsxjngkirncuy1yzho.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205357/io2ygjdephs2ufzv133d.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205290/r3hm9neakhl3lxyiseju.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205292/jasnol7orezj790psdxv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205294/tp3zzxyom7kg9g40bnug.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205296/lbmq4786zitdm7sqf2gh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205300/szighhczcmlvktpwcu0c.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205301/zc9grwxp77zytgruhujb.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205305/ip9ubuw7yzb1loywx9hp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205303/srdszj6njhkynu6hedrq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205303/srdszj6njhkynu6hedrq.png"],"darkblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205310/in2uykc5yibqy3ii59yd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205312/auuktvqrfwlpu4yf5zxq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205314/p8f8kh4dqcbkefuzbxv1.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205317/masdfk78uq1h1ocqnxon.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205320/ib4jb51wjac4tnbizgel.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205321/bjwnz5zmham8542llwvl.png"],"turquoise":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205323/ghweohyghfzxnp3autyo.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205326/ztc53cu857yxbfpqp193.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205328/ay9h3tyk1kikgchkgh1r.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205329/hgsinisspnemzvna56cg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205332/u7f9tauhwezirlpxvghh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205335/ryi88h3pmqpwnjvruazi.png"],"darkgreen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205339/eezvjpd0anxakn1d1eir.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205366/afcwdckametvhcm2vdnk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205339/sj4x0jejmfcckjyjcgff.png"],"skyblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205340/ly5tvmjhv2exoglszokt.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205345/mbswblamqqdllr1hzulb.png"],"peru":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205349/ptzps64butp9eg2kdvn5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205354/spdvczuhihi0kmjzwygz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205353/uwy3dpacpekdc1mh1k76.png"]}</t>
   </si>
   <si>
     <t>{"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246712/gotvnqbl4y3hdyauibw5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246707/yonflyqalxcl4c9if2bj.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246709/xbj5qrmtoxxcqq5damdg.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246714/thwkb1zhc1xobjfnlkec.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246717/lsxqmrzz8lwomqaaua16.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246719/eq8r76oqa5gnfh9gvln8.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246722/ppj4owyqnlqcuebnxv4t.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246725/zzyif5jcihzmwccgjfkf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246730/dauki5afyvny7y19x5sp.png"],"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246732/wd38ed0dzdwcjwiwzflh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246737/swfnbkucmbke4llvpasp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246739/j9jizettng9z4ufui6mh.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246745/qjkntjcqnncozqokqdai.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246746/dici1svfsqmtnwbaxh3r.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246812/dkdxyqkjivhmzzyiqh8o.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246817/snvmvdacyeefzgztoegr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246819/llsaoy4lp3xuig0mzgkz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246824/qkhbddvmlcesobq3axsl.png"],"skyblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246828/yjyw5k38esggufh9nxoz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246832/i4h1qxhsejjbg5xnnamq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773246835/wwsyptj2wb0253mmnltu.png"]}</t>
@@ -1732,25 +1710,6 @@
     <t>blue,red,black, darkred, royalblue</t>
   </si>
   <si>
-    <t>{ "blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253382/k5shc79l7qjtrz6ci2u8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662299/g4llyutemrjvlpsyhbjl.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662300/qtwerqw10yv6wxqpb1cl.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662299/scdqmabiuqxkreow7u6c.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662302/wghzvjuaajuwpbfddzvk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253384/fa3gtcxcbbujpmz1q32y.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662299/ys0v7pwpkcommwyjadtf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662310/tbrnns244roeseqtkxrr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/dxofsgljvhppxhvxcf9q.png"],"darkred":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/uqqd6kygifncoygwvzfk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253382/kiy5vdzzlhglrhntyfpf.png"], "royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662300/t7f9xsg5ij4gmjrmoyso.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662304/k5128obkwuopjaualtol.png"]}</t>
-  </si>
-  <si>
-    <r>
-      <t>{"lime":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242437/dmbpdy0o8zo774yg0esp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242493/phwa4ghsnghxaad8rs0s.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242496/z0ckuych5747dbdjbblh.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242497/mllydvsxp8bsmjxtudpf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242438/gbxh6ouluwykgpjacnn5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242440/jbincqszbskytgzid1xr.png"],"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242442/rjagdaxpyr2ekyatvpnc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242443/omnxdetafnsovhyqsrrk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242445/tfuorgusbozzg5qangpa.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242446/vrqh5h2ds6suivfhxsg9.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242448/arvjdgaypjnno56lfvbk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242450/yzbjosqrehdwxvwhcyfo.png"],"orange":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242452/mzxqsxz8cz3pfkwggyzv.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242454/xburffuwfdwwt6917fav.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242455/qgkevnsapc7o43ad0bq7.png"],"gray":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774664553/ckjrrp0qrdw6vn6yqjmf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774664554/neg0acxwxh0mhhfynsh6.png</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"],"olive":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242498/c9jctj0oy5awxkw7qhps.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242456/lqgzodgnyvwdgdski6al.png"],"deepink":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242501/dzn9seysibv5yjlylqkz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242464/lxs8m7ci4bwqqyfbrjz5.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242485/t4lvqrs96uqcbrzscv68.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242488/c7sam295q1wiuiiakyt7.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242489/n1csydhjwtdmhlpf30te.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242479/ony3dvs6kvxistz3fxic.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242481/mmu22qpkw9rz2ecm79rk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242484/afwxcc8qacktmzbo5pcn.png"],"green":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242473/h5jrcvlasfsfetqinrzi.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242473/dfhfnav2renc5azvzicn.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242474/dcsjwceh9gzre70xl9n7.png"],"aqua":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242466/wxbkzpewkatvhqphl8vc.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242469/zlrfrhmdw24co5sql2xg.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242469/oxccamqqxqe81hbdryqd.png"]}</t>
-    </r>
-  </si>
-  <si>
     <t>Enterizo para Ciclismo</t>
   </si>
   <si>
@@ -1968,52 +1927,6 @@
   </si>
   <si>
     <t>Enterizo para Ciclismo.</t>
-  </si>
-  <si>
-    <t>{
-  "black": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715391/agiednmodeb5yfpahlp1.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715392/tofa7d0ks3nqok7en9j6.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715395/cdbcpgyhms197nffsus0.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715394/jpithdawvqp2tmmz4sbr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715398/aonotdgo3ttkxg3vxife.png"
-  ],
-  "blue": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715399/ga18nxoi4pcosvxkgd6x.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715402/u2jtujngu7yuuqdbfo7r.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715403/q1bwntcbzvnilh5xyumu.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715406/nbo3egml3xzqqkgj2yqk.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715407/zdjxkw4a53r0j2kjn5zi.png"
-  ],
-  "gray": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715412/fpyfapenk9fxym7eewmu.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715410/z4kcqsfgasg1z53yarur.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715414/m23amhh21mpotdp88sjn.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715416/ydmz1uralgltpdeevcbc.png"
-  ],
-  "green": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715418/x2rtdwfrfwecvxs84i7l.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715421/ebbezh68fixgh6o84qli.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715423/a7wjeymergff40uhpykt.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715427/oq9maqfvtwrz5cfpmnnw.png"
-  ],
-  "darkblue": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715428/espsoggmadkxd6weqeb8.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715429/drdkltcampvjzfzc0ifn.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715434/ufwqg1cmoeslcqafsaw9.png"
-  ],
-  "hotpink": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715436/fn4lbigoobdn5xjbm8jh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715440/ddhq5u6ubbdbbw1no78m.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715441/vb5pyt9y9flu8fh0f45c.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715447/cksicv1hldfrcxgapuug.png"
-  ],
-  "steelblue": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715449/zhcwcrbc5dkixpezz70b.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715445/koyfabdm2bhnjhkcamu4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715453/rrada8pae4w27xmxzimc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715453/ee4ronykxwaebzdtzx8c.png"
-      ],
-  "purple": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715458/uc7n4i1rqltsbblh1ftl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715460/on3p22rgtcgnqndozwu3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715460/on3p22rgtcgnqndozwu3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715465/xxg2fwuxia77qn9dxqtv.png"
-  ],
-  "skyblue": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715467/bni8lwrz38khcg0wjqss.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715469/zds8ckdyanvwacjut2if.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715475/i3us2trdde2od7imi4yp.png"
-  ]
-}</t>
   </si>
   <si>
     <t>black,blue,gray,green,darkblue,hotpink,steelblue</t>
@@ -2521,23 +2434,6 @@
   </si>
   <si>
     <t>{
-  "green": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058812/wpybvhkk9ugsy6gnxkkm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058811/d8lzuacyktsdlepm9qcd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058811/jdmi9kwuwllmglwhhcbc.png"  ],
-  "red": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058814/buq9q1wtddmrrkg6iakf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058812/b7emupdqe6witatlqvq4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058814/mkbq6zncote7su95rhag.png" ],
-  "yellow": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058812/d6j3vnuq23pr3pvlqrrc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058813/sldsj7nnpogk2gxufpxz.png", " https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058814/dmsndzjcdeiql1crljdb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058814/etvlgtogg1be4ui79eux.png" ],
-  "blue": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058814/pwpefqqs0ay3xfzyqep5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058815/vfq45emabazi47rx4wd0.png" ],
-  "orange": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058815/esequ0cwic5ues3kyrck.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058817/yikzlztavx3gaci9xpfr.png"],
-  "darkblue": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058816/bg7eetec0kwqfntlzhdu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058817/hel3nql1dp0vfvjpieyk.png" ],
-  "olive": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058817/xnmxv2e9memmagybowsd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058816/s6zbit7x8tejpcfnv3s0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058817/wqonc9kcviofhs7qiatn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058818/ht4eo6wpkw58c3zsjttb.png" ]}</t>
-  </si>
-  <si>
-    <t>{
   "blue": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059351/ms0pfrg6qexy7pvp2b2d.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059359/knvhre2v1jzwh6slg2m7.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059355/hgbv0fwafwvnznmhyojl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775059363/gsrwyckhl9luqezcaslx.png"  ],
   "darkblue": [
@@ -2592,15 +2488,535 @@
     <t>gray,black,darkblue,olive</t>
   </si>
   <si>
+    <t>Esqueleto en Tela Burda</t>
+  </si>
+  <si>
+    <t>olive,red,gray,crimson,purple,white,black,darkblue,darkgreen,blue</t>
+  </si>
+  <si>
+    <t>{
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155269/de0pp7uo7t4rwrcy9na5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155273/ka4gk0rcnldhraqdzbjt.png" ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155271/sfmzhsktumxhhiykmyl1.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155277/sptbvii9bdz3mfxmmh5u.png"],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155269/uuxdbe3zyuwqasfswvxp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155270/pcurilqozy4guyqhrr0n.png" ],
+  "crimson": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155273/ldlwpglhvi9ja5q6nmxv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155271/y805zyiv6vaivssobjjc.png"],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155271/fwxxwy7bm2f04pld8gpf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155277/dokov3qhbtqdpxnwjvbg.png"],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155273/sarg592ljgtrlegxr9dg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155275/b2b7ywzj4heuodk4kd0w.png" ], "black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155272/flxhhmuujdjpezxmkmqn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155273/j2qcht36qgzywyshdgjj.png"], "darkblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155272/dscu8zuigconhfyshe6z.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155277/eane79kkqkqetsbzchi5.png"],"darkgreen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155276/jw0lguqjixqg7ke6adqs.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155275/yzp0sx5ta5dlqsraanw6.png"], "blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155273/lyu53mfn62se2kcebbee.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155278/oiguw01ughqg2mldahy7.png"]}</t>
+  </si>
+  <si>
+    <t>Conjunto Baicker</t>
+  </si>
+  <si>
+    <t>{
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158910/bqfemdrldelrb5vv7s7h.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158925/okysbbknpxhsxub6mctr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158913/cj8v7h1il0icgey5tw6i.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158921/syghxqv6xfjjwueepbkd.png" ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158914/qqrsusoyogh2qss4s0ec.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158899/a8gwkfjllecgstudd7k3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158908/unnoqdfkillvgor1ciub.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158912/mo8pyirjuzat9woipnsx.png"],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158906/klvf37lcsveljtrpv2ky.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158911/lwnr8ej3zk5oecuwedv1.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158904/sumzz8ofqyggr6ppc8f0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158917/pbqufwwuq7ydtcdf17kd.png" ],
+  "crimson": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158910/s0bgdglskoxld0lcd4b9.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158900/ffcz0shmkborvjpnej91.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158897/pdsrxaqwdn0pca9sytz7.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158908/q8pg8snwlwbrbttcpzzm.png"],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158897/dw9z0ou5vv2bdsodqiub.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158901/vgoxnbpcqdigubexlgno.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158905/nc0ggeaic6thlw8vf6ki.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158922/aoivbzcf7oykus3fcofn.png"],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158888/txin7lhw1hczv1xuqxli.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158887/kdbl9tymc289uyzuiss9.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158888/xrbsm8ivhriszmgokuyi.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158889/nhfvfrnwobb9f1bb8zlo.png" ], "black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158890/ptpqfainiwqfsxac5lp6.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158891/vukm3jfqq4ejhrzhbzdb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158926/d7mjjss8uxmfdk6jf5ic.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158893/vbpzm6fdkugn7qog1lcp.png"], "darkblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158892/fnctdf2syv6su6ji0dq9.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158919/hcco7fyk6y9o2q4yhi3m.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158907/y4snteswyqdoelc3v0ko.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158916/eiwterq5vxyrduxwyzs0.png"],"darkgreen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158899/ryrtyjyqbj7ddofhzbin.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158915/jb4asboucaownuqyv4z1.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158925/okysbbknpxhsxub6mctr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158923/dlvn22nkbnjxtroryyar.png"], "blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158902/ilhxes69tiijyclldzar.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158928/jg9ttyjltwuq8zl5gkbn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158921/syghxqv6xfjjwueepbkd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158918/n3jlvokwmaohwiqnmhgx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158922/npox0trdbvgwyrlimqa8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158903/suojpmygqtfzusyrkh1j.png"]}</t>
+  </si>
+  <si>
+    <t>Camiseta Dama</t>
+  </si>
+  <si>
+    <t>red,green,blue</t>
+  </si>
+  <si>
+    <t>{
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775159919/fnfvrj84oklumcmewxlj.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775159917/qcixu8tbtylkifx7oco7.png"],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775159916/cm4hdwxjr7f2istbkskv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775159921/p5wmomgof1thgldi8ew1.png"],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775159924/osz4oskycnc1mht1s0ig.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775159918/x560apajnl06u2hbsvdl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775159920/pfesp6ejczmc9rnodkkk.png" ]}</t>
+  </si>
+  <si>
+    <t>Conjunto Esqueleto+Pantaloneta</t>
+  </si>
+  <si>
+    <t>{
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244394/m0lw2mmjnwkzubnnawdt.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244395/b8r0cobeqs1akga3ncs4.png" ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244393/uzxchvtxbxypuk7g8gb0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244394/hn7z8d0eqzf1zdglzfbn.png"],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244396/uxlcu7efqzqzqjvygtlm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244395/qioevzt73er4u4wygd7h.png" ],
+  "crimson": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244395/ggmrt6q9supmc1twty5f.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244396/gsmkakv8eh2c5kt9onq7.png"],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244397/usdxd7zbntng5eunzqce.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244397/jjdhzlbyv3pjqibm8bnl.png"],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244397/lmewpapkk3yqjsagu9lj.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244396/h67pjz4epcgahkndfmg0.png" ], "black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244399/hljbavtshkwprodqxbpc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244398/mnpxnp2fo9l1goot4ni4.png"], "darkblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244398/suq0rp40vj6ypzfvvjgb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244410/eutztd2cwgmy1ttnfpvi.png"], "blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244412/xzu6lrtk6rmmspssdvde.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244410/qyxtqokw0bwqf4aouh9d.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244410/ov9r6no428uzisyopj4y.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244411/py1iq21blxizcyungzy3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244411/uufydwggwngrrecy6pk4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775244411/xcagxfzz1uquo6labld0.png"]}</t>
+  </si>
+  <si>
+    <t>Conjunto Jogger+Chaqueta Algodón</t>
+  </si>
+  <si>
+    <t>olive,red,gray,crimson,purple,white</t>
+  </si>
+  <si>
+    <t>Conjunto Jogger+Esqueleto</t>
+  </si>
+  <si>
+    <t>{
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775188918/gwsz251dgpsj1hew0oya.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775188916/blubovl0lekvda8wz28m.png" ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775188913/ddpvqzyduogcjuw1fwnn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775188913/l1mde2lin9bwxxd4su3m.png"],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775188914/ogdotcnkkdv8rfzbse3i.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775188914/mj2tdabjjxpdcr65awvm.png" ],
+  "crimson": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775188916/y1qw6mknpnhqwdvbamuq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775188915/kkpxlded8hkqkp5wofp1.png"],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775188915/kq5lpwtcrzbnnubmh54y.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775188915/njinwwsp8q6dpnmrwtfg.png"],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775188917/vkukktckpia1d7issavr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775188916/xsvvbtlifwxr6wnptmrp.png" ], "black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775188918/rybfs9fg7wcmiicwprrv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775188918/kmwubgf9nz3ocioc5qfn.png"], "darkblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775188919/n40kc2secr3lstdyyjh1.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775188920/kxlkdyalzfnri32qe0ox.png"]}</t>
+  </si>
+  <si>
+    <t>{
+  "lime": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205288/smm8fjw9rl4bnfqartjf.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205287/xibsxjngkirncuy1yzho.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205357/io2ygjdephs2ufzv133d.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205290/r3hm9neakhl3lxyiseju.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205292/jasnol7orezj790psdxv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205294/tp3zzxyom7kg9g40bnug.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205296/lbmq4786zitdm7sqf2gh.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205300/szighhczcmlvktpwcu0c.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205301/zc9grwxp77zytgruhujb.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205305/ip9ubuw7yzb1loywx9hp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205303/srdszj6njhkynu6hedrq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205308/byyt2ryop0d8dr46xt9o.png"
+  ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205310/in2uykc5yibqy3ii59yd.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205312/auuktvqrfwlpu4yf5zxq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205314/p8f8kh4dqcbkefuzbxv1.png"
+  ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205317/masdfk78uq1h1ocqnxon.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205320/ib4jb51wjac4tnbizgel.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205321/bjwnz5zmham8542llwvl.png"
+  ],
+  "turquoise": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205323/ghweohyghfzxnp3autyo.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205326/ztc53cu857yxbfpqp193.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205328/ay9h3tyk1kikgchkgh1r.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205329/hgsinisspnemzvna56cg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205332/u7f9tauhwezirlpxvghh.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205335/ryi88h3pmqpwnjvruazi.png"
+  ],
+  "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205339/eezvjpd0anxakn1d1eir.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205366/afcwdckametvhcm2vdnk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205339/sj4x0jejmfcckjyjcgff.png"
+  ],
+  "skyblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205340/ly5tvmjhv2exoglszokt.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205345/mbswblamqqdllr1hzulb.png"
+  ],
+  "peru": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205349/ptzps64butp9eg2kdvn5.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205354/spdvczuhihi0kmjzwygz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773205353/uwy3dpacpekdc1mh1k76.png"
+  ]
+}</t>
+  </si>
+  <si>
     <t>{
   "gray": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080255/czlfuvutd72atp0ojhqh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080247/xpw55vkz1revjayfz3zz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080238/itypiaz7qmh7ralcuari.png" ],
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080255/czlfuvutd72atp0ojhqh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080247/xpw55vkz1revjayfz3zz.png" ],
   "black": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080241/h3g6polr1fdcf8ygdklb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080252/yzndprsrmahdoeruuzlt.png" ],
   "darkblue": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080244/mlvuk1yzzwhccuyxm6hn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080250/xigvnqz7go87woirjlvb.png" ],
   "olive": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080236/pxianovllar2lhhacceh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775080258/jravrpw6pis8ehszhslp.png" ]}</t>
+  </si>
+  <si>
+    <t>{
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058812/wpybvhkk9ugsy6gnxkkm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058811/d8lzuacyktsdlepm9qcd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058811/jdmi9kwuwllmglwhhcbc.png"  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058812/b7emupdqe6witatlqvq4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058814/mkbq6zncote7su95rhag.png" ],
+  "yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058812/d6j3vnuq23pr3pvlqrrc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058813/sldsj7nnpogk2gxufpxz.png", " https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058814/dmsndzjcdeiql1crljdb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775267134/mjsaav0j45wdiagbpw6b.png" ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058814/pwpefqqs0ay3xfzyqep5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058815/vfq45emabazi47rx4wd0.png" ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058815/esequ0cwic5ues3kyrck.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058817/yikzlztavx3gaci9xpfr.png"],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058816/bg7eetec0kwqfntlzhdu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058817/hel3nql1dp0vfvjpieyk.png" ],
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058817/xnmxv2e9memmagybowsd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058816/s6zbit7x8tejpcfnv3s0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058817/wqonc9kcviofhs7qiatn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058818/ht4eo6wpkw58c3zsjttb.png" ]}</t>
+  </si>
+  <si>
+    <t>{ "blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253382/k5shc79l7qjtrz6ci2u8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662299/g4llyutemrjvlpsyhbjl.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662300/qtwerqw10yv6wxqpb1cl.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775267794/oq0hzp8xiepkigd8hytz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662302/wghzvjuaajuwpbfddzvk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253384/fa3gtcxcbbujpmz1q32y.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662299/ys0v7pwpkcommwyjadtf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662310/tbrnns244roeseqtkxrr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/dxofsgljvhppxhvxcf9q.png"],"darkred":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/uqqd6kygifncoygwvzfk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253382/kiy5vdzzlhglrhntyfpf.png"], "royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662300/t7f9xsg5ij4gmjrmoyso.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662304/k5128obkwuopjaualtol.png"]}</t>
+  </si>
+  <si>
+    <t>{
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715391/agiednmodeb5yfpahlp1.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715392/tofa7d0ks3nqok7en9j6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715395/cdbcpgyhms197nffsus0.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715394/jpithdawvqp2tmmz4sbr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715398/aonotdgo3ttkxg3vxife.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715399/ga18nxoi4pcosvxkgd6x.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715402/u2jtujngu7yuuqdbfo7r.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715403/q1bwntcbzvnilh5xyumu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715406/nbo3egml3xzqqkgj2yqk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715407/zdjxkw4a53r0j2kjn5zi.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715412/fpyfapenk9fxym7eewmu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715410/z4kcqsfgasg1z53yarur.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715414/m23amhh21mpotdp88sjn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715416/ydmz1uralgltpdeevcbc.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715418/x2rtdwfrfwecvxs84i7l.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715421/ebbezh68fixgh6o84qli.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715423/a7wjeymergff40uhpykt.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715427/oq9maqfvtwrz5cfpmnnw.png"
+  ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715428/espsoggmadkxd6weqeb8.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715429/drdkltcampvjzfzc0ifn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715434/ufwqg1cmoeslcqafsaw9.png"
+  ],
+  "hotpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715436/fn4lbigoobdn5xjbm8jh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715440/ddhq5u6ubbdbbw1no78m.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715441/vb5pyt9y9flu8fh0f45c.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715447/cksicv1hldfrcxgapuug.png"
+  ],
+  "steelblue": [
+   "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715445/koyfabdm2bhnjhkcamu4.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715453/rrada8pae4w27xmxzimc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715453/ee4ronykxwaebzdtzx8c.png"
+      ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715458/uc7n4i1rqltsbblh1ftl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715460/on3p22rgtcgnqndozwu3.png",  "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715465/xxg2fwuxia77qn9dxqtv.png"
+  ],
+  "skyblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715467/bni8lwrz38khcg0wjqss.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715469/zds8ckdyanvwacjut2if.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715475/i3us2trdde2od7imi4yp.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775189074/gizojaz37bkgea5euugi.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775189074/wo3zqlyxwleaxljrpqgm.png" ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775189075/mb7ijcwbyzhvmzawc4xc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775189074/fckvvtdkspk6hunvwqcp.png"],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775189076/uu44dr65piwmneepq9rb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775189076/mciathn6oxa4yn9rb39w.png" ],
+  "crimson": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775189077/zymwn2nrvphztcctx0t0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775189076/lko4bl0upfxl6bpbwcem.png"],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775189078/a1wayfl41mw4zuhlqdrv.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775189078/ns2ivpdujrzoqasx3y3p.png"],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775189080/w1yav2h8ahdxk9vzel5s.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775189078/ilfiofrwu6y4huewkksx.png" ]}</t>
+  </si>
+  <si>
+    <t>{
+  "lime": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242437/dmbpdy0o8zo774yg0esp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242493/phwa4ghsnghxaad8rs0s.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242496/z0ckuych5747dbdjbblh.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242497/mllydvsxp8bsmjxtudpf.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242438/gbxh6ouluwykgpjacnn5.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242440/jbincqszbskytgzid1xr.png"
+  ],
+  "yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775270172/c3g6aegbowyrofjqwwyy.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242443/omnxdetafnsovhyqsrrk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242445/tfuorgusbozzg5qangpa.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242446/vrqh5h2ds6suivfhxsg9.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242448/arvjdgaypjnno56lfvbk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242450/yzbjosqrehdwxvwhcyfo.png"
+  ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242452/mzxqsxz8cz3pfkwggyzv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242454/xburffuwfdwwt6917fav.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242455/qgkevnsapc7o43ad0bq7.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774664553/ckjrrp0qrdw6vn6yqjmf.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774664554/neg0acxwxh0mhhfynsh6.png"
+  ],
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242498/c9jctj0oy5awxkw7qhps.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242456/lqgzodgnyvwdgdski6al.png"
+  ],
+  "deepink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242501/dzn9seysibv5yjlylqkz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242464/lxs8m7ci4bwqqyfbrjz5.png"
+  ],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242485/t4lvqrs96uqcbrzscv68.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242488/c7sam295q1wiuiiakyt7.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242489/n1csydhjwtdmhlpf30te.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242479/ony3dvs6kvxistz3fxic.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242481/mmu22qpkw9rz2ecm79rk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242484/afwxcc8qacktmzbo5pcn.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242473/h5jrcvlasfsfetqinrzi.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242473/dfhfnav2renc5azvzicn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242474/dcsjwceh9gzre70xl9n7.png"
+  ],
+  "aqua": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242466/wxbkzpewkatvhqphl8vc.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242469/zlrfrhmdw24co5sql2xg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242469/oxccamqqxqe81hbdryqd.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>blue,red,yellow,lime,orange,gray,olive,deepink,white,black,green,aqua</t>
+  </si>
+  <si>
+    <t>{
+"blue": [
+   "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242450/yzbjosqrehdwxvwhcyfo.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242448/arvjdgaypjnno56lfvbk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242446/vrqh5h2ds6suivfhxsg9.png"  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242497/mllydvsxp8bsmjxtudpf.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242438/gbxh6ouluwykgpjacnn5.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242440/jbincqszbskytgzid1xr.png"
+  ],
+  "yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775270172/c3g6aegbowyrofjqwwyy.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242443/omnxdetafnsovhyqsrrk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242445/tfuorgusbozzg5qangpa.png"
+  ],
+ "lime": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242437/dmbpdy0o8zo774yg0esp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242493/phwa4ghsnghxaad8rs0s.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242496/z0ckuych5747dbdjbblh.png"  ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242452/mzxqsxz8cz3pfkwggyzv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242454/xburffuwfdwwt6917fav.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242455/qgkevnsapc7o43ad0bq7.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774664553/ckjrrp0qrdw6vn6yqjmf.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774664554/neg0acxwxh0mhhfynsh6.png"
+  ],
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242498/c9jctj0oy5awxkw7qhps.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242456/lqgzodgnyvwdgdski6al.png"
+  ],
+  "deepink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242501/dzn9seysibv5yjlylqkz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242464/lxs8m7ci4bwqqyfbrjz5.png"
+  ],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242485/t4lvqrs96uqcbrzscv68.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242488/c7sam295q1wiuiiakyt7.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242489/n1csydhjwtdmhlpf30te.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242479/ony3dvs6kvxistz3fxic.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242481/mmu22qpkw9rz2ecm79rk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242484/afwxcc8qacktmzbo5pcn.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242473/h5jrcvlasfsfetqinrzi.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242473/dfhfnav2renc5azvzicn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242474/dcsjwceh9gzre70xl9n7.png"
+  ],
+  "aqua": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242466/wxbkzpewkatvhqphl8vc.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242469/zlrfrhmdw24co5sql2xg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773242469/oxccamqqxqe81hbdryqd.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "deeppink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775272048/seolatvo5ibeptxp0qph.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250947/ypiwxkfwgbloipv08r3c.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250921/ahlr0dgh0r98xw4wqud5.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250918/fqhuo4tjpp4yczwzdshf.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775272044/kzue8vfokuxiyls8okxw.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250911/indvbpbsahhllbr2demt.png"
+  ],
+  "orange": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250943/raziqm5ewrpzzjidxqim.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250940/hi9axizusckhejfco5s0.png"
+  ],
+  "darkred": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775272045/ntqkfjp3ulurkxy4ygdt.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250891/zcfxokfughsvu67yjcdh.png"
+  ],
+  "cyan": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250907/onk3n4ptbomthsd5ycfk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250901/nndijkiq3dplak0kmfwk.png"
+      ],
+  "royalblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250928/xhpn1wpn0hhufkbbxbci.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250924/ur5hr32mcpowkradyc1d.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775272044/k0odmztsbytujwkwbj4b.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250932/hwq3ugjjcdq3xshspdyf.png"
+  ],
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250982/dvmu9dgiwvufb7191usm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773250955/slshdhn4kio9xddrtrmq.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>Conjunto Trio</t>
+  </si>
+  <si>
+    <t>{
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530933/uils4eimclbswiqglxwb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530932/ii7ghf3qbpsqh0hkcx2f.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530933/wjmxysz83faelacafesh.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530933/javfoagq5gzr7uhizidl.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530935/tx26xvxynmnt13g6jxny.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530937/kxkvlgrfktgso9c0hvwz.png"
+  ],
+  "crimson": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530936/l95akyd4bhk03kowv3yv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530941/iy0aijqwamomh0fnm5wg.png"
+  ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530937/h6rh57doz4ykiom9af59.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530941/rx9im8mi455aitzydnxu.png"
+  ],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530939/twawwnanaibt5slxbfse.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530939/qqz70mll8slv7me5rlku.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530942/zg4ps6taox8va1al4zug.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530942/b639r0xzf46exnqiqnx1.png"
+  ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530934/jjpiskpvm5rsgrpq61an.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530936/cfngz0v2uin3r9pvcnxq.png"
+  ],
+  "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530943/q3xp8jlyr1vds4wnzk9a.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530946/lmuxsq2llfvyfdjout9x.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530946/itxk54mzlv2ipq17sply.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530944/vo0to0xaxlpifpgzrhde.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775530942/powgxa12h1ygcmpoxuas.png"]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528550/gmdzzwnh5cdpqtvymjyv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528568/tcvv05bz7szpvpwd8zop.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528550/p3hydwhpjpslxexdpanl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528568/do8kkgmi36vittvqbkiv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528552/yzfbvjblgnrxzwd29cid.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528552/lvtqga1qb6uwyarixgq6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528581/dygj9mq5mdrljvnpmrgd.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528552/w6jbg5hjogzaln3jl4j4.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528571/mne0aojjckwvv6fgp5va.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528552/d8xid8l05vqntghit17l.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528558/kppkvltsc9g6e9skxs60.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528554/zb2b7bs1zohuizr6bhs4.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528617/qjkcgmpyv6z2hrbz0vu9.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528554/ijyksc5bqk511ozo8ych.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528556/z5spj2xo5uvzajchpmqd.png"
+  ],
+  "crimson": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528556/igtbdhfrhc50dar5nhrk.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528567/x2tmdjwsfn85bl3gj2wx.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528658/ztufsmufdck5qppl7xvc.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528557/stin5xulbccessuu2nip.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528557/oqebc4rgn3p6hhafbhtp.png"
+  ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528558/msp7kipsfbr6mmzyapzy.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528558/iv8tqyczrfqdk4evrc9i.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528649/hmgwu4h2vjdjta0hwbr3.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528559/t3po7d7m9za9l0dkz994.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528648/arkglftnemydihnmtnlq.png"
+  ],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528559/sjuzzpzilfyiw13k7yes.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528548/aobit1wtczidpesdlq24.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528571/tzuoxfrhjjfssqfrgiym.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528560/fj74tlmoybiupta0nvbr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528560/lwjlw7wsprqwzppl3yd9.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528561/rbs2w7fsxdjvmqeb9p2f.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528561/g33p8hylieoiax9n58kr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528562/jxlvjt6p60as4zefxihn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528564/e4awddsekmuh4tau6sfj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528562/zruwjeglcmotxuo76adj.png"
+  ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528558/msp7kipsfbr6mmzyapzy.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528546/ilqc1rrwwsfztfcqeuyo.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528546/b8hnh8lbhlwpzvbbh0t3.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528558/kppkvltsc9g6e9skxs60.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528554/cqouzdts64ocfzsl4yof.png"
+  ],
+  "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528546/shatbfwovg3gkyct0jkn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528568/ljtaegezd3usfkzt2fr3.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528546/qfpysihe3ejliouiacok.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528547/lqhbyrqo4q8ej53scjdh.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528549/fksujv4reastgqspo0hz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528548/j9yicnf1rr2oncnc1vpi.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528548/aobit1wtczidpesdlq24.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528548/oszx1czsx1bzzf0wdcjq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775528550/lpfuftrqkjjmufahmofb.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>Leggins transparencia Feng Shui</t>
+  </si>
+  <si>
+    <t>Licra de Pecho (Dama).</t>
   </si>
 </sst>
 </file>
@@ -2805,6 +3221,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3092,7 +3512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}">
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="57.54296875" style="2" customWidth="1"/>
@@ -3113,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>1</v>
@@ -3151,10 +3571,10 @@
         <v>16</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>11</v>
@@ -3172,10 +3592,10 @@
         <v>17</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>243</v>
+        <v>344</v>
       </c>
       <c r="K2" s="6" t="b">
         <v>0</v>
@@ -3186,13 +3606,13 @@
     </row>
     <row r="3" spans="1:12" s="3" customFormat="1" ht="99.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>11</v>
@@ -3211,7 +3631,7 @@
         <v>70</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="K3" s="6" t="b">
         <v>0</v>
@@ -3222,13 +3642,13 @@
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="89.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>11</v>
@@ -3258,15 +3678,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="3" customFormat="1" ht="145" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" s="3" customFormat="1" ht="158.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>20</v>
@@ -3287,7 +3707,7 @@
         <v>73</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>74</v>
+        <v>350</v>
       </c>
       <c r="K5" s="6" t="b">
         <v>0</v>
@@ -3302,7 +3722,7 @@
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>11</v>
@@ -3318,10 +3738,10 @@
         <v>14</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="K6" s="6" t="b">
         <v>0</v>
@@ -3336,7 +3756,7 @@
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>11</v>
@@ -3352,10 +3772,10 @@
         <v>12</v>
       </c>
       <c r="I7" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>76</v>
       </c>
       <c r="K7" s="6" t="b">
         <v>0</v>
@@ -3370,7 +3790,7 @@
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>11</v>
@@ -3388,10 +3808,10 @@
         <v>13</v>
       </c>
       <c r="I8" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="J8" s="11" t="s">
         <v>77</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>78</v>
       </c>
       <c r="K8" s="6" t="b">
         <v>0</v>
@@ -3402,11 +3822,11 @@
     </row>
     <row r="9" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>11</v>
@@ -3424,10 +3844,10 @@
         <v>13</v>
       </c>
       <c r="I9" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="J9" s="11" t="s">
         <v>77</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>78</v>
       </c>
       <c r="K9" s="6" t="b">
         <v>0</v>
@@ -3442,7 +3862,7 @@
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>11</v>
@@ -3458,10 +3878,10 @@
         <v>14</v>
       </c>
       <c r="I10" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="J10" s="12" t="s">
         <v>79</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>80</v>
       </c>
       <c r="K10" s="6" t="b">
         <v>0</v>
@@ -3472,11 +3892,11 @@
     </row>
     <row r="11" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>11</v>
@@ -3492,10 +3912,10 @@
         <v>14</v>
       </c>
       <c r="I11" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" s="12" t="s">
         <v>79</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>80</v>
       </c>
       <c r="K11" s="6" t="b">
         <v>0</v>
@@ -3506,11 +3926,11 @@
     </row>
     <row r="12" spans="1:12" ht="47" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>11</v>
@@ -3525,11 +3945,11 @@
       <c r="H12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>82</v>
+      <c r="I12" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>128</v>
+        <v>347</v>
       </c>
       <c r="K12" s="6" t="b">
         <v>0</v>
@@ -3540,11 +3960,11 @@
     </row>
     <row r="13" spans="1:12" ht="47" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>11</v>
@@ -3559,11 +3979,11 @@
       <c r="H13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>82</v>
+      <c r="I13" s="7" t="s">
+        <v>348</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>244</v>
+        <v>349</v>
       </c>
       <c r="K13" s="6" t="b">
         <v>0</v>
@@ -3574,11 +3994,11 @@
     </row>
     <row r="14" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>27</v>
@@ -3596,10 +4016,10 @@
         <v>26</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K14" s="6" t="b">
         <v>0</v>
@@ -3610,11 +4030,11 @@
     </row>
     <row r="15" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>27</v>
@@ -3632,10 +4052,10 @@
         <v>26</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K15" s="6" t="b">
         <v>0</v>
@@ -3646,11 +4066,11 @@
     </row>
     <row r="16" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>11</v>
@@ -3668,10 +4088,10 @@
         <v>26</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K16" s="6" t="b">
         <v>0</v>
@@ -3682,11 +4102,11 @@
     </row>
     <row r="17" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>11</v>
@@ -3704,10 +4124,10 @@
         <v>26</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K17" s="6" t="b">
         <v>0</v>
@@ -3722,7 +4142,7 @@
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>30</v>
@@ -3738,10 +4158,10 @@
         <v>28</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K18" s="6" t="b">
         <v>0</v>
@@ -3752,7 +4172,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6" t="s">
@@ -3772,10 +4192,10 @@
         <v>28</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K19" s="6" t="b">
         <v>0</v>
@@ -3786,11 +4206,11 @@
     </row>
     <row r="20" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>11</v>
@@ -3806,10 +4226,10 @@
         <v>14</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K20" s="6" t="b">
         <v>0</v>
@@ -3824,7 +4244,7 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>11</v>
@@ -3840,10 +4260,10 @@
         <v>14</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K21" s="6" t="b">
         <v>0</v>
@@ -3858,7 +4278,7 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>11</v>
@@ -3874,10 +4294,10 @@
         <v>32</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K22" s="6" t="b">
         <v>0</v>
@@ -3892,7 +4312,7 @@
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>11</v>
@@ -3908,10 +4328,10 @@
         <v>14</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K23" s="6" t="b">
         <v>0</v>
@@ -3926,7 +4346,7 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>11</v>
@@ -3942,10 +4362,10 @@
         <v>14</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K24" s="6" t="b">
         <v>0</v>
@@ -3960,7 +4380,7 @@
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>11</v>
@@ -3976,10 +4396,10 @@
         <v>14</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="K25" s="6" t="b">
         <v>0</v>
@@ -3990,7 +4410,7 @@
     </row>
     <row r="26" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
@@ -4010,10 +4430,10 @@
         <v>14</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="K26" s="6" t="b">
         <v>0</v>
@@ -4028,7 +4448,7 @@
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>11</v>
@@ -4044,10 +4464,10 @@
         <v>14</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="K27" s="6" t="b">
         <v>0</v>
@@ -4062,7 +4482,7 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>11</v>
@@ -4078,10 +4498,10 @@
         <v>14</v>
       </c>
       <c r="I28" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="J28" s="12" t="s">
         <v>88</v>
-      </c>
-      <c r="J28" s="12" t="s">
-        <v>89</v>
       </c>
       <c r="K28" s="6" t="b">
         <v>0</v>
@@ -4092,7 +4512,7 @@
     </row>
     <row r="29" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
@@ -4112,10 +4532,10 @@
         <v>41</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K29" s="6" t="b">
         <v>0</v>
@@ -4126,7 +4546,7 @@
     </row>
     <row r="30" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6" t="s">
@@ -4146,10 +4566,10 @@
         <v>41</v>
       </c>
       <c r="I30" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="J30" s="12" t="s">
         <v>91</v>
-      </c>
-      <c r="J30" s="12" t="s">
-        <v>92</v>
       </c>
       <c r="K30" s="6" t="b">
         <v>0</v>
@@ -4182,10 +4602,10 @@
         <v>44</v>
       </c>
       <c r="I31" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J31" s="12" t="s">
         <v>93</v>
-      </c>
-      <c r="J31" s="12" t="s">
-        <v>94</v>
       </c>
       <c r="K31" s="6" t="b">
         <v>0</v>
@@ -4218,10 +4638,10 @@
         <v>45</v>
       </c>
       <c r="I32" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="J32" s="12" t="s">
         <v>95</v>
-      </c>
-      <c r="J32" s="12" t="s">
-        <v>96</v>
       </c>
       <c r="K32" s="6" t="b">
         <v>0</v>
@@ -4252,10 +4672,10 @@
         <v>14</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K33" s="6" t="b">
         <v>0</v>
@@ -4286,10 +4706,10 @@
         <v>14</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="K34" s="6" t="b">
         <v>0</v>
@@ -4300,7 +4720,7 @@
     </row>
     <row r="35" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6" t="s">
@@ -4313,7 +4733,7 @@
         <v>17000</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G35" s="6">
         <v>34000</v>
@@ -4322,10 +4742,10 @@
         <v>41</v>
       </c>
       <c r="I35" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="J35" s="8" t="s">
         <v>98</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>99</v>
       </c>
       <c r="K35" s="6" t="b">
         <v>0</v>
@@ -4336,7 +4756,7 @@
     </row>
     <row r="36" spans="1:12" ht="126.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6" t="s">
@@ -4349,7 +4769,7 @@
         <v>17000</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G36" s="6">
         <v>34000</v>
@@ -4358,10 +4778,10 @@
         <v>41</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K36" s="6" t="b">
         <v>0</v>
@@ -4372,7 +4792,7 @@
     </row>
     <row r="37" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6" t="s">
@@ -4385,7 +4805,7 @@
         <v>17000</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G37" s="6">
         <v>34000</v>
@@ -4394,10 +4814,10 @@
         <v>41</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K37" s="6" t="b">
         <v>0</v>
@@ -4408,7 +4828,7 @@
     </row>
     <row r="38" spans="1:12" ht="91" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6" t="s">
@@ -4421,7 +4841,7 @@
         <v>17000</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G38" s="6">
         <v>34000</v>
@@ -4430,10 +4850,10 @@
         <v>41</v>
       </c>
       <c r="I38" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="J38" s="8" t="s">
         <v>102</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>103</v>
       </c>
       <c r="K38" s="6" t="b">
         <v>0</v>
@@ -4444,7 +4864,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
@@ -4464,10 +4884,10 @@
         <v>52</v>
       </c>
       <c r="I39" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="J39" s="12" t="s">
         <v>104</v>
-      </c>
-      <c r="J39" s="12" t="s">
-        <v>105</v>
       </c>
       <c r="K39" s="6" t="b">
         <v>0</v>
@@ -4498,10 +4918,10 @@
         <v>52</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K40" s="6" t="b">
         <v>0</v>
@@ -4532,10 +4952,10 @@
         <v>14</v>
       </c>
       <c r="I41" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="J41" s="14" t="s">
         <v>107</v>
-      </c>
-      <c r="J41" s="14" t="s">
-        <v>108</v>
       </c>
       <c r="K41" s="6" t="b">
         <v>0</v>
@@ -4546,7 +4966,7 @@
     </row>
     <row r="42" spans="1:12" ht="98.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
@@ -4566,10 +4986,10 @@
         <v>45</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J42" s="15" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K42" s="6" t="b">
         <v>0</v>
@@ -4600,10 +5020,10 @@
         <v>45</v>
       </c>
       <c r="I43" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="J43" s="15" t="s">
         <v>110</v>
-      </c>
-      <c r="J43" s="15" t="s">
-        <v>111</v>
       </c>
       <c r="K43" s="6" t="b">
         <v>0</v>
@@ -4634,10 +5054,10 @@
         <v>14</v>
       </c>
       <c r="I44" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="J44" s="8" t="s">
         <v>300</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>306</v>
       </c>
       <c r="K44" s="6" t="b">
         <v>0</v>
@@ -4670,10 +5090,10 @@
         <v>56</v>
       </c>
       <c r="I45" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="J45" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="J45" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="K45" s="6" t="b">
         <v>0</v>
@@ -4704,10 +5124,10 @@
         <v>59</v>
       </c>
       <c r="I46" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="J46" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>115</v>
       </c>
       <c r="K46" s="6" t="b">
         <v>0</v>
@@ -4738,10 +5158,10 @@
         <v>13</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K47" s="6" t="b">
         <v>0</v>
@@ -4752,7 +5172,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6" t="s">
@@ -4772,10 +5192,10 @@
         <v>61</v>
       </c>
       <c r="I48" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J48" s="14" t="s">
         <v>117</v>
-      </c>
-      <c r="J48" s="14" t="s">
-        <v>118</v>
       </c>
       <c r="K48" s="6" t="b">
         <v>0</v>
@@ -4806,10 +5226,10 @@
         <v>12</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K49" s="6" t="b">
         <v>0</v>
@@ -4824,7 +5244,7 @@
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>11</v>
@@ -4840,10 +5260,10 @@
         <v>12</v>
       </c>
       <c r="I50" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="J50" s="14" t="s">
         <v>120</v>
-      </c>
-      <c r="J50" s="14" t="s">
-        <v>121</v>
       </c>
       <c r="K50" s="6" t="b">
         <v>0</v>
@@ -4874,10 +5294,10 @@
         <v>12</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="K51" s="6" t="b">
         <v>0</v>
@@ -4908,10 +5328,10 @@
         <v>14</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J52" s="15" t="s">
-        <v>143</v>
+        <v>341</v>
       </c>
       <c r="K52" s="6" t="b">
         <v>0</v>
@@ -4926,7 +5346,7 @@
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>11</v>
@@ -4942,10 +5362,10 @@
         <v>14</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K53" s="6" t="b">
         <v>0</v>
@@ -4960,7 +5380,7 @@
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>11</v>
@@ -4976,10 +5396,10 @@
         <v>14</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="K54" s="6" t="b">
         <v>0</v>
@@ -4994,7 +5414,7 @@
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>11</v>
@@ -5010,10 +5430,10 @@
         <v>14</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="K55" s="6" t="b">
         <v>0</v>
@@ -5028,7 +5448,7 @@
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>11</v>
@@ -5044,10 +5464,10 @@
         <v>32</v>
       </c>
       <c r="I56" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="J56" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="K56" s="6" t="b">
         <v>0</v>
@@ -5058,11 +5478,11 @@
     </row>
     <row r="57" spans="1:12" ht="377" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>11</v>
@@ -5071,7 +5491,7 @@
         <v>22000</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G57" s="6">
         <v>27000</v>
@@ -5080,10 +5500,10 @@
         <v>17</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="K57" s="6" t="b">
         <v>0</v>
@@ -5094,11 +5514,11 @@
     </row>
     <row r="58" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A58" s="16" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B58" s="16"/>
       <c r="C58" s="16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D58" s="16" t="s">
         <v>27</v>
@@ -5114,10 +5534,10 @@
         <v>14</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J58" s="18" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K58" s="19" t="b">
         <v>0</v>
@@ -5128,11 +5548,11 @@
     </row>
     <row r="59" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A59" s="16" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B59" s="16"/>
       <c r="C59" s="16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D59" s="16" t="s">
         <v>20</v>
@@ -5148,10 +5568,10 @@
         <v>14</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J59" s="18" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K59" s="19" t="b">
         <v>0</v>
@@ -5162,11 +5582,11 @@
     </row>
     <row r="60" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A60" s="16" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B60" s="16"/>
       <c r="C60" s="16" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D60" s="16" t="s">
         <v>20</v>
@@ -5182,10 +5602,10 @@
         <v>14</v>
       </c>
       <c r="I60" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="J60" s="18" t="s">
         <v>181</v>
-      </c>
-      <c r="J60" s="18" t="s">
-        <v>184</v>
       </c>
       <c r="K60" s="19" t="b">
         <v>0</v>
@@ -5196,11 +5616,11 @@
     </row>
     <row r="61" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A61" s="16" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B61" s="16"/>
       <c r="C61" s="16" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D61" s="16" t="s">
         <v>20</v>
@@ -5216,10 +5636,10 @@
         <v>14</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="J61" s="18" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K61" s="19" t="b">
         <v>0</v>
@@ -5230,11 +5650,11 @@
     </row>
     <row r="62" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A62" s="16" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B62" s="16"/>
       <c r="C62" s="16" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D62" s="16" t="s">
         <v>20</v>
@@ -5250,10 +5670,10 @@
         <v>14</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J62" s="18" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="K62" s="19" t="b">
         <v>0</v>
@@ -5264,11 +5684,11 @@
     </row>
     <row r="63" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A63" s="16" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B63" s="16"/>
       <c r="C63" s="16" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D63" s="16" t="s">
         <v>20</v>
@@ -5284,10 +5704,10 @@
         <v>14</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J63" s="18" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K63" s="19" t="b">
         <v>0</v>
@@ -5298,11 +5718,11 @@
     </row>
     <row r="64" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A64" s="16" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B64" s="16"/>
       <c r="C64" s="16" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D64" s="16" t="s">
         <v>20</v>
@@ -5318,10 +5738,10 @@
         <v>14</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J64" s="18" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K64" s="19" t="b">
         <v>0</v>
@@ -5332,11 +5752,11 @@
     </row>
     <row r="65" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A65" s="16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B65" s="16"/>
       <c r="C65" s="16" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D65" s="16" t="s">
         <v>20</v>
@@ -5352,10 +5772,10 @@
         <v>14</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J65" s="18" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="K65" s="19" t="b">
         <v>0</v>
@@ -5366,11 +5786,11 @@
     </row>
     <row r="66" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A66" s="16" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B66" s="16"/>
       <c r="C66" s="16" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D66" s="16" t="s">
         <v>20</v>
@@ -5386,10 +5806,10 @@
         <v>14</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J66" s="18" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K66" s="19" t="b">
         <v>0</v>
@@ -5400,11 +5820,11 @@
     </row>
     <row r="67" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A67" s="16" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B67" s="16"/>
       <c r="C67" s="16" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D67" s="16" t="s">
         <v>20</v>
@@ -5420,10 +5840,10 @@
         <v>14</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J67" s="18" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="K67" s="19" t="b">
         <v>0</v>
@@ -5434,11 +5854,11 @@
     </row>
     <row r="68" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A68" s="16" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B68" s="16"/>
       <c r="C68" s="16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D68" s="16" t="s">
         <v>20</v>
@@ -5454,10 +5874,10 @@
         <v>14</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J68" s="18" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="K68" s="19" t="b">
         <v>0</v>
@@ -5468,11 +5888,11 @@
     </row>
     <row r="69" spans="1:12" ht="406" x14ac:dyDescent="0.35">
       <c r="A69" s="16" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B69" s="16"/>
       <c r="C69" s="16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D69" s="16" t="s">
         <v>20</v>
@@ -5488,10 +5908,10 @@
         <v>14</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J69" s="18" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K69" s="19" t="b">
         <v>0</v>
@@ -5502,11 +5922,11 @@
     </row>
     <row r="70" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A70" s="16" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B70" s="16"/>
       <c r="C70" s="16" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D70" s="16" t="s">
         <v>20</v>
@@ -5522,10 +5942,10 @@
         <v>14</v>
       </c>
       <c r="I70" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="J70" s="17" t="s">
         <v>213</v>
-      </c>
-      <c r="J70" s="17" t="s">
-        <v>216</v>
       </c>
       <c r="K70" s="19" t="b">
         <v>0</v>
@@ -5536,11 +5956,11 @@
     </row>
     <row r="71" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A71" s="16" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B71" s="16"/>
       <c r="C71" s="16" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D71" s="16" t="s">
         <v>20</v>
@@ -5556,10 +5976,10 @@
         <v>14</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J71" s="18" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K71" s="19" t="b">
         <v>0</v>
@@ -5570,11 +5990,11 @@
     </row>
     <row r="72" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A72" s="16" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B72" s="16"/>
       <c r="C72" s="16" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D72" s="16" t="s">
         <v>20</v>
@@ -5590,10 +6010,10 @@
         <v>14</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J72" s="18" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="K72" s="19" t="b">
         <v>0</v>
@@ -5604,11 +6024,11 @@
     </row>
     <row r="73" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A73" s="16" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B73" s="16"/>
       <c r="C73" s="16" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D73" s="16" t="s">
         <v>20</v>
@@ -5624,10 +6044,10 @@
         <v>14</v>
       </c>
       <c r="I73" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="J73" s="18" t="s">
         <v>219</v>
-      </c>
-      <c r="J73" s="18" t="s">
-        <v>222</v>
       </c>
       <c r="K73" s="19" t="b">
         <v>0</v>
@@ -5638,13 +6058,13 @@
     </row>
     <row r="74" spans="1:12" ht="319" x14ac:dyDescent="0.35">
       <c r="A74" s="16" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D74" s="16" t="s">
         <v>11</v>
@@ -5657,13 +6077,13 @@
         <v>34000</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I74" s="16" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="J74" s="18" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="K74" s="19" t="b">
         <v>0</v>
@@ -5674,11 +6094,11 @@
     </row>
     <row r="75" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A75" s="16" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B75" s="16"/>
       <c r="C75" s="16" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D75" s="16" t="s">
         <v>20</v>
@@ -5694,10 +6114,10 @@
         <v>14</v>
       </c>
       <c r="I75" s="16" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="J75" s="18" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="K75" s="19" t="b">
         <v>0</v>
@@ -5708,11 +6128,11 @@
     </row>
     <row r="76" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A76" s="16" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B76" s="16"/>
       <c r="C76" s="16" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D76" s="16" t="s">
         <v>20</v>
@@ -5728,10 +6148,10 @@
         <v>14</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="K76" s="19" t="b">
         <v>0</v>
@@ -5742,11 +6162,11 @@
     </row>
     <row r="77" spans="1:12" ht="87" x14ac:dyDescent="0.35">
       <c r="A77" s="16" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B77" s="16"/>
       <c r="C77" s="16" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D77" s="16" t="s">
         <v>20</v>
@@ -5762,10 +6182,10 @@
         <v>14</v>
       </c>
       <c r="I77" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J77" s="18" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="K77" s="19" t="b">
         <v>0</v>
@@ -5776,13 +6196,13 @@
     </row>
     <row r="78" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A78" s="16" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D78" s="16" t="s">
         <v>20</v>
@@ -5798,10 +6218,10 @@
         <v>14</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="J78" s="18" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="K78" s="19" t="b">
         <v>0</v>
@@ -5812,13 +6232,13 @@
     </row>
     <row r="79" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A79" s="16" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D79" s="16" t="s">
         <v>20</v>
@@ -5834,10 +6254,10 @@
         <v>14</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="J79" s="18" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="K79" s="19" t="b">
         <v>0</v>
@@ -5848,11 +6268,11 @@
     </row>
     <row r="80" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A80" s="16" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B80" s="16"/>
       <c r="C80" s="16" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D80" s="16" t="s">
         <v>20</v>
@@ -5868,10 +6288,10 @@
         <v>14</v>
       </c>
       <c r="I80" s="16" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="K80" s="19" t="b">
         <v>0</v>
@@ -5882,11 +6302,11 @@
     </row>
     <row r="81" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A81" s="16" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B81" s="16"/>
       <c r="C81" s="16" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D81" s="16" t="s">
         <v>20</v>
@@ -5902,10 +6322,10 @@
         <v>14</v>
       </c>
       <c r="I81" s="16" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="J81" s="17" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="K81" s="19" t="b">
         <v>0</v>
@@ -5916,11 +6336,11 @@
     </row>
     <row r="82" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A82" s="16" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B82" s="16"/>
       <c r="C82" s="16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D82" s="16" t="s">
         <v>20</v>
@@ -5936,10 +6356,10 @@
         <v>14</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="J82" s="18" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="K82" s="19" t="b">
         <v>0</v>
@@ -5950,11 +6370,11 @@
     </row>
     <row r="83" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A83" s="16" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B83" s="16"/>
       <c r="C83" s="16" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D83" s="16" t="s">
         <v>20</v>
@@ -5970,10 +6390,10 @@
         <v>14</v>
       </c>
       <c r="I83" s="17" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="J83" s="21" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="K83" s="19" t="b">
         <v>0</v>
@@ -5984,11 +6404,11 @@
     </row>
     <row r="84" spans="1:12" ht="261" x14ac:dyDescent="0.35">
       <c r="A84" s="16" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B84" s="16"/>
       <c r="C84" s="16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D84" s="16" t="s">
         <v>20</v>
@@ -6004,10 +6424,10 @@
         <v>14</v>
       </c>
       <c r="I84" s="16" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="J84" s="21" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="K84" s="19" t="b">
         <v>0</v>
@@ -6018,11 +6438,11 @@
     </row>
     <row r="85" spans="1:12" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A85" s="16" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B85" s="16"/>
       <c r="C85" s="16" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D85" s="16" t="s">
         <v>20</v>
@@ -6031,7 +6451,7 @@
         <v>25000</v>
       </c>
       <c r="F85" s="17" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="G85" s="16">
         <v>36000</v>
@@ -6040,10 +6460,10 @@
         <v>13</v>
       </c>
       <c r="I85" s="16" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="J85" s="21" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="K85" s="19" t="b">
         <v>0</v>
@@ -6054,11 +6474,11 @@
     </row>
     <row r="86" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A86" s="16" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B86" s="16"/>
       <c r="C86" s="16" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D86" s="16" t="s">
         <v>20</v>
@@ -6074,10 +6494,10 @@
         <v>14</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="J86" s="21" t="s">
-        <v>271</v>
+        <v>345</v>
       </c>
       <c r="K86" s="19" t="b">
         <v>0</v>
@@ -6088,11 +6508,11 @@
     </row>
     <row r="87" spans="1:12" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>11</v>
@@ -6108,10 +6528,10 @@
         <v>12</v>
       </c>
       <c r="I87" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J87" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="J87" s="11" t="s">
-        <v>76</v>
       </c>
       <c r="K87" s="6" t="b">
         <v>0</v>
@@ -6122,7 +6542,7 @@
     </row>
     <row r="88" spans="1:12" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A88" s="6" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6" t="s">
@@ -6139,13 +6559,13 @@
         <v>27000</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="I88" s="7" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="J88" s="22" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="K88" s="6" t="b">
         <v>0</v>
@@ -6156,7 +6576,7 @@
     </row>
     <row r="89" spans="1:12" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A89" s="6" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6" t="s">
@@ -6176,10 +6596,10 @@
         <v>14</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="J89" s="22" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="K89" s="6" t="b">
         <v>0</v>
@@ -6190,11 +6610,11 @@
     </row>
     <row r="90" spans="1:12" ht="319" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>11</v>
@@ -6210,10 +6630,10 @@
         <v>12</v>
       </c>
       <c r="I90" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J90" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K90" s="6" t="b">
         <v>0</v>
@@ -6224,11 +6644,11 @@
     </row>
     <row r="91" spans="1:12" ht="319" x14ac:dyDescent="0.35">
       <c r="A91" s="23" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B91" s="23"/>
       <c r="C91" s="23" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D91" s="23" t="s">
         <v>11</v>
@@ -6241,13 +6661,13 @@
         <v>45000</v>
       </c>
       <c r="H91" s="23" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="J91" s="22" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="K91" s="6" t="b">
         <v>0</v>
@@ -6258,7 +6678,7 @@
     </row>
     <row r="92" spans="1:12" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A92" s="23" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B92" s="23"/>
       <c r="C92" s="23" t="s">
@@ -6278,10 +6698,10 @@
         <v>14</v>
       </c>
       <c r="I92" s="24" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J92" s="22" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="K92" s="6" t="b">
         <v>0</v>
@@ -6292,11 +6712,11 @@
     </row>
     <row r="93" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A93" s="23" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B93" s="23"/>
       <c r="C93" s="23" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D93" s="23" t="s">
         <v>20</v>
@@ -6312,10 +6732,10 @@
         <v>14</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="J93" s="11" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="K93" s="6" t="b">
         <v>0</v>
@@ -6326,11 +6746,11 @@
     </row>
     <row r="94" spans="1:12" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A94" s="25" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B94" s="25"/>
       <c r="C94" s="25" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D94" s="25" t="s">
         <v>20</v>
@@ -6346,10 +6766,10 @@
         <v>14</v>
       </c>
       <c r="I94" s="25" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="J94" s="26" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="K94" s="25" t="b">
         <v>0</v>
@@ -6360,11 +6780,11 @@
     </row>
     <row r="95" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A95" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B95" s="25"/>
       <c r="C95" s="25" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D95" s="25" t="s">
         <v>20</v>
@@ -6380,10 +6800,10 @@
         <v>61</v>
       </c>
       <c r="I95" s="26" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="J95" s="27" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="K95" s="25" t="b">
         <v>0</v>
@@ -6394,11 +6814,11 @@
     </row>
     <row r="96" spans="1:12" ht="261" x14ac:dyDescent="0.35">
       <c r="A96" s="25" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B96" s="25"/>
       <c r="C96" s="25" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D96" s="25" t="s">
         <v>20</v>
@@ -6414,10 +6834,10 @@
         <v>14</v>
       </c>
       <c r="I96" s="25" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="J96" s="27" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="K96" s="25" t="b">
         <v>0</v>
@@ -6428,11 +6848,11 @@
     </row>
     <row r="97" spans="1:12" ht="174" x14ac:dyDescent="0.35">
       <c r="A97" s="25" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B97" s="25"/>
       <c r="C97" s="25" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D97" s="25" t="s">
         <v>20</v>
@@ -6448,10 +6868,10 @@
         <v>14</v>
       </c>
       <c r="I97" s="25" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="J97" s="26" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="K97" s="25" t="b">
         <v>0</v>
@@ -6462,11 +6882,11 @@
     </row>
     <row r="98" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A98" s="25" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B98" s="25"/>
       <c r="C98" s="25" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D98" s="25" t="s">
         <v>20</v>
@@ -6482,10 +6902,10 @@
         <v>14</v>
       </c>
       <c r="I98" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="J98" s="26" t="s">
         <v>320</v>
-      </c>
-      <c r="J98" s="26" t="s">
-        <v>327</v>
       </c>
       <c r="K98" s="25" t="b">
         <v>0</v>
@@ -6496,11 +6916,11 @@
     </row>
     <row r="99" spans="1:12" ht="319" x14ac:dyDescent="0.35">
       <c r="A99" s="25" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B99" s="25"/>
       <c r="C99" s="25" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D99" s="25" t="s">
         <v>20</v>
@@ -6516,10 +6936,10 @@
         <v>14</v>
       </c>
       <c r="I99" s="26" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="J99" s="26" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="K99" s="25" t="b">
         <v>0</v>
@@ -6530,11 +6950,11 @@
     </row>
     <row r="100" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A100" s="25" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B100" s="25"/>
       <c r="C100" s="25" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D100" s="25" t="s">
         <v>20</v>
@@ -6550,10 +6970,10 @@
         <v>14</v>
       </c>
       <c r="I100" s="26" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="J100" s="26" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="K100" s="25" t="b">
         <v>0</v>
@@ -6562,13 +6982,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="406" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:12" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A101" s="28" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B101" s="28"/>
       <c r="C101" s="28" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D101" s="28" t="s">
         <v>20</v>
@@ -6584,10 +7004,10 @@
         <v>14</v>
       </c>
       <c r="I101" s="29" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="J101" s="29" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="K101" s="28" t="b">
         <v>0</v>
@@ -6598,11 +7018,11 @@
     </row>
     <row r="102" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A102" s="25" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B102" s="25"/>
       <c r="C102" s="25" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D102" s="25" t="s">
         <v>20</v>
@@ -6618,10 +7038,10 @@
         <v>14</v>
       </c>
       <c r="I102" s="26" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="J102" s="26" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="K102" s="25" t="b">
         <v>0</v>
@@ -6630,13 +7050,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="203" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:12" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A103" s="28" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B103" s="28"/>
       <c r="C103" s="28" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D103" s="28" t="s">
         <v>11</v>
@@ -6652,15 +7072,321 @@
         <v>14</v>
       </c>
       <c r="I103" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="J103" s="29" t="s">
+        <v>342</v>
+      </c>
+      <c r="K103" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L103" s="28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="391.5" x14ac:dyDescent="0.35">
+      <c r="A104" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="B104" s="28"/>
+      <c r="C104" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="D104" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" s="28">
+        <v>20000</v>
+      </c>
+      <c r="F104" s="28"/>
+      <c r="G104" s="28">
+        <v>24000</v>
+      </c>
+      <c r="H104" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I104" s="29" t="s">
+        <v>328</v>
+      </c>
+      <c r="J104" s="29" t="s">
+        <v>329</v>
+      </c>
+      <c r="K104" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L104" s="28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A105" s="25" t="s">
+        <v>330</v>
+      </c>
+      <c r="B105" s="25"/>
+      <c r="C105" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="D105" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E105" s="25">
+        <v>21000</v>
+      </c>
+      <c r="F105" s="25"/>
+      <c r="G105" s="25">
+        <v>31500</v>
+      </c>
+      <c r="H105" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I105" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="J105" s="26" t="s">
+        <v>331</v>
+      </c>
+      <c r="K105" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L105" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A106" s="25" t="s">
+        <v>332</v>
+      </c>
+      <c r="B106" s="25"/>
+      <c r="C106" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="D106" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E106" s="25">
+        <v>8000</v>
+      </c>
+      <c r="F106" s="25"/>
+      <c r="G106" s="25">
+        <v>12000</v>
+      </c>
+      <c r="H106" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I106" s="25" t="s">
         <v>333</v>
       </c>
-      <c r="J103" s="29" t="s">
+      <c r="J106" s="26" t="s">
         <v>334</v>
       </c>
-      <c r="K103" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="L103" s="28" t="b">
+      <c r="K106" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L106" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A107" s="28" t="s">
+        <v>335</v>
+      </c>
+      <c r="B107" s="28"/>
+      <c r="C107" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="D107" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E107" s="28">
+        <v>46000</v>
+      </c>
+      <c r="F107" s="28"/>
+      <c r="G107" s="28">
+        <v>68500</v>
+      </c>
+      <c r="H107" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I107" s="29" t="s">
+        <v>328</v>
+      </c>
+      <c r="J107" s="29" t="s">
+        <v>336</v>
+      </c>
+      <c r="K107" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L107" s="28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A108" s="28" t="s">
+        <v>337</v>
+      </c>
+      <c r="B108" s="28"/>
+      <c r="C108" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="D108" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E108" s="28">
+        <v>68000</v>
+      </c>
+      <c r="F108" s="28"/>
+      <c r="G108" s="28">
+        <v>102000</v>
+      </c>
+      <c r="H108" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I108" s="28" t="s">
+        <v>338</v>
+      </c>
+      <c r="J108" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="K108" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L108" s="28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="333.5" x14ac:dyDescent="0.35">
+      <c r="A109" s="28" t="s">
+        <v>339</v>
+      </c>
+      <c r="B109" s="28"/>
+      <c r="C109" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="D109" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" s="28">
+        <v>58000</v>
+      </c>
+      <c r="F109" s="28"/>
+      <c r="G109" s="28">
+        <v>87000</v>
+      </c>
+      <c r="H109" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I109" s="29" t="s">
+        <v>338</v>
+      </c>
+      <c r="J109" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="K109" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L109" s="28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A110" s="25" t="s">
+        <v>351</v>
+      </c>
+      <c r="B110" s="25"/>
+      <c r="C110" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="D110" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E110" s="25">
+        <v>27000</v>
+      </c>
+      <c r="F110" s="25"/>
+      <c r="G110" s="25">
+        <v>40500</v>
+      </c>
+      <c r="H110" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I110" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="J110" s="26" t="s">
+        <v>353</v>
+      </c>
+      <c r="K110" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L110" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A111" s="25" t="s">
+        <v>354</v>
+      </c>
+      <c r="B111" s="25"/>
+      <c r="C111" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="D111" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E111" s="25">
+        <v>15000</v>
+      </c>
+      <c r="F111" s="25"/>
+      <c r="G111" s="25">
+        <v>22500</v>
+      </c>
+      <c r="H111" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I111" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="J111" s="26" t="s">
+        <v>352</v>
+      </c>
+      <c r="K111" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L111" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A112" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="B112" s="25"/>
+      <c r="C112" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="D112" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E112" s="25">
+        <v>19000</v>
+      </c>
+      <c r="F112" s="25"/>
+      <c r="G112" s="25">
+        <v>19000</v>
+      </c>
+      <c r="H112" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I112" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="J112" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="K112" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L112" s="25" t="b">
         <v>0</v>
       </c>
     </row>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0526577688ca4eec/Escritorio/Proyectos developer/Diseños_Gasper/Back-end/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1224" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{475A7107-F44D-4D35-AFB3-5531D56FB622}"/>
+  <xr:revisionPtr revIDLastSave="1276" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3F27347-06D3-45D9-A37E-364C6C39D771}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="369">
   <si>
     <t>name</t>
   </si>
@@ -91,9 +91,6 @@
     <t xml:space="preserve"> Chaqueta Semireflectiva </t>
   </si>
   <si>
-    <t>Reflectivo Seme-Impermeable en Conjunto</t>
-  </si>
-  <si>
     <t>Reflectiva con Cinta Rompevientos Cola de Pato</t>
   </si>
   <si>
@@ -214,9 +211,6 @@
     <t>Chaqueta en Tela Antifluido</t>
   </si>
   <si>
-    <t>Chaqueta Baiker-Pro</t>
-  </si>
-  <si>
     <t>Chaqueta Tricolor Rompevientos</t>
   </si>
   <si>
@@ -353,9 +347,6 @@
   </si>
   <si>
     <t>mediumblue,black,yellow,blue,red,white,royalblue</t>
-  </si>
-  <si>
-    <t>{"mediumblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240533/n60eaikcezvynntuau0v.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240528/zyo9kzojtxho9wvesmrp.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240531/ooyr3pz6uhvfsm77ejvk.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240532/bz2psdzgpyuyvjzjsdel.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240534/ub1joafbr0olhdtmbw0i.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240535/lwawv9dqvmiu5lxu728m.png"],"yellow":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240515/p9y8b9e5niqyywlk9sui.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240516/jp1rmju1wb5fxw9bxn3n.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240517/aafn2qd9tgpmekskj9vh.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240517/mudhcxxp6flsivis2qbr.png"],"blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240522/zfl1xwdjcwzcxpwwbqdw.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240523/vgozlwbmddque7ctdpxu.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240525/ypie8z5xidufdlcheiso.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240520/gsfb4nwft4oko0lkclv1.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240519/xurbgbhtwpunfux4x3tq.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240520/vyqamob8xq85rfqkr6q1.png"],"white":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240526/cxrgavd3mfsemkwkyatd.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240527/zdq90d5lcagyjfdkjji5.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240526/nqsgpezieko4rfklfth6.png"],"royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240540/ytouuhvitxe4wl7xmgcz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240541/geo8emnkqncogehf5qxb.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240540/risndn1ndpkwnagacnsn.png"]}</t>
   </si>
   <si>
     <t>aqua,white,orange,lime,red,blue,black,darkblue,pink</t>
@@ -1932,9 +1923,6 @@
     <t>black,blue,gray,green,darkblue,hotpink,steelblue</t>
   </si>
   <si>
-    <t>Reflectivo Seme-Impermeable en Conjunto.</t>
-  </si>
-  <si>
     <t>Buso Combinado.</t>
   </si>
   <si>
@@ -2509,9 +2497,6 @@
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155273/sarg592ljgtrlegxr9dg.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155275/b2b7ywzj4heuodk4kd0w.png" ], "black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155272/flxhhmuujdjpezxmkmqn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155273/j2qcht36qgzywyshdgjj.png"], "darkblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155272/dscu8zuigconhfyshe6z.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155277/eane79kkqkqetsbzchi5.png"],"darkgreen":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155276/jw0lguqjixqg7ke6adqs.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155275/yzp0sx5ta5dlqsraanw6.png"], "blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155273/lyu53mfn62se2kcebbee.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775155278/oiguw01ughqg2mldahy7.png"]}</t>
   </si>
   <si>
-    <t>Conjunto Baicker</t>
-  </si>
-  <si>
     <t>{
   "olive": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158910/bqfemdrldelrb5vv7s7h.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158925/okysbbknpxhsxub6mctr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158913/cj8v7h1il0icgey5tw6i.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775158921/syghxqv6xfjjwueepbkd.png" ],
@@ -3017,6 +3002,214 @@
   </si>
   <si>
     <t>Licra de Pecho (Dama).</t>
+  </si>
+  <si>
+    <t>{
+  "mediumblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240533/n60eaikcezvynntuau0v.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240528/zyo9kzojtxho9wvesmrp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240531/ooyr3pz6uhvfsm77ejvk.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240532/bz2psdzgpyuyvjzjsdel.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240534/ub1joafbr0olhdtmbw0i.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240535/lwawv9dqvmiu5lxu728m.png"
+  ],
+  "yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240515/p9y8b9e5niqyywlk9sui.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240516/jp1rmju1wb5fxw9bxn3n.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240517/aafn2qd9tgpmekskj9vh.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240517/mudhcxxp6flsivis2qbr.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240522/zfl1xwdjcwzcxpwwbqdw.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240523/vgozlwbmddque7ctdpxu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240525/ypie8z5xidufdlcheiso.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240520/gsfb4nwft4oko0lkclv1.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240519/xurbgbhtwpunfux4x3tq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775574769/tsg8ghtsviyzrzpzbxho.png"
+  ],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240526/cxrgavd3mfsemkwkyatd.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240527/zdq90d5lcagyjfdkjji5.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775574766/fhoorqhu6kvf7uhuqwb9.png"
+  ],
+  "royalblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240540/ytouuhvitxe4wl7xmgcz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773240541/geo8emnkqncogehf5qxb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775574766/dnjkxauwzrmzoznqk01h.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>Reflectivo Semi-Impermeable en Conjunto</t>
+  </si>
+  <si>
+    <t>Chaqueta Biker-Pro</t>
+  </si>
+  <si>
+    <t>Reflectivo Semi-Impermeable en Conjunto.</t>
+  </si>
+  <si>
+    <t>Conjunto Biker</t>
+  </si>
+  <si>
+    <t>Pantaloneta Caballero</t>
+  </si>
+  <si>
+    <t>{
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651814/wlacwyblnhi32escpo4o.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651825/bhtpynxanx04inbktyj6.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651810/ct2jayrr6bxdasybqzgm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651826/mbcnfoo65co268ztwwo5.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651816/etfkojr7ryug7ygrdn00.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651808/w9cftiufnqnfpp1eueiy.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651820/s6pvdqys3nmwokav5dzr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651822/z22hk0aru0ybl4gxdw9g.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651807/k93nuv6vxdalw8wy7umd.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651826/gzfwhs13fojdt8fympfc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651817/vd1mxgdkqbgkdmpchmgb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651811/lwc00imfrkyyu69tle1r.png"
+  ],
+  "crimson": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651829/wquwceqwrbdxwjh25ryq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651815/rufva87pedbz61giwxxa.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651818/tdlk5htahjm0s5snhqli.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651813/kweq2shg5rlqzrn9m4el.png"
+  ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651812/sefxwphiqxqxjzkklkxx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651828/g7suupjvvemlzo6msafd.png", 
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651809/ntzbwlnxc0xauq9gupdf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651824/gzattowud9p0a7zpsmhm.png"
+  ],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651824/kmb6emjozrqejxbufgus.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651808/u1lxpykge4i9glvakpue.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651823/lzicrtwio8bfoxbudxwz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651811/lhridwrfeye1rh1r0l2q.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651827/g3z7gel91pdstlv2e1l8.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651816/kq826xuhdsbye5vyupwr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651821/sc7zzv2u4jkpawuzpdcu.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651819/wd6hvrxu5emoawuzy27y.png"
+  ]}</t>
+  </si>
+  <si>
+    <t>olive,red,gray,crimson,purple,white,black</t>
+  </si>
+  <si>
+    <t>Bicicletero Biker</t>
+  </si>
+  <si>
+    <t>{
+  "crimson": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651361/xkrtvse1len5cz0sxma3.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651360/to29gsujtardajw2povw.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651360/s2swnqqb697iomkawz62.png"
+  ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651363/j8pcrhsmwtr0vso9inhq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651360/p7j7y4la6egbkogqid8j.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651364/z1iq0bncqovbpv7onvhj.png"
+  ],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651360/hlktxxkyxuqr9nwqkwt5.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651361/bespsqon4rpkafd8unbk.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651363/lmeuqck8agxgf1ewbfob.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651360/x70qf7bay6bfnkcvjvte.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651362/osvjngd5ja8veyccefjd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651362/ibhtlw5eq9yuvecpbrxo.png"
+  ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651367/cwmihjqh6o8sy2qyngos.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651366/xony7fij7etidcummcnh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651362/xn466n2ruzpnfkufxgsf.png"
+  ],
+  "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651365/kzry4z53mogxm51hyhjc.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651365/kskjaxdm8fmmipappuxl.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651366/elp4hmu1izgtdvwmldww.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651363/qg89gjeltetn079otd0v.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>crimson,purple,white,black,darkblue,darkgreen</t>
+  </si>
+  <si>
+    <t>Pantaloneta Rompevientos hombre</t>
+  </si>
+  <si>
+    <t>olive,red,gray,crimson,purple,white,black,darkblue,darkgreen,blue,yellow,darkred</t>
+  </si>
+  <si>
+    <t>Pantaloneta con licra Interna</t>
+  </si>
+  <si>
+    <t>L, XL</t>
+  </si>
+  <si>
+    <t>olive,red,gray,crimson,purple</t>
+  </si>
+  <si>
+    <t>{
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651666/dsssejqwq73b7kwjmmit.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651661/biiarcayfymv2q2gf9tc.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651663/z4kcg7icwsiqfcxolm3d.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651664/pogz0zbt82aim6s4jxlo.png"  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651663/kdun2vswsj1ytpcox3ew.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651664/qu8yet73kshag5euozkj.png"  ],
+  "crimson": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651661/wzy9lwf9omt225bpfsbr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651667/xnud45iqezvvno4dqfdi.png"  ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651661/qkifqvxrtub1qcts8ayy.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651666/xejrb8ewgq3xsereyoms.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651667/v4kqkfbudd5iqwcd5luo.png"  ]
+  }</t>
+  </si>
+  <si>
+    <t>{
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651807/k93nuv6vxdalw8wy7umd.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651822/z22hk0aru0ybl4gxdw9g.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651814/wlacwyblnhi32escpo4o.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651825/bhtpynxanx04inbktyj6.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651810/ct2jayrr6bxdasybqzgm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651826/mbcnfoo65co268ztwwo5.png"
+  ],
+  "crimson": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651816/etfkojr7ryug7ygrdn00.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651808/w9cftiufnqnfpp1eueiy.png"
+  ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651820/s6pvdqys3nmwokav5dzr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651812/sefxwphiqxqxjzkklkxx.png"
+  ],
+  "white": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651828/g7suupjvvemlzo6msafd.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651826/gzfwhs13fojdt8fympfc.png"
+  ],
+  "black": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651817/vd1mxgdkqbgkdmpchmgb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651811/lwc00imfrkyyu69tle1r.png"
+  ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651829/wquwceqwrbdxwjh25ryq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651815/rufva87pedbz61giwxxa.png"
+  ],
+  "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651818/tdlk5htahjm0s5snhqli.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651813/kweq2shg5rlqzrn9m4el.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651823/lzicrtwio8bfoxbudxwz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651811/lhridwrfeye1rh1r0l2q.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651824/kmb6emjozrqejxbufgus.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651808/u1lxpykge4i9glvakpue.png"
+  ],
+  "yellow": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651821/sc7zzv2u4jkpawuzpdcu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651816/kq826xuhdsbye5vyupwr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651827/g3z7gel91pdstlv2e1l8.png"
+  ],
+  "darkred": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651809/ntzbwlnxc0xauq9gupdf.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651824/gzattowud9p0a7zpsmhm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651819/wd6hvrxu5emoawuzy27y.png"
+  ]
+}</t>
   </si>
 </sst>
 </file>
@@ -3512,7 +3705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}">
-  <dimension ref="A1:L112"/>
+  <dimension ref="A1:L116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="57.54296875" style="2" customWidth="1"/>
@@ -3533,7 +3726,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>1</v>
@@ -3571,10 +3764,10 @@
         <v>16</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>11</v>
@@ -3583,7 +3776,7 @@
         <v>33000</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2" s="6">
         <v>49500</v>
@@ -3592,10 +3785,10 @@
         <v>17</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="K2" s="6" t="b">
         <v>0</v>
@@ -3606,13 +3799,13 @@
     </row>
     <row r="3" spans="1:12" s="3" customFormat="1" ht="99.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>11</v>
@@ -3628,10 +3821,10 @@
         <v>14</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="K3" s="6" t="b">
         <v>0</v>
@@ -3642,13 +3835,13 @@
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="89.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>11</v>
@@ -3657,7 +3850,7 @@
         <v>28000</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G4" s="6">
         <v>42000</v>
@@ -3666,10 +3859,10 @@
         <v>17</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K4" s="6" t="b">
         <v>0</v>
@@ -3683,10 +3876,10 @@
         <v>19</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>20</v>
@@ -3695,7 +3888,7 @@
         <v>28000</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5" s="6">
         <v>42000</v>
@@ -3704,10 +3897,10 @@
         <v>17</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="K5" s="6" t="b">
         <v>0</v>
@@ -3722,7 +3915,7 @@
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>11</v>
@@ -3738,10 +3931,10 @@
         <v>14</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="K6" s="6" t="b">
         <v>0</v>
@@ -3752,11 +3945,11 @@
     </row>
     <row r="7" spans="1:12" ht="77.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>22</v>
+        <v>352</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>11</v>
@@ -3772,10 +3965,10 @@
         <v>12</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K7" s="6" t="b">
         <v>0</v>
@@ -3786,11 +3979,11 @@
     </row>
     <row r="8" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>11</v>
@@ -3799,7 +3992,7 @@
         <v>20000</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G8" s="6">
         <v>30000</v>
@@ -3808,10 +4001,10 @@
         <v>13</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K8" s="6" t="b">
         <v>0</v>
@@ -3822,11 +4015,11 @@
     </row>
     <row r="9" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>11</v>
@@ -3835,7 +4028,7 @@
         <v>20000</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G9" s="6">
         <v>30000</v>
@@ -3844,10 +4037,10 @@
         <v>13</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K9" s="6" t="b">
         <v>0</v>
@@ -3858,11 +4051,11 @@
     </row>
     <row r="10" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>11</v>
@@ -3878,10 +4071,10 @@
         <v>14</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K10" s="6" t="b">
         <v>0</v>
@@ -3892,11 +4085,11 @@
     </row>
     <row r="11" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>11</v>
@@ -3912,10 +4105,10 @@
         <v>14</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K11" s="6" t="b">
         <v>0</v>
@@ -3926,11 +4119,11 @@
     </row>
     <row r="12" spans="1:12" ht="47" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>11</v>
@@ -3946,10 +4139,10 @@
         <v>14</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="K12" s="6" t="b">
         <v>0</v>
@@ -3960,11 +4153,11 @@
     </row>
     <row r="13" spans="1:12" ht="47" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>11</v>
@@ -3980,10 +4173,10 @@
         <v>14</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="K13" s="6" t="b">
         <v>0</v>
@@ -3994,32 +4187,32 @@
     </row>
     <row r="14" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" s="6">
         <v>38000</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G14" s="6">
         <v>57000</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K14" s="6" t="b">
         <v>0</v>
@@ -4030,32 +4223,32 @@
     </row>
     <row r="15" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" s="6">
         <v>38000</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G15" s="6">
         <v>57000</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K15" s="6" t="b">
         <v>0</v>
@@ -4066,11 +4259,11 @@
     </row>
     <row r="16" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>11</v>
@@ -4079,19 +4272,19 @@
         <v>38000</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G16" s="6">
         <v>57000</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="K16" s="6" t="b">
         <v>0</v>
@@ -4102,11 +4295,11 @@
     </row>
     <row r="17" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>11</v>
@@ -4115,19 +4308,19 @@
         <v>38000</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G17" s="6">
         <v>57000</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="K17" s="6" t="b">
         <v>0</v>
@@ -4138,14 +4331,14 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E18" s="6">
         <v>21000</v>
@@ -4155,13 +4348,13 @@
         <v>31500</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K18" s="6" t="b">
         <v>0</v>
@@ -4172,14 +4365,14 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" s="6">
         <v>21000</v>
@@ -4189,13 +4382,13 @@
         <v>31500</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K19" s="6" t="b">
         <v>0</v>
@@ -4206,11 +4399,11 @@
     </row>
     <row r="20" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>11</v>
@@ -4226,10 +4419,10 @@
         <v>14</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K20" s="6" t="b">
         <v>0</v>
@@ -4240,11 +4433,11 @@
     </row>
     <row r="21" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>11</v>
@@ -4260,10 +4453,10 @@
         <v>14</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K21" s="6" t="b">
         <v>0</v>
@@ -4274,11 +4467,11 @@
     </row>
     <row r="22" spans="1:12" ht="54.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>11</v>
@@ -4291,13 +4484,13 @@
         <v>31500</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K22" s="6" t="b">
         <v>0</v>
@@ -4308,11 +4501,11 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>11</v>
@@ -4328,10 +4521,10 @@
         <v>14</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K23" s="6" t="b">
         <v>0</v>
@@ -4342,11 +4535,11 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>11</v>
@@ -4362,10 +4555,10 @@
         <v>14</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K24" s="6" t="b">
         <v>0</v>
@@ -4376,11 +4569,11 @@
     </row>
     <row r="25" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>11</v>
@@ -4396,10 +4589,10 @@
         <v>14</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="K25" s="6" t="b">
         <v>0</v>
@@ -4410,7 +4603,7 @@
     </row>
     <row r="26" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
@@ -4430,10 +4623,10 @@
         <v>14</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="K26" s="6" t="b">
         <v>0</v>
@@ -4448,7 +4641,7 @@
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>11</v>
@@ -4464,10 +4657,10 @@
         <v>14</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="K27" s="6" t="b">
         <v>0</v>
@@ -4478,11 +4671,11 @@
     </row>
     <row r="28" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>11</v>
@@ -4498,10 +4691,10 @@
         <v>14</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K28" s="6" t="b">
         <v>0</v>
@@ -4512,7 +4705,7 @@
     </row>
     <row r="29" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
@@ -4529,13 +4722,13 @@
         <v>18000</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K29" s="6" t="b">
         <v>0</v>
@@ -4546,14 +4739,14 @@
     </row>
     <row r="30" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E30" s="6">
         <v>12000</v>
@@ -4563,13 +4756,13 @@
         <v>18000</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K30" s="6" t="b">
         <v>0</v>
@@ -4580,7 +4773,7 @@
     </row>
     <row r="31" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6" t="s">
@@ -4593,19 +4786,19 @@
         <v>20000</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G31" s="6">
         <v>28500</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K31" s="6" t="b">
         <v>0</v>
@@ -4616,7 +4809,7 @@
     </row>
     <row r="32" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6" t="s">
@@ -4629,19 +4822,19 @@
         <v>18000</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G32" s="6">
         <v>27000</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K32" s="6" t="b">
         <v>0</v>
@@ -4652,7 +4845,7 @@
     </row>
     <row r="33" spans="1:12" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6" t="s">
@@ -4672,10 +4865,10 @@
         <v>14</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="K33" s="6" t="b">
         <v>0</v>
@@ -4686,7 +4879,7 @@
     </row>
     <row r="34" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6" t="s">
@@ -4706,10 +4899,10 @@
         <v>14</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="K34" s="6" t="b">
         <v>0</v>
@@ -4720,7 +4913,7 @@
     </row>
     <row r="35" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6" t="s">
@@ -4733,19 +4926,19 @@
         <v>17000</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G35" s="6">
         <v>34000</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K35" s="6" t="b">
         <v>0</v>
@@ -4756,7 +4949,7 @@
     </row>
     <row r="36" spans="1:12" ht="126.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6" t="s">
@@ -4769,19 +4962,19 @@
         <v>17000</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G36" s="6">
         <v>34000</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K36" s="6" t="b">
         <v>0</v>
@@ -4792,32 +4985,32 @@
     </row>
     <row r="37" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E37" s="6">
         <v>17000</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G37" s="6">
         <v>34000</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="K37" s="6" t="b">
         <v>0</v>
@@ -4828,32 +5021,32 @@
     </row>
     <row r="38" spans="1:12" ht="91" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E38" s="6">
         <v>17000</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G38" s="6">
         <v>34000</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K38" s="6" t="b">
         <v>0</v>
@@ -4864,7 +5057,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
@@ -4881,13 +5074,13 @@
         <v>30000</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K39" s="6" t="b">
         <v>0</v>
@@ -4898,14 +5091,14 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E40" s="6">
         <v>20000</v>
@@ -4915,13 +5108,13 @@
         <v>30000</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I40" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="J40" s="13" t="s">
         <v>103</v>
-      </c>
-      <c r="J40" s="13" t="s">
-        <v>105</v>
       </c>
       <c r="K40" s="6" t="b">
         <v>0</v>
@@ -4932,7 +5125,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6" t="s">
@@ -4952,10 +5145,10 @@
         <v>14</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J41" s="14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K41" s="6" t="b">
         <v>0</v>
@@ -4966,14 +5159,14 @@
     </row>
     <row r="42" spans="1:12" ht="98.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E42" s="6">
         <v>24000</v>
@@ -4983,13 +5176,13 @@
         <v>36000</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J42" s="15" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="K42" s="6" t="b">
         <v>0</v>
@@ -5000,7 +5193,7 @@
     </row>
     <row r="43" spans="1:12" ht="95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6" t="s">
@@ -5017,13 +5210,13 @@
         <v>36000</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>110</v>
+        <v>351</v>
       </c>
       <c r="K43" s="6" t="b">
         <v>0</v>
@@ -5034,7 +5227,7 @@
     </row>
     <row r="44" spans="1:12" ht="158" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6" t="s">
@@ -5054,10 +5247,10 @@
         <v>14</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="K44" s="6" t="b">
         <v>0</v>
@@ -5068,32 +5261,32 @@
     </row>
     <row r="45" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E45" s="6">
         <v>10000</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G45" s="6">
         <v>19000</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K45" s="6" t="b">
         <v>0</v>
@@ -5104,14 +5297,14 @@
     </row>
     <row r="46" spans="1:12" ht="82" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E46" s="6">
         <v>13000</v>
@@ -5121,13 +5314,13 @@
         <v>20000</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K46" s="6" t="b">
         <v>0</v>
@@ -5138,7 +5331,7 @@
     </row>
     <row r="47" spans="1:12" ht="302.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6" t="s">
@@ -5158,10 +5351,10 @@
         <v>13</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K47" s="6" t="b">
         <v>0</v>
@@ -5172,14 +5365,14 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E48" s="6">
         <v>22000</v>
@@ -5189,13 +5382,13 @@
         <v>30000</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="K48" s="6" t="b">
         <v>0</v>
@@ -5206,7 +5399,7 @@
     </row>
     <row r="49" spans="1:12" ht="261.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6" t="s">
@@ -5226,10 +5419,10 @@
         <v>12</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="K49" s="6" t="b">
         <v>0</v>
@@ -5240,11 +5433,11 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
-        <v>63</v>
+        <v>353</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>11</v>
@@ -5260,10 +5453,10 @@
         <v>12</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="K50" s="6" t="b">
         <v>0</v>
@@ -5274,7 +5467,7 @@
     </row>
     <row r="51" spans="1:12" ht="406" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6" t="s">
@@ -5294,10 +5487,10 @@
         <v>12</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="K51" s="6" t="b">
         <v>0</v>
@@ -5308,7 +5501,7 @@
     </row>
     <row r="52" spans="1:12" ht="121.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="6" t="s">
@@ -5328,10 +5521,10 @@
         <v>14</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="J52" s="15" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="K52" s="6" t="b">
         <v>0</v>
@@ -5342,11 +5535,11 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>11</v>
@@ -5362,10 +5555,10 @@
         <v>14</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="K53" s="6" t="b">
         <v>0</v>
@@ -5376,11 +5569,11 @@
     </row>
     <row r="54" spans="1:12" ht="141.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>11</v>
@@ -5396,10 +5589,10 @@
         <v>14</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K54" s="6" t="b">
         <v>0</v>
@@ -5410,11 +5603,11 @@
     </row>
     <row r="55" spans="1:12" ht="276.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>11</v>
@@ -5430,10 +5623,10 @@
         <v>14</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K55" s="6" t="b">
         <v>0</v>
@@ -5444,11 +5637,11 @@
     </row>
     <row r="56" spans="1:12" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>11</v>
@@ -5461,13 +5654,13 @@
         <v>78000</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K56" s="6" t="b">
         <v>0</v>
@@ -5478,11 +5671,11 @@
     </row>
     <row r="57" spans="1:12" ht="377" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>11</v>
@@ -5491,7 +5684,7 @@
         <v>22000</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G57" s="6">
         <v>27000</v>
@@ -5500,10 +5693,10 @@
         <v>17</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="K57" s="6" t="b">
         <v>0</v>
@@ -5514,14 +5707,14 @@
     </row>
     <row r="58" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A58" s="16" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B58" s="16"/>
       <c r="C58" s="16" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E58" s="16">
         <v>17000</v>
@@ -5534,10 +5727,10 @@
         <v>14</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J58" s="18" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K58" s="19" t="b">
         <v>0</v>
@@ -5548,11 +5741,11 @@
     </row>
     <row r="59" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A59" s="16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B59" s="16"/>
       <c r="C59" s="16" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D59" s="16" t="s">
         <v>20</v>
@@ -5568,10 +5761,10 @@
         <v>14</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J59" s="18" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="K59" s="19" t="b">
         <v>0</v>
@@ -5582,11 +5775,11 @@
     </row>
     <row r="60" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A60" s="16" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B60" s="16"/>
       <c r="C60" s="16" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D60" s="16" t="s">
         <v>20</v>
@@ -5602,10 +5795,10 @@
         <v>14</v>
       </c>
       <c r="I60" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="J60" s="18" t="s">
         <v>178</v>
-      </c>
-      <c r="J60" s="18" t="s">
-        <v>181</v>
       </c>
       <c r="K60" s="19" t="b">
         <v>0</v>
@@ -5616,11 +5809,11 @@
     </row>
     <row r="61" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A61" s="16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B61" s="16"/>
       <c r="C61" s="16" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D61" s="16" t="s">
         <v>20</v>
@@ -5636,10 +5829,10 @@
         <v>14</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J61" s="18" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="K61" s="19" t="b">
         <v>0</v>
@@ -5650,11 +5843,11 @@
     </row>
     <row r="62" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A62" s="16" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B62" s="16"/>
       <c r="C62" s="16" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D62" s="16" t="s">
         <v>20</v>
@@ -5670,10 +5863,10 @@
         <v>14</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="J62" s="18" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K62" s="19" t="b">
         <v>0</v>
@@ -5684,11 +5877,11 @@
     </row>
     <row r="63" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A63" s="16" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B63" s="16"/>
       <c r="C63" s="16" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D63" s="16" t="s">
         <v>20</v>
@@ -5704,10 +5897,10 @@
         <v>14</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J63" s="18" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K63" s="19" t="b">
         <v>0</v>
@@ -5718,11 +5911,11 @@
     </row>
     <row r="64" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A64" s="16" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B64" s="16"/>
       <c r="C64" s="16" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D64" s="16" t="s">
         <v>20</v>
@@ -5738,10 +5931,10 @@
         <v>14</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J64" s="18" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K64" s="19" t="b">
         <v>0</v>
@@ -5752,11 +5945,11 @@
     </row>
     <row r="65" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A65" s="16" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B65" s="16"/>
       <c r="C65" s="16" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D65" s="16" t="s">
         <v>20</v>
@@ -5772,10 +5965,10 @@
         <v>14</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J65" s="18" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K65" s="19" t="b">
         <v>0</v>
@@ -5786,11 +5979,11 @@
     </row>
     <row r="66" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A66" s="16" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B66" s="16"/>
       <c r="C66" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D66" s="16" t="s">
         <v>20</v>
@@ -5806,10 +5999,10 @@
         <v>14</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J66" s="18" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="K66" s="19" t="b">
         <v>0</v>
@@ -5820,11 +6013,11 @@
     </row>
     <row r="67" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A67" s="16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B67" s="16"/>
       <c r="C67" s="16" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D67" s="16" t="s">
         <v>20</v>
@@ -5840,10 +6033,10 @@
         <v>14</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="J67" s="18" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="K67" s="19" t="b">
         <v>0</v>
@@ -5854,11 +6047,11 @@
     </row>
     <row r="68" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A68" s="16" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B68" s="16"/>
       <c r="C68" s="16" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D68" s="16" t="s">
         <v>20</v>
@@ -5874,10 +6067,10 @@
         <v>14</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J68" s="18" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="K68" s="19" t="b">
         <v>0</v>
@@ -5888,11 +6081,11 @@
     </row>
     <row r="69" spans="1:12" ht="406" x14ac:dyDescent="0.35">
       <c r="A69" s="16" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B69" s="16"/>
       <c r="C69" s="16" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D69" s="16" t="s">
         <v>20</v>
@@ -5908,10 +6101,10 @@
         <v>14</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J69" s="18" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K69" s="19" t="b">
         <v>0</v>
@@ -5922,11 +6115,11 @@
     </row>
     <row r="70" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A70" s="16" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B70" s="16"/>
       <c r="C70" s="16" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D70" s="16" t="s">
         <v>20</v>
@@ -5942,10 +6135,10 @@
         <v>14</v>
       </c>
       <c r="I70" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="J70" s="17" t="s">
         <v>210</v>
-      </c>
-      <c r="J70" s="17" t="s">
-        <v>213</v>
       </c>
       <c r="K70" s="19" t="b">
         <v>0</v>
@@ -5956,11 +6149,11 @@
     </row>
     <row r="71" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A71" s="16" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B71" s="16"/>
       <c r="C71" s="16" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D71" s="16" t="s">
         <v>20</v>
@@ -5976,10 +6169,10 @@
         <v>14</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J71" s="18" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="K71" s="19" t="b">
         <v>0</v>
@@ -5990,11 +6183,11 @@
     </row>
     <row r="72" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A72" s="16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B72" s="16"/>
       <c r="C72" s="16" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D72" s="16" t="s">
         <v>20</v>
@@ -6010,10 +6203,10 @@
         <v>14</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J72" s="18" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K72" s="19" t="b">
         <v>0</v>
@@ -6024,11 +6217,11 @@
     </row>
     <row r="73" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A73" s="16" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B73" s="16"/>
       <c r="C73" s="16" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D73" s="16" t="s">
         <v>20</v>
@@ -6044,10 +6237,10 @@
         <v>14</v>
       </c>
       <c r="I73" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="J73" s="18" t="s">
         <v>216</v>
-      </c>
-      <c r="J73" s="18" t="s">
-        <v>219</v>
       </c>
       <c r="K73" s="19" t="b">
         <v>0</v>
@@ -6058,13 +6251,13 @@
     </row>
     <row r="74" spans="1:12" ht="319" x14ac:dyDescent="0.35">
       <c r="A74" s="16" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D74" s="16" t="s">
         <v>11</v>
@@ -6077,13 +6270,13 @@
         <v>34000</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I74" s="16" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="J74" s="18" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="K74" s="19" t="b">
         <v>0</v>
@@ -6094,11 +6287,11 @@
     </row>
     <row r="75" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A75" s="16" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B75" s="16"/>
       <c r="C75" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D75" s="16" t="s">
         <v>20</v>
@@ -6114,10 +6307,10 @@
         <v>14</v>
       </c>
       <c r="I75" s="16" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J75" s="18" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K75" s="19" t="b">
         <v>0</v>
@@ -6128,11 +6321,11 @@
     </row>
     <row r="76" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A76" s="16" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B76" s="16"/>
       <c r="C76" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D76" s="16" t="s">
         <v>20</v>
@@ -6148,10 +6341,10 @@
         <v>14</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="K76" s="19" t="b">
         <v>0</v>
@@ -6162,11 +6355,11 @@
     </row>
     <row r="77" spans="1:12" ht="87" x14ac:dyDescent="0.35">
       <c r="A77" s="16" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B77" s="16"/>
       <c r="C77" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D77" s="16" t="s">
         <v>20</v>
@@ -6182,10 +6375,10 @@
         <v>14</v>
       </c>
       <c r="I77" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="J77" s="18" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="K77" s="19" t="b">
         <v>0</v>
@@ -6196,13 +6389,13 @@
     </row>
     <row r="78" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A78" s="16" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D78" s="16" t="s">
         <v>20</v>
@@ -6218,10 +6411,10 @@
         <v>14</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="J78" s="18" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="K78" s="19" t="b">
         <v>0</v>
@@ -6232,13 +6425,13 @@
     </row>
     <row r="79" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A79" s="16" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D79" s="16" t="s">
         <v>20</v>
@@ -6254,10 +6447,10 @@
         <v>14</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J79" s="18" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="K79" s="19" t="b">
         <v>0</v>
@@ -6268,11 +6461,11 @@
     </row>
     <row r="80" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A80" s="16" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B80" s="16"/>
       <c r="C80" s="16" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D80" s="16" t="s">
         <v>20</v>
@@ -6288,10 +6481,10 @@
         <v>14</v>
       </c>
       <c r="I80" s="16" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="K80" s="19" t="b">
         <v>0</v>
@@ -6302,11 +6495,11 @@
     </row>
     <row r="81" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A81" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B81" s="16"/>
       <c r="C81" s="16" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D81" s="16" t="s">
         <v>20</v>
@@ -6322,10 +6515,10 @@
         <v>14</v>
       </c>
       <c r="I81" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J81" s="17" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K81" s="19" t="b">
         <v>0</v>
@@ -6336,11 +6529,11 @@
     </row>
     <row r="82" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A82" s="16" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B82" s="16"/>
       <c r="C82" s="16" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D82" s="16" t="s">
         <v>20</v>
@@ -6356,10 +6549,10 @@
         <v>14</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="J82" s="18" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="K82" s="19" t="b">
         <v>0</v>
@@ -6370,11 +6563,11 @@
     </row>
     <row r="83" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A83" s="16" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B83" s="16"/>
       <c r="C83" s="16" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D83" s="16" t="s">
         <v>20</v>
@@ -6390,10 +6583,10 @@
         <v>14</v>
       </c>
       <c r="I83" s="17" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="J83" s="21" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="K83" s="19" t="b">
         <v>0</v>
@@ -6404,11 +6597,11 @@
     </row>
     <row r="84" spans="1:12" ht="261" x14ac:dyDescent="0.35">
       <c r="A84" s="16" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B84" s="16"/>
       <c r="C84" s="16" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D84" s="16" t="s">
         <v>20</v>
@@ -6424,10 +6617,10 @@
         <v>14</v>
       </c>
       <c r="I84" s="16" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="J84" s="21" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="K84" s="19" t="b">
         <v>0</v>
@@ -6438,11 +6631,11 @@
     </row>
     <row r="85" spans="1:12" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A85" s="16" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B85" s="16"/>
       <c r="C85" s="16" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D85" s="16" t="s">
         <v>20</v>
@@ -6451,7 +6644,7 @@
         <v>25000</v>
       </c>
       <c r="F85" s="17" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G85" s="16">
         <v>36000</v>
@@ -6460,10 +6653,10 @@
         <v>13</v>
       </c>
       <c r="I85" s="16" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="J85" s="21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="K85" s="19" t="b">
         <v>0</v>
@@ -6474,11 +6667,11 @@
     </row>
     <row r="86" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A86" s="16" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B86" s="16"/>
       <c r="C86" s="16" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D86" s="16" t="s">
         <v>20</v>
@@ -6494,10 +6687,10 @@
         <v>14</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="J86" s="21" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="K86" s="19" t="b">
         <v>0</v>
@@ -6508,11 +6701,11 @@
     </row>
     <row r="87" spans="1:12" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
-        <v>267</v>
+        <v>354</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>11</v>
@@ -6528,10 +6721,10 @@
         <v>12</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K87" s="6" t="b">
         <v>0</v>
@@ -6542,7 +6735,7 @@
     </row>
     <row r="88" spans="1:12" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A88" s="6" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6" t="s">
@@ -6559,13 +6752,13 @@
         <v>27000</v>
       </c>
       <c r="H88" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="I88" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="J88" s="22" t="s">
         <v>269</v>
-      </c>
-      <c r="I88" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="J88" s="22" t="s">
-        <v>273</v>
       </c>
       <c r="K88" s="6" t="b">
         <v>0</v>
@@ -6576,7 +6769,7 @@
     </row>
     <row r="89" spans="1:12" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A89" s="6" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6" t="s">
@@ -6596,10 +6789,10 @@
         <v>14</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="J89" s="22" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="K89" s="6" t="b">
         <v>0</v>
@@ -6610,11 +6803,11 @@
     </row>
     <row r="90" spans="1:12" ht="319" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>11</v>
@@ -6630,10 +6823,10 @@
         <v>12</v>
       </c>
       <c r="I90" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J90" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="K90" s="6" t="b">
         <v>0</v>
@@ -6644,11 +6837,11 @@
     </row>
     <row r="91" spans="1:12" ht="319" x14ac:dyDescent="0.35">
       <c r="A91" s="23" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B91" s="23"/>
       <c r="C91" s="23" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D91" s="23" t="s">
         <v>11</v>
@@ -6661,13 +6854,13 @@
         <v>45000</v>
       </c>
       <c r="H91" s="23" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="J91" s="22" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="K91" s="6" t="b">
         <v>0</v>
@@ -6678,7 +6871,7 @@
     </row>
     <row r="92" spans="1:12" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A92" s="23" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B92" s="23"/>
       <c r="C92" s="23" t="s">
@@ -6698,10 +6891,10 @@
         <v>14</v>
       </c>
       <c r="I92" s="24" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="J92" s="22" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="K92" s="6" t="b">
         <v>0</v>
@@ -6712,11 +6905,11 @@
     </row>
     <row r="93" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A93" s="23" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B93" s="23"/>
       <c r="C93" s="23" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D93" s="23" t="s">
         <v>20</v>
@@ -6732,10 +6925,10 @@
         <v>14</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="J93" s="11" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="K93" s="6" t="b">
         <v>0</v>
@@ -6746,11 +6939,11 @@
     </row>
     <row r="94" spans="1:12" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A94" s="25" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B94" s="25"/>
       <c r="C94" s="25" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D94" s="25" t="s">
         <v>20</v>
@@ -6766,10 +6959,10 @@
         <v>14</v>
       </c>
       <c r="I94" s="25" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="J94" s="26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="K94" s="25" t="b">
         <v>0</v>
@@ -6780,11 +6973,11 @@
     </row>
     <row r="95" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A95" s="25" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B95" s="25"/>
       <c r="C95" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D95" s="25" t="s">
         <v>20</v>
@@ -6797,13 +6990,13 @@
         <v>15000</v>
       </c>
       <c r="H95" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I95" s="26" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="J95" s="27" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="K95" s="25" t="b">
         <v>0</v>
@@ -6814,11 +7007,11 @@
     </row>
     <row r="96" spans="1:12" ht="261" x14ac:dyDescent="0.35">
       <c r="A96" s="25" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B96" s="25"/>
       <c r="C96" s="25" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D96" s="25" t="s">
         <v>20</v>
@@ -6834,10 +7027,10 @@
         <v>14</v>
       </c>
       <c r="I96" s="25" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J96" s="27" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="K96" s="25" t="b">
         <v>0</v>
@@ -6848,11 +7041,11 @@
     </row>
     <row r="97" spans="1:12" ht="174" x14ac:dyDescent="0.35">
       <c r="A97" s="25" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B97" s="25"/>
       <c r="C97" s="25" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D97" s="25" t="s">
         <v>20</v>
@@ -6868,10 +7061,10 @@
         <v>14</v>
       </c>
       <c r="I97" s="25" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="J97" s="26" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="K97" s="25" t="b">
         <v>0</v>
@@ -6882,11 +7075,11 @@
     </row>
     <row r="98" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A98" s="25" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B98" s="25"/>
       <c r="C98" s="25" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D98" s="25" t="s">
         <v>20</v>
@@ -6902,10 +7095,10 @@
         <v>14</v>
       </c>
       <c r="I98" s="26" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J98" s="26" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="K98" s="25" t="b">
         <v>0</v>
@@ -6916,11 +7109,11 @@
     </row>
     <row r="99" spans="1:12" ht="319" x14ac:dyDescent="0.35">
       <c r="A99" s="25" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B99" s="25"/>
       <c r="C99" s="25" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D99" s="25" t="s">
         <v>20</v>
@@ -6936,10 +7129,10 @@
         <v>14</v>
       </c>
       <c r="I99" s="26" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="J99" s="26" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="K99" s="25" t="b">
         <v>0</v>
@@ -6950,11 +7143,11 @@
     </row>
     <row r="100" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A100" s="25" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B100" s="25"/>
       <c r="C100" s="25" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D100" s="25" t="s">
         <v>20</v>
@@ -6970,10 +7163,10 @@
         <v>14</v>
       </c>
       <c r="I100" s="26" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="J100" s="26" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="K100" s="25" t="b">
         <v>0</v>
@@ -6984,11 +7177,11 @@
     </row>
     <row r="101" spans="1:12" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A101" s="28" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B101" s="28"/>
       <c r="C101" s="28" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D101" s="28" t="s">
         <v>20</v>
@@ -7004,10 +7197,10 @@
         <v>14</v>
       </c>
       <c r="I101" s="29" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="J101" s="29" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="K101" s="28" t="b">
         <v>0</v>
@@ -7018,11 +7211,11 @@
     </row>
     <row r="102" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A102" s="25" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B102" s="25"/>
       <c r="C102" s="25" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D102" s="25" t="s">
         <v>20</v>
@@ -7038,10 +7231,10 @@
         <v>14</v>
       </c>
       <c r="I102" s="26" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="J102" s="26" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="K102" s="25" t="b">
         <v>0</v>
@@ -7052,11 +7245,11 @@
     </row>
     <row r="103" spans="1:12" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A103" s="28" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B103" s="28"/>
       <c r="C103" s="28" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D103" s="28" t="s">
         <v>11</v>
@@ -7072,10 +7265,10 @@
         <v>14</v>
       </c>
       <c r="I103" s="28" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="J103" s="29" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="K103" s="28" t="b">
         <v>0</v>
@@ -7086,11 +7279,11 @@
     </row>
     <row r="104" spans="1:12" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A104" s="28" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B104" s="28"/>
       <c r="C104" s="28" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D104" s="28" t="s">
         <v>11</v>
@@ -7106,10 +7299,10 @@
         <v>14</v>
       </c>
       <c r="I104" s="29" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J104" s="29" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="K104" s="28" t="b">
         <v>0</v>
@@ -7120,11 +7313,11 @@
     </row>
     <row r="105" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A105" s="25" t="s">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="B105" s="25"/>
       <c r="C105" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D105" s="25" t="s">
         <v>20</v>
@@ -7140,10 +7333,10 @@
         <v>14</v>
       </c>
       <c r="I105" s="26" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J105" s="26" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="K105" s="25" t="b">
         <v>0</v>
@@ -7154,11 +7347,11 @@
     </row>
     <row r="106" spans="1:12" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A106" s="25" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B106" s="25"/>
       <c r="C106" s="25" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D106" s="25" t="s">
         <v>20</v>
@@ -7174,10 +7367,10 @@
         <v>14</v>
       </c>
       <c r="I106" s="25" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J106" s="26" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="K106" s="25" t="b">
         <v>0</v>
@@ -7188,11 +7381,11 @@
     </row>
     <row r="107" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A107" s="28" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B107" s="28"/>
       <c r="C107" s="28" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D107" s="28" t="s">
         <v>11</v>
@@ -7208,10 +7401,10 @@
         <v>14</v>
       </c>
       <c r="I107" s="29" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J107" s="29" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="K107" s="28" t="b">
         <v>0</v>
@@ -7222,11 +7415,11 @@
     </row>
     <row r="108" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A108" s="28" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B108" s="28"/>
       <c r="C108" s="28" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D108" s="28" t="s">
         <v>11</v>
@@ -7242,10 +7435,10 @@
         <v>14</v>
       </c>
       <c r="I108" s="28" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="J108" s="29" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="K108" s="28" t="b">
         <v>0</v>
@@ -7256,11 +7449,11 @@
     </row>
     <row r="109" spans="1:12" ht="333.5" x14ac:dyDescent="0.35">
       <c r="A109" s="28" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B109" s="28"/>
       <c r="C109" s="28" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D109" s="28" t="s">
         <v>11</v>
@@ -7276,10 +7469,10 @@
         <v>14</v>
       </c>
       <c r="I109" s="29" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="J109" s="29" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="K109" s="28" t="b">
         <v>0</v>
@@ -7290,14 +7483,14 @@
     </row>
     <row r="110" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A110" s="25" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B110" s="25"/>
       <c r="C110" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D110" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E110" s="25">
         <v>27000</v>
@@ -7310,10 +7503,10 @@
         <v>14</v>
       </c>
       <c r="I110" s="26" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J110" s="26" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="K110" s="25" t="b">
         <v>0</v>
@@ -7324,14 +7517,14 @@
     </row>
     <row r="111" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A111" s="25" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B111" s="25"/>
       <c r="C111" s="25" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D111" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E111" s="25">
         <v>15000</v>
@@ -7344,10 +7537,10 @@
         <v>14</v>
       </c>
       <c r="I111" s="26" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J111" s="26" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="K111" s="25" t="b">
         <v>0</v>
@@ -7358,11 +7551,11 @@
     </row>
     <row r="112" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A112" s="25" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B112" s="25"/>
       <c r="C112" s="25" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D112" s="25" t="s">
         <v>20</v>
@@ -7378,15 +7571,151 @@
         <v>14</v>
       </c>
       <c r="I112" s="26" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J112" s="26" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="K112" s="25" t="b">
         <v>0</v>
       </c>
       <c r="L112" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A113" s="25" t="s">
+        <v>356</v>
+      </c>
+      <c r="B113" s="25"/>
+      <c r="C113" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="D113" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" s="25">
+        <v>14000</v>
+      </c>
+      <c r="F113" s="25"/>
+      <c r="G113" s="25">
+        <v>17000</v>
+      </c>
+      <c r="H113" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I113" s="26" t="s">
+        <v>358</v>
+      </c>
+      <c r="J113" s="26" t="s">
+        <v>357</v>
+      </c>
+      <c r="K113" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L113" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A114" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="B114" s="25"/>
+      <c r="C114" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="D114" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E114" s="25">
+        <v>11000</v>
+      </c>
+      <c r="F114" s="25"/>
+      <c r="G114" s="25">
+        <v>16500</v>
+      </c>
+      <c r="H114" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I114" s="26" t="s">
+        <v>361</v>
+      </c>
+      <c r="J114" s="26" t="s">
+        <v>360</v>
+      </c>
+      <c r="K114" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L114" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A115" s="25" t="s">
+        <v>362</v>
+      </c>
+      <c r="B115" s="25"/>
+      <c r="C115" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="D115" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E115" s="25">
+        <v>13000</v>
+      </c>
+      <c r="F115" s="25"/>
+      <c r="G115" s="25">
+        <v>17000</v>
+      </c>
+      <c r="H115" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I115" s="26" t="s">
+        <v>363</v>
+      </c>
+      <c r="J115" s="26" t="s">
+        <v>368</v>
+      </c>
+      <c r="K115" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L115" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A116" s="25" t="s">
+        <v>364</v>
+      </c>
+      <c r="B116" s="25"/>
+      <c r="C116" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="D116" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E116" s="25">
+        <v>26000</v>
+      </c>
+      <c r="F116" s="25"/>
+      <c r="G116" s="25">
+        <v>34000</v>
+      </c>
+      <c r="H116" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="I116" s="26" t="s">
+        <v>366</v>
+      </c>
+      <c r="J116" s="26" t="s">
+        <v>367</v>
+      </c>
+      <c r="K116" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L116" s="25" t="b">
         <v>0</v>
       </c>
     </row>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0526577688ca4eec/Escritorio/Proyectos developer/Diseños_Gasper/Back-end/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1276" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3F27347-06D3-45D9-A37E-364C6C39D771}"/>
+  <xr:revisionPtr revIDLastSave="1301" documentId="8_{ADBBDD1F-37F2-455A-919D-03174E12E1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4505801C-7DFA-48C9-9E4A-9720EA84FEE9}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="productos" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="371">
   <si>
     <t>name</t>
   </si>
@@ -179,9 +179,6 @@
   </si>
   <si>
     <t>S,M,L</t>
-  </si>
-  <si>
-    <t>Rompevientos Maya Interna</t>
   </si>
   <si>
     <t>Chaqueta Selección Colombia</t>
@@ -1167,28 +1164,6 @@
     <t>Conjunto Deportivo Buso y Leggins</t>
   </si>
   <si>
-    <t>{
-  "pink": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420046/o4phycvt82wjz8kplszr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420265/twvchekif2zodyxanc1i.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420049/db3k6djx5iehvdk5tzsb.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420266/s8wejcy8ethxjhvwfim1.png"
-  ],
-  "blue": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420039/zy4nsioggmxibakgkmnq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420258/befqhobvwpandubpdwnx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420208/nsi9nfrc9iwjh549x27f.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420041/oscbxkl0amqrovmxdl96.png"
-    ],
-  "gray": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420271/emoayd31qpmmzq1e3cow.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420209/grarwuvkojfsxp3zkkea.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420219/iej9eryy6zmsqpxbtren.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420269/ssqsptxxtzk5242meapv.png"
-   ],
-  "green": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420212/dwppw1yttgi1glfoirjp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420261/tsukkdewe1ssc9fx1xyf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420213/nslqbwrpsalmznectkju.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420205/tjubdm4z489rrllcpjae.png"
-    ],
-  "darkblue": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420050/a3sah9k0vso0yczkejjp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420217/qqxejrn7vafzp7mxinpd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420203/tjmfayvfgtfwvotp3w7b.png" ],
-  "hotpink": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420202/mllthenng41x09edlbhz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420045/a2ajlcckgz0jrgzkc5ym.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420259/rpf0na4o552r5leox8lp.png"  ],
-  "steelblue": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420215/ctwopprmeqldjrqo7ore.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420277/vme2qfi6m8fkbpuuwwmw.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420273/eigh1jdqa5mypkwg9lf9.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420043/hgp1p2lxyof2jxtglg7u.png"
-  ]}</t>
-  </si>
-  <si>
     <t>Conjunto Bicicletero y Top Combinado</t>
   </si>
   <si>
@@ -1207,174 +1182,6 @@
     ],
   "darkblue": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421319/d9qqgtc0yluoaqb2nhss.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773421294/hniugnmmmcgs8gfc3kyq.png"]}</t>
-  </si>
-  <si>
-    <t>{
-  "pink": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072753/dsppjvpwowbghyyabeog.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072754/iufnbxgh8v2t6nun4m8f.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072791/lycg5baqgojxovlk3klq.png"
-  ],
-  "blue": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072764/q9ui9mat04sqcn7jpqb8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072753/vaefzvoqosvza2tjc04h.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072751/tktrkjoftskg81kjytab.png"
-    ],
-  "gray": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072762/oxepi3ridavl6iaquioe.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072768/jibcdv8zdbbnl2shknx5.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415974/zlvlfegmwgwtj3uegmf6.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072784/lkxruusxffwbja8pvoem.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072794/htikpbl3pq2mpqp2ps8r.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072753/egdi0tylliek1qyjso6x.png"
-   ],
-  "green": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072758/tfir7j2qcftiffz8aca6.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072757/schvcegqk9teituzut2v.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072772/fuhllgv2gcygjv5uvhqx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072786/iulimynpkmgyp1lrfyca.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072787/fhvdbb22uf43y6a8y3pz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072763/xjzgglbt4ryzsr1dvjul.png"
-    ],
-  "darkblue": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072771/ocuhg6y7bx3q4k6qswwm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072761/to6r3iw5czbnugwicbyo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072755/njj3ykdg4wphlwueohpp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072772/smojgyyxywm1ppopmhac.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072766/ehfpqr0onlnnfcmxkw6g.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072765/aijvgan44bsdlarde9hu.png"],
-  "hotpink": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072776/xy0oq8u2z354b9irwdi0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072760/f7qv7ihynasmahakerzr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072759/khvijabocbvnua4rq4vt.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072778/mey8d1cqjigzohe2kfsh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072791/pglujdgbvmqn12el2igs.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072752/lud7tphmwdzz98gq2bkm.png"  ],
-  "steelblue": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072778/rt8jsbd8g77dtmflde6n.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072783/qzzslyqihjzfteprnqu3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072756/nrlasih250wtk3djzpne.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072781/ecdvpj1gcs5bf219hskg.png"
-  ]}</t>
-  </si>
-  <si>
-    <t>{
-  "pink": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416290/qrlowbtwfkpfypavclt5.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416053/k746fugxvqwjknpiychz.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416262/wqdfvzcho2lfxta4gzgz.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416311/ooa4txwpixsa1zktiz0o.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416190/nf2325leitsuv0tua7lf.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416250/ets5y8x1rkziuisz27vd.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416286/bn9euxkqhrbqlmvuhxiz.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416207/bmecxkohc2lcciefvprm.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416302/fc0pvuenvqudhe0ry818.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416195/kqzwt4sp5q0ge1hh8dwq.png"
-  ],
-  "blue": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416294/pmshoq3tjgafq6gpcbt9.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416273/uogfsfsucmmsnyepdtbb.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416220/jdzz1cc3iaizq4j4dz6e.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416183/filmlgbtdgt2pd2pjeuo.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416323/qmthfapue8mwtsxurtfz.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416244/vxyttjxduexjvje1lvm6.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416215/snrk8fldawf0oirrvquv.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416178/pr4qhmhhxtvt0d5apipa.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415980/gzezgzr4ue2yp3mu5rzo.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416196/f9jdzglnonjv9mrqmrea.png"
-  ],
-  "gray": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415970/j0emdwlkpwvkwyofrxkv.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416208/jksbv56emig4qz94gmu9.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415974/zlvlfegmwgwtj3uegmf6.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416294/gom3hdiys0lpegiucrfa.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416262/hqptcmqk7le05zjivb2k.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416312/tbaamx57e76vf6gpb7wz.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416316/yvchju9wkaf9elfxm2w6.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416263/xdmzoozc7dhxq6cuze6i.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416320/iq8yndysogkwqyeie3t1.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415991/t796xjnfo98lb7bhmvsq.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416310/ohb69dmxvobxucufp8fz.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416289/hycllrw7ygufhch0nysq.png"
-  ],
-  "green": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416166/qrqgdfj7kqlb9zfng6og.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415990/j3al7u3gj7mkaku0qoby.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415980/cnnqftkwrshlexyjlapl.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415959/kjxny6jnzipqvk91ok2x.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415995/na8186pgdaqwniyxhose.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416176/s1w9mmdlhvuqb2avrrad.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415984/dpccybijitpf8ji3iteu.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416285/ybuu7gx8wzf3jejflzts.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416187/vioijghseh9sdqf2nkal.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416300/divgdwrvstqluscll2lf.png"
-  ],
-  "darkblue": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416299/fpqonbmnz6qfdppdzmsl.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416295/cwxjgbndrpebrw4dya7c.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416272/yutx8qm1vkjeggh99ew7.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416177/gsen39sqfogt42jmlpez.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415973/voeon9pukrdqtvq128kv.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416211/ubqgbda3rjout3urkw09.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416168/se1krtmrlk6epe6mmqzz.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416242/wtlrtruu93kuzt61p55z.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416243/fcuvs7v55a66f46l0jed.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416310/bjypkov8tqc4gvms7tod.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415965/cvx3oyygwzfxfgj3mgof.png"
-  ],
-  "hotpink": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415987/iuyjozzwro18snorgkaz.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416003/vou1uotpawlgvdow6blj.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416228/grpnayzcsu7pwysdpm9l.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416336/so117psdpsxbfxn86aa4.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416212/clo6omrpdsqacmfbyx2e.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416003/nal0y1aousnydel9c9bh.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416167/wh3yinojxhalhz4qe3rg.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416180/yariiiyggalcawpthysm.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416317/eonvxsrpzrhn2vlcjatj.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416203/lv6d9y5cicybrhhqsa95.png"
-  ],
-  "steelblue": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416197/amqyro3gix08x6shrfse.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416249/zunvoy8vibbzqefqfkg0.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416255/whzbzzogzo5d9u1s3oym.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416307/sxqy71iwrzngraaqy41z.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416257/zx2rocsa6yo0hlfr6g3f.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416172/ufxqq1uylrgqzklew8dx.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416227/sstrutfjlgnriihaeiqr.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416304/saebaj98hfibjsrxh6pe.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416282/n7j0vwkpwaw9gdh5yqh6.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416270/cujzcybg3letrklfedyq.png"
-  ],
-  "purple": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415976/c49c6b4ghcascmn4xfsm.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416276/zar1mfht0oqihxq7ciek.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416204/qknnwtey3qjb5madflre.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416330/khsiuv0wjbulqncixkxh.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416326/lvofqnvvvshtuacbat9c.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416217/bdwtuvpgbhbx7gjwlteb.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416280/t9udoglicwhgict1zcxf.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416218/kstch50r1aejy5lnqm8p.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416281/z2abttmsbynsnumwlqg3.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416257/nilon24mjwuwkewq0gae.png"
-  ],
-  "skyblue": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416235/kpslv6ns5dpnneniazhg.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416170/sfzqob28zvb9uw2sftum.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415967/cr1iwmrjopvh4oiz6tdg.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416202/r5vobz5we7aegrustg9y.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415983/fpryq4gkkdmkuoldsy7p.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415979/y9pwxvqyhqqiupsxoo78.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415960/i5ifavyrvgy1ay4u1isg.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416230/uydhjaphwoaowfm0sxzu.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416331/dqozvw2bjohcfo3zrwko.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416249/chdorgyrnfbpq49xgxew.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415998/i4wzvtqzfymknwyfuyc6.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416182/ztobiv6hgdafne2jw3s7.png"
-  ],
-  "aqua": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416340/h1kuqgcqpjzwu0ljgjzl.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416321/dzi2zp9sztzqtw9uee7r.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416174/ud2uehcqq1qyghq0utcp.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415964/ksisxgqdtz2vjyxxf0h5.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415963/op7g9sppryp1h2szkawc.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416330/odo3lr9n9qslrpelpf17.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416341/qq7aqw8a1tbjnzua5ofy.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416237/rlj8h5vqatrvid2htupx.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415962/lc02levu16k5xkcsdkqw.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416239/gnttl90pitpt5isdqvxb.png"
-  ],
-  "darkgreen": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416264/hgfibbhawru3agvmqhmp.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416251/neqrvs4qgeumrv4vfmwp.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416234/dgzqkw1d2n6ndcit4wnb.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416188/ug26ujte97hoqtgj8gxt.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416232/woljjv2lj53ioyvydv6b.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415972/apqgw44r8kjxf6wpevyl.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415968/mzxgjg1w67lfns5fcbsq.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416222/yoloxsbdp4fsergeernp.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416268/cjwpdaow3vxkyxv3n5pn.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415996/yczrjb9sqy1e1nhwcmq1.png"
-  ],
-  "violet": [
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416223/umysgecl2lxao9ujbupq.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416187/gn4k5mcwnhft4suls5r8.png",
-    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416275/aj6ismbfekdqh41mffaa.png"
-  ]
-}</t>
   </si>
   <si>
     <t>Chaqueta Yoga en licra</t>
@@ -2025,9 +1832,6 @@
   </si>
   <si>
     <t>Chaqueta en Algodón Perchado</t>
-  </si>
-  <si>
-    <t>L.XL</t>
   </si>
   <si>
     <t>{
@@ -2371,9 +2175,6 @@
 }</t>
   </si>
   <si>
-    <t>Enterizo 3 huecos</t>
-  </si>
-  <si>
     <t>blue,white,black</t>
   </si>
   <si>
@@ -2655,9 +2456,6 @@
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058817/xnmxv2e9memmagybowsd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058816/s6zbit7x8tejpcfnv3s0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058817/wqonc9kcviofhs7qiatn.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775058818/ht4eo6wpkw58c3zsjttb.png" ]}</t>
   </si>
   <si>
-    <t>{ "blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253382/k5shc79l7qjtrz6ci2u8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662299/g4llyutemrjvlpsyhbjl.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662300/qtwerqw10yv6wxqpb1cl.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775267794/oq0hzp8xiepkigd8hytz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662302/wghzvjuaajuwpbfddzvk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253384/fa3gtcxcbbujpmz1q32y.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662299/ys0v7pwpkcommwyjadtf.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662310/tbrnns244roeseqtkxrr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/dxofsgljvhppxhvxcf9q.png"],"darkred":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/uqqd6kygifncoygwvzfk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253382/kiy5vdzzlhglrhntyfpf.png"], "royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662300/t7f9xsg5ij4gmjrmoyso.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662304/k5128obkwuopjaualtol.png"]}</t>
-  </si>
-  <si>
     <t>{
   "black": [
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774715391/agiednmodeb5yfpahlp1.png",
@@ -3210,6 +3008,226 @@
     "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775651819/wd6hvrxu5emoawuzy27y.png"
   ]
 }</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420046/o4phycvt82wjz8kplszr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420265/twvchekif2zodyxanc1i.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775713801/p2wxvvbmc7ugko9h06yo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775713802/umoe5klkejubiyq5x6qm.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420039/zy4nsioggmxibakgkmnq.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420258/befqhobvwpandubpdwnx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420208/nsi9nfrc9iwjh549x27f.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420041/oscbxkl0amqrovmxdl96.png"
+    ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420271/emoayd31qpmmzq1e3cow.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420209/grarwuvkojfsxp3zkkea.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420219/iej9eryy6zmsqpxbtren.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420269/ssqsptxxtzk5242meapv.png"
+   ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420212/dwppw1yttgi1glfoirjp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420261/tsukkdewe1ssc9fx1xyf.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420213/nslqbwrpsalmznectkju.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420205/tjubdm4z489rrllcpjae.png"
+    ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420050/a3sah9k0vso0yczkejjp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420217/qqxejrn7vafzp7mxinpd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420203/tjmfayvfgtfwvotp3w7b.png" ],
+  "hotpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420202/mllthenng41x09edlbhz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420045/a2ajlcckgz0jrgzkc5ym.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420259/rpf0na4o552r5leox8lp.png"  ],
+  "steelblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420215/ctwopprmeqldjrqo7ore.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773420277/vme2qfi6m8fkbpuuwwmw.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775713803/wwstemtvnkfhxfdsqyja.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775713802/lnhhqbsbq7hh058lp3s7.png"
+  ]}</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072753/dsppjvpwowbghyyabeog.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072754/iufnbxgh8v2t6nun4m8f.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072791/lycg5baqgojxovlk3klq.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072764/q9ui9mat04sqcn7jpqb8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072753/vaefzvoqosvza2tjc04h.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072751/tktrkjoftskg81kjytab.png"
+    ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072762/oxepi3ridavl6iaquioe.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072768/jibcdv8zdbbnl2shknx5.png",  "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072784/lkxruusxffwbja8pvoem.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072794/htikpbl3pq2mpqp2ps8r.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072753/egdi0tylliek1qyjso6x.png"
+   ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072758/tfir7j2qcftiffz8aca6.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072757/schvcegqk9teituzut2v.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072772/fuhllgv2gcygjv5uvhqx.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072786/iulimynpkmgyp1lrfyca.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072787/fhvdbb22uf43y6a8y3pz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072763/xjzgglbt4ryzsr1dvjul.png"
+    ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072771/ocuhg6y7bx3q4k6qswwm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072761/to6r3iw5czbnugwicbyo.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072755/njj3ykdg4wphlwueohpp.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072772/smojgyyxywm1ppopmhac.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072766/ehfpqr0onlnnfcmxkw6g.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072765/aijvgan44bsdlarde9hu.png"],
+  "hotpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072776/xy0oq8u2z354b9irwdi0.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072760/f7qv7ihynasmahakerzr.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072759/khvijabocbvnua4rq4vt.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072778/mey8d1cqjigzohe2kfsh.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072791/pglujdgbvmqn12el2igs.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072752/lud7tphmwdzz98gq2bkm.png"  ],
+  "steelblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072778/rt8jsbd8g77dtmflde6n.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072783/qzzslyqihjzfteprnqu3.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072756/nrlasih250wtk3djzpne.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1772072781/ecdvpj1gcs5bf219hskg.png"
+  ]}</t>
+  </si>
+  <si>
+    <t>{
+  "pink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416290/qrlowbtwfkpfypavclt5.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416053/k746fugxvqwjknpiychz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416262/wqdfvzcho2lfxta4gzgz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416311/ooa4txwpixsa1zktiz0o.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416250/ets5y8x1rkziuisz27vd.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416286/bn9euxkqhrbqlmvuhxiz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416207/bmecxkohc2lcciefvprm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416302/fc0pvuenvqudhe0ry818.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416195/kqzwt4sp5q0ge1hh8dwq.png"
+  ],
+  "blue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416294/pmshoq3tjgafq6gpcbt9.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416273/uogfsfsucmmsnyepdtbb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416220/jdzz1cc3iaizq4j4dz6e.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416183/filmlgbtdgt2pd2pjeuo.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416323/qmthfapue8mwtsxurtfz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416244/vxyttjxduexjvje1lvm6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416215/snrk8fldawf0oirrvquv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416178/pr4qhmhhxtvt0d5apipa.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415980/gzezgzr4ue2yp3mu5rzo.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416196/f9jdzglnonjv9mrqmrea.png"
+  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415970/j0emdwlkpwvkwyofrxkv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416208/jksbv56emig4qz94gmu9.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415974/zlvlfegmwgwtj3uegmf6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416294/gom3hdiys0lpegiucrfa.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416262/hqptcmqk7le05zjivb2k.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416312/tbaamx57e76vf6gpb7wz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416316/yvchju9wkaf9elfxm2w6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416263/xdmzoozc7dhxq6cuze6i.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416320/iq8yndysogkwqyeie3t1.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415991/t796xjnfo98lb7bhmvsq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416310/ohb69dmxvobxucufp8fz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416289/hycllrw7ygufhch0nysq.png"
+  ],
+  "green": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416166/qrqgdfj7kqlb9zfng6og.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415990/j3al7u3gj7mkaku0qoby.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415980/cnnqftkwrshlexyjlapl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415959/kjxny6jnzipqvk91ok2x.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415995/na8186pgdaqwniyxhose.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416176/s1w9mmdlhvuqb2avrrad.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415984/dpccybijitpf8ji3iteu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416285/ybuu7gx8wzf3jejflzts.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416187/vioijghseh9sdqf2nkal.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416300/divgdwrvstqluscll2lf.png"
+  ],
+  "darkblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416299/fpqonbmnz6qfdppdzmsl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416295/cwxjgbndrpebrw4dya7c.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416272/yutx8qm1vkjeggh99ew7.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416177/gsen39sqfogt42jmlpez.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415973/voeon9pukrdqtvq128kv.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416211/ubqgbda3rjout3urkw09.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416168/se1krtmrlk6epe6mmqzz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416242/wtlrtruu93kuzt61p55z.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416243/fcuvs7v55a66f46l0jed.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416310/bjypkov8tqc4gvms7tod.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415965/cvx3oyygwzfxfgj3mgof.png"
+  ],
+  "hotpink": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415987/iuyjozzwro18snorgkaz.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416003/vou1uotpawlgvdow6blj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416228/grpnayzcsu7pwysdpm9l.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416336/so117psdpsxbfxn86aa4.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416212/clo6omrpdsqacmfbyx2e.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416003/nal0y1aousnydel9c9bh.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416167/wh3yinojxhalhz4qe3rg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416180/yariiiyggalcawpthysm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416317/eonvxsrpzrhn2vlcjatj.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416203/lv6d9y5cicybrhhqsa95.png"
+  ],
+  "steelblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416197/amqyro3gix08x6shrfse.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416249/zunvoy8vibbzqefqfkg0.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416255/whzbzzogzo5d9u1s3oym.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416307/sxqy71iwrzngraaqy41z.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416257/zx2rocsa6yo0hlfr6g3f.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416172/ufxqq1uylrgqzklew8dx.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416227/sstrutfjlgnriihaeiqr.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416304/saebaj98hfibjsrxh6pe.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416282/n7j0vwkpwaw9gdh5yqh6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416270/cujzcybg3letrklfedyq.png"
+  ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415976/c49c6b4ghcascmn4xfsm.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416276/zar1mfht0oqihxq7ciek.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416204/qknnwtey3qjb5madflre.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416330/khsiuv0wjbulqncixkxh.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416326/lvofqnvvvshtuacbat9c.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416217/bdwtuvpgbhbx7gjwlteb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416280/t9udoglicwhgict1zcxf.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416218/kstch50r1aejy5lnqm8p.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416281/z2abttmsbynsnumwlqg3.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416257/nilon24mjwuwkewq0gae.png"
+  ],
+  "skyblue": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416235/kpslv6ns5dpnneniazhg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416170/sfzqob28zvb9uw2sftum.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415967/cr1iwmrjopvh4oiz6tdg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416202/r5vobz5we7aegrustg9y.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415983/fpryq4gkkdmkuoldsy7p.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415979/y9pwxvqyhqqiupsxoo78.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415960/i5ifavyrvgy1ay4u1isg.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416230/uydhjaphwoaowfm0sxzu.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416331/dqozvw2bjohcfo3zrwko.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416249/chdorgyrnfbpq49xgxew.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415998/i4wzvtqzfymknwyfuyc6.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416182/ztobiv6hgdafne2jw3s7.png"
+  ],
+  "aqua": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416340/h1kuqgcqpjzwu0ljgjzl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416321/dzi2zp9sztzqtw9uee7r.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416174/ud2uehcqq1qyghq0utcp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415964/ksisxgqdtz2vjyxxf0h5.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415963/op7g9sppryp1h2szkawc.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416330/odo3lr9n9qslrpelpf17.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416341/qq7aqw8a1tbjnzua5ofy.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416237/rlj8h5vqatrvid2htupx.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415962/lc02levu16k5xkcsdkqw.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416239/gnttl90pitpt5isdqvxb.png"
+  ],
+  "darkgreen": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416264/hgfibbhawru3agvmqhmp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416251/neqrvs4qgeumrv4vfmwp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416234/dgzqkw1d2n6ndcit4wnb.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416188/ug26ujte97hoqtgj8gxt.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416232/woljjv2lj53ioyvydv6b.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415972/apqgw44r8kjxf6wpevyl.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415968/mzxgjg1w67lfns5fcbsq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416222/yoloxsbdp4fsergeernp.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416268/cjwpdaow3vxkyxv3n5pn.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773415996/yczrjb9sqy1e1nhwcmq1.png"
+  ],
+  "violet": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416223/umysgecl2lxao9ujbupq.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416187/gn4k5mcwnhft4suls5r8.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773416275/aj6ismbfekdqh41mffaa.png"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{ "blue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253382/k5shc79l7qjtrz6ci2u8.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662299/g4llyutemrjvlpsyhbjl.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662300/qtwerqw10yv6wxqpb1cl.png"],"red":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775267794/oq0hzp8xiepkigd8hytz.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662302/wghzvjuaajuwpbfddzvk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253384/fa3gtcxcbbujpmz1q32y.png"],"black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775714831/nhh5gtcr98xedfimwedl.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662310/tbrnns244roeseqtkxrr.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/dxofsgljvhppxhvxcf9q.png"],"darkred":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253383/uqqd6kygifncoygwvzfk.png","https://res.cloudinary.com/dtwqvxhnm/image/upload/v1773253382/kiy5vdzzlhglrhntyfpf.png"], "royalblue":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662300/t7f9xsg5ij4gmjrmoyso.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1774662304/k5128obkwuopjaualtol.png"]}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantaloneta Running </t>
+  </si>
+  <si>
+    <t>olive,red,gray,crimson,purple,black</t>
+  </si>
+  <si>
+    <t>{
+  "olive": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775713346/tirpl3vsebbxrpsfldwa.png",
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775713346/lw9j7utvommec2ljjdiz.png"
+  ],
+  "red": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775713349/zpibbakrvtjje3uwbvzm.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775713347/msywbixpzz0lwwozubzc.png"  ],
+  "gray": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775713349/qb9trx4cyydbujc20cyz.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775713348/wholmpws1svmvxqluujx.png"  ],
+  "crimson": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775713351/byvtbwdxluxnxvkvux3v.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775713349/yss9zulo0nkd0he9rkan.png"  ],
+  "purple": [
+    "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775713350/uns1jry9u4vcyoyupwtd.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775713347/xfvipr4dadf6rc2qpct4.png"], "black":["https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775713350/xnyrgtj0p8li9nkwj020.png", "https://res.cloudinary.com/dtwqvxhnm/image/upload/v1775713350/g8mxtmqu5p9mwegpqbnz.png"   ]
+  }</t>
+  </si>
+  <si>
+    <t>Rompevientos Malla Interna</t>
+  </si>
+  <si>
+    <t>Enterizo Tentación</t>
   </si>
 </sst>
 </file>
@@ -3233,7 +3251,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3288,6 +3306,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -3316,7 +3340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3397,6 +3421,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3705,7 +3735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9C4F76-C123-4A10-B08E-8C496E2AA870}">
-  <dimension ref="A1:L116"/>
+  <dimension ref="A1:L117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="57.54296875" style="2" customWidth="1"/>
@@ -3726,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>1</v>
@@ -3764,10 +3794,10 @@
         <v>16</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>11</v>
@@ -3785,10 +3815,10 @@
         <v>17</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="K2" s="6" t="b">
         <v>0</v>
@@ -3799,13 +3829,13 @@
     </row>
     <row r="3" spans="1:12" s="3" customFormat="1" ht="99.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>11</v>
@@ -3821,10 +3851,10 @@
         <v>14</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="K3" s="6" t="b">
         <v>0</v>
@@ -3835,13 +3865,13 @@
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="89.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>11</v>
@@ -3859,10 +3889,10 @@
         <v>17</v>
       </c>
       <c r="I4" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>70</v>
       </c>
       <c r="K4" s="6" t="b">
         <v>0</v>
@@ -3876,10 +3906,10 @@
         <v>19</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>20</v>
@@ -3897,10 +3927,10 @@
         <v>17</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="K5" s="6" t="b">
         <v>0</v>
@@ -3915,7 +3945,7 @@
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>11</v>
@@ -3931,10 +3961,10 @@
         <v>14</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="K6" s="6" t="b">
         <v>0</v>
@@ -3945,11 +3975,11 @@
     </row>
     <row r="7" spans="1:12" ht="77.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>11</v>
@@ -3965,10 +3995,10 @@
         <v>12</v>
       </c>
       <c r="I7" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>72</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>73</v>
       </c>
       <c r="K7" s="6" t="b">
         <v>0</v>
@@ -3983,7 +4013,7 @@
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>11</v>
@@ -4001,10 +4031,10 @@
         <v>13</v>
       </c>
       <c r="I8" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="J8" s="11" t="s">
         <v>74</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>75</v>
       </c>
       <c r="K8" s="6" t="b">
         <v>0</v>
@@ -4015,11 +4045,11 @@
     </row>
     <row r="9" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>11</v>
@@ -4037,10 +4067,10 @@
         <v>13</v>
       </c>
       <c r="I9" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="11" t="s">
         <v>74</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>75</v>
       </c>
       <c r="K9" s="6" t="b">
         <v>0</v>
@@ -4055,7 +4085,7 @@
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>11</v>
@@ -4071,10 +4101,10 @@
         <v>14</v>
       </c>
       <c r="I10" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J10" s="12" t="s">
         <v>76</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>77</v>
       </c>
       <c r="K10" s="6" t="b">
         <v>0</v>
@@ -4085,11 +4115,11 @@
     </row>
     <row r="11" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>11</v>
@@ -4105,10 +4135,10 @@
         <v>14</v>
       </c>
       <c r="I11" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J11" s="12" t="s">
         <v>76</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>77</v>
       </c>
       <c r="K11" s="6" t="b">
         <v>0</v>
@@ -4119,11 +4149,11 @@
     </row>
     <row r="12" spans="1:12" ht="47" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>11</v>
@@ -4139,10 +4169,10 @@
         <v>14</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="K12" s="6" t="b">
         <v>0</v>
@@ -4153,11 +4183,11 @@
     </row>
     <row r="13" spans="1:12" ht="47" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>11</v>
@@ -4173,10 +4203,10 @@
         <v>14</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="K13" s="6" t="b">
         <v>0</v>
@@ -4187,11 +4217,11 @@
     </row>
     <row r="14" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>26</v>
@@ -4209,10 +4239,10 @@
         <v>25</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K14" s="6" t="b">
         <v>0</v>
@@ -4223,11 +4253,11 @@
     </row>
     <row r="15" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>26</v>
@@ -4245,10 +4275,10 @@
         <v>25</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K15" s="6" t="b">
         <v>0</v>
@@ -4259,11 +4289,11 @@
     </row>
     <row r="16" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>11</v>
@@ -4281,10 +4311,10 @@
         <v>25</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K16" s="6" t="b">
         <v>0</v>
@@ -4295,11 +4325,11 @@
     </row>
     <row r="17" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>11</v>
@@ -4317,10 +4347,10 @@
         <v>25</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K17" s="6" t="b">
         <v>0</v>
@@ -4335,7 +4365,7 @@
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>29</v>
@@ -4351,10 +4381,10 @@
         <v>27</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K18" s="6" t="b">
         <v>0</v>
@@ -4365,7 +4395,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6" t="s">
@@ -4385,10 +4415,10 @@
         <v>27</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K19" s="6" t="b">
         <v>0</v>
@@ -4399,11 +4429,11 @@
     </row>
     <row r="20" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>11</v>
@@ -4419,10 +4449,10 @@
         <v>14</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K20" s="6" t="b">
         <v>0</v>
@@ -4437,7 +4467,7 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>11</v>
@@ -4453,10 +4483,10 @@
         <v>14</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K21" s="6" t="b">
         <v>0</v>
@@ -4471,7 +4501,7 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>11</v>
@@ -4487,10 +4517,10 @@
         <v>31</v>
       </c>
       <c r="I22" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="J22" s="12" t="s">
         <v>128</v>
-      </c>
-      <c r="J22" s="12" t="s">
-        <v>129</v>
       </c>
       <c r="K22" s="6" t="b">
         <v>0</v>
@@ -4505,7 +4535,7 @@
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>11</v>
@@ -4521,10 +4551,10 @@
         <v>14</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K23" s="6" t="b">
         <v>0</v>
@@ -4539,7 +4569,7 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>11</v>
@@ -4555,10 +4585,10 @@
         <v>14</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K24" s="6" t="b">
         <v>0</v>
@@ -4573,7 +4603,7 @@
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>11</v>
@@ -4589,10 +4619,10 @@
         <v>14</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K25" s="6" t="b">
         <v>0</v>
@@ -4603,7 +4633,7 @@
     </row>
     <row r="26" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
@@ -4623,10 +4653,10 @@
         <v>14</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K26" s="6" t="b">
         <v>0</v>
@@ -4641,7 +4671,7 @@
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>11</v>
@@ -4657,10 +4687,10 @@
         <v>14</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="K27" s="6" t="b">
         <v>0</v>
@@ -4675,7 +4705,7 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>11</v>
@@ -4691,10 +4721,10 @@
         <v>14</v>
       </c>
       <c r="I28" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="J28" s="12" t="s">
         <v>85</v>
-      </c>
-      <c r="J28" s="12" t="s">
-        <v>86</v>
       </c>
       <c r="K28" s="6" t="b">
         <v>0</v>
@@ -4705,7 +4735,7 @@
     </row>
     <row r="29" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
@@ -4725,10 +4755,10 @@
         <v>40</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K29" s="6" t="b">
         <v>0</v>
@@ -4739,7 +4769,7 @@
     </row>
     <row r="30" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6" t="s">
@@ -4759,10 +4789,10 @@
         <v>40</v>
       </c>
       <c r="I30" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="J30" s="12" t="s">
         <v>88</v>
-      </c>
-      <c r="J30" s="12" t="s">
-        <v>89</v>
       </c>
       <c r="K30" s="6" t="b">
         <v>0</v>
@@ -4795,10 +4825,10 @@
         <v>43</v>
       </c>
       <c r="I31" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J31" s="12" t="s">
         <v>90</v>
-      </c>
-      <c r="J31" s="12" t="s">
-        <v>91</v>
       </c>
       <c r="K31" s="6" t="b">
         <v>0</v>
@@ -4831,10 +4861,10 @@
         <v>44</v>
       </c>
       <c r="I32" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="J32" s="12" t="s">
         <v>92</v>
-      </c>
-      <c r="J32" s="12" t="s">
-        <v>93</v>
       </c>
       <c r="K32" s="6" t="b">
         <v>0</v>
@@ -4865,10 +4895,10 @@
         <v>14</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="K33" s="6" t="b">
         <v>0</v>
@@ -4899,10 +4929,10 @@
         <v>14</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="K34" s="6" t="b">
         <v>0</v>
@@ -4913,7 +4943,7 @@
     </row>
     <row r="35" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6" t="s">
@@ -4926,7 +4956,7 @@
         <v>17000</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G35" s="6">
         <v>34000</v>
@@ -4935,10 +4965,10 @@
         <v>40</v>
       </c>
       <c r="I35" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="J35" s="8" t="s">
         <v>95</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>96</v>
       </c>
       <c r="K35" s="6" t="b">
         <v>0</v>
@@ -4949,7 +4979,7 @@
     </row>
     <row r="36" spans="1:12" ht="126.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6" t="s">
@@ -4962,7 +4992,7 @@
         <v>17000</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G36" s="6">
         <v>34000</v>
@@ -4971,10 +5001,10 @@
         <v>40</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K36" s="6" t="b">
         <v>0</v>
@@ -4985,7 +5015,7 @@
     </row>
     <row r="37" spans="1:12" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6" t="s">
@@ -4998,7 +5028,7 @@
         <v>17000</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G37" s="6">
         <v>34000</v>
@@ -5007,10 +5037,10 @@
         <v>40</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K37" s="6" t="b">
         <v>0</v>
@@ -5021,7 +5051,7 @@
     </row>
     <row r="38" spans="1:12" ht="91" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6" t="s">
@@ -5034,7 +5064,7 @@
         <v>17000</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G38" s="6">
         <v>34000</v>
@@ -5043,10 +5073,10 @@
         <v>40</v>
       </c>
       <c r="I38" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="J38" s="8" t="s">
         <v>99</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>100</v>
       </c>
       <c r="K38" s="6" t="b">
         <v>0</v>
@@ -5057,7 +5087,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
@@ -5077,10 +5107,10 @@
         <v>51</v>
       </c>
       <c r="I39" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="J39" s="12" t="s">
         <v>101</v>
-      </c>
-      <c r="J39" s="12" t="s">
-        <v>102</v>
       </c>
       <c r="K39" s="6" t="b">
         <v>0</v>
@@ -5111,10 +5141,10 @@
         <v>51</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K40" s="6" t="b">
         <v>0</v>
@@ -5125,7 +5155,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
-        <v>52</v>
+        <v>369</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6" t="s">
@@ -5145,10 +5175,10 @@
         <v>14</v>
       </c>
       <c r="I41" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="J41" s="14" t="s">
         <v>104</v>
-      </c>
-      <c r="J41" s="14" t="s">
-        <v>105</v>
       </c>
       <c r="K41" s="6" t="b">
         <v>0</v>
@@ -5159,7 +5189,7 @@
     </row>
     <row r="42" spans="1:12" ht="98.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
@@ -5179,10 +5209,10 @@
         <v>44</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J42" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K42" s="6" t="b">
         <v>0</v>
@@ -5193,7 +5223,7 @@
     </row>
     <row r="43" spans="1:12" ht="95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6" t="s">
@@ -5213,10 +5243,10 @@
         <v>44</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="K43" s="6" t="b">
         <v>0</v>
@@ -5227,7 +5257,7 @@
     </row>
     <row r="44" spans="1:12" ht="158" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6" t="s">
@@ -5247,10 +5277,10 @@
         <v>14</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="K44" s="6" t="b">
         <v>0</v>
@@ -5274,19 +5304,19 @@
         <v>10000</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G45" s="6">
         <v>19000</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I45" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="J45" s="8" t="s">
         <v>108</v>
-      </c>
-      <c r="J45" s="8" t="s">
-        <v>109</v>
       </c>
       <c r="K45" s="6" t="b">
         <v>0</v>
@@ -5297,7 +5327,7 @@
     </row>
     <row r="46" spans="1:12" ht="82" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6" t="s">
@@ -5314,13 +5344,13 @@
         <v>20000</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I46" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="J46" s="8" t="s">
         <v>110</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>111</v>
       </c>
       <c r="K46" s="6" t="b">
         <v>0</v>
@@ -5331,7 +5361,7 @@
     </row>
     <row r="47" spans="1:12" ht="302.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6" t="s">
@@ -5351,10 +5381,10 @@
         <v>13</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K47" s="6" t="b">
         <v>0</v>
@@ -5365,7 +5395,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6" t="s">
@@ -5382,13 +5412,13 @@
         <v>30000</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I48" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="J48" s="14" t="s">
         <v>113</v>
-      </c>
-      <c r="J48" s="14" t="s">
-        <v>114</v>
       </c>
       <c r="K48" s="6" t="b">
         <v>0</v>
@@ -5399,7 +5429,7 @@
     </row>
     <row r="49" spans="1:12" ht="261.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6" t="s">
@@ -5419,10 +5449,10 @@
         <v>12</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K49" s="6" t="b">
         <v>0</v>
@@ -5433,11 +5463,11 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>11</v>
@@ -5453,10 +5483,10 @@
         <v>12</v>
       </c>
       <c r="I50" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J50" s="14" t="s">
         <v>116</v>
-      </c>
-      <c r="J50" s="14" t="s">
-        <v>117</v>
       </c>
       <c r="K50" s="6" t="b">
         <v>0</v>
@@ -5467,7 +5497,7 @@
     </row>
     <row r="51" spans="1:12" ht="406" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6" t="s">
@@ -5487,10 +5517,10 @@
         <v>12</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="K51" s="6" t="b">
         <v>0</v>
@@ -5501,7 +5531,7 @@
     </row>
     <row r="52" spans="1:12" ht="121.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="6" t="s">
@@ -5521,10 +5551,10 @@
         <v>14</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J52" s="15" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="K52" s="6" t="b">
         <v>0</v>
@@ -5535,11 +5565,11 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>11</v>
@@ -5555,10 +5585,10 @@
         <v>14</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K53" s="6" t="b">
         <v>0</v>
@@ -5569,11 +5599,11 @@
     </row>
     <row r="54" spans="1:12" ht="141.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>11</v>
@@ -5589,10 +5619,10 @@
         <v>14</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K54" s="6" t="b">
         <v>0</v>
@@ -5603,11 +5633,11 @@
     </row>
     <row r="55" spans="1:12" ht="276.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>11</v>
@@ -5623,10 +5653,10 @@
         <v>14</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K55" s="6" t="b">
         <v>0</v>
@@ -5637,11 +5667,11 @@
     </row>
     <row r="56" spans="1:12" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>11</v>
@@ -5657,10 +5687,10 @@
         <v>31</v>
       </c>
       <c r="I56" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="J56" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="K56" s="6" t="b">
         <v>0</v>
@@ -5671,11 +5701,11 @@
     </row>
     <row r="57" spans="1:12" ht="377" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>11</v>
@@ -5684,7 +5714,7 @@
         <v>22000</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G57" s="6">
         <v>27000</v>
@@ -5693,10 +5723,10 @@
         <v>17</v>
       </c>
       <c r="I57" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="J57" s="15" t="s">
         <v>166</v>
-      </c>
-      <c r="J57" s="15" t="s">
-        <v>167</v>
       </c>
       <c r="K57" s="6" t="b">
         <v>0</v>
@@ -5707,11 +5737,11 @@
     </row>
     <row r="58" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A58" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B58" s="16"/>
       <c r="C58" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D58" s="16" t="s">
         <v>26</v>
@@ -5727,10 +5757,10 @@
         <v>14</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J58" s="18" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="K58" s="19" t="b">
         <v>0</v>
@@ -5741,11 +5771,11 @@
     </row>
     <row r="59" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A59" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B59" s="16"/>
       <c r="C59" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D59" s="16" t="s">
         <v>20</v>
@@ -5761,10 +5791,10 @@
         <v>14</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J59" s="18" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K59" s="19" t="b">
         <v>0</v>
@@ -5775,11 +5805,11 @@
     </row>
     <row r="60" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A60" s="16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B60" s="16"/>
       <c r="C60" s="16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D60" s="16" t="s">
         <v>20</v>
@@ -5795,10 +5825,10 @@
         <v>14</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J60" s="18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K60" s="19" t="b">
         <v>0</v>
@@ -5809,11 +5839,11 @@
     </row>
     <row r="61" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A61" s="16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B61" s="16"/>
       <c r="C61" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D61" s="16" t="s">
         <v>20</v>
@@ -5829,10 +5859,10 @@
         <v>14</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J61" s="18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K61" s="19" t="b">
         <v>0</v>
@@ -5843,11 +5873,11 @@
     </row>
     <row r="62" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A62" s="16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B62" s="16"/>
       <c r="C62" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D62" s="16" t="s">
         <v>20</v>
@@ -5863,10 +5893,10 @@
         <v>14</v>
       </c>
       <c r="I62" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="J62" s="18" t="s">
         <v>183</v>
-      </c>
-      <c r="J62" s="18" t="s">
-        <v>184</v>
       </c>
       <c r="K62" s="19" t="b">
         <v>0</v>
@@ -5877,11 +5907,11 @@
     </row>
     <row r="63" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A63" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B63" s="16"/>
       <c r="C63" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D63" s="16" t="s">
         <v>20</v>
@@ -5897,10 +5927,10 @@
         <v>14</v>
       </c>
       <c r="I63" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="J63" s="18" t="s">
         <v>189</v>
-      </c>
-      <c r="J63" s="18" t="s">
-        <v>190</v>
       </c>
       <c r="K63" s="19" t="b">
         <v>0</v>
@@ -5911,11 +5941,11 @@
     </row>
     <row r="64" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A64" s="16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B64" s="16"/>
       <c r="C64" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D64" s="16" t="s">
         <v>20</v>
@@ -5931,10 +5961,10 @@
         <v>14</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J64" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K64" s="19" t="b">
         <v>0</v>
@@ -5945,11 +5975,11 @@
     </row>
     <row r="65" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A65" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B65" s="16"/>
       <c r="C65" s="16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D65" s="16" t="s">
         <v>20</v>
@@ -5965,10 +5995,10 @@
         <v>14</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J65" s="18" t="s">
-        <v>205</v>
+        <v>364</v>
       </c>
       <c r="K65" s="19" t="b">
         <v>0</v>
@@ -5979,11 +6009,11 @@
     </row>
     <row r="66" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A66" s="16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B66" s="16"/>
       <c r="C66" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D66" s="16" t="s">
         <v>20</v>
@@ -5999,10 +6029,10 @@
         <v>14</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J66" s="18" t="s">
-        <v>204</v>
+        <v>363</v>
       </c>
       <c r="K66" s="19" t="b">
         <v>0</v>
@@ -6013,11 +6043,11 @@
     </row>
     <row r="67" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A67" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B67" s="16"/>
       <c r="C67" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D67" s="16" t="s">
         <v>20</v>
@@ -6033,10 +6063,10 @@
         <v>14</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J67" s="18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K67" s="19" t="b">
         <v>0</v>
@@ -6047,11 +6077,11 @@
     </row>
     <row r="68" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A68" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B68" s="16"/>
       <c r="C68" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D68" s="16" t="s">
         <v>20</v>
@@ -6067,10 +6097,10 @@
         <v>14</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J68" s="18" t="s">
-        <v>201</v>
+        <v>362</v>
       </c>
       <c r="K68" s="19" t="b">
         <v>0</v>
@@ -6081,11 +6111,11 @@
     </row>
     <row r="69" spans="1:12" ht="406" x14ac:dyDescent="0.35">
       <c r="A69" s="16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B69" s="16"/>
       <c r="C69" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D69" s="16" t="s">
         <v>20</v>
@@ -6101,10 +6131,10 @@
         <v>14</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J69" s="18" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K69" s="19" t="b">
         <v>0</v>
@@ -6115,11 +6145,11 @@
     </row>
     <row r="70" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A70" s="16" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B70" s="16"/>
       <c r="C70" s="16" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D70" s="16" t="s">
         <v>20</v>
@@ -6135,10 +6165,10 @@
         <v>14</v>
       </c>
       <c r="I70" s="16" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="K70" s="19" t="b">
         <v>0</v>
@@ -6149,11 +6179,11 @@
     </row>
     <row r="71" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A71" s="16" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B71" s="16"/>
       <c r="C71" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D71" s="16" t="s">
         <v>20</v>
@@ -6169,10 +6199,10 @@
         <v>14</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J71" s="18" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="K71" s="19" t="b">
         <v>0</v>
@@ -6183,11 +6213,11 @@
     </row>
     <row r="72" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A72" s="16" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B72" s="16"/>
       <c r="C72" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D72" s="16" t="s">
         <v>20</v>
@@ -6203,10 +6233,10 @@
         <v>14</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J72" s="18" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="K72" s="19" t="b">
         <v>0</v>
@@ -6217,11 +6247,11 @@
     </row>
     <row r="73" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A73" s="16" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B73" s="16"/>
       <c r="C73" s="16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D73" s="16" t="s">
         <v>20</v>
@@ -6237,10 +6267,10 @@
         <v>14</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J73" s="18" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="K73" s="19" t="b">
         <v>0</v>
@@ -6251,13 +6281,13 @@
     </row>
     <row r="74" spans="1:12" ht="319" x14ac:dyDescent="0.35">
       <c r="A74" s="16" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D74" s="16" t="s">
         <v>11</v>
@@ -6270,13 +6300,13 @@
         <v>34000</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I74" s="16" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J74" s="18" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K74" s="19" t="b">
         <v>0</v>
@@ -6287,11 +6317,11 @@
     </row>
     <row r="75" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A75" s="16" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B75" s="16"/>
       <c r="C75" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D75" s="16" t="s">
         <v>20</v>
@@ -6307,10 +6337,10 @@
         <v>14</v>
       </c>
       <c r="I75" s="16" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="J75" s="18" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K75" s="19" t="b">
         <v>0</v>
@@ -6321,11 +6351,11 @@
     </row>
     <row r="76" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A76" s="16" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B76" s="16"/>
       <c r="C76" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D76" s="16" t="s">
         <v>20</v>
@@ -6341,10 +6371,10 @@
         <v>14</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K76" s="19" t="b">
         <v>0</v>
@@ -6355,11 +6385,11 @@
     </row>
     <row r="77" spans="1:12" ht="87" x14ac:dyDescent="0.35">
       <c r="A77" s="16" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B77" s="16"/>
       <c r="C77" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D77" s="16" t="s">
         <v>20</v>
@@ -6375,10 +6405,10 @@
         <v>14</v>
       </c>
       <c r="I77" s="16" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="J77" s="18" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="K77" s="19" t="b">
         <v>0</v>
@@ -6389,13 +6419,13 @@
     </row>
     <row r="78" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A78" s="16" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D78" s="16" t="s">
         <v>20</v>
@@ -6411,10 +6441,10 @@
         <v>14</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J78" s="18" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="K78" s="19" t="b">
         <v>0</v>
@@ -6425,13 +6455,13 @@
     </row>
     <row r="79" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A79" s="16" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D79" s="16" t="s">
         <v>20</v>
@@ -6447,10 +6477,10 @@
         <v>14</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J79" s="18" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="K79" s="19" t="b">
         <v>0</v>
@@ -6461,11 +6491,11 @@
     </row>
     <row r="80" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A80" s="16" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B80" s="16"/>
       <c r="C80" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D80" s="16" t="s">
         <v>20</v>
@@ -6481,10 +6511,10 @@
         <v>14</v>
       </c>
       <c r="I80" s="16" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="K80" s="19" t="b">
         <v>0</v>
@@ -6495,11 +6525,11 @@
     </row>
     <row r="81" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A81" s="16" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B81" s="16"/>
       <c r="C81" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D81" s="16" t="s">
         <v>20</v>
@@ -6515,10 +6545,10 @@
         <v>14</v>
       </c>
       <c r="I81" s="16" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J81" s="17" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="K81" s="19" t="b">
         <v>0</v>
@@ -6529,11 +6559,11 @@
     </row>
     <row r="82" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A82" s="16" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B82" s="16"/>
       <c r="C82" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D82" s="16" t="s">
         <v>20</v>
@@ -6549,10 +6579,10 @@
         <v>14</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="J82" s="18" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="K82" s="19" t="b">
         <v>0</v>
@@ -6563,11 +6593,11 @@
     </row>
     <row r="83" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A83" s="16" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B83" s="16"/>
       <c r="C83" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D83" s="16" t="s">
         <v>20</v>
@@ -6583,10 +6613,10 @@
         <v>14</v>
       </c>
       <c r="I83" s="17" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J83" s="21" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="K83" s="19" t="b">
         <v>0</v>
@@ -6597,11 +6627,11 @@
     </row>
     <row r="84" spans="1:12" ht="261" x14ac:dyDescent="0.35">
       <c r="A84" s="16" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B84" s="16"/>
       <c r="C84" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D84" s="16" t="s">
         <v>20</v>
@@ -6617,10 +6647,10 @@
         <v>14</v>
       </c>
       <c r="I84" s="16" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J84" s="21" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="K84" s="19" t="b">
         <v>0</v>
@@ -6631,11 +6661,11 @@
     </row>
     <row r="85" spans="1:12" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A85" s="16" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B85" s="16"/>
       <c r="C85" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D85" s="16" t="s">
         <v>20</v>
@@ -6644,7 +6674,7 @@
         <v>25000</v>
       </c>
       <c r="F85" s="17" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G85" s="16">
         <v>36000</v>
@@ -6653,10 +6683,10 @@
         <v>13</v>
       </c>
       <c r="I85" s="16" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J85" s="21" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="K85" s="19" t="b">
         <v>0</v>
@@ -6667,11 +6697,11 @@
     </row>
     <row r="86" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A86" s="16" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B86" s="16"/>
       <c r="C86" s="16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D86" s="16" t="s">
         <v>20</v>
@@ -6687,10 +6717,10 @@
         <v>14</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="J86" s="21" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="K86" s="19" t="b">
         <v>0</v>
@@ -6701,11 +6731,11 @@
     </row>
     <row r="87" spans="1:12" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>11</v>
@@ -6721,10 +6751,10 @@
         <v>12</v>
       </c>
       <c r="I87" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="J87" s="11" t="s">
         <v>72</v>
-      </c>
-      <c r="J87" s="11" t="s">
-        <v>73</v>
       </c>
       <c r="K87" s="6" t="b">
         <v>0</v>
@@ -6735,7 +6765,7 @@
     </row>
     <row r="88" spans="1:12" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A88" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6" t="s">
@@ -6752,13 +6782,13 @@
         <v>27000</v>
       </c>
       <c r="H88" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="I88" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="J88" s="22" t="s">
         <v>265</v>
-      </c>
-      <c r="I88" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="J88" s="22" t="s">
-        <v>269</v>
       </c>
       <c r="K88" s="6" t="b">
         <v>0</v>
@@ -6769,7 +6799,7 @@
     </row>
     <row r="89" spans="1:12" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A89" s="6" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6" t="s">
@@ -6789,10 +6819,10 @@
         <v>14</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J89" s="22" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="K89" s="6" t="b">
         <v>0</v>
@@ -6803,11 +6833,11 @@
     </row>
     <row r="90" spans="1:12" ht="319" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>11</v>
@@ -6823,10 +6853,10 @@
         <v>12</v>
       </c>
       <c r="I90" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J90" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K90" s="6" t="b">
         <v>0</v>
@@ -6837,11 +6867,11 @@
     </row>
     <row r="91" spans="1:12" ht="319" x14ac:dyDescent="0.35">
       <c r="A91" s="23" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B91" s="23"/>
       <c r="C91" s="23" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D91" s="23" t="s">
         <v>11</v>
@@ -6854,13 +6884,13 @@
         <v>45000</v>
       </c>
       <c r="H91" s="23" t="s">
-        <v>277</v>
+        <v>358</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="J91" s="22" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="K91" s="6" t="b">
         <v>0</v>
@@ -6871,7 +6901,7 @@
     </row>
     <row r="92" spans="1:12" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A92" s="23" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B92" s="23"/>
       <c r="C92" s="23" t="s">
@@ -6891,10 +6921,10 @@
         <v>14</v>
       </c>
       <c r="I92" s="24" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="J92" s="22" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="K92" s="6" t="b">
         <v>0</v>
@@ -6905,11 +6935,11 @@
     </row>
     <row r="93" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A93" s="23" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B93" s="23"/>
       <c r="C93" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D93" s="23" t="s">
         <v>20</v>
@@ -6925,10 +6955,10 @@
         <v>14</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="J93" s="11" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="K93" s="6" t="b">
         <v>0</v>
@@ -6939,11 +6969,11 @@
     </row>
     <row r="94" spans="1:12" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A94" s="25" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B94" s="25"/>
       <c r="C94" s="25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D94" s="25" t="s">
         <v>20</v>
@@ -6959,10 +6989,10 @@
         <v>14</v>
       </c>
       <c r="I94" s="25" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="J94" s="26" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="K94" s="25" t="b">
         <v>0</v>
@@ -6973,11 +7003,11 @@
     </row>
     <row r="95" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A95" s="25" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B95" s="25"/>
       <c r="C95" s="25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D95" s="25" t="s">
         <v>20</v>
@@ -6990,13 +7020,13 @@
         <v>15000</v>
       </c>
       <c r="H95" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I95" s="26" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J95" s="27" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="K95" s="25" t="b">
         <v>0</v>
@@ -7007,11 +7037,11 @@
     </row>
     <row r="96" spans="1:12" ht="261" x14ac:dyDescent="0.35">
       <c r="A96" s="25" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B96" s="25"/>
       <c r="C96" s="25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D96" s="25" t="s">
         <v>20</v>
@@ -7027,10 +7057,10 @@
         <v>14</v>
       </c>
       <c r="I96" s="25" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="J96" s="27" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="K96" s="25" t="b">
         <v>0</v>
@@ -7041,30 +7071,30 @@
     </row>
     <row r="97" spans="1:12" ht="174" x14ac:dyDescent="0.35">
       <c r="A97" s="25" t="s">
-        <v>306</v>
+        <v>370</v>
       </c>
       <c r="B97" s="25"/>
       <c r="C97" s="25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D97" s="25" t="s">
         <v>20</v>
       </c>
       <c r="E97" s="25">
-        <v>24000</v>
+        <v>25000</v>
       </c>
       <c r="F97" s="25"/>
       <c r="G97" s="25">
-        <v>36000</v>
+        <v>37500</v>
       </c>
       <c r="H97" s="25" t="s">
         <v>14</v>
       </c>
       <c r="I97" s="25" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="J97" s="26" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="K97" s="25" t="b">
         <v>0</v>
@@ -7075,11 +7105,11 @@
     </row>
     <row r="98" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A98" s="25" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B98" s="25"/>
       <c r="C98" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D98" s="25" t="s">
         <v>20</v>
@@ -7095,10 +7125,10 @@
         <v>14</v>
       </c>
       <c r="I98" s="26" t="s">
+        <v>304</v>
+      </c>
+      <c r="J98" s="26" t="s">
         <v>310</v>
-      </c>
-      <c r="J98" s="26" t="s">
-        <v>316</v>
       </c>
       <c r="K98" s="25" t="b">
         <v>0</v>
@@ -7109,11 +7139,11 @@
     </row>
     <row r="99" spans="1:12" ht="319" x14ac:dyDescent="0.35">
       <c r="A99" s="25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B99" s="25"/>
       <c r="C99" s="25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D99" s="25" t="s">
         <v>20</v>
@@ -7129,10 +7159,10 @@
         <v>14</v>
       </c>
       <c r="I99" s="26" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J99" s="26" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="K99" s="25" t="b">
         <v>0</v>
@@ -7143,11 +7173,11 @@
     </row>
     <row r="100" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A100" s="25" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B100" s="25"/>
       <c r="C100" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D100" s="25" t="s">
         <v>20</v>
@@ -7163,10 +7193,10 @@
         <v>14</v>
       </c>
       <c r="I100" s="26" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J100" s="26" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="K100" s="25" t="b">
         <v>0</v>
@@ -7177,11 +7207,11 @@
     </row>
     <row r="101" spans="1:12" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A101" s="28" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B101" s="28"/>
       <c r="C101" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D101" s="28" t="s">
         <v>20</v>
@@ -7197,10 +7227,10 @@
         <v>14</v>
       </c>
       <c r="I101" s="29" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J101" s="29" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="K101" s="28" t="b">
         <v>0</v>
@@ -7211,11 +7241,11 @@
     </row>
     <row r="102" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A102" s="25" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B102" s="25"/>
       <c r="C102" s="25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D102" s="25" t="s">
         <v>20</v>
@@ -7231,10 +7261,10 @@
         <v>14</v>
       </c>
       <c r="I102" s="26" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="J102" s="26" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="K102" s="25" t="b">
         <v>0</v>
@@ -7245,11 +7275,11 @@
     </row>
     <row r="103" spans="1:12" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A103" s="28" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B103" s="28"/>
       <c r="C103" s="28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D103" s="28" t="s">
         <v>11</v>
@@ -7265,10 +7295,10 @@
         <v>14</v>
       </c>
       <c r="I103" s="28" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="J103" s="29" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="K103" s="28" t="b">
         <v>0</v>
@@ -7279,11 +7309,11 @@
     </row>
     <row r="104" spans="1:12" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A104" s="28" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B104" s="28"/>
       <c r="C104" s="28" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D104" s="28" t="s">
         <v>11</v>
@@ -7299,10 +7329,10 @@
         <v>14</v>
       </c>
       <c r="I104" s="29" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="J104" s="29" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="K104" s="28" t="b">
         <v>0</v>
@@ -7313,11 +7343,11 @@
     </row>
     <row r="105" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A105" s="25" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="B105" s="25"/>
       <c r="C105" s="25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D105" s="25" t="s">
         <v>20</v>
@@ -7333,10 +7363,10 @@
         <v>14</v>
       </c>
       <c r="I105" s="26" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="J105" s="26" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="K105" s="25" t="b">
         <v>0</v>
@@ -7347,11 +7377,11 @@
     </row>
     <row r="106" spans="1:12" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A106" s="25" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B106" s="25"/>
       <c r="C106" s="25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D106" s="25" t="s">
         <v>20</v>
@@ -7367,10 +7397,10 @@
         <v>14</v>
       </c>
       <c r="I106" s="25" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="J106" s="26" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="K106" s="25" t="b">
         <v>0</v>
@@ -7381,11 +7411,11 @@
     </row>
     <row r="107" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A107" s="28" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B107" s="28"/>
       <c r="C107" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D107" s="28" t="s">
         <v>11</v>
@@ -7401,10 +7431,10 @@
         <v>14</v>
       </c>
       <c r="I107" s="29" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="J107" s="29" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="K107" s="28" t="b">
         <v>0</v>
@@ -7415,11 +7445,11 @@
     </row>
     <row r="108" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A108" s="28" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B108" s="28"/>
       <c r="C108" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D108" s="28" t="s">
         <v>11</v>
@@ -7435,10 +7465,10 @@
         <v>14</v>
       </c>
       <c r="I108" s="28" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="J108" s="29" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="K108" s="28" t="b">
         <v>0</v>
@@ -7449,11 +7479,11 @@
     </row>
     <row r="109" spans="1:12" ht="333.5" x14ac:dyDescent="0.35">
       <c r="A109" s="28" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B109" s="28"/>
       <c r="C109" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D109" s="28" t="s">
         <v>11</v>
@@ -7469,10 +7499,10 @@
         <v>14</v>
       </c>
       <c r="I109" s="29" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="J109" s="29" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="K109" s="28" t="b">
         <v>0</v>
@@ -7483,11 +7513,11 @@
     </row>
     <row r="110" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A110" s="25" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B110" s="25"/>
       <c r="C110" s="25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D110" s="25" t="s">
         <v>26</v>
@@ -7503,10 +7533,10 @@
         <v>14</v>
       </c>
       <c r="I110" s="26" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="J110" s="26" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="K110" s="25" t="b">
         <v>0</v>
@@ -7517,11 +7547,11 @@
     </row>
     <row r="111" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A111" s="25" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B111" s="25"/>
       <c r="C111" s="25" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D111" s="25" t="s">
         <v>26</v>
@@ -7537,10 +7567,10 @@
         <v>14</v>
       </c>
       <c r="I111" s="26" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="J111" s="26" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="K111" s="25" t="b">
         <v>0</v>
@@ -7551,11 +7581,11 @@
     </row>
     <row r="112" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A112" s="25" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B112" s="25"/>
       <c r="C112" s="25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D112" s="25" t="s">
         <v>20</v>
@@ -7571,10 +7601,10 @@
         <v>14</v>
       </c>
       <c r="I112" s="26" t="s">
+        <v>304</v>
+      </c>
+      <c r="J112" s="26" t="s">
         <v>310</v>
-      </c>
-      <c r="J112" s="26" t="s">
-        <v>316</v>
       </c>
       <c r="K112" s="25" t="b">
         <v>0</v>
@@ -7585,11 +7615,11 @@
     </row>
     <row r="113" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A113" s="25" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B113" s="25"/>
       <c r="C113" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D113" s="25" t="s">
         <v>11</v>
@@ -7605,10 +7635,10 @@
         <v>14</v>
       </c>
       <c r="I113" s="26" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="J113" s="26" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="K113" s="25" t="b">
         <v>0</v>
@@ -7619,11 +7649,11 @@
     </row>
     <row r="114" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A114" s="25" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B114" s="25"/>
       <c r="C114" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D114" s="25" t="s">
         <v>26</v>
@@ -7639,10 +7669,10 @@
         <v>14</v>
       </c>
       <c r="I114" s="26" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="J114" s="26" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="K114" s="25" t="b">
         <v>0</v>
@@ -7653,11 +7683,11 @@
     </row>
     <row r="115" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A115" s="25" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="B115" s="25"/>
       <c r="C115" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D115" s="25" t="s">
         <v>11</v>
@@ -7673,10 +7703,10 @@
         <v>14</v>
       </c>
       <c r="I115" s="26" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="J115" s="26" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="K115" s="25" t="b">
         <v>0</v>
@@ -7687,11 +7717,11 @@
     </row>
     <row r="116" spans="1:12" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A116" s="25" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B116" s="25"/>
       <c r="C116" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D116" s="25" t="s">
         <v>11</v>
@@ -7704,18 +7734,52 @@
         <v>34000</v>
       </c>
       <c r="H116" s="25" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="I116" s="26" t="s">
+        <v>359</v>
+      </c>
+      <c r="J116" s="26" t="s">
+        <v>360</v>
+      </c>
+      <c r="K116" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L116" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" ht="290" x14ac:dyDescent="0.35">
+      <c r="A117" s="30" t="s">
         <v>366</v>
       </c>
-      <c r="J116" s="26" t="s">
+      <c r="B117" s="30"/>
+      <c r="C117" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="D117" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="E117" s="30">
+        <v>26000</v>
+      </c>
+      <c r="F117" s="30"/>
+      <c r="G117" s="30">
+        <v>37500</v>
+      </c>
+      <c r="H117" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="I117" s="31" t="s">
         <v>367</v>
       </c>
-      <c r="K116" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L116" s="25" t="b">
+      <c r="J117" s="31" t="s">
+        <v>368</v>
+      </c>
+      <c r="K117" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L117" s="30" t="b">
         <v>0</v>
       </c>
     </row>
